--- a/data/backup-jobs.xlsx
+++ b/data/backup-jobs.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="146">
   <si>
     <t>id</t>
   </si>
@@ -428,6 +428,27 @@
   </si>
   <si>
     <t>{"job":{"id":"J02-dc56","title":"Recondition Transmission 16H,G","unit":"E448 — D10T","unit_id":"a5c2144b-1b29-40f7-9b5c-cfbbc03c3387","description":"Job recondition Transmission 16H,G (time frame standar).","status":"in_progress","technician_id":"T-75034b10","template_id":"ne-transmission-16h-g","created_at":"2026-08-09T14:29:20.672Z","started_at":"2026-08-09T15:02:48.075Z","completed_at":"","paused_at":"","total_paused_sec":89,"estimated_minutes":5340},"steps":[{"id":"91804ed8-5ad4-4ffd-aaad-beba64eb9cb2","job_id":"J02-dc56","name":"Dismantle: Washing Transmission gp","order":1,"status":"done","started_at":"2026-08-09T15:02:48.075Z","completed_at":"2026-08-09T15:20:47.571Z","duration_sec":1079,"std_minutes":240},{"id":"a127f857-f092-4b21-b197-3e3c8a02d549","job_id":"J02-dc56","name":"Dismantle: Control Valve 2EA","order":2,"status":"done","started_at":"2026-08-10T01:30:25.210Z","completed_at":"2026-08-10T01:30:32.748Z","duration_sec":36495,"std_minutes":300},{"id":"3bc8becf-2b5e-4391-8c9f-619d63d7281c","job_id":"J02-dc56","name":"Dismantle: Pump, Lines, &amp; Screen","order":3,"status":"done","started_at":"2026-08-10T01:30:32.748Z","completed_at":"2026-08-10T08:27:37.616Z","duration_sec":25024,"std_minutes":240},{"id":"bacf6ce8-8a97-4831-9f38-3010f4d64a9a","job_id":"J02-dc56","name":"Dismantle: Planetary GP","order":4,"status":"done","started_at":"2026-08-10T08:27:37.616Z","completed_at":"2026-08-11T05:36:57.526Z","duration_sec":76159,"std_minutes":900},{"id":"74bc5c28-b84c-4cfa-b429-25198c968f30","job_id":"J02-dc56","name":"Dismantle: Directional &amp; Idler gear","order":5,"status":"in_progress","started_at":"2026-08-11T05:36:57.526Z","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"c3ce574f-16e3-4ce2-815e-10a842f608de","job_id":"J02-dc56","name":"Dismantle: Clean up Housing 2ea","order":6,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":120},{"id":"b57a5afd-0b62-47a8-a149-df57cdbec92f","job_id":"J02-dc56","name":"Dismantle: Part list &amp; Tear Down","order":7,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"ef67991d-4f1b-4929-b4b9-3bd70d1c1a8b","job_id":"J02-dc56","name":"Assemble: Directional &amp; Idler gear","order":8,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"19689610-ed31-4c36-959c-6233ef31d9cc","job_id":"J02-dc56","name":"Assemble: Planetary GP","order":9,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"572f712a-0376-495f-a98f-9ee71ead12b3","job_id":"J02-dc56","name":"Assemble: CV 2EA","order":10,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"033a6b1b-8daf-46cc-a1e1-292ad2451d5f","job_id":"J02-dc56","name":"Assemble: Pump, Lines, &amp; Screen","order":11,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"f52cc000-4714-474d-a6c4-a3f41408fbb7","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Set up","order":12,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"a9b889d6-b2f7-4421-a27a-fcd6a2fde9f9","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Test","order":13,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"3edd89d2-41a4-4856-976b-cbc716dc3788","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Release","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"4d87b720-179e-4dbd-bf95-3d44c356f29e","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300}],"assignees":[{"id":"8f6f2232-50e1-4ad3-88b9-fddd08fa3833","job_id":"J02-dc56","technician_id":"T-75034b10","assigned_at":"2026-08-09T15:02:36.172Z","is_lead":"1"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-75034b10","status":"busy","current_job_id":"J02-dc56"}]}</t>
+  </si>
+  <si>
+    <t>28015d62-411b-4be1-85e7-77c9f3f8f959</t>
+  </si>
+  <si>
+    <t>2026-08-11T14:50:26.802Z</t>
+  </si>
+  <si>
+    <t>{"job":{"id":"J02-dc56","title":"Recondition Transmission 16H,G","unit":"E448 — D10T","unit_id":"a5c2144b-1b29-40f7-9b5c-cfbbc03c3387","description":"Job recondition Transmission 16H,G (time frame standar).","status":"in_progress","technician_id":"T-75034b10","template_id":"ne-transmission-16h-g","created_at":"2026-08-09T14:29:20.672Z","started_at":"2026-08-09T15:02:48.075Z","completed_at":"","paused_at":"","total_paused_sec":89,"estimated_minutes":5340},"steps":[{"id":"91804ed8-5ad4-4ffd-aaad-beba64eb9cb2","job_id":"J02-dc56","name":"Dismantle: Washing Transmission gp","order":1,"status":"done","started_at":"2026-08-09T15:02:48.075Z","completed_at":"2026-08-09T15:20:47.571Z","duration_sec":1079,"std_minutes":240},{"id":"a127f857-f092-4b21-b197-3e3c8a02d549","job_id":"J02-dc56","name":"Dismantle: Control Valve 2EA","order":2,"status":"done","started_at":"2026-08-10T01:30:25.210Z","completed_at":"2026-08-10T01:30:32.748Z","duration_sec":36495,"std_minutes":300},{"id":"3bc8becf-2b5e-4391-8c9f-619d63d7281c","job_id":"J02-dc56","name":"Dismantle: Pump, Lines, &amp; Screen","order":3,"status":"done","started_at":"2026-08-10T01:30:32.748Z","completed_at":"2026-08-10T08:27:37.616Z","duration_sec":25024,"std_minutes":240},{"id":"bacf6ce8-8a97-4831-9f38-3010f4d64a9a","job_id":"J02-dc56","name":"Dismantle: Planetary GP","order":4,"status":"done","started_at":"2026-08-10T08:27:37.616Z","completed_at":"2026-08-11T05:36:57.526Z","duration_sec":76159,"std_minutes":900},{"id":"74bc5c28-b84c-4cfa-b429-25198c968f30","job_id":"J02-dc56","name":"Dismantle: Directional &amp; Idler gear","order":5,"status":"done","started_at":"2026-08-11T05:36:57.526Z","completed_at":"2026-08-11T14:50:26.762Z","duration_sec":33209,"std_minutes":300},{"id":"c3ce574f-16e3-4ce2-815e-10a842f608de","job_id":"J02-dc56","name":"Dismantle: Clean up Housing 2ea","order":6,"status":"in_progress","started_at":"2026-08-11T14:50:26.763Z","completed_at":"","duration_sec":0,"std_minutes":120},{"id":"b57a5afd-0b62-47a8-a149-df57cdbec92f","job_id":"J02-dc56","name":"Dismantle: Part list &amp; Tear Down","order":7,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"ef67991d-4f1b-4929-b4b9-3bd70d1c1a8b","job_id":"J02-dc56","name":"Assemble: Directional &amp; Idler gear","order":8,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"19689610-ed31-4c36-959c-6233ef31d9cc","job_id":"J02-dc56","name":"Assemble: Planetary GP","order":9,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"572f712a-0376-495f-a98f-9ee71ead12b3","job_id":"J02-dc56","name":"Assemble: CV 2EA","order":10,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"033a6b1b-8daf-46cc-a1e1-292ad2451d5f","job_id":"J02-dc56","name":"Assemble: Pump, Lines, &amp; Screen","order":11,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"f52cc000-4714-474d-a6c4-a3f41408fbb7","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Set up","order":12,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"a9b889d6-b2f7-4421-a27a-fcd6a2fde9f9","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Test","order":13,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"3edd89d2-41a4-4856-976b-cbc716dc3788","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Release","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"4d87b720-179e-4dbd-bf95-3d44c356f29e","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300}],"assignees":[{"id":"8f6f2232-50e1-4ad3-88b9-fddd08fa3833","job_id":"J02-dc56","technician_id":"T-75034b10","assigned_at":"2026-08-09T15:02:36.172Z","is_lead":"1"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-75034b10","status":"busy","current_job_id":"J02-dc56"}]}</t>
+  </si>
+  <si>
+    <t>76bb4fc2-d2ce-4505-b838-fab0b9422fc4</t>
+  </si>
+  <si>
+    <t>2026-08-11T14:56:11.277Z</t>
+  </si>
+  <si>
+    <t>assign · Recondition Transmission 16H,G · status in_progress</t>
+  </si>
+  <si>
+    <t>{"job":{"id":"J02-dc56","title":"Recondition Transmission 16H,G","unit":"E448 — D10T","unit_id":"a5c2144b-1b29-40f7-9b5c-cfbbc03c3387","description":"Job recondition Transmission 16H,G (time frame standar).","status":"in_progress","technician_id":"T-37cadb58","template_id":"ne-transmission-16h-g","created_at":"2026-08-09T14:29:20.672Z","started_at":"2026-08-09T15:02:48.075Z","completed_at":"","paused_at":"","total_paused_sec":89,"estimated_minutes":5340},"steps":[{"id":"91804ed8-5ad4-4ffd-aaad-beba64eb9cb2","job_id":"J02-dc56","name":"Dismantle: Washing Transmission gp","order":1,"status":"done","started_at":"2026-08-09T15:02:48.075Z","completed_at":"2026-08-09T15:20:47.571Z","duration_sec":1079,"std_minutes":240},{"id":"a127f857-f092-4b21-b197-3e3c8a02d549","job_id":"J02-dc56","name":"Dismantle: Control Valve 2EA","order":2,"status":"done","started_at":"2026-08-10T01:30:25.210Z","completed_at":"2026-08-10T01:30:32.748Z","duration_sec":36495,"std_minutes":300},{"id":"3bc8becf-2b5e-4391-8c9f-619d63d7281c","job_id":"J02-dc56","name":"Dismantle: Pump, Lines, &amp; Screen","order":3,"status":"done","started_at":"2026-08-10T01:30:32.748Z","completed_at":"2026-08-10T08:27:37.616Z","duration_sec":25024,"std_minutes":240},{"id":"bacf6ce8-8a97-4831-9f38-3010f4d64a9a","job_id":"J02-dc56","name":"Dismantle: Planetary GP","order":4,"status":"done","started_at":"2026-08-10T08:27:37.616Z","completed_at":"2026-08-11T05:36:57.526Z","duration_sec":76159,"std_minutes":900},{"id":"74bc5c28-b84c-4cfa-b429-25198c968f30","job_id":"J02-dc56","name":"Dismantle: Directional &amp; Idler gear","order":5,"status":"done","started_at":"2026-08-11T05:36:57.526Z","completed_at":"2026-08-11T14:50:26.762Z","duration_sec":33209,"std_minutes":300},{"id":"c3ce574f-16e3-4ce2-815e-10a842f608de","job_id":"J02-dc56","name":"Dismantle: Clean up Housing 2ea","order":6,"status":"in_progress","started_at":"2026-08-11T14:50:26.763Z","completed_at":"","duration_sec":0,"std_minutes":120},{"id":"b57a5afd-0b62-47a8-a149-df57cdbec92f","job_id":"J02-dc56","name":"Dismantle: Part list &amp; Tear Down","order":7,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"ef67991d-4f1b-4929-b4b9-3bd70d1c1a8b","job_id":"J02-dc56","name":"Assemble: Directional &amp; Idler gear","order":8,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"19689610-ed31-4c36-959c-6233ef31d9cc","job_id":"J02-dc56","name":"Assemble: Planetary GP","order":9,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"572f712a-0376-495f-a98f-9ee71ead12b3","job_id":"J02-dc56","name":"Assemble: CV 2EA","order":10,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"033a6b1b-8daf-46cc-a1e1-292ad2451d5f","job_id":"J02-dc56","name":"Assemble: Pump, Lines, &amp; Screen","order":11,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"f52cc000-4714-474d-a6c4-a3f41408fbb7","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Set up","order":12,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"a9b889d6-b2f7-4421-a27a-fcd6a2fde9f9","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Test","order":13,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"3edd89d2-41a4-4856-976b-cbc716dc3788","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Release","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"4d87b720-179e-4dbd-bf95-3d44c356f29e","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300}],"assignees":[{"id":"e39218a1-186b-46ca-b35a-d999eac3307c","job_id":"J02-dc56","technician_id":"T-37cadb58","assigned_at":"2026-08-11T14:56:11.247Z","is_lead":"1"},{"id":"56cff857-6f11-4d4f-889c-272de87907ef","job_id":"J02-dc56","technician_id":"T-e4a06545","assigned_at":"2026-08-11T14:56:11.247Z","is_lead":"0"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-37cadb58","status":"busy","current_job_id":"J02-dc56"},{"id":"T-e4a06545","status":"busy","current_job_id":"J02-dc56"}]}</t>
   </si>
 </sst>
 </file>
@@ -804,7 +825,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q28"/>
+  <dimension ref="A1:Q30"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -2291,6 +2312,112 @@
         <v>36</v>
       </c>
     </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>139</v>
+      </c>
+      <c r="B29" t="s">
+        <v>140</v>
+      </c>
+      <c r="C29" t="s">
+        <v>19</v>
+      </c>
+      <c r="D29" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" t="s">
+        <v>21</v>
+      </c>
+      <c r="F29" t="s">
+        <v>32</v>
+      </c>
+      <c r="G29" t="s">
+        <v>23</v>
+      </c>
+      <c r="H29" t="s">
+        <v>24</v>
+      </c>
+      <c r="I29" t="s">
+        <v>24</v>
+      </c>
+      <c r="J29" t="s">
+        <v>33</v>
+      </c>
+      <c r="K29" t="s">
+        <v>138</v>
+      </c>
+      <c r="L29" t="s">
+        <v>141</v>
+      </c>
+      <c r="M29" t="s">
+        <v>35</v>
+      </c>
+      <c r="N29" t="s">
+        <v>36</v>
+      </c>
+      <c r="O29" t="s">
+        <v>36</v>
+      </c>
+      <c r="P29" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>142</v>
+      </c>
+      <c r="B30" t="s">
+        <v>143</v>
+      </c>
+      <c r="C30" t="s">
+        <v>19</v>
+      </c>
+      <c r="D30" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" t="s">
+        <v>21</v>
+      </c>
+      <c r="F30" t="s">
+        <v>73</v>
+      </c>
+      <c r="G30" t="s">
+        <v>23</v>
+      </c>
+      <c r="H30" t="s">
+        <v>24</v>
+      </c>
+      <c r="I30" t="s">
+        <v>24</v>
+      </c>
+      <c r="J30" t="s">
+        <v>144</v>
+      </c>
+      <c r="K30" t="s">
+        <v>141</v>
+      </c>
+      <c r="L30" t="s">
+        <v>145</v>
+      </c>
+      <c r="M30" t="s">
+        <v>35</v>
+      </c>
+      <c r="N30" t="s">
+        <v>36</v>
+      </c>
+      <c r="O30" t="s">
+        <v>36</v>
+      </c>
+      <c r="P30" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>36</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/data/backup-jobs.xlsx
+++ b/data/backup-jobs.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="714" uniqueCount="182">
   <si>
     <t>id</t>
   </si>
@@ -449,6 +449,114 @@
   </si>
   <si>
     <t>{"job":{"id":"J02-dc56","title":"Recondition Transmission 16H,G","unit":"E448 — D10T","unit_id":"a5c2144b-1b29-40f7-9b5c-cfbbc03c3387","description":"Job recondition Transmission 16H,G (time frame standar).","status":"in_progress","technician_id":"T-37cadb58","template_id":"ne-transmission-16h-g","created_at":"2026-08-09T14:29:20.672Z","started_at":"2026-08-09T15:02:48.075Z","completed_at":"","paused_at":"","total_paused_sec":89,"estimated_minutes":5340},"steps":[{"id":"91804ed8-5ad4-4ffd-aaad-beba64eb9cb2","job_id":"J02-dc56","name":"Dismantle: Washing Transmission gp","order":1,"status":"done","started_at":"2026-08-09T15:02:48.075Z","completed_at":"2026-08-09T15:20:47.571Z","duration_sec":1079,"std_minutes":240},{"id":"a127f857-f092-4b21-b197-3e3c8a02d549","job_id":"J02-dc56","name":"Dismantle: Control Valve 2EA","order":2,"status":"done","started_at":"2026-08-10T01:30:25.210Z","completed_at":"2026-08-10T01:30:32.748Z","duration_sec":36495,"std_minutes":300},{"id":"3bc8becf-2b5e-4391-8c9f-619d63d7281c","job_id":"J02-dc56","name":"Dismantle: Pump, Lines, &amp; Screen","order":3,"status":"done","started_at":"2026-08-10T01:30:32.748Z","completed_at":"2026-08-10T08:27:37.616Z","duration_sec":25024,"std_minutes":240},{"id":"bacf6ce8-8a97-4831-9f38-3010f4d64a9a","job_id":"J02-dc56","name":"Dismantle: Planetary GP","order":4,"status":"done","started_at":"2026-08-10T08:27:37.616Z","completed_at":"2026-08-11T05:36:57.526Z","duration_sec":76159,"std_minutes":900},{"id":"74bc5c28-b84c-4cfa-b429-25198c968f30","job_id":"J02-dc56","name":"Dismantle: Directional &amp; Idler gear","order":5,"status":"done","started_at":"2026-08-11T05:36:57.526Z","completed_at":"2026-08-11T14:50:26.762Z","duration_sec":33209,"std_minutes":300},{"id":"c3ce574f-16e3-4ce2-815e-10a842f608de","job_id":"J02-dc56","name":"Dismantle: Clean up Housing 2ea","order":6,"status":"in_progress","started_at":"2026-08-11T14:50:26.763Z","completed_at":"","duration_sec":0,"std_minutes":120},{"id":"b57a5afd-0b62-47a8-a149-df57cdbec92f","job_id":"J02-dc56","name":"Dismantle: Part list &amp; Tear Down","order":7,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"ef67991d-4f1b-4929-b4b9-3bd70d1c1a8b","job_id":"J02-dc56","name":"Assemble: Directional &amp; Idler gear","order":8,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"19689610-ed31-4c36-959c-6233ef31d9cc","job_id":"J02-dc56","name":"Assemble: Planetary GP","order":9,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"572f712a-0376-495f-a98f-9ee71ead12b3","job_id":"J02-dc56","name":"Assemble: CV 2EA","order":10,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"033a6b1b-8daf-46cc-a1e1-292ad2451d5f","job_id":"J02-dc56","name":"Assemble: Pump, Lines, &amp; Screen","order":11,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"f52cc000-4714-474d-a6c4-a3f41408fbb7","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Set up","order":12,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"a9b889d6-b2f7-4421-a27a-fcd6a2fde9f9","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Test","order":13,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"3edd89d2-41a4-4856-976b-cbc716dc3788","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Release","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"4d87b720-179e-4dbd-bf95-3d44c356f29e","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300}],"assignees":[{"id":"e39218a1-186b-46ca-b35a-d999eac3307c","job_id":"J02-dc56","technician_id":"T-37cadb58","assigned_at":"2026-08-11T14:56:11.247Z","is_lead":"1"},{"id":"56cff857-6f11-4d4f-889c-272de87907ef","job_id":"J02-dc56","technician_id":"T-e4a06545","assigned_at":"2026-08-11T14:56:11.247Z","is_lead":"0"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-37cadb58","status":"busy","current_job_id":"J02-dc56"},{"id":"T-e4a06545","status":"busy","current_job_id":"J02-dc56"}]}</t>
+  </si>
+  <si>
+    <t>cae3617f-e7e3-4b27-926b-b76493793a43</t>
+  </si>
+  <si>
+    <t>2026-08-12T14:15:23.788Z</t>
+  </si>
+  <si>
+    <t>{"job":{"id":"J03-1833","title":"Recondition Transmission 16H,G","unit":"E448 — D10T","unit_id":"a5c2144b-1b29-40f7-9b5c-cfbbc03c3387","description":"Job recondition Transmission 16H,G (time frame standar).","status":"in_progress","technician_id":"T-c23ed9a4","template_id":"ne-transmission-16h-g","created_at":"2026-08-11T05:30:21.056Z","started_at":"2026-08-11T05:32:14.074Z","completed_at":"","paused_at":"","total_paused_sec":0,"estimated_minutes":5340},"steps":[{"id":"e21019ab-05cb-4d4f-8f8f-fb85fa9004da","job_id":"J03-1833","name":"Dismantle: Washing Transmission gp","order":1,"status":"done","started_at":"2026-08-11T05:32:14.074Z","completed_at":"2026-08-12T14:15:23.702Z","duration_sec":117789,"std_minutes":240},{"id":"5ceecb87-2473-4297-a2a0-db873217f383","job_id":"J03-1833","name":"Dismantle: Control Valve 2EA","order":2,"status":"in_progress","started_at":"2026-08-11T05:32:33.253Z","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"11997f0b-4cc8-4b54-8bdd-db3614b948c1","job_id":"J03-1833","name":"Dismantle: Pump, Lines, &amp; Screen","order":3,"status":"in_progress","started_at":"2026-08-11T05:32:33.253Z","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"6c426149-ef7a-48c2-9585-5909fe86eca9","job_id":"J03-1833","name":"Dismantle: Planetary GP","order":4,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":900},{"id":"5d3baced-8d6d-491b-9df4-09eaef47f6b9","job_id":"J03-1833","name":"Dismantle: Directional &amp; Idler gear","order":5,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"0feaac14-da1a-4360-98f3-a99ad7b2fd45","job_id":"J03-1833","name":"Dismantle: Clean up Housing 2ea","order":6,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":120},{"id":"5b00b8bb-18f9-4ef9-ac8c-5d5f25f11170","job_id":"J03-1833","name":"Dismantle: Part list &amp; Tear Down","order":7,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"c536fdc6-3459-4ab5-a588-3454f07f08c7","job_id":"J03-1833","name":"Assemble: Directional &amp; Idler gear","order":8,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"89d1ae15-daf2-4871-9bc0-5940279c96f6","job_id":"J03-1833","name":"Assemble: Planetary GP","order":9,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"1197b5dd-9928-4565-ae50-91f382e2beb0","job_id":"J03-1833","name":"Assemble: CV 2EA","order":10,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"6a936f7e-e97a-47f4-9e03-24e38ef315fc","job_id":"J03-1833","name":"Assemble: Pump, Lines, &amp; Screen","order":11,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"80894723-ea93-40ff-aa35-420c027d3f95","job_id":"J03-1833","name":"Test Bench &amp; Completed: Set up","order":12,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"acf6bd0c-0d96-40b6-8b9e-ee8c27ee1625","job_id":"J03-1833","name":"Test Bench &amp; Completed: Test","order":13,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"81692dde-b76a-433d-9b5d-3476cf3cd7f6","job_id":"J03-1833","name":"Test Bench &amp; Completed: Release","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"b69b87c3-9d4b-450e-8c0e-162eb755ff75","job_id":"J03-1833","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300}],"assignees":[{"id":"a58e3fbd-80eb-4c64-bd6b-bb7196830ed8","job_id":"J03-1833","technician_id":"T-c23ed9a4","assigned_at":"2026-08-11T05:31:58.767Z","is_lead":"1"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-c23ed9a4","status":"busy","current_job_id":"J03-1833"}]}</t>
+  </si>
+  <si>
+    <t>80d97294-01e9-4ba6-a47e-5e80ac03597c</t>
+  </si>
+  <si>
+    <t>2026-08-12T14:15:27.922Z</t>
+  </si>
+  <si>
+    <t>{"job":{"id":"J03-1833","title":"Recondition Transmission 16H,G","unit":"E448 — D10T","unit_id":"a5c2144b-1b29-40f7-9b5c-cfbbc03c3387","description":"Job recondition Transmission 16H,G (time frame standar).","status":"in_progress","technician_id":"T-c23ed9a4","template_id":"ne-transmission-16h-g","created_at":"2026-08-11T05:30:21.056Z","started_at":"2026-08-11T05:32:14.074Z","completed_at":"","paused_at":"","total_paused_sec":0,"estimated_minutes":5340},"steps":[{"id":"e21019ab-05cb-4d4f-8f8f-fb85fa9004da","job_id":"J03-1833","name":"Dismantle: Washing Transmission gp","order":1,"status":"done","started_at":"2026-08-11T05:32:14.074Z","completed_at":"2026-08-12T14:15:23.702Z","duration_sec":117789,"std_minutes":240},{"id":"5ceecb87-2473-4297-a2a0-db873217f383","job_id":"J03-1833","name":"Dismantle: Control Valve 2EA","order":2,"status":"done","started_at":"2026-08-11T05:32:33.253Z","completed_at":"2026-08-12T14:15:27.902Z","duration_sec":117774,"std_minutes":300},{"id":"11997f0b-4cc8-4b54-8bdd-db3614b948c1","job_id":"J03-1833","name":"Dismantle: Pump, Lines, &amp; Screen","order":3,"status":"in_progress","started_at":"2026-08-11T05:32:33.253Z","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"6c426149-ef7a-48c2-9585-5909fe86eca9","job_id":"J03-1833","name":"Dismantle: Planetary GP","order":4,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":900},{"id":"5d3baced-8d6d-491b-9df4-09eaef47f6b9","job_id":"J03-1833","name":"Dismantle: Directional &amp; Idler gear","order":5,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"0feaac14-da1a-4360-98f3-a99ad7b2fd45","job_id":"J03-1833","name":"Dismantle: Clean up Housing 2ea","order":6,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":120},{"id":"5b00b8bb-18f9-4ef9-ac8c-5d5f25f11170","job_id":"J03-1833","name":"Dismantle: Part list &amp; Tear Down","order":7,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"c536fdc6-3459-4ab5-a588-3454f07f08c7","job_id":"J03-1833","name":"Assemble: Directional &amp; Idler gear","order":8,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"89d1ae15-daf2-4871-9bc0-5940279c96f6","job_id":"J03-1833","name":"Assemble: Planetary GP","order":9,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"1197b5dd-9928-4565-ae50-91f382e2beb0","job_id":"J03-1833","name":"Assemble: CV 2EA","order":10,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"6a936f7e-e97a-47f4-9e03-24e38ef315fc","job_id":"J03-1833","name":"Assemble: Pump, Lines, &amp; Screen","order":11,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"80894723-ea93-40ff-aa35-420c027d3f95","job_id":"J03-1833","name":"Test Bench &amp; Completed: Set up","order":12,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"acf6bd0c-0d96-40b6-8b9e-ee8c27ee1625","job_id":"J03-1833","name":"Test Bench &amp; Completed: Test","order":13,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"81692dde-b76a-433d-9b5d-3476cf3cd7f6","job_id":"J03-1833","name":"Test Bench &amp; Completed: Release","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"b69b87c3-9d4b-450e-8c0e-162eb755ff75","job_id":"J03-1833","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300}],"assignees":[{"id":"a58e3fbd-80eb-4c64-bd6b-bb7196830ed8","job_id":"J03-1833","technician_id":"T-c23ed9a4","assigned_at":"2026-08-11T05:31:58.767Z","is_lead":"1"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-c23ed9a4","status":"busy","current_job_id":"J03-1833"}]}</t>
+  </si>
+  <si>
+    <t>86f10083-460f-4251-86f2-46b81f482239</t>
+  </si>
+  <si>
+    <t>2026-08-12T14:15:30.325Z</t>
+  </si>
+  <si>
+    <t>{"job":{"id":"J03-1833","title":"Recondition Transmission 16H,G","unit":"E448 — D10T","unit_id":"a5c2144b-1b29-40f7-9b5c-cfbbc03c3387","description":"Job recondition Transmission 16H,G (time frame standar).","status":"in_progress","technician_id":"T-c23ed9a4","template_id":"ne-transmission-16h-g","created_at":"2026-08-11T05:30:21.056Z","started_at":"2026-08-11T05:32:14.074Z","completed_at":"","paused_at":"","total_paused_sec":0,"estimated_minutes":5340},"steps":[{"id":"e21019ab-05cb-4d4f-8f8f-fb85fa9004da","job_id":"J03-1833","name":"Dismantle: Washing Transmission gp","order":1,"status":"done","started_at":"2026-08-11T05:32:14.074Z","completed_at":"2026-08-12T14:15:23.702Z","duration_sec":117789,"std_minutes":240},{"id":"5ceecb87-2473-4297-a2a0-db873217f383","job_id":"J03-1833","name":"Dismantle: Control Valve 2EA","order":2,"status":"done","started_at":"2026-08-11T05:32:33.253Z","completed_at":"2026-08-12T14:15:27.902Z","duration_sec":117774,"std_minutes":300},{"id":"11997f0b-4cc8-4b54-8bdd-db3614b948c1","job_id":"J03-1833","name":"Dismantle: Pump, Lines, &amp; Screen","order":3,"status":"done","started_at":"2026-08-11T05:32:33.253Z","completed_at":"2026-08-12T14:15:30.280Z","duration_sec":117777,"std_minutes":240},{"id":"6c426149-ef7a-48c2-9585-5909fe86eca9","job_id":"J03-1833","name":"Dismantle: Planetary GP","order":4,"status":"in_progress","started_at":"2026-08-12T14:15:30.280Z","completed_at":"","duration_sec":0,"std_minutes":900},{"id":"5d3baced-8d6d-491b-9df4-09eaef47f6b9","job_id":"J03-1833","name":"Dismantle: Directional &amp; Idler gear","order":5,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"0feaac14-da1a-4360-98f3-a99ad7b2fd45","job_id":"J03-1833","name":"Dismantle: Clean up Housing 2ea","order":6,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":120},{"id":"5b00b8bb-18f9-4ef9-ac8c-5d5f25f11170","job_id":"J03-1833","name":"Dismantle: Part list &amp; Tear Down","order":7,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"c536fdc6-3459-4ab5-a588-3454f07f08c7","job_id":"J03-1833","name":"Assemble: Directional &amp; Idler gear","order":8,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"89d1ae15-daf2-4871-9bc0-5940279c96f6","job_id":"J03-1833","name":"Assemble: Planetary GP","order":9,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"1197b5dd-9928-4565-ae50-91f382e2beb0","job_id":"J03-1833","name":"Assemble: CV 2EA","order":10,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"6a936f7e-e97a-47f4-9e03-24e38ef315fc","job_id":"J03-1833","name":"Assemble: Pump, Lines, &amp; Screen","order":11,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"80894723-ea93-40ff-aa35-420c027d3f95","job_id":"J03-1833","name":"Test Bench &amp; Completed: Set up","order":12,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"acf6bd0c-0d96-40b6-8b9e-ee8c27ee1625","job_id":"J03-1833","name":"Test Bench &amp; Completed: Test","order":13,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"81692dde-b76a-433d-9b5d-3476cf3cd7f6","job_id":"J03-1833","name":"Test Bench &amp; Completed: Release","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"b69b87c3-9d4b-450e-8c0e-162eb755ff75","job_id":"J03-1833","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300}],"assignees":[{"id":"a58e3fbd-80eb-4c64-bd6b-bb7196830ed8","job_id":"J03-1833","technician_id":"T-c23ed9a4","assigned_at":"2026-08-11T05:31:58.767Z","is_lead":"1"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-c23ed9a4","status":"busy","current_job_id":"J03-1833"}]}</t>
+  </si>
+  <si>
+    <t>5a906024-6eb8-4be4-a138-d16162fd4f10</t>
+  </si>
+  <si>
+    <t>2026-08-12T14:16:16.676Z</t>
+  </si>
+  <si>
+    <t>{"job":{"id":"J03-1833","title":"Recondition Transmission 16H,G","unit":"E448 — D10T","unit_id":"a5c2144b-1b29-40f7-9b5c-cfbbc03c3387","description":"Job recondition Transmission 16H,G (time frame standar).","status":"paused","technician_id":"T-c23ed9a4","template_id":"ne-transmission-16h-g","created_at":"2026-08-11T05:30:21.056Z","started_at":"2026-08-11T05:32:14.074Z","completed_at":"","paused_at":"2026-08-12T14:16:16.648Z","total_paused_sec":0,"estimated_minutes":5340},"steps":[{"id":"e21019ab-05cb-4d4f-8f8f-fb85fa9004da","job_id":"J03-1833","name":"Dismantle: Washing Transmission gp","order":1,"status":"done","started_at":"2026-08-11T05:32:14.074Z","completed_at":"2026-08-12T14:15:23.702Z","duration_sec":117789,"std_minutes":240},{"id":"5ceecb87-2473-4297-a2a0-db873217f383","job_id":"J03-1833","name":"Dismantle: Control Valve 2EA","order":2,"status":"done","started_at":"2026-08-11T05:32:33.253Z","completed_at":"2026-08-12T14:15:27.902Z","duration_sec":117774,"std_minutes":300},{"id":"11997f0b-4cc8-4b54-8bdd-db3614b948c1","job_id":"J03-1833","name":"Dismantle: Pump, Lines, &amp; Screen","order":3,"status":"done","started_at":"2026-08-11T05:32:33.253Z","completed_at":"2026-08-12T14:15:30.280Z","duration_sec":117777,"std_minutes":240},{"id":"6c426149-ef7a-48c2-9585-5909fe86eca9","job_id":"J03-1833","name":"Dismantle: Planetary GP","order":4,"status":"in_progress","started_at":"","completed_at":"","duration_sec":46,"std_minutes":900},{"id":"5d3baced-8d6d-491b-9df4-09eaef47f6b9","job_id":"J03-1833","name":"Dismantle: Directional &amp; Idler gear","order":5,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"0feaac14-da1a-4360-98f3-a99ad7b2fd45","job_id":"J03-1833","name":"Dismantle: Clean up Housing 2ea","order":6,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":120},{"id":"5b00b8bb-18f9-4ef9-ac8c-5d5f25f11170","job_id":"J03-1833","name":"Dismantle: Part list &amp; Tear Down","order":7,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"c536fdc6-3459-4ab5-a588-3454f07f08c7","job_id":"J03-1833","name":"Assemble: Directional &amp; Idler gear","order":8,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"89d1ae15-daf2-4871-9bc0-5940279c96f6","job_id":"J03-1833","name":"Assemble: Planetary GP","order":9,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"1197b5dd-9928-4565-ae50-91f382e2beb0","job_id":"J03-1833","name":"Assemble: CV 2EA","order":10,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"6a936f7e-e97a-47f4-9e03-24e38ef315fc","job_id":"J03-1833","name":"Assemble: Pump, Lines, &amp; Screen","order":11,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"80894723-ea93-40ff-aa35-420c027d3f95","job_id":"J03-1833","name":"Test Bench &amp; Completed: Set up","order":12,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"acf6bd0c-0d96-40b6-8b9e-ee8c27ee1625","job_id":"J03-1833","name":"Test Bench &amp; Completed: Test","order":13,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"81692dde-b76a-433d-9b5d-3476cf3cd7f6","job_id":"J03-1833","name":"Test Bench &amp; Completed: Release","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"b69b87c3-9d4b-450e-8c0e-162eb755ff75","job_id":"J03-1833","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300}],"assignees":[{"id":"a58e3fbd-80eb-4c64-bd6b-bb7196830ed8","job_id":"J03-1833","technician_id":"T-c23ed9a4","assigned_at":"2026-08-11T05:31:58.767Z","is_lead":"1"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-c23ed9a4","status":"busy","current_job_id":"J03-1833"}]}</t>
+  </si>
+  <si>
+    <t>392a79d1-e38a-4185-aead-f240b414dfc9</t>
+  </si>
+  <si>
+    <t>2026-08-12T14:16:20.429Z</t>
+  </si>
+  <si>
+    <t>{"job":{"id":"J03-1833","title":"Recondition Transmission 16H,G","unit":"E448 — D10T","unit_id":"a5c2144b-1b29-40f7-9b5c-cfbbc03c3387","description":"Job recondition Transmission 16H,G (time frame standar).","status":"in_progress","technician_id":"T-c23ed9a4","template_id":"ne-transmission-16h-g","created_at":"2026-08-11T05:30:21.056Z","started_at":"2026-08-11T05:32:14.074Z","completed_at":"","paused_at":"","total_paused_sec":3,"estimated_minutes":5340},"steps":[{"id":"e21019ab-05cb-4d4f-8f8f-fb85fa9004da","job_id":"J03-1833","name":"Dismantle: Washing Transmission gp","order":1,"status":"done","started_at":"2026-08-11T05:32:14.074Z","completed_at":"2026-08-12T14:15:23.702Z","duration_sec":117789,"std_minutes":240},{"id":"5ceecb87-2473-4297-a2a0-db873217f383","job_id":"J03-1833","name":"Dismantle: Control Valve 2EA","order":2,"status":"done","started_at":"2026-08-11T05:32:33.253Z","completed_at":"2026-08-12T14:15:27.902Z","duration_sec":117774,"std_minutes":300},{"id":"11997f0b-4cc8-4b54-8bdd-db3614b948c1","job_id":"J03-1833","name":"Dismantle: Pump, Lines, &amp; Screen","order":3,"status":"done","started_at":"2026-08-11T05:32:33.253Z","completed_at":"2026-08-12T14:15:30.280Z","duration_sec":117777,"std_minutes":240},{"id":"6c426149-ef7a-48c2-9585-5909fe86eca9","job_id":"J03-1833","name":"Dismantle: Planetary GP","order":4,"status":"in_progress","started_at":"2026-08-12T14:16:20.400Z","completed_at":"","duration_sec":46,"std_minutes":900},{"id":"5d3baced-8d6d-491b-9df4-09eaef47f6b9","job_id":"J03-1833","name":"Dismantle: Directional &amp; Idler gear","order":5,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"0feaac14-da1a-4360-98f3-a99ad7b2fd45","job_id":"J03-1833","name":"Dismantle: Clean up Housing 2ea","order":6,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":120},{"id":"5b00b8bb-18f9-4ef9-ac8c-5d5f25f11170","job_id":"J03-1833","name":"Dismantle: Part list &amp; Tear Down","order":7,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"c536fdc6-3459-4ab5-a588-3454f07f08c7","job_id":"J03-1833","name":"Assemble: Directional &amp; Idler gear","order":8,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"89d1ae15-daf2-4871-9bc0-5940279c96f6","job_id":"J03-1833","name":"Assemble: Planetary GP","order":9,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"1197b5dd-9928-4565-ae50-91f382e2beb0","job_id":"J03-1833","name":"Assemble: CV 2EA","order":10,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"6a936f7e-e97a-47f4-9e03-24e38ef315fc","job_id":"J03-1833","name":"Assemble: Pump, Lines, &amp; Screen","order":11,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"80894723-ea93-40ff-aa35-420c027d3f95","job_id":"J03-1833","name":"Test Bench &amp; Completed: Set up","order":12,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"acf6bd0c-0d96-40b6-8b9e-ee8c27ee1625","job_id":"J03-1833","name":"Test Bench &amp; Completed: Test","order":13,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"81692dde-b76a-433d-9b5d-3476cf3cd7f6","job_id":"J03-1833","name":"Test Bench &amp; Completed: Release","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"b69b87c3-9d4b-450e-8c0e-162eb755ff75","job_id":"J03-1833","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300}],"assignees":[{"id":"a58e3fbd-80eb-4c64-bd6b-bb7196830ed8","job_id":"J03-1833","technician_id":"T-c23ed9a4","assigned_at":"2026-08-11T05:31:58.767Z","is_lead":"1"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-c23ed9a4","status":"busy","current_job_id":"J03-1833"}]}</t>
+  </si>
+  <si>
+    <t>34c150b1-6bd8-4596-901e-e48a6334a2ca</t>
+  </si>
+  <si>
+    <t>2026-08-12T14:16:30.215Z</t>
+  </si>
+  <si>
+    <t>{"job":{"id":"J03-1833","title":"Recondition Transmission 16H,G","unit":"E448 — D10T","unit_id":"a5c2144b-1b29-40f7-9b5c-cfbbc03c3387","description":"Job recondition Transmission 16H,G (time frame standar).","status":"in_progress","technician_id":"T-c23ed9a4","template_id":"ne-transmission-16h-g","created_at":"2026-08-11T05:30:21.056Z","started_at":"2026-08-11T05:32:14.074Z","completed_at":"","paused_at":"","total_paused_sec":3,"estimated_minutes":5340},"steps":[{"id":"e21019ab-05cb-4d4f-8f8f-fb85fa9004da","job_id":"J03-1833","name":"Dismantle: Washing Transmission gp","order":1,"status":"done","started_at":"2026-08-11T05:32:14.074Z","completed_at":"2026-08-12T14:15:23.702Z","duration_sec":117789,"std_minutes":240},{"id":"5ceecb87-2473-4297-a2a0-db873217f383","job_id":"J03-1833","name":"Dismantle: Control Valve 2EA","order":2,"status":"done","started_at":"2026-08-11T05:32:33.253Z","completed_at":"2026-08-12T14:15:27.902Z","duration_sec":117774,"std_minutes":300},{"id":"11997f0b-4cc8-4b54-8bdd-db3614b948c1","job_id":"J03-1833","name":"Dismantle: Pump, Lines, &amp; Screen","order":3,"status":"done","started_at":"2026-08-11T05:32:33.253Z","completed_at":"2026-08-12T14:15:30.280Z","duration_sec":117777,"std_minutes":240},{"id":"6c426149-ef7a-48c2-9585-5909fe86eca9","job_id":"J03-1833","name":"Dismantle: Planetary GP","order":4,"status":"done","started_at":"2026-08-12T14:16:20.400Z","completed_at":"2026-08-12T14:16:30.166Z","duration_sec":55,"std_minutes":900},{"id":"5d3baced-8d6d-491b-9df4-09eaef47f6b9","job_id":"J03-1833","name":"Dismantle: Directional &amp; Idler gear","order":5,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"0feaac14-da1a-4360-98f3-a99ad7b2fd45","job_id":"J03-1833","name":"Dismantle: Clean up Housing 2ea","order":6,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":120},{"id":"5b00b8bb-18f9-4ef9-ac8c-5d5f25f11170","job_id":"J03-1833","name":"Dismantle: Part list &amp; Tear Down","order":7,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"c536fdc6-3459-4ab5-a588-3454f07f08c7","job_id":"J03-1833","name":"Assemble: Directional &amp; Idler gear","order":8,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"89d1ae15-daf2-4871-9bc0-5940279c96f6","job_id":"J03-1833","name":"Assemble: Planetary GP","order":9,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"1197b5dd-9928-4565-ae50-91f382e2beb0","job_id":"J03-1833","name":"Assemble: CV 2EA","order":10,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"6a936f7e-e97a-47f4-9e03-24e38ef315fc","job_id":"J03-1833","name":"Assemble: Pump, Lines, &amp; Screen","order":11,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"80894723-ea93-40ff-aa35-420c027d3f95","job_id":"J03-1833","name":"Test Bench &amp; Completed: Set up","order":12,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"acf6bd0c-0d96-40b6-8b9e-ee8c27ee1625","job_id":"J03-1833","name":"Test Bench &amp; Completed: Test","order":13,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"81692dde-b76a-433d-9b5d-3476cf3cd7f6","job_id":"J03-1833","name":"Test Bench &amp; Completed: Release","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"b69b87c3-9d4b-450e-8c0e-162eb755ff75","job_id":"J03-1833","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300}],"assignees":[{"id":"a58e3fbd-80eb-4c64-bd6b-bb7196830ed8","job_id":"J03-1833","technician_id":"T-c23ed9a4","assigned_at":"2026-08-11T05:31:58.767Z","is_lead":"1"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-c23ed9a4","status":"busy","current_job_id":"J03-1833"}]}</t>
+  </si>
+  <si>
+    <t>8f28bbc1-f811-49f9-9bcc-1be8042bfb47</t>
+  </si>
+  <si>
+    <t>2026-08-12T14:24:49.848Z</t>
+  </si>
+  <si>
+    <t>{"job":{"id":"J03-c0e2","title":"Recondition Transmission D10T,R","unit":"E448 — D10T","unit_id":"a5c2144b-1b29-40f7-9b5c-cfbbc03c3387","description":"Job recondition Transmission D10T,R (time frame standar).","status":"in_progress","technician_id":"T-533ca22c","template_id":"ne-transmission-d10t-r","created_at":"2026-08-10T08:22:13.799Z","started_at":"2026-08-10T08:23:20.053Z","completed_at":"","paused_at":"","total_paused_sec":3,"estimated_minutes":5820},"steps":[{"id":"7609ebf3-f1eb-4d9d-9591-f21d853034e1","job_id":"J03-c0e2","name":"Dismantle: Washing Transmission","order":1,"status":"done","started_at":"2026-08-10T08:23:20.053Z","completed_at":"2026-08-10T08:24:03.692Z","duration_sec":43,"std_minutes":60},{"id":"a3923555-21a4-4b60-9959-c48d814bf136","job_id":"J03-c0e2","name":"Dismantle: Trans Gear","order":2,"status":"done","started_at":"2026-08-10T08:23:32.872Z","completed_at":"2026-08-10T08:24:06.672Z","duration_sec":33,"std_minutes":600},{"id":"39c70957-da00-4dc8-a988-36ee41ef9841","job_id":"J03-c0e2","name":"Dismantle: CV, Harness, &amp; Sensor","order":3,"status":"done","started_at":"2026-08-10T08:24:08.700Z","completed_at":"2026-08-10T08:24:14.772Z","duration_sec":6,"std_minutes":300},{"id":"6feb4f63-8277-4c8a-a4cf-8d8a3d660682","job_id":"J03-c0e2","name":"Dismantle: Clutch 5","order":4,"status":"done","started_at":"2026-08-10T08:23:32.872Z","completed_at":"2026-08-10T08:24:08.700Z","duration_sec":35,"std_minutes":180},{"id":"179574f5-b3d7-43e4-a065-977ebd015bfc","job_id":"J03-c0e2","name":"Dismantle: Clutch 4","order":5,"status":"done","started_at":"2026-08-10T08:24:14.772Z","completed_at":"2026-08-10T10:10:28.558Z","duration_sec":6373,"std_minutes":180},{"id":"8aff0e07-0f40-4945-a9dc-7a8867ffccf4","job_id":"J03-c0e2","name":"Dismantle: Clutch 3","order":6,"status":"done","started_at":"2026-08-11T05:33:18.994Z","completed_at":"2026-08-11T05:33:34.800Z","duration_sec":69782,"std_minutes":180},{"id":"82415ef2-23b1-4eb2-b027-a268df0f4189","job_id":"J03-c0e2","name":"Dismantle: Clutch 2","order":7,"status":"done","started_at":"2026-08-11T05:33:34.800Z","completed_at":"2026-08-11T05:33:47.115Z","duration_sec":12,"std_minutes":180},{"id":"f7c8bcdc-e2d1-4856-aea1-f577d25b0550","job_id":"J03-c0e2","name":"Dismantle: Clutch 1","order":8,"status":"done","started_at":"2026-08-11T05:33:47.115Z","completed_at":"2026-08-12T14:24:49.765Z","duration_sec":118262,"std_minutes":180},{"id":"4391d523-f1d0-4922-95fb-d3827a21b813","job_id":"J03-c0e2","name":"Dismantle: Planetary &amp; Shaft","order":9,"status":"in_progress","started_at":"2026-08-12T14:24:49.766Z","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"bdcc79ae-9f46-46e2-963d-fd2ba3d40a2e","job_id":"J03-c0e2","name":"Dismantle: Part list &amp; Tear Down","order":10,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"0670c5ee-3df9-46ba-a7e5-790a2591233a","job_id":"J03-c0e2","name":"Assemble: Planetary &amp; Shaft In-Out","order":11,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"7276104d-e8c7-4ea6-aac7-6cd975141c45","job_id":"J03-c0e2","name":"Assemble: Clutch 1","order":12,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"1781ebaa-7fb0-4896-b642-71d33b8c4878","job_id":"J03-c0e2","name":"Assemble: Clutch 2","order":13,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"5532b99d-a7fd-4b7d-a752-796f7bc5daff","job_id":"J03-c0e2","name":"Assemble: Clutch 3","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"ff0ed73f-27d1-4b0a-a4f2-7818d3cfbc7e","job_id":"J03-c0e2","name":"Assemble: Clutch 4","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"970a35a3-a96b-48b4-9f04-a2b921b013f0","job_id":"J03-c0e2","name":"Assemble: Clutch 5","order":16,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"698b11d9-e1a3-451f-8a47-ccabcc5718c6","job_id":"J03-c0e2","name":"Assemble: CV, Harness &amp; Sensor","order":17,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"0620fee8-23da-434a-85e6-6354dee830d7","job_id":"J03-c0e2","name":"Assemble: Trans Gear","order":18,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":900},{"id":"ca31c8c2-4542-42f7-be4e-86974a63447b","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Set up","order":19,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"ba2d158c-a9f5-4d98-aea1-fd1f7983c4eb","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Test","order":20,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"d2f96316-8f95-487c-a7ee-94ba19ef4354","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Release","order":21,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"050b2cfc-5ea2-4926-b9c1-c7bdfe6bbd49","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":22,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240}],"assignees":[{"id":"5ece1c51-c36b-46e5-a9d2-f9106a729470","job_id":"J03-c0e2","technician_id":"T-533ca22c","assigned_at":"2026-08-10T08:23:08.120Z","is_lead":"1"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-533ca22c","status":"busy","current_job_id":"J03-c0e2"}]}</t>
+  </si>
+  <si>
+    <t>cfbe10ea-7adc-4f92-8326-483852d10eef</t>
+  </si>
+  <si>
+    <t>2026-08-12T14:25:18.211Z</t>
+  </si>
+  <si>
+    <t>{"job":{"id":"J02-dc56","title":"Recondition Transmission 16H,G","unit":"E448 — D10T","unit_id":"a5c2144b-1b29-40f7-9b5c-cfbbc03c3387","description":"Job recondition Transmission 16H,G (time frame standar).","status":"in_progress","technician_id":"T-37cadb58","template_id":"ne-transmission-16h-g","created_at":"2026-08-09T14:29:20.672Z","started_at":"2026-08-09T15:02:48.075Z","completed_at":"","paused_at":"","total_paused_sec":89,"estimated_minutes":5340},"steps":[{"id":"91804ed8-5ad4-4ffd-aaad-beba64eb9cb2","job_id":"J02-dc56","name":"Dismantle: Washing Transmission gp","order":1,"status":"done","started_at":"2026-08-09T15:02:48.075Z","completed_at":"2026-08-09T15:20:47.571Z","duration_sec":1079,"std_minutes":240},{"id":"a127f857-f092-4b21-b197-3e3c8a02d549","job_id":"J02-dc56","name":"Dismantle: Control Valve 2EA","order":2,"status":"done","started_at":"2026-08-10T01:30:25.210Z","completed_at":"2026-08-10T01:30:32.748Z","duration_sec":36495,"std_minutes":300},{"id":"3bc8becf-2b5e-4391-8c9f-619d63d7281c","job_id":"J02-dc56","name":"Dismantle: Pump, Lines, &amp; Screen","order":3,"status":"done","started_at":"2026-08-10T01:30:32.748Z","completed_at":"2026-08-10T08:27:37.616Z","duration_sec":25024,"std_minutes":240},{"id":"bacf6ce8-8a97-4831-9f38-3010f4d64a9a","job_id":"J02-dc56","name":"Dismantle: Planetary GP","order":4,"status":"done","started_at":"2026-08-10T08:27:37.616Z","completed_at":"2026-08-11T05:36:57.526Z","duration_sec":76159,"std_minutes":900},{"id":"74bc5c28-b84c-4cfa-b429-25198c968f30","job_id":"J02-dc56","name":"Dismantle: Directional &amp; Idler gear","order":5,"status":"done","started_at":"2026-08-11T05:36:57.526Z","completed_at":"2026-08-11T14:50:26.762Z","duration_sec":33209,"std_minutes":300},{"id":"c3ce574f-16e3-4ce2-815e-10a842f608de","job_id":"J02-dc56","name":"Dismantle: Clean up Housing 2ea","order":6,"status":"done","started_at":"2026-08-11T14:50:26.763Z","completed_at":"2026-08-12T14:25:17.931Z","duration_sec":84891,"std_minutes":120},{"id":"b57a5afd-0b62-47a8-a149-df57cdbec92f","job_id":"J02-dc56","name":"Dismantle: Part list &amp; Tear Down","order":7,"status":"in_progress","started_at":"2026-08-12T14:25:17.931Z","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"ef67991d-4f1b-4929-b4b9-3bd70d1c1a8b","job_id":"J02-dc56","name":"Assemble: Directional &amp; Idler gear","order":8,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"19689610-ed31-4c36-959c-6233ef31d9cc","job_id":"J02-dc56","name":"Assemble: Planetary GP","order":9,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"572f712a-0376-495f-a98f-9ee71ead12b3","job_id":"J02-dc56","name":"Assemble: CV 2EA","order":10,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"033a6b1b-8daf-46cc-a1e1-292ad2451d5f","job_id":"J02-dc56","name":"Assemble: Pump, Lines, &amp; Screen","order":11,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"f52cc000-4714-474d-a6c4-a3f41408fbb7","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Set up","order":12,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"a9b889d6-b2f7-4421-a27a-fcd6a2fde9f9","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Test","order":13,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"3edd89d2-41a4-4856-976b-cbc716dc3788","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Release","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"4d87b720-179e-4dbd-bf95-3d44c356f29e","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300}],"assignees":[{"id":"e39218a1-186b-46ca-b35a-d999eac3307c","job_id":"J02-dc56","technician_id":"T-37cadb58","assigned_at":"2026-08-11T14:56:11.247Z","is_lead":"1"},{"id":"56cff857-6f11-4d4f-889c-272de87907ef","job_id":"J02-dc56","technician_id":"T-e4a06545","assigned_at":"2026-08-11T14:56:11.247Z","is_lead":"0"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-37cadb58","status":"busy","current_job_id":"J02-dc56"},{"id":"T-e4a06545","status":"busy","current_job_id":"J02-dc56"}]}</t>
+  </si>
+  <si>
+    <t>e40b2a80-772a-4b22-be21-7a670a14a7a6</t>
+  </si>
+  <si>
+    <t>2026-08-12T14:28:07.888Z</t>
+  </si>
+  <si>
+    <t>{"job":{"id":"J03-1833","title":"Recondition Transmission 16H,G","unit":"E448 — D10T","unit_id":"a5c2144b-1b29-40f7-9b5c-cfbbc03c3387","description":"Job recondition Transmission 16H,G (time frame standar).","status":"in_progress","technician_id":"T-c23ed9a4","template_id":"ne-transmission-16h-g","created_at":"2026-08-11T05:30:21.056Z","started_at":"2026-08-11T05:32:14.074Z","completed_at":"","paused_at":"","total_paused_sec":3,"estimated_minutes":5340},"steps":[{"id":"e21019ab-05cb-4d4f-8f8f-fb85fa9004da","job_id":"J03-1833","name":"Dismantle: Washing Transmission gp","order":1,"status":"done","started_at":"2026-08-11T05:32:14.074Z","completed_at":"2026-08-12T14:15:23.702Z","duration_sec":117789,"std_minutes":240},{"id":"5ceecb87-2473-4297-a2a0-db873217f383","job_id":"J03-1833","name":"Dismantle: Control Valve 2EA","order":2,"status":"done","started_at":"2026-08-11T05:32:33.253Z","completed_at":"2026-08-12T14:15:27.902Z","duration_sec":117774,"std_minutes":300},{"id":"11997f0b-4cc8-4b54-8bdd-db3614b948c1","job_id":"J03-1833","name":"Dismantle: Pump, Lines, &amp; Screen","order":3,"status":"done","started_at":"2026-08-11T05:32:33.253Z","completed_at":"2026-08-12T14:15:30.280Z","duration_sec":117777,"std_minutes":240},{"id":"6c426149-ef7a-48c2-9585-5909fe86eca9","job_id":"J03-1833","name":"Dismantle: Planetary GP","order":4,"status":"done","started_at":"2026-08-12T14:16:20.400Z","completed_at":"2026-08-12T14:16:30.166Z","duration_sec":55,"std_minutes":900},{"id":"5d3baced-8d6d-491b-9df4-09eaef47f6b9","job_id":"J03-1833","name":"Dismantle: Directional &amp; Idler gear","order":5,"status":"in_progress","started_at":"2026-08-12T14:28:07.854Z","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"0feaac14-da1a-4360-98f3-a99ad7b2fd45","job_id":"J03-1833","name":"Dismantle: Clean up Housing 2ea","order":6,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":120},{"id":"5b00b8bb-18f9-4ef9-ac8c-5d5f25f11170","job_id":"J03-1833","name":"Dismantle: Part list &amp; Tear Down","order":7,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"c536fdc6-3459-4ab5-a588-3454f07f08c7","job_id":"J03-1833","name":"Assemble: Directional &amp; Idler gear","order":8,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"89d1ae15-daf2-4871-9bc0-5940279c96f6","job_id":"J03-1833","name":"Assemble: Planetary GP","order":9,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"1197b5dd-9928-4565-ae50-91f382e2beb0","job_id":"J03-1833","name":"Assemble: CV 2EA","order":10,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"6a936f7e-e97a-47f4-9e03-24e38ef315fc","job_id":"J03-1833","name":"Assemble: Pump, Lines, &amp; Screen","order":11,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"80894723-ea93-40ff-aa35-420c027d3f95","job_id":"J03-1833","name":"Test Bench &amp; Completed: Set up","order":12,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"acf6bd0c-0d96-40b6-8b9e-ee8c27ee1625","job_id":"J03-1833","name":"Test Bench &amp; Completed: Test","order":13,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"81692dde-b76a-433d-9b5d-3476cf3cd7f6","job_id":"J03-1833","name":"Test Bench &amp; Completed: Release","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"b69b87c3-9d4b-450e-8c0e-162eb755ff75","job_id":"J03-1833","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300}],"assignees":[{"id":"a58e3fbd-80eb-4c64-bd6b-bb7196830ed8","job_id":"J03-1833","technician_id":"T-c23ed9a4","assigned_at":"2026-08-11T05:31:58.767Z","is_lead":"1"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-c23ed9a4","status":"busy","current_job_id":"J03-1833"}]}</t>
+  </si>
+  <si>
+    <t>34a68c29-3c19-4495-a4fa-e07282e99275</t>
+  </si>
+  <si>
+    <t>2026-08-12T14:28:34.178Z</t>
+  </si>
+  <si>
+    <t>{"job":{"id":"J03-c0e2","title":"Recondition Transmission D10T,R","unit":"E448 — D10T","unit_id":"a5c2144b-1b29-40f7-9b5c-cfbbc03c3387","description":"Job recondition Transmission D10T,R (time frame standar).","status":"in_progress","technician_id":"T-533ca22c","template_id":"ne-transmission-d10t-r","created_at":"2026-08-10T08:22:13.799Z","started_at":"2026-08-10T08:23:20.053Z","completed_at":"","paused_at":"","total_paused_sec":3,"estimated_minutes":5820},"steps":[{"id":"7609ebf3-f1eb-4d9d-9591-f21d853034e1","job_id":"J03-c0e2","name":"Dismantle: Washing Transmission","order":1,"status":"done","started_at":"2026-08-10T08:23:20.053Z","completed_at":"2026-08-10T08:24:03.692Z","duration_sec":43,"std_minutes":60},{"id":"a3923555-21a4-4b60-9959-c48d814bf136","job_id":"J03-c0e2","name":"Dismantle: Trans Gear","order":2,"status":"done","started_at":"2026-08-10T08:23:32.872Z","completed_at":"2026-08-10T08:24:06.672Z","duration_sec":33,"std_minutes":600},{"id":"39c70957-da00-4dc8-a988-36ee41ef9841","job_id":"J03-c0e2","name":"Dismantle: CV, Harness, &amp; Sensor","order":3,"status":"done","started_at":"2026-08-10T08:24:08.700Z","completed_at":"2026-08-10T08:24:14.772Z","duration_sec":6,"std_minutes":300},{"id":"6feb4f63-8277-4c8a-a4cf-8d8a3d660682","job_id":"J03-c0e2","name":"Dismantle: Clutch 5","order":4,"status":"done","started_at":"2026-08-10T08:23:32.872Z","completed_at":"2026-08-10T08:24:08.700Z","duration_sec":35,"std_minutes":180},{"id":"179574f5-b3d7-43e4-a065-977ebd015bfc","job_id":"J03-c0e2","name":"Dismantle: Clutch 4","order":5,"status":"done","started_at":"2026-08-10T08:24:14.772Z","completed_at":"2026-08-10T10:10:28.558Z","duration_sec":6373,"std_minutes":180},{"id":"8aff0e07-0f40-4945-a9dc-7a8867ffccf4","job_id":"J03-c0e2","name":"Dismantle: Clutch 3","order":6,"status":"done","started_at":"2026-08-11T05:33:18.994Z","completed_at":"2026-08-11T05:33:34.800Z","duration_sec":69782,"std_minutes":180},{"id":"82415ef2-23b1-4eb2-b027-a268df0f4189","job_id":"J03-c0e2","name":"Dismantle: Clutch 2","order":7,"status":"done","started_at":"2026-08-11T05:33:34.800Z","completed_at":"2026-08-11T05:33:47.115Z","duration_sec":12,"std_minutes":180},{"id":"f7c8bcdc-e2d1-4856-aea1-f577d25b0550","job_id":"J03-c0e2","name":"Dismantle: Clutch 1","order":8,"status":"done","started_at":"2026-08-11T05:33:47.115Z","completed_at":"2026-08-12T14:24:49.765Z","duration_sec":118262,"std_minutes":180},{"id":"4391d523-f1d0-4922-95fb-d3827a21b813","job_id":"J03-c0e2","name":"Dismantle: Planetary &amp; Shaft","order":9,"status":"done","started_at":"2026-08-12T14:24:49.766Z","completed_at":"2026-08-12T14:28:34.119Z","duration_sec":224,"std_minutes":300},{"id":"bdcc79ae-9f46-46e2-963d-fd2ba3d40a2e","job_id":"J03-c0e2","name":"Dismantle: Part list &amp; Tear Down","order":10,"status":"in_progress","started_at":"2026-08-12T14:28:34.120Z","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"0670c5ee-3df9-46ba-a7e5-790a2591233a","job_id":"J03-c0e2","name":"Assemble: Planetary &amp; Shaft In-Out","order":11,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"7276104d-e8c7-4ea6-aac7-6cd975141c45","job_id":"J03-c0e2","name":"Assemble: Clutch 1","order":12,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"1781ebaa-7fb0-4896-b642-71d33b8c4878","job_id":"J03-c0e2","name":"Assemble: Clutch 2","order":13,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"5532b99d-a7fd-4b7d-a752-796f7bc5daff","job_id":"J03-c0e2","name":"Assemble: Clutch 3","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"ff0ed73f-27d1-4b0a-a4f2-7818d3cfbc7e","job_id":"J03-c0e2","name":"Assemble: Clutch 4","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"970a35a3-a96b-48b4-9f04-a2b921b013f0","job_id":"J03-c0e2","name":"Assemble: Clutch 5","order":16,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"698b11d9-e1a3-451f-8a47-ccabcc5718c6","job_id":"J03-c0e2","name":"Assemble: CV, Harness &amp; Sensor","order":17,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"0620fee8-23da-434a-85e6-6354dee830d7","job_id":"J03-c0e2","name":"Assemble: Trans Gear","order":18,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":900},{"id":"ca31c8c2-4542-42f7-be4e-86974a63447b","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Set up","order":19,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"ba2d158c-a9f5-4d98-aea1-fd1f7983c4eb","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Test","order":20,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"d2f96316-8f95-487c-a7ee-94ba19ef4354","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Release","order":21,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"050b2cfc-5ea2-4926-b9c1-c7bdfe6bbd49","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":22,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240}],"assignees":[{"id":"5ece1c51-c36b-46e5-a9d2-f9106a729470","job_id":"J03-c0e2","technician_id":"T-533ca22c","assigned_at":"2026-08-10T08:23:08.120Z","is_lead":"1"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-533ca22c","status":"busy","current_job_id":"J03-c0e2"}]}</t>
+  </si>
+  <si>
+    <t>029ce3ee-a424-401b-a179-4bf59e1f717b</t>
+  </si>
+  <si>
+    <t>2026-08-12T14:28:53.561Z</t>
+  </si>
+  <si>
+    <t>{"job":{"id":"J02-dc56","title":"Recondition Transmission 16H,G","unit":"E448 — D10T","unit_id":"a5c2144b-1b29-40f7-9b5c-cfbbc03c3387","description":"Job recondition Transmission 16H,G (time frame standar).","status":"paused","technician_id":"T-37cadb58","template_id":"ne-transmission-16h-g","created_at":"2026-08-09T14:29:20.672Z","started_at":"2026-08-09T15:02:48.075Z","completed_at":"","paused_at":"2026-08-12T14:28:53.512Z","total_paused_sec":89,"estimated_minutes":5340},"steps":[{"id":"91804ed8-5ad4-4ffd-aaad-beba64eb9cb2","job_id":"J02-dc56","name":"Dismantle: Washing Transmission gp","order":1,"status":"done","started_at":"2026-08-09T15:02:48.075Z","completed_at":"2026-08-09T15:20:47.571Z","duration_sec":1079,"std_minutes":240},{"id":"a127f857-f092-4b21-b197-3e3c8a02d549","job_id":"J02-dc56","name":"Dismantle: Control Valve 2EA","order":2,"status":"done","started_at":"2026-08-10T01:30:25.210Z","completed_at":"2026-08-10T01:30:32.748Z","duration_sec":36495,"std_minutes":300},{"id":"3bc8becf-2b5e-4391-8c9f-619d63d7281c","job_id":"J02-dc56","name":"Dismantle: Pump, Lines, &amp; Screen","order":3,"status":"done","started_at":"2026-08-10T01:30:32.748Z","completed_at":"2026-08-10T08:27:37.616Z","duration_sec":25024,"std_minutes":240},{"id":"bacf6ce8-8a97-4831-9f38-3010f4d64a9a","job_id":"J02-dc56","name":"Dismantle: Planetary GP","order":4,"status":"done","started_at":"2026-08-10T08:27:37.616Z","completed_at":"2026-08-11T05:36:57.526Z","duration_sec":76159,"std_minutes":900},{"id":"74bc5c28-b84c-4cfa-b429-25198c968f30","job_id":"J02-dc56","name":"Dismantle: Directional &amp; Idler gear","order":5,"status":"done","started_at":"2026-08-11T05:36:57.526Z","completed_at":"2026-08-11T14:50:26.762Z","duration_sec":33209,"std_minutes":300},{"id":"c3ce574f-16e3-4ce2-815e-10a842f608de","job_id":"J02-dc56","name":"Dismantle: Clean up Housing 2ea","order":6,"status":"done","started_at":"2026-08-11T14:50:26.763Z","completed_at":"2026-08-12T14:25:17.931Z","duration_sec":84891,"std_minutes":120},{"id":"b57a5afd-0b62-47a8-a149-df57cdbec92f","job_id":"J02-dc56","name":"Dismantle: Part list &amp; Tear Down","order":7,"status":"in_progress","started_at":"","completed_at":"","duration_sec":215,"std_minutes":240},{"id":"ef67991d-4f1b-4929-b4b9-3bd70d1c1a8b","job_id":"J02-dc56","name":"Assemble: Directional &amp; Idler gear","order":8,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"19689610-ed31-4c36-959c-6233ef31d9cc","job_id":"J02-dc56","name":"Assemble: Planetary GP","order":9,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"572f712a-0376-495f-a98f-9ee71ead12b3","job_id":"J02-dc56","name":"Assemble: CV 2EA","order":10,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"033a6b1b-8daf-46cc-a1e1-292ad2451d5f","job_id":"J02-dc56","name":"Assemble: Pump, Lines, &amp; Screen","order":11,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"f52cc000-4714-474d-a6c4-a3f41408fbb7","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Set up","order":12,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"a9b889d6-b2f7-4421-a27a-fcd6a2fde9f9","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Test","order":13,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"3edd89d2-41a4-4856-976b-cbc716dc3788","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Release","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"4d87b720-179e-4dbd-bf95-3d44c356f29e","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300}],"assignees":[{"id":"e39218a1-186b-46ca-b35a-d999eac3307c","job_id":"J02-dc56","technician_id":"T-37cadb58","assigned_at":"2026-08-11T14:56:11.247Z","is_lead":"1"},{"id":"56cff857-6f11-4d4f-889c-272de87907ef","job_id":"J02-dc56","technician_id":"T-e4a06545","assigned_at":"2026-08-11T14:56:11.247Z","is_lead":"0"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-37cadb58","status":"busy","current_job_id":"J02-dc56"},{"id":"T-e4a06545","status":"busy","current_job_id":"J02-dc56"}]}</t>
+  </si>
+  <si>
+    <t>e8d9c702-a95b-4a30-a427-3ac25f8ccf29</t>
+  </si>
+  <si>
+    <t>2026-08-12T14:28:56.726Z</t>
+  </si>
+  <si>
+    <t>{"job":{"id":"J02-dc56","title":"Recondition Transmission 16H,G","unit":"E448 — D10T","unit_id":"a5c2144b-1b29-40f7-9b5c-cfbbc03c3387","description":"Job recondition Transmission 16H,G (time frame standar).","status":"in_progress","technician_id":"T-37cadb58","template_id":"ne-transmission-16h-g","created_at":"2026-08-09T14:29:20.672Z","started_at":"2026-08-09T15:02:48.075Z","completed_at":"","paused_at":"","total_paused_sec":92,"estimated_minutes":5340},"steps":[{"id":"91804ed8-5ad4-4ffd-aaad-beba64eb9cb2","job_id":"J02-dc56","name":"Dismantle: Washing Transmission gp","order":1,"status":"done","started_at":"2026-08-09T15:02:48.075Z","completed_at":"2026-08-09T15:20:47.571Z","duration_sec":1079,"std_minutes":240},{"id":"a127f857-f092-4b21-b197-3e3c8a02d549","job_id":"J02-dc56","name":"Dismantle: Control Valve 2EA","order":2,"status":"done","started_at":"2026-08-10T01:30:25.210Z","completed_at":"2026-08-10T01:30:32.748Z","duration_sec":36495,"std_minutes":300},{"id":"3bc8becf-2b5e-4391-8c9f-619d63d7281c","job_id":"J02-dc56","name":"Dismantle: Pump, Lines, &amp; Screen","order":3,"status":"done","started_at":"2026-08-10T01:30:32.748Z","completed_at":"2026-08-10T08:27:37.616Z","duration_sec":25024,"std_minutes":240},{"id":"bacf6ce8-8a97-4831-9f38-3010f4d64a9a","job_id":"J02-dc56","name":"Dismantle: Planetary GP","order":4,"status":"done","started_at":"2026-08-10T08:27:37.616Z","completed_at":"2026-08-11T05:36:57.526Z","duration_sec":76159,"std_minutes":900},{"id":"74bc5c28-b84c-4cfa-b429-25198c968f30","job_id":"J02-dc56","name":"Dismantle: Directional &amp; Idler gear","order":5,"status":"done","started_at":"2026-08-11T05:36:57.526Z","completed_at":"2026-08-11T14:50:26.762Z","duration_sec":33209,"std_minutes":300},{"id":"c3ce574f-16e3-4ce2-815e-10a842f608de","job_id":"J02-dc56","name":"Dismantle: Clean up Housing 2ea","order":6,"status":"done","started_at":"2026-08-11T14:50:26.763Z","completed_at":"2026-08-12T14:25:17.931Z","duration_sec":84891,"std_minutes":120},{"id":"b57a5afd-0b62-47a8-a149-df57cdbec92f","job_id":"J02-dc56","name":"Dismantle: Part list &amp; Tear Down","order":7,"status":"in_progress","started_at":"2026-08-12T14:28:56.705Z","completed_at":"","duration_sec":215,"std_minutes":240},{"id":"ef67991d-4f1b-4929-b4b9-3bd70d1c1a8b","job_id":"J02-dc56","name":"Assemble: Directional &amp; Idler gear","order":8,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"19689610-ed31-4c36-959c-6233ef31d9cc","job_id":"J02-dc56","name":"Assemble: Planetary GP","order":9,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"572f712a-0376-495f-a98f-9ee71ead12b3","job_id":"J02-dc56","name":"Assemble: CV 2EA","order":10,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"033a6b1b-8daf-46cc-a1e1-292ad2451d5f","job_id":"J02-dc56","name":"Assemble: Pump, Lines, &amp; Screen","order":11,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"f52cc000-4714-474d-a6c4-a3f41408fbb7","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Set up","order":12,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"a9b889d6-b2f7-4421-a27a-fcd6a2fde9f9","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Test","order":13,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"3edd89d2-41a4-4856-976b-cbc716dc3788","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Release","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"4d87b720-179e-4dbd-bf95-3d44c356f29e","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300}],"assignees":[{"id":"e39218a1-186b-46ca-b35a-d999eac3307c","job_id":"J02-dc56","technician_id":"T-37cadb58","assigned_at":"2026-08-11T14:56:11.247Z","is_lead":"1"},{"id":"56cff857-6f11-4d4f-889c-272de87907ef","job_id":"J02-dc56","technician_id":"T-e4a06545","assigned_at":"2026-08-11T14:56:11.247Z","is_lead":"0"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-37cadb58","status":"busy","current_job_id":"J02-dc56"},{"id":"T-e4a06545","status":"busy","current_job_id":"J02-dc56"}]}</t>
   </si>
 </sst>
 </file>
@@ -825,7 +933,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q30"/>
+  <dimension ref="A1:Q42"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -2418,6 +2526,642 @@
         <v>36</v>
       </c>
     </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>146</v>
+      </c>
+      <c r="B31" t="s">
+        <v>147</v>
+      </c>
+      <c r="C31" t="s">
+        <v>19</v>
+      </c>
+      <c r="D31" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" t="s">
+        <v>21</v>
+      </c>
+      <c r="F31" t="s">
+        <v>32</v>
+      </c>
+      <c r="G31" t="s">
+        <v>23</v>
+      </c>
+      <c r="H31" t="s">
+        <v>107</v>
+      </c>
+      <c r="I31" t="s">
+        <v>107</v>
+      </c>
+      <c r="J31" t="s">
+        <v>33</v>
+      </c>
+      <c r="K31" t="s">
+        <v>121</v>
+      </c>
+      <c r="L31" t="s">
+        <v>148</v>
+      </c>
+      <c r="M31" t="s">
+        <v>35</v>
+      </c>
+      <c r="N31" t="s">
+        <v>36</v>
+      </c>
+      <c r="O31" t="s">
+        <v>36</v>
+      </c>
+      <c r="P31" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>149</v>
+      </c>
+      <c r="B32" t="s">
+        <v>150</v>
+      </c>
+      <c r="C32" t="s">
+        <v>19</v>
+      </c>
+      <c r="D32" t="s">
+        <v>20</v>
+      </c>
+      <c r="E32" t="s">
+        <v>21</v>
+      </c>
+      <c r="F32" t="s">
+        <v>32</v>
+      </c>
+      <c r="G32" t="s">
+        <v>23</v>
+      </c>
+      <c r="H32" t="s">
+        <v>107</v>
+      </c>
+      <c r="I32" t="s">
+        <v>107</v>
+      </c>
+      <c r="J32" t="s">
+        <v>33</v>
+      </c>
+      <c r="K32" t="s">
+        <v>148</v>
+      </c>
+      <c r="L32" t="s">
+        <v>151</v>
+      </c>
+      <c r="M32" t="s">
+        <v>35</v>
+      </c>
+      <c r="N32" t="s">
+        <v>36</v>
+      </c>
+      <c r="O32" t="s">
+        <v>36</v>
+      </c>
+      <c r="P32" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B33" t="s">
+        <v>153</v>
+      </c>
+      <c r="C33" t="s">
+        <v>19</v>
+      </c>
+      <c r="D33" t="s">
+        <v>20</v>
+      </c>
+      <c r="E33" t="s">
+        <v>21</v>
+      </c>
+      <c r="F33" t="s">
+        <v>32</v>
+      </c>
+      <c r="G33" t="s">
+        <v>23</v>
+      </c>
+      <c r="H33" t="s">
+        <v>107</v>
+      </c>
+      <c r="I33" t="s">
+        <v>107</v>
+      </c>
+      <c r="J33" t="s">
+        <v>33</v>
+      </c>
+      <c r="K33" t="s">
+        <v>151</v>
+      </c>
+      <c r="L33" t="s">
+        <v>154</v>
+      </c>
+      <c r="M33" t="s">
+        <v>35</v>
+      </c>
+      <c r="N33" t="s">
+        <v>36</v>
+      </c>
+      <c r="O33" t="s">
+        <v>36</v>
+      </c>
+      <c r="P33" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>155</v>
+      </c>
+      <c r="B34" t="s">
+        <v>156</v>
+      </c>
+      <c r="C34" t="s">
+        <v>19</v>
+      </c>
+      <c r="D34" t="s">
+        <v>20</v>
+      </c>
+      <c r="E34" t="s">
+        <v>21</v>
+      </c>
+      <c r="F34" t="s">
+        <v>41</v>
+      </c>
+      <c r="G34" t="s">
+        <v>23</v>
+      </c>
+      <c r="H34" t="s">
+        <v>107</v>
+      </c>
+      <c r="I34" t="s">
+        <v>107</v>
+      </c>
+      <c r="J34" t="s">
+        <v>42</v>
+      </c>
+      <c r="K34" t="s">
+        <v>154</v>
+      </c>
+      <c r="L34" t="s">
+        <v>157</v>
+      </c>
+      <c r="M34" t="s">
+        <v>35</v>
+      </c>
+      <c r="N34" t="s">
+        <v>36</v>
+      </c>
+      <c r="O34" t="s">
+        <v>36</v>
+      </c>
+      <c r="P34" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>158</v>
+      </c>
+      <c r="B35" t="s">
+        <v>159</v>
+      </c>
+      <c r="C35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D35" t="s">
+        <v>20</v>
+      </c>
+      <c r="E35" t="s">
+        <v>21</v>
+      </c>
+      <c r="F35" t="s">
+        <v>46</v>
+      </c>
+      <c r="G35" t="s">
+        <v>23</v>
+      </c>
+      <c r="H35" t="s">
+        <v>107</v>
+      </c>
+      <c r="I35" t="s">
+        <v>107</v>
+      </c>
+      <c r="J35" t="s">
+        <v>47</v>
+      </c>
+      <c r="K35" t="s">
+        <v>157</v>
+      </c>
+      <c r="L35" t="s">
+        <v>160</v>
+      </c>
+      <c r="M35" t="s">
+        <v>35</v>
+      </c>
+      <c r="N35" t="s">
+        <v>36</v>
+      </c>
+      <c r="O35" t="s">
+        <v>36</v>
+      </c>
+      <c r="P35" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>161</v>
+      </c>
+      <c r="B36" t="s">
+        <v>162</v>
+      </c>
+      <c r="C36" t="s">
+        <v>19</v>
+      </c>
+      <c r="D36" t="s">
+        <v>20</v>
+      </c>
+      <c r="E36" t="s">
+        <v>21</v>
+      </c>
+      <c r="F36" t="s">
+        <v>32</v>
+      </c>
+      <c r="G36" t="s">
+        <v>23</v>
+      </c>
+      <c r="H36" t="s">
+        <v>107</v>
+      </c>
+      <c r="I36" t="s">
+        <v>107</v>
+      </c>
+      <c r="J36" t="s">
+        <v>33</v>
+      </c>
+      <c r="K36" t="s">
+        <v>160</v>
+      </c>
+      <c r="L36" t="s">
+        <v>163</v>
+      </c>
+      <c r="M36" t="s">
+        <v>35</v>
+      </c>
+      <c r="N36" t="s">
+        <v>36</v>
+      </c>
+      <c r="O36" t="s">
+        <v>36</v>
+      </c>
+      <c r="P36" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>164</v>
+      </c>
+      <c r="B37" t="s">
+        <v>165</v>
+      </c>
+      <c r="C37" t="s">
+        <v>19</v>
+      </c>
+      <c r="D37" t="s">
+        <v>20</v>
+      </c>
+      <c r="E37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F37" t="s">
+        <v>32</v>
+      </c>
+      <c r="G37" t="s">
+        <v>23</v>
+      </c>
+      <c r="H37" t="s">
+        <v>55</v>
+      </c>
+      <c r="I37" t="s">
+        <v>55</v>
+      </c>
+      <c r="J37" t="s">
+        <v>88</v>
+      </c>
+      <c r="K37" t="s">
+        <v>135</v>
+      </c>
+      <c r="L37" t="s">
+        <v>166</v>
+      </c>
+      <c r="M37" t="s">
+        <v>35</v>
+      </c>
+      <c r="N37" t="s">
+        <v>36</v>
+      </c>
+      <c r="O37" t="s">
+        <v>36</v>
+      </c>
+      <c r="P37" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>167</v>
+      </c>
+      <c r="B38" t="s">
+        <v>168</v>
+      </c>
+      <c r="C38" t="s">
+        <v>19</v>
+      </c>
+      <c r="D38" t="s">
+        <v>20</v>
+      </c>
+      <c r="E38" t="s">
+        <v>21</v>
+      </c>
+      <c r="F38" t="s">
+        <v>32</v>
+      </c>
+      <c r="G38" t="s">
+        <v>23</v>
+      </c>
+      <c r="H38" t="s">
+        <v>24</v>
+      </c>
+      <c r="I38" t="s">
+        <v>24</v>
+      </c>
+      <c r="J38" t="s">
+        <v>33</v>
+      </c>
+      <c r="K38" t="s">
+        <v>145</v>
+      </c>
+      <c r="L38" t="s">
+        <v>169</v>
+      </c>
+      <c r="M38" t="s">
+        <v>35</v>
+      </c>
+      <c r="N38" t="s">
+        <v>36</v>
+      </c>
+      <c r="O38" t="s">
+        <v>36</v>
+      </c>
+      <c r="P38" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>170</v>
+      </c>
+      <c r="B39" t="s">
+        <v>171</v>
+      </c>
+      <c r="C39" t="s">
+        <v>19</v>
+      </c>
+      <c r="D39" t="s">
+        <v>20</v>
+      </c>
+      <c r="E39" t="s">
+        <v>21</v>
+      </c>
+      <c r="F39" t="s">
+        <v>83</v>
+      </c>
+      <c r="G39" t="s">
+        <v>23</v>
+      </c>
+      <c r="H39" t="s">
+        <v>107</v>
+      </c>
+      <c r="I39" t="s">
+        <v>107</v>
+      </c>
+      <c r="J39" t="s">
+        <v>120</v>
+      </c>
+      <c r="K39" t="s">
+        <v>163</v>
+      </c>
+      <c r="L39" t="s">
+        <v>172</v>
+      </c>
+      <c r="M39" t="s">
+        <v>35</v>
+      </c>
+      <c r="N39" t="s">
+        <v>36</v>
+      </c>
+      <c r="O39" t="s">
+        <v>36</v>
+      </c>
+      <c r="P39" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>173</v>
+      </c>
+      <c r="B40" t="s">
+        <v>174</v>
+      </c>
+      <c r="C40" t="s">
+        <v>19</v>
+      </c>
+      <c r="D40" t="s">
+        <v>20</v>
+      </c>
+      <c r="E40" t="s">
+        <v>21</v>
+      </c>
+      <c r="F40" t="s">
+        <v>32</v>
+      </c>
+      <c r="G40" t="s">
+        <v>23</v>
+      </c>
+      <c r="H40" t="s">
+        <v>55</v>
+      </c>
+      <c r="I40" t="s">
+        <v>55</v>
+      </c>
+      <c r="J40" t="s">
+        <v>88</v>
+      </c>
+      <c r="K40" t="s">
+        <v>166</v>
+      </c>
+      <c r="L40" t="s">
+        <v>175</v>
+      </c>
+      <c r="M40" t="s">
+        <v>35</v>
+      </c>
+      <c r="N40" t="s">
+        <v>36</v>
+      </c>
+      <c r="O40" t="s">
+        <v>36</v>
+      </c>
+      <c r="P40" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>176</v>
+      </c>
+      <c r="B41" t="s">
+        <v>177</v>
+      </c>
+      <c r="C41" t="s">
+        <v>19</v>
+      </c>
+      <c r="D41" t="s">
+        <v>20</v>
+      </c>
+      <c r="E41" t="s">
+        <v>21</v>
+      </c>
+      <c r="F41" t="s">
+        <v>41</v>
+      </c>
+      <c r="G41" t="s">
+        <v>23</v>
+      </c>
+      <c r="H41" t="s">
+        <v>24</v>
+      </c>
+      <c r="I41" t="s">
+        <v>24</v>
+      </c>
+      <c r="J41" t="s">
+        <v>42</v>
+      </c>
+      <c r="K41" t="s">
+        <v>169</v>
+      </c>
+      <c r="L41" t="s">
+        <v>178</v>
+      </c>
+      <c r="M41" t="s">
+        <v>35</v>
+      </c>
+      <c r="N41" t="s">
+        <v>36</v>
+      </c>
+      <c r="O41" t="s">
+        <v>36</v>
+      </c>
+      <c r="P41" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>179</v>
+      </c>
+      <c r="B42" t="s">
+        <v>180</v>
+      </c>
+      <c r="C42" t="s">
+        <v>19</v>
+      </c>
+      <c r="D42" t="s">
+        <v>20</v>
+      </c>
+      <c r="E42" t="s">
+        <v>21</v>
+      </c>
+      <c r="F42" t="s">
+        <v>46</v>
+      </c>
+      <c r="G42" t="s">
+        <v>23</v>
+      </c>
+      <c r="H42" t="s">
+        <v>24</v>
+      </c>
+      <c r="I42" t="s">
+        <v>24</v>
+      </c>
+      <c r="J42" t="s">
+        <v>47</v>
+      </c>
+      <c r="K42" t="s">
+        <v>178</v>
+      </c>
+      <c r="L42" t="s">
+        <v>181</v>
+      </c>
+      <c r="M42" t="s">
+        <v>35</v>
+      </c>
+      <c r="N42" t="s">
+        <v>36</v>
+      </c>
+      <c r="O42" t="s">
+        <v>36</v>
+      </c>
+      <c r="P42" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>36</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/data/backup-jobs.xlsx
+++ b/data/backup-jobs.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="714" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="680" uniqueCount="176">
   <si>
     <t>id</t>
   </si>
@@ -451,112 +451,94 @@
     <t>{"job":{"id":"J02-dc56","title":"Recondition Transmission 16H,G","unit":"E448 — D10T","unit_id":"a5c2144b-1b29-40f7-9b5c-cfbbc03c3387","description":"Job recondition Transmission 16H,G (time frame standar).","status":"in_progress","technician_id":"T-37cadb58","template_id":"ne-transmission-16h-g","created_at":"2026-08-09T14:29:20.672Z","started_at":"2026-08-09T15:02:48.075Z","completed_at":"","paused_at":"","total_paused_sec":89,"estimated_minutes":5340},"steps":[{"id":"91804ed8-5ad4-4ffd-aaad-beba64eb9cb2","job_id":"J02-dc56","name":"Dismantle: Washing Transmission gp","order":1,"status":"done","started_at":"2026-08-09T15:02:48.075Z","completed_at":"2026-08-09T15:20:47.571Z","duration_sec":1079,"std_minutes":240},{"id":"a127f857-f092-4b21-b197-3e3c8a02d549","job_id":"J02-dc56","name":"Dismantle: Control Valve 2EA","order":2,"status":"done","started_at":"2026-08-10T01:30:25.210Z","completed_at":"2026-08-10T01:30:32.748Z","duration_sec":36495,"std_minutes":300},{"id":"3bc8becf-2b5e-4391-8c9f-619d63d7281c","job_id":"J02-dc56","name":"Dismantle: Pump, Lines, &amp; Screen","order":3,"status":"done","started_at":"2026-08-10T01:30:32.748Z","completed_at":"2026-08-10T08:27:37.616Z","duration_sec":25024,"std_minutes":240},{"id":"bacf6ce8-8a97-4831-9f38-3010f4d64a9a","job_id":"J02-dc56","name":"Dismantle: Planetary GP","order":4,"status":"done","started_at":"2026-08-10T08:27:37.616Z","completed_at":"2026-08-11T05:36:57.526Z","duration_sec":76159,"std_minutes":900},{"id":"74bc5c28-b84c-4cfa-b429-25198c968f30","job_id":"J02-dc56","name":"Dismantle: Directional &amp; Idler gear","order":5,"status":"done","started_at":"2026-08-11T05:36:57.526Z","completed_at":"2026-08-11T14:50:26.762Z","duration_sec":33209,"std_minutes":300},{"id":"c3ce574f-16e3-4ce2-815e-10a842f608de","job_id":"J02-dc56","name":"Dismantle: Clean up Housing 2ea","order":6,"status":"in_progress","started_at":"2026-08-11T14:50:26.763Z","completed_at":"","duration_sec":0,"std_minutes":120},{"id":"b57a5afd-0b62-47a8-a149-df57cdbec92f","job_id":"J02-dc56","name":"Dismantle: Part list &amp; Tear Down","order":7,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"ef67991d-4f1b-4929-b4b9-3bd70d1c1a8b","job_id":"J02-dc56","name":"Assemble: Directional &amp; Idler gear","order":8,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"19689610-ed31-4c36-959c-6233ef31d9cc","job_id":"J02-dc56","name":"Assemble: Planetary GP","order":9,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"572f712a-0376-495f-a98f-9ee71ead12b3","job_id":"J02-dc56","name":"Assemble: CV 2EA","order":10,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"033a6b1b-8daf-46cc-a1e1-292ad2451d5f","job_id":"J02-dc56","name":"Assemble: Pump, Lines, &amp; Screen","order":11,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"f52cc000-4714-474d-a6c4-a3f41408fbb7","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Set up","order":12,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"a9b889d6-b2f7-4421-a27a-fcd6a2fde9f9","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Test","order":13,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"3edd89d2-41a4-4856-976b-cbc716dc3788","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Release","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"4d87b720-179e-4dbd-bf95-3d44c356f29e","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300}],"assignees":[{"id":"e39218a1-186b-46ca-b35a-d999eac3307c","job_id":"J02-dc56","technician_id":"T-37cadb58","assigned_at":"2026-08-11T14:56:11.247Z","is_lead":"1"},{"id":"56cff857-6f11-4d4f-889c-272de87907ef","job_id":"J02-dc56","technician_id":"T-e4a06545","assigned_at":"2026-08-11T14:56:11.247Z","is_lead":"0"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-37cadb58","status":"busy","current_job_id":"J02-dc56"},{"id":"T-e4a06545","status":"busy","current_job_id":"J02-dc56"}]}</t>
   </si>
   <si>
-    <t>cae3617f-e7e3-4b27-926b-b76493793a43</t>
-  </si>
-  <si>
-    <t>2026-08-12T14:15:23.788Z</t>
-  </si>
-  <si>
-    <t>{"job":{"id":"J03-1833","title":"Recondition Transmission 16H,G","unit":"E448 — D10T","unit_id":"a5c2144b-1b29-40f7-9b5c-cfbbc03c3387","description":"Job recondition Transmission 16H,G (time frame standar).","status":"in_progress","technician_id":"T-c23ed9a4","template_id":"ne-transmission-16h-g","created_at":"2026-08-11T05:30:21.056Z","started_at":"2026-08-11T05:32:14.074Z","completed_at":"","paused_at":"","total_paused_sec":0,"estimated_minutes":5340},"steps":[{"id":"e21019ab-05cb-4d4f-8f8f-fb85fa9004da","job_id":"J03-1833","name":"Dismantle: Washing Transmission gp","order":1,"status":"done","started_at":"2026-08-11T05:32:14.074Z","completed_at":"2026-08-12T14:15:23.702Z","duration_sec":117789,"std_minutes":240},{"id":"5ceecb87-2473-4297-a2a0-db873217f383","job_id":"J03-1833","name":"Dismantle: Control Valve 2EA","order":2,"status":"in_progress","started_at":"2026-08-11T05:32:33.253Z","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"11997f0b-4cc8-4b54-8bdd-db3614b948c1","job_id":"J03-1833","name":"Dismantle: Pump, Lines, &amp; Screen","order":3,"status":"in_progress","started_at":"2026-08-11T05:32:33.253Z","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"6c426149-ef7a-48c2-9585-5909fe86eca9","job_id":"J03-1833","name":"Dismantle: Planetary GP","order":4,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":900},{"id":"5d3baced-8d6d-491b-9df4-09eaef47f6b9","job_id":"J03-1833","name":"Dismantle: Directional &amp; Idler gear","order":5,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"0feaac14-da1a-4360-98f3-a99ad7b2fd45","job_id":"J03-1833","name":"Dismantle: Clean up Housing 2ea","order":6,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":120},{"id":"5b00b8bb-18f9-4ef9-ac8c-5d5f25f11170","job_id":"J03-1833","name":"Dismantle: Part list &amp; Tear Down","order":7,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"c536fdc6-3459-4ab5-a588-3454f07f08c7","job_id":"J03-1833","name":"Assemble: Directional &amp; Idler gear","order":8,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"89d1ae15-daf2-4871-9bc0-5940279c96f6","job_id":"J03-1833","name":"Assemble: Planetary GP","order":9,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"1197b5dd-9928-4565-ae50-91f382e2beb0","job_id":"J03-1833","name":"Assemble: CV 2EA","order":10,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"6a936f7e-e97a-47f4-9e03-24e38ef315fc","job_id":"J03-1833","name":"Assemble: Pump, Lines, &amp; Screen","order":11,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"80894723-ea93-40ff-aa35-420c027d3f95","job_id":"J03-1833","name":"Test Bench &amp; Completed: Set up","order":12,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"acf6bd0c-0d96-40b6-8b9e-ee8c27ee1625","job_id":"J03-1833","name":"Test Bench &amp; Completed: Test","order":13,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"81692dde-b76a-433d-9b5d-3476cf3cd7f6","job_id":"J03-1833","name":"Test Bench &amp; Completed: Release","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"b69b87c3-9d4b-450e-8c0e-162eb755ff75","job_id":"J03-1833","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300}],"assignees":[{"id":"a58e3fbd-80eb-4c64-bd6b-bb7196830ed8","job_id":"J03-1833","technician_id":"T-c23ed9a4","assigned_at":"2026-08-11T05:31:58.767Z","is_lead":"1"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-c23ed9a4","status":"busy","current_job_id":"J03-1833"}]}</t>
-  </si>
-  <si>
-    <t>80d97294-01e9-4ba6-a47e-5e80ac03597c</t>
-  </si>
-  <si>
-    <t>2026-08-12T14:15:27.922Z</t>
-  </si>
-  <si>
-    <t>{"job":{"id":"J03-1833","title":"Recondition Transmission 16H,G","unit":"E448 — D10T","unit_id":"a5c2144b-1b29-40f7-9b5c-cfbbc03c3387","description":"Job recondition Transmission 16H,G (time frame standar).","status":"in_progress","technician_id":"T-c23ed9a4","template_id":"ne-transmission-16h-g","created_at":"2026-08-11T05:30:21.056Z","started_at":"2026-08-11T05:32:14.074Z","completed_at":"","paused_at":"","total_paused_sec":0,"estimated_minutes":5340},"steps":[{"id":"e21019ab-05cb-4d4f-8f8f-fb85fa9004da","job_id":"J03-1833","name":"Dismantle: Washing Transmission gp","order":1,"status":"done","started_at":"2026-08-11T05:32:14.074Z","completed_at":"2026-08-12T14:15:23.702Z","duration_sec":117789,"std_minutes":240},{"id":"5ceecb87-2473-4297-a2a0-db873217f383","job_id":"J03-1833","name":"Dismantle: Control Valve 2EA","order":2,"status":"done","started_at":"2026-08-11T05:32:33.253Z","completed_at":"2026-08-12T14:15:27.902Z","duration_sec":117774,"std_minutes":300},{"id":"11997f0b-4cc8-4b54-8bdd-db3614b948c1","job_id":"J03-1833","name":"Dismantle: Pump, Lines, &amp; Screen","order":3,"status":"in_progress","started_at":"2026-08-11T05:32:33.253Z","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"6c426149-ef7a-48c2-9585-5909fe86eca9","job_id":"J03-1833","name":"Dismantle: Planetary GP","order":4,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":900},{"id":"5d3baced-8d6d-491b-9df4-09eaef47f6b9","job_id":"J03-1833","name":"Dismantle: Directional &amp; Idler gear","order":5,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"0feaac14-da1a-4360-98f3-a99ad7b2fd45","job_id":"J03-1833","name":"Dismantle: Clean up Housing 2ea","order":6,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":120},{"id":"5b00b8bb-18f9-4ef9-ac8c-5d5f25f11170","job_id":"J03-1833","name":"Dismantle: Part list &amp; Tear Down","order":7,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"c536fdc6-3459-4ab5-a588-3454f07f08c7","job_id":"J03-1833","name":"Assemble: Directional &amp; Idler gear","order":8,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"89d1ae15-daf2-4871-9bc0-5940279c96f6","job_id":"J03-1833","name":"Assemble: Planetary GP","order":9,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"1197b5dd-9928-4565-ae50-91f382e2beb0","job_id":"J03-1833","name":"Assemble: CV 2EA","order":10,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"6a936f7e-e97a-47f4-9e03-24e38ef315fc","job_id":"J03-1833","name":"Assemble: Pump, Lines, &amp; Screen","order":11,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"80894723-ea93-40ff-aa35-420c027d3f95","job_id":"J03-1833","name":"Test Bench &amp; Completed: Set up","order":12,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"acf6bd0c-0d96-40b6-8b9e-ee8c27ee1625","job_id":"J03-1833","name":"Test Bench &amp; Completed: Test","order":13,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"81692dde-b76a-433d-9b5d-3476cf3cd7f6","job_id":"J03-1833","name":"Test Bench &amp; Completed: Release","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"b69b87c3-9d4b-450e-8c0e-162eb755ff75","job_id":"J03-1833","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300}],"assignees":[{"id":"a58e3fbd-80eb-4c64-bd6b-bb7196830ed8","job_id":"J03-1833","technician_id":"T-c23ed9a4","assigned_at":"2026-08-11T05:31:58.767Z","is_lead":"1"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-c23ed9a4","status":"busy","current_job_id":"J03-1833"}]}</t>
-  </si>
-  <si>
-    <t>86f10083-460f-4251-86f2-46b81f482239</t>
-  </si>
-  <si>
-    <t>2026-08-12T14:15:30.325Z</t>
-  </si>
-  <si>
-    <t>{"job":{"id":"J03-1833","title":"Recondition Transmission 16H,G","unit":"E448 — D10T","unit_id":"a5c2144b-1b29-40f7-9b5c-cfbbc03c3387","description":"Job recondition Transmission 16H,G (time frame standar).","status":"in_progress","technician_id":"T-c23ed9a4","template_id":"ne-transmission-16h-g","created_at":"2026-08-11T05:30:21.056Z","started_at":"2026-08-11T05:32:14.074Z","completed_at":"","paused_at":"","total_paused_sec":0,"estimated_minutes":5340},"steps":[{"id":"e21019ab-05cb-4d4f-8f8f-fb85fa9004da","job_id":"J03-1833","name":"Dismantle: Washing Transmission gp","order":1,"status":"done","started_at":"2026-08-11T05:32:14.074Z","completed_at":"2026-08-12T14:15:23.702Z","duration_sec":117789,"std_minutes":240},{"id":"5ceecb87-2473-4297-a2a0-db873217f383","job_id":"J03-1833","name":"Dismantle: Control Valve 2EA","order":2,"status":"done","started_at":"2026-08-11T05:32:33.253Z","completed_at":"2026-08-12T14:15:27.902Z","duration_sec":117774,"std_minutes":300},{"id":"11997f0b-4cc8-4b54-8bdd-db3614b948c1","job_id":"J03-1833","name":"Dismantle: Pump, Lines, &amp; Screen","order":3,"status":"done","started_at":"2026-08-11T05:32:33.253Z","completed_at":"2026-08-12T14:15:30.280Z","duration_sec":117777,"std_minutes":240},{"id":"6c426149-ef7a-48c2-9585-5909fe86eca9","job_id":"J03-1833","name":"Dismantle: Planetary GP","order":4,"status":"in_progress","started_at":"2026-08-12T14:15:30.280Z","completed_at":"","duration_sec":0,"std_minutes":900},{"id":"5d3baced-8d6d-491b-9df4-09eaef47f6b9","job_id":"J03-1833","name":"Dismantle: Directional &amp; Idler gear","order":5,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"0feaac14-da1a-4360-98f3-a99ad7b2fd45","job_id":"J03-1833","name":"Dismantle: Clean up Housing 2ea","order":6,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":120},{"id":"5b00b8bb-18f9-4ef9-ac8c-5d5f25f11170","job_id":"J03-1833","name":"Dismantle: Part list &amp; Tear Down","order":7,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"c536fdc6-3459-4ab5-a588-3454f07f08c7","job_id":"J03-1833","name":"Assemble: Directional &amp; Idler gear","order":8,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"89d1ae15-daf2-4871-9bc0-5940279c96f6","job_id":"J03-1833","name":"Assemble: Planetary GP","order":9,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"1197b5dd-9928-4565-ae50-91f382e2beb0","job_id":"J03-1833","name":"Assemble: CV 2EA","order":10,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"6a936f7e-e97a-47f4-9e03-24e38ef315fc","job_id":"J03-1833","name":"Assemble: Pump, Lines, &amp; Screen","order":11,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"80894723-ea93-40ff-aa35-420c027d3f95","job_id":"J03-1833","name":"Test Bench &amp; Completed: Set up","order":12,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"acf6bd0c-0d96-40b6-8b9e-ee8c27ee1625","job_id":"J03-1833","name":"Test Bench &amp; Completed: Test","order":13,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"81692dde-b76a-433d-9b5d-3476cf3cd7f6","job_id":"J03-1833","name":"Test Bench &amp; Completed: Release","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"b69b87c3-9d4b-450e-8c0e-162eb755ff75","job_id":"J03-1833","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300}],"assignees":[{"id":"a58e3fbd-80eb-4c64-bd6b-bb7196830ed8","job_id":"J03-1833","technician_id":"T-c23ed9a4","assigned_at":"2026-08-11T05:31:58.767Z","is_lead":"1"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-c23ed9a4","status":"busy","current_job_id":"J03-1833"}]}</t>
-  </si>
-  <si>
-    <t>5a906024-6eb8-4be4-a138-d16162fd4f10</t>
-  </si>
-  <si>
-    <t>2026-08-12T14:16:16.676Z</t>
-  </si>
-  <si>
-    <t>{"job":{"id":"J03-1833","title":"Recondition Transmission 16H,G","unit":"E448 — D10T","unit_id":"a5c2144b-1b29-40f7-9b5c-cfbbc03c3387","description":"Job recondition Transmission 16H,G (time frame standar).","status":"paused","technician_id":"T-c23ed9a4","template_id":"ne-transmission-16h-g","created_at":"2026-08-11T05:30:21.056Z","started_at":"2026-08-11T05:32:14.074Z","completed_at":"","paused_at":"2026-08-12T14:16:16.648Z","total_paused_sec":0,"estimated_minutes":5340},"steps":[{"id":"e21019ab-05cb-4d4f-8f8f-fb85fa9004da","job_id":"J03-1833","name":"Dismantle: Washing Transmission gp","order":1,"status":"done","started_at":"2026-08-11T05:32:14.074Z","completed_at":"2026-08-12T14:15:23.702Z","duration_sec":117789,"std_minutes":240},{"id":"5ceecb87-2473-4297-a2a0-db873217f383","job_id":"J03-1833","name":"Dismantle: Control Valve 2EA","order":2,"status":"done","started_at":"2026-08-11T05:32:33.253Z","completed_at":"2026-08-12T14:15:27.902Z","duration_sec":117774,"std_minutes":300},{"id":"11997f0b-4cc8-4b54-8bdd-db3614b948c1","job_id":"J03-1833","name":"Dismantle: Pump, Lines, &amp; Screen","order":3,"status":"done","started_at":"2026-08-11T05:32:33.253Z","completed_at":"2026-08-12T14:15:30.280Z","duration_sec":117777,"std_minutes":240},{"id":"6c426149-ef7a-48c2-9585-5909fe86eca9","job_id":"J03-1833","name":"Dismantle: Planetary GP","order":4,"status":"in_progress","started_at":"","completed_at":"","duration_sec":46,"std_minutes":900},{"id":"5d3baced-8d6d-491b-9df4-09eaef47f6b9","job_id":"J03-1833","name":"Dismantle: Directional &amp; Idler gear","order":5,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"0feaac14-da1a-4360-98f3-a99ad7b2fd45","job_id":"J03-1833","name":"Dismantle: Clean up Housing 2ea","order":6,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":120},{"id":"5b00b8bb-18f9-4ef9-ac8c-5d5f25f11170","job_id":"J03-1833","name":"Dismantle: Part list &amp; Tear Down","order":7,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"c536fdc6-3459-4ab5-a588-3454f07f08c7","job_id":"J03-1833","name":"Assemble: Directional &amp; Idler gear","order":8,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"89d1ae15-daf2-4871-9bc0-5940279c96f6","job_id":"J03-1833","name":"Assemble: Planetary GP","order":9,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"1197b5dd-9928-4565-ae50-91f382e2beb0","job_id":"J03-1833","name":"Assemble: CV 2EA","order":10,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"6a936f7e-e97a-47f4-9e03-24e38ef315fc","job_id":"J03-1833","name":"Assemble: Pump, Lines, &amp; Screen","order":11,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"80894723-ea93-40ff-aa35-420c027d3f95","job_id":"J03-1833","name":"Test Bench &amp; Completed: Set up","order":12,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"acf6bd0c-0d96-40b6-8b9e-ee8c27ee1625","job_id":"J03-1833","name":"Test Bench &amp; Completed: Test","order":13,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"81692dde-b76a-433d-9b5d-3476cf3cd7f6","job_id":"J03-1833","name":"Test Bench &amp; Completed: Release","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"b69b87c3-9d4b-450e-8c0e-162eb755ff75","job_id":"J03-1833","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300}],"assignees":[{"id":"a58e3fbd-80eb-4c64-bd6b-bb7196830ed8","job_id":"J03-1833","technician_id":"T-c23ed9a4","assigned_at":"2026-08-11T05:31:58.767Z","is_lead":"1"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-c23ed9a4","status":"busy","current_job_id":"J03-1833"}]}</t>
-  </si>
-  <si>
-    <t>392a79d1-e38a-4185-aead-f240b414dfc9</t>
-  </si>
-  <si>
-    <t>2026-08-12T14:16:20.429Z</t>
-  </si>
-  <si>
-    <t>{"job":{"id":"J03-1833","title":"Recondition Transmission 16H,G","unit":"E448 — D10T","unit_id":"a5c2144b-1b29-40f7-9b5c-cfbbc03c3387","description":"Job recondition Transmission 16H,G (time frame standar).","status":"in_progress","technician_id":"T-c23ed9a4","template_id":"ne-transmission-16h-g","created_at":"2026-08-11T05:30:21.056Z","started_at":"2026-08-11T05:32:14.074Z","completed_at":"","paused_at":"","total_paused_sec":3,"estimated_minutes":5340},"steps":[{"id":"e21019ab-05cb-4d4f-8f8f-fb85fa9004da","job_id":"J03-1833","name":"Dismantle: Washing Transmission gp","order":1,"status":"done","started_at":"2026-08-11T05:32:14.074Z","completed_at":"2026-08-12T14:15:23.702Z","duration_sec":117789,"std_minutes":240},{"id":"5ceecb87-2473-4297-a2a0-db873217f383","job_id":"J03-1833","name":"Dismantle: Control Valve 2EA","order":2,"status":"done","started_at":"2026-08-11T05:32:33.253Z","completed_at":"2026-08-12T14:15:27.902Z","duration_sec":117774,"std_minutes":300},{"id":"11997f0b-4cc8-4b54-8bdd-db3614b948c1","job_id":"J03-1833","name":"Dismantle: Pump, Lines, &amp; Screen","order":3,"status":"done","started_at":"2026-08-11T05:32:33.253Z","completed_at":"2026-08-12T14:15:30.280Z","duration_sec":117777,"std_minutes":240},{"id":"6c426149-ef7a-48c2-9585-5909fe86eca9","job_id":"J03-1833","name":"Dismantle: Planetary GP","order":4,"status":"in_progress","started_at":"2026-08-12T14:16:20.400Z","completed_at":"","duration_sec":46,"std_minutes":900},{"id":"5d3baced-8d6d-491b-9df4-09eaef47f6b9","job_id":"J03-1833","name":"Dismantle: Directional &amp; Idler gear","order":5,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"0feaac14-da1a-4360-98f3-a99ad7b2fd45","job_id":"J03-1833","name":"Dismantle: Clean up Housing 2ea","order":6,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":120},{"id":"5b00b8bb-18f9-4ef9-ac8c-5d5f25f11170","job_id":"J03-1833","name":"Dismantle: Part list &amp; Tear Down","order":7,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"c536fdc6-3459-4ab5-a588-3454f07f08c7","job_id":"J03-1833","name":"Assemble: Directional &amp; Idler gear","order":8,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"89d1ae15-daf2-4871-9bc0-5940279c96f6","job_id":"J03-1833","name":"Assemble: Planetary GP","order":9,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"1197b5dd-9928-4565-ae50-91f382e2beb0","job_id":"J03-1833","name":"Assemble: CV 2EA","order":10,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"6a936f7e-e97a-47f4-9e03-24e38ef315fc","job_id":"J03-1833","name":"Assemble: Pump, Lines, &amp; Screen","order":11,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"80894723-ea93-40ff-aa35-420c027d3f95","job_id":"J03-1833","name":"Test Bench &amp; Completed: Set up","order":12,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"acf6bd0c-0d96-40b6-8b9e-ee8c27ee1625","job_id":"J03-1833","name":"Test Bench &amp; Completed: Test","order":13,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"81692dde-b76a-433d-9b5d-3476cf3cd7f6","job_id":"J03-1833","name":"Test Bench &amp; Completed: Release","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"b69b87c3-9d4b-450e-8c0e-162eb755ff75","job_id":"J03-1833","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300}],"assignees":[{"id":"a58e3fbd-80eb-4c64-bd6b-bb7196830ed8","job_id":"J03-1833","technician_id":"T-c23ed9a4","assigned_at":"2026-08-11T05:31:58.767Z","is_lead":"1"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-c23ed9a4","status":"busy","current_job_id":"J03-1833"}]}</t>
-  </si>
-  <si>
-    <t>34c150b1-6bd8-4596-901e-e48a6334a2ca</t>
-  </si>
-  <si>
-    <t>2026-08-12T14:16:30.215Z</t>
-  </si>
-  <si>
-    <t>{"job":{"id":"J03-1833","title":"Recondition Transmission 16H,G","unit":"E448 — D10T","unit_id":"a5c2144b-1b29-40f7-9b5c-cfbbc03c3387","description":"Job recondition Transmission 16H,G (time frame standar).","status":"in_progress","technician_id":"T-c23ed9a4","template_id":"ne-transmission-16h-g","created_at":"2026-08-11T05:30:21.056Z","started_at":"2026-08-11T05:32:14.074Z","completed_at":"","paused_at":"","total_paused_sec":3,"estimated_minutes":5340},"steps":[{"id":"e21019ab-05cb-4d4f-8f8f-fb85fa9004da","job_id":"J03-1833","name":"Dismantle: Washing Transmission gp","order":1,"status":"done","started_at":"2026-08-11T05:32:14.074Z","completed_at":"2026-08-12T14:15:23.702Z","duration_sec":117789,"std_minutes":240},{"id":"5ceecb87-2473-4297-a2a0-db873217f383","job_id":"J03-1833","name":"Dismantle: Control Valve 2EA","order":2,"status":"done","started_at":"2026-08-11T05:32:33.253Z","completed_at":"2026-08-12T14:15:27.902Z","duration_sec":117774,"std_minutes":300},{"id":"11997f0b-4cc8-4b54-8bdd-db3614b948c1","job_id":"J03-1833","name":"Dismantle: Pump, Lines, &amp; Screen","order":3,"status":"done","started_at":"2026-08-11T05:32:33.253Z","completed_at":"2026-08-12T14:15:30.280Z","duration_sec":117777,"std_minutes":240},{"id":"6c426149-ef7a-48c2-9585-5909fe86eca9","job_id":"J03-1833","name":"Dismantle: Planetary GP","order":4,"status":"done","started_at":"2026-08-12T14:16:20.400Z","completed_at":"2026-08-12T14:16:30.166Z","duration_sec":55,"std_minutes":900},{"id":"5d3baced-8d6d-491b-9df4-09eaef47f6b9","job_id":"J03-1833","name":"Dismantle: Directional &amp; Idler gear","order":5,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"0feaac14-da1a-4360-98f3-a99ad7b2fd45","job_id":"J03-1833","name":"Dismantle: Clean up Housing 2ea","order":6,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":120},{"id":"5b00b8bb-18f9-4ef9-ac8c-5d5f25f11170","job_id":"J03-1833","name":"Dismantle: Part list &amp; Tear Down","order":7,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"c536fdc6-3459-4ab5-a588-3454f07f08c7","job_id":"J03-1833","name":"Assemble: Directional &amp; Idler gear","order":8,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"89d1ae15-daf2-4871-9bc0-5940279c96f6","job_id":"J03-1833","name":"Assemble: Planetary GP","order":9,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"1197b5dd-9928-4565-ae50-91f382e2beb0","job_id":"J03-1833","name":"Assemble: CV 2EA","order":10,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"6a936f7e-e97a-47f4-9e03-24e38ef315fc","job_id":"J03-1833","name":"Assemble: Pump, Lines, &amp; Screen","order":11,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"80894723-ea93-40ff-aa35-420c027d3f95","job_id":"J03-1833","name":"Test Bench &amp; Completed: Set up","order":12,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"acf6bd0c-0d96-40b6-8b9e-ee8c27ee1625","job_id":"J03-1833","name":"Test Bench &amp; Completed: Test","order":13,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"81692dde-b76a-433d-9b5d-3476cf3cd7f6","job_id":"J03-1833","name":"Test Bench &amp; Completed: Release","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"b69b87c3-9d4b-450e-8c0e-162eb755ff75","job_id":"J03-1833","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300}],"assignees":[{"id":"a58e3fbd-80eb-4c64-bd6b-bb7196830ed8","job_id":"J03-1833","technician_id":"T-c23ed9a4","assigned_at":"2026-08-11T05:31:58.767Z","is_lead":"1"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-c23ed9a4","status":"busy","current_job_id":"J03-1833"}]}</t>
-  </si>
-  <si>
-    <t>8f28bbc1-f811-49f9-9bcc-1be8042bfb47</t>
-  </si>
-  <si>
-    <t>2026-08-12T14:24:49.848Z</t>
-  </si>
-  <si>
-    <t>{"job":{"id":"J03-c0e2","title":"Recondition Transmission D10T,R","unit":"E448 — D10T","unit_id":"a5c2144b-1b29-40f7-9b5c-cfbbc03c3387","description":"Job recondition Transmission D10T,R (time frame standar).","status":"in_progress","technician_id":"T-533ca22c","template_id":"ne-transmission-d10t-r","created_at":"2026-08-10T08:22:13.799Z","started_at":"2026-08-10T08:23:20.053Z","completed_at":"","paused_at":"","total_paused_sec":3,"estimated_minutes":5820},"steps":[{"id":"7609ebf3-f1eb-4d9d-9591-f21d853034e1","job_id":"J03-c0e2","name":"Dismantle: Washing Transmission","order":1,"status":"done","started_at":"2026-08-10T08:23:20.053Z","completed_at":"2026-08-10T08:24:03.692Z","duration_sec":43,"std_minutes":60},{"id":"a3923555-21a4-4b60-9959-c48d814bf136","job_id":"J03-c0e2","name":"Dismantle: Trans Gear","order":2,"status":"done","started_at":"2026-08-10T08:23:32.872Z","completed_at":"2026-08-10T08:24:06.672Z","duration_sec":33,"std_minutes":600},{"id":"39c70957-da00-4dc8-a988-36ee41ef9841","job_id":"J03-c0e2","name":"Dismantle: CV, Harness, &amp; Sensor","order":3,"status":"done","started_at":"2026-08-10T08:24:08.700Z","completed_at":"2026-08-10T08:24:14.772Z","duration_sec":6,"std_minutes":300},{"id":"6feb4f63-8277-4c8a-a4cf-8d8a3d660682","job_id":"J03-c0e2","name":"Dismantle: Clutch 5","order":4,"status":"done","started_at":"2026-08-10T08:23:32.872Z","completed_at":"2026-08-10T08:24:08.700Z","duration_sec":35,"std_minutes":180},{"id":"179574f5-b3d7-43e4-a065-977ebd015bfc","job_id":"J03-c0e2","name":"Dismantle: Clutch 4","order":5,"status":"done","started_at":"2026-08-10T08:24:14.772Z","completed_at":"2026-08-10T10:10:28.558Z","duration_sec":6373,"std_minutes":180},{"id":"8aff0e07-0f40-4945-a9dc-7a8867ffccf4","job_id":"J03-c0e2","name":"Dismantle: Clutch 3","order":6,"status":"done","started_at":"2026-08-11T05:33:18.994Z","completed_at":"2026-08-11T05:33:34.800Z","duration_sec":69782,"std_minutes":180},{"id":"82415ef2-23b1-4eb2-b027-a268df0f4189","job_id":"J03-c0e2","name":"Dismantle: Clutch 2","order":7,"status":"done","started_at":"2026-08-11T05:33:34.800Z","completed_at":"2026-08-11T05:33:47.115Z","duration_sec":12,"std_minutes":180},{"id":"f7c8bcdc-e2d1-4856-aea1-f577d25b0550","job_id":"J03-c0e2","name":"Dismantle: Clutch 1","order":8,"status":"done","started_at":"2026-08-11T05:33:47.115Z","completed_at":"2026-08-12T14:24:49.765Z","duration_sec":118262,"std_minutes":180},{"id":"4391d523-f1d0-4922-95fb-d3827a21b813","job_id":"J03-c0e2","name":"Dismantle: Planetary &amp; Shaft","order":9,"status":"in_progress","started_at":"2026-08-12T14:24:49.766Z","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"bdcc79ae-9f46-46e2-963d-fd2ba3d40a2e","job_id":"J03-c0e2","name":"Dismantle: Part list &amp; Tear Down","order":10,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"0670c5ee-3df9-46ba-a7e5-790a2591233a","job_id":"J03-c0e2","name":"Assemble: Planetary &amp; Shaft In-Out","order":11,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"7276104d-e8c7-4ea6-aac7-6cd975141c45","job_id":"J03-c0e2","name":"Assemble: Clutch 1","order":12,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"1781ebaa-7fb0-4896-b642-71d33b8c4878","job_id":"J03-c0e2","name":"Assemble: Clutch 2","order":13,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"5532b99d-a7fd-4b7d-a752-796f7bc5daff","job_id":"J03-c0e2","name":"Assemble: Clutch 3","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"ff0ed73f-27d1-4b0a-a4f2-7818d3cfbc7e","job_id":"J03-c0e2","name":"Assemble: Clutch 4","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"970a35a3-a96b-48b4-9f04-a2b921b013f0","job_id":"J03-c0e2","name":"Assemble: Clutch 5","order":16,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"698b11d9-e1a3-451f-8a47-ccabcc5718c6","job_id":"J03-c0e2","name":"Assemble: CV, Harness &amp; Sensor","order":17,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"0620fee8-23da-434a-85e6-6354dee830d7","job_id":"J03-c0e2","name":"Assemble: Trans Gear","order":18,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":900},{"id":"ca31c8c2-4542-42f7-be4e-86974a63447b","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Set up","order":19,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"ba2d158c-a9f5-4d98-aea1-fd1f7983c4eb","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Test","order":20,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"d2f96316-8f95-487c-a7ee-94ba19ef4354","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Release","order":21,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"050b2cfc-5ea2-4926-b9c1-c7bdfe6bbd49","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":22,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240}],"assignees":[{"id":"5ece1c51-c36b-46e5-a9d2-f9106a729470","job_id":"J03-c0e2","technician_id":"T-533ca22c","assigned_at":"2026-08-10T08:23:08.120Z","is_lead":"1"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-533ca22c","status":"busy","current_job_id":"J03-c0e2"}]}</t>
-  </si>
-  <si>
-    <t>cfbe10ea-7adc-4f92-8326-483852d10eef</t>
-  </si>
-  <si>
-    <t>2026-08-12T14:25:18.211Z</t>
-  </si>
-  <si>
-    <t>{"job":{"id":"J02-dc56","title":"Recondition Transmission 16H,G","unit":"E448 — D10T","unit_id":"a5c2144b-1b29-40f7-9b5c-cfbbc03c3387","description":"Job recondition Transmission 16H,G (time frame standar).","status":"in_progress","technician_id":"T-37cadb58","template_id":"ne-transmission-16h-g","created_at":"2026-08-09T14:29:20.672Z","started_at":"2026-08-09T15:02:48.075Z","completed_at":"","paused_at":"","total_paused_sec":89,"estimated_minutes":5340},"steps":[{"id":"91804ed8-5ad4-4ffd-aaad-beba64eb9cb2","job_id":"J02-dc56","name":"Dismantle: Washing Transmission gp","order":1,"status":"done","started_at":"2026-08-09T15:02:48.075Z","completed_at":"2026-08-09T15:20:47.571Z","duration_sec":1079,"std_minutes":240},{"id":"a127f857-f092-4b21-b197-3e3c8a02d549","job_id":"J02-dc56","name":"Dismantle: Control Valve 2EA","order":2,"status":"done","started_at":"2026-08-10T01:30:25.210Z","completed_at":"2026-08-10T01:30:32.748Z","duration_sec":36495,"std_minutes":300},{"id":"3bc8becf-2b5e-4391-8c9f-619d63d7281c","job_id":"J02-dc56","name":"Dismantle: Pump, Lines, &amp; Screen","order":3,"status":"done","started_at":"2026-08-10T01:30:32.748Z","completed_at":"2026-08-10T08:27:37.616Z","duration_sec":25024,"std_minutes":240},{"id":"bacf6ce8-8a97-4831-9f38-3010f4d64a9a","job_id":"J02-dc56","name":"Dismantle: Planetary GP","order":4,"status":"done","started_at":"2026-08-10T08:27:37.616Z","completed_at":"2026-08-11T05:36:57.526Z","duration_sec":76159,"std_minutes":900},{"id":"74bc5c28-b84c-4cfa-b429-25198c968f30","job_id":"J02-dc56","name":"Dismantle: Directional &amp; Idler gear","order":5,"status":"done","started_at":"2026-08-11T05:36:57.526Z","completed_at":"2026-08-11T14:50:26.762Z","duration_sec":33209,"std_minutes":300},{"id":"c3ce574f-16e3-4ce2-815e-10a842f608de","job_id":"J02-dc56","name":"Dismantle: Clean up Housing 2ea","order":6,"status":"done","started_at":"2026-08-11T14:50:26.763Z","completed_at":"2026-08-12T14:25:17.931Z","duration_sec":84891,"std_minutes":120},{"id":"b57a5afd-0b62-47a8-a149-df57cdbec92f","job_id":"J02-dc56","name":"Dismantle: Part list &amp; Tear Down","order":7,"status":"in_progress","started_at":"2026-08-12T14:25:17.931Z","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"ef67991d-4f1b-4929-b4b9-3bd70d1c1a8b","job_id":"J02-dc56","name":"Assemble: Directional &amp; Idler gear","order":8,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"19689610-ed31-4c36-959c-6233ef31d9cc","job_id":"J02-dc56","name":"Assemble: Planetary GP","order":9,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"572f712a-0376-495f-a98f-9ee71ead12b3","job_id":"J02-dc56","name":"Assemble: CV 2EA","order":10,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"033a6b1b-8daf-46cc-a1e1-292ad2451d5f","job_id":"J02-dc56","name":"Assemble: Pump, Lines, &amp; Screen","order":11,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"f52cc000-4714-474d-a6c4-a3f41408fbb7","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Set up","order":12,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"a9b889d6-b2f7-4421-a27a-fcd6a2fde9f9","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Test","order":13,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"3edd89d2-41a4-4856-976b-cbc716dc3788","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Release","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"4d87b720-179e-4dbd-bf95-3d44c356f29e","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300}],"assignees":[{"id":"e39218a1-186b-46ca-b35a-d999eac3307c","job_id":"J02-dc56","technician_id":"T-37cadb58","assigned_at":"2026-08-11T14:56:11.247Z","is_lead":"1"},{"id":"56cff857-6f11-4d4f-889c-272de87907ef","job_id":"J02-dc56","technician_id":"T-e4a06545","assigned_at":"2026-08-11T14:56:11.247Z","is_lead":"0"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-37cadb58","status":"busy","current_job_id":"J02-dc56"},{"id":"T-e4a06545","status":"busy","current_job_id":"J02-dc56"}]}</t>
-  </si>
-  <si>
-    <t>e40b2a80-772a-4b22-be21-7a670a14a7a6</t>
-  </si>
-  <si>
-    <t>2026-08-12T14:28:07.888Z</t>
-  </si>
-  <si>
-    <t>{"job":{"id":"J03-1833","title":"Recondition Transmission 16H,G","unit":"E448 — D10T","unit_id":"a5c2144b-1b29-40f7-9b5c-cfbbc03c3387","description":"Job recondition Transmission 16H,G (time frame standar).","status":"in_progress","technician_id":"T-c23ed9a4","template_id":"ne-transmission-16h-g","created_at":"2026-08-11T05:30:21.056Z","started_at":"2026-08-11T05:32:14.074Z","completed_at":"","paused_at":"","total_paused_sec":3,"estimated_minutes":5340},"steps":[{"id":"e21019ab-05cb-4d4f-8f8f-fb85fa9004da","job_id":"J03-1833","name":"Dismantle: Washing Transmission gp","order":1,"status":"done","started_at":"2026-08-11T05:32:14.074Z","completed_at":"2026-08-12T14:15:23.702Z","duration_sec":117789,"std_minutes":240},{"id":"5ceecb87-2473-4297-a2a0-db873217f383","job_id":"J03-1833","name":"Dismantle: Control Valve 2EA","order":2,"status":"done","started_at":"2026-08-11T05:32:33.253Z","completed_at":"2026-08-12T14:15:27.902Z","duration_sec":117774,"std_minutes":300},{"id":"11997f0b-4cc8-4b54-8bdd-db3614b948c1","job_id":"J03-1833","name":"Dismantle: Pump, Lines, &amp; Screen","order":3,"status":"done","started_at":"2026-08-11T05:32:33.253Z","completed_at":"2026-08-12T14:15:30.280Z","duration_sec":117777,"std_minutes":240},{"id":"6c426149-ef7a-48c2-9585-5909fe86eca9","job_id":"J03-1833","name":"Dismantle: Planetary GP","order":4,"status":"done","started_at":"2026-08-12T14:16:20.400Z","completed_at":"2026-08-12T14:16:30.166Z","duration_sec":55,"std_minutes":900},{"id":"5d3baced-8d6d-491b-9df4-09eaef47f6b9","job_id":"J03-1833","name":"Dismantle: Directional &amp; Idler gear","order":5,"status":"in_progress","started_at":"2026-08-12T14:28:07.854Z","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"0feaac14-da1a-4360-98f3-a99ad7b2fd45","job_id":"J03-1833","name":"Dismantle: Clean up Housing 2ea","order":6,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":120},{"id":"5b00b8bb-18f9-4ef9-ac8c-5d5f25f11170","job_id":"J03-1833","name":"Dismantle: Part list &amp; Tear Down","order":7,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"c536fdc6-3459-4ab5-a588-3454f07f08c7","job_id":"J03-1833","name":"Assemble: Directional &amp; Idler gear","order":8,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"89d1ae15-daf2-4871-9bc0-5940279c96f6","job_id":"J03-1833","name":"Assemble: Planetary GP","order":9,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"1197b5dd-9928-4565-ae50-91f382e2beb0","job_id":"J03-1833","name":"Assemble: CV 2EA","order":10,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"6a936f7e-e97a-47f4-9e03-24e38ef315fc","job_id":"J03-1833","name":"Assemble: Pump, Lines, &amp; Screen","order":11,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"80894723-ea93-40ff-aa35-420c027d3f95","job_id":"J03-1833","name":"Test Bench &amp; Completed: Set up","order":12,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"acf6bd0c-0d96-40b6-8b9e-ee8c27ee1625","job_id":"J03-1833","name":"Test Bench &amp; Completed: Test","order":13,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"81692dde-b76a-433d-9b5d-3476cf3cd7f6","job_id":"J03-1833","name":"Test Bench &amp; Completed: Release","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"b69b87c3-9d4b-450e-8c0e-162eb755ff75","job_id":"J03-1833","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300}],"assignees":[{"id":"a58e3fbd-80eb-4c64-bd6b-bb7196830ed8","job_id":"J03-1833","technician_id":"T-c23ed9a4","assigned_at":"2026-08-11T05:31:58.767Z","is_lead":"1"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-c23ed9a4","status":"busy","current_job_id":"J03-1833"}]}</t>
-  </si>
-  <si>
-    <t>34a68c29-3c19-4495-a4fa-e07282e99275</t>
-  </si>
-  <si>
-    <t>2026-08-12T14:28:34.178Z</t>
-  </si>
-  <si>
-    <t>{"job":{"id":"J03-c0e2","title":"Recondition Transmission D10T,R","unit":"E448 — D10T","unit_id":"a5c2144b-1b29-40f7-9b5c-cfbbc03c3387","description":"Job recondition Transmission D10T,R (time frame standar).","status":"in_progress","technician_id":"T-533ca22c","template_id":"ne-transmission-d10t-r","created_at":"2026-08-10T08:22:13.799Z","started_at":"2026-08-10T08:23:20.053Z","completed_at":"","paused_at":"","total_paused_sec":3,"estimated_minutes":5820},"steps":[{"id":"7609ebf3-f1eb-4d9d-9591-f21d853034e1","job_id":"J03-c0e2","name":"Dismantle: Washing Transmission","order":1,"status":"done","started_at":"2026-08-10T08:23:20.053Z","completed_at":"2026-08-10T08:24:03.692Z","duration_sec":43,"std_minutes":60},{"id":"a3923555-21a4-4b60-9959-c48d814bf136","job_id":"J03-c0e2","name":"Dismantle: Trans Gear","order":2,"status":"done","started_at":"2026-08-10T08:23:32.872Z","completed_at":"2026-08-10T08:24:06.672Z","duration_sec":33,"std_minutes":600},{"id":"39c70957-da00-4dc8-a988-36ee41ef9841","job_id":"J03-c0e2","name":"Dismantle: CV, Harness, &amp; Sensor","order":3,"status":"done","started_at":"2026-08-10T08:24:08.700Z","completed_at":"2026-08-10T08:24:14.772Z","duration_sec":6,"std_minutes":300},{"id":"6feb4f63-8277-4c8a-a4cf-8d8a3d660682","job_id":"J03-c0e2","name":"Dismantle: Clutch 5","order":4,"status":"done","started_at":"2026-08-10T08:23:32.872Z","completed_at":"2026-08-10T08:24:08.700Z","duration_sec":35,"std_minutes":180},{"id":"179574f5-b3d7-43e4-a065-977ebd015bfc","job_id":"J03-c0e2","name":"Dismantle: Clutch 4","order":5,"status":"done","started_at":"2026-08-10T08:24:14.772Z","completed_at":"2026-08-10T10:10:28.558Z","duration_sec":6373,"std_minutes":180},{"id":"8aff0e07-0f40-4945-a9dc-7a8867ffccf4","job_id":"J03-c0e2","name":"Dismantle: Clutch 3","order":6,"status":"done","started_at":"2026-08-11T05:33:18.994Z","completed_at":"2026-08-11T05:33:34.800Z","duration_sec":69782,"std_minutes":180},{"id":"82415ef2-23b1-4eb2-b027-a268df0f4189","job_id":"J03-c0e2","name":"Dismantle: Clutch 2","order":7,"status":"done","started_at":"2026-08-11T05:33:34.800Z","completed_at":"2026-08-11T05:33:47.115Z","duration_sec":12,"std_minutes":180},{"id":"f7c8bcdc-e2d1-4856-aea1-f577d25b0550","job_id":"J03-c0e2","name":"Dismantle: Clutch 1","order":8,"status":"done","started_at":"2026-08-11T05:33:47.115Z","completed_at":"2026-08-12T14:24:49.765Z","duration_sec":118262,"std_minutes":180},{"id":"4391d523-f1d0-4922-95fb-d3827a21b813","job_id":"J03-c0e2","name":"Dismantle: Planetary &amp; Shaft","order":9,"status":"done","started_at":"2026-08-12T14:24:49.766Z","completed_at":"2026-08-12T14:28:34.119Z","duration_sec":224,"std_minutes":300},{"id":"bdcc79ae-9f46-46e2-963d-fd2ba3d40a2e","job_id":"J03-c0e2","name":"Dismantle: Part list &amp; Tear Down","order":10,"status":"in_progress","started_at":"2026-08-12T14:28:34.120Z","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"0670c5ee-3df9-46ba-a7e5-790a2591233a","job_id":"J03-c0e2","name":"Assemble: Planetary &amp; Shaft In-Out","order":11,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"7276104d-e8c7-4ea6-aac7-6cd975141c45","job_id":"J03-c0e2","name":"Assemble: Clutch 1","order":12,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"1781ebaa-7fb0-4896-b642-71d33b8c4878","job_id":"J03-c0e2","name":"Assemble: Clutch 2","order":13,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"5532b99d-a7fd-4b7d-a752-796f7bc5daff","job_id":"J03-c0e2","name":"Assemble: Clutch 3","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"ff0ed73f-27d1-4b0a-a4f2-7818d3cfbc7e","job_id":"J03-c0e2","name":"Assemble: Clutch 4","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"970a35a3-a96b-48b4-9f04-a2b921b013f0","job_id":"J03-c0e2","name":"Assemble: Clutch 5","order":16,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"698b11d9-e1a3-451f-8a47-ccabcc5718c6","job_id":"J03-c0e2","name":"Assemble: CV, Harness &amp; Sensor","order":17,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"0620fee8-23da-434a-85e6-6354dee830d7","job_id":"J03-c0e2","name":"Assemble: Trans Gear","order":18,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":900},{"id":"ca31c8c2-4542-42f7-be4e-86974a63447b","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Set up","order":19,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"ba2d158c-a9f5-4d98-aea1-fd1f7983c4eb","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Test","order":20,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"d2f96316-8f95-487c-a7ee-94ba19ef4354","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Release","order":21,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"050b2cfc-5ea2-4926-b9c1-c7bdfe6bbd49","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":22,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240}],"assignees":[{"id":"5ece1c51-c36b-46e5-a9d2-f9106a729470","job_id":"J03-c0e2","technician_id":"T-533ca22c","assigned_at":"2026-08-10T08:23:08.120Z","is_lead":"1"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-533ca22c","status":"busy","current_job_id":"J03-c0e2"}]}</t>
-  </si>
-  <si>
-    <t>029ce3ee-a424-401b-a179-4bf59e1f717b</t>
-  </si>
-  <si>
-    <t>2026-08-12T14:28:53.561Z</t>
-  </si>
-  <si>
-    <t>{"job":{"id":"J02-dc56","title":"Recondition Transmission 16H,G","unit":"E448 — D10T","unit_id":"a5c2144b-1b29-40f7-9b5c-cfbbc03c3387","description":"Job recondition Transmission 16H,G (time frame standar).","status":"paused","technician_id":"T-37cadb58","template_id":"ne-transmission-16h-g","created_at":"2026-08-09T14:29:20.672Z","started_at":"2026-08-09T15:02:48.075Z","completed_at":"","paused_at":"2026-08-12T14:28:53.512Z","total_paused_sec":89,"estimated_minutes":5340},"steps":[{"id":"91804ed8-5ad4-4ffd-aaad-beba64eb9cb2","job_id":"J02-dc56","name":"Dismantle: Washing Transmission gp","order":1,"status":"done","started_at":"2026-08-09T15:02:48.075Z","completed_at":"2026-08-09T15:20:47.571Z","duration_sec":1079,"std_minutes":240},{"id":"a127f857-f092-4b21-b197-3e3c8a02d549","job_id":"J02-dc56","name":"Dismantle: Control Valve 2EA","order":2,"status":"done","started_at":"2026-08-10T01:30:25.210Z","completed_at":"2026-08-10T01:30:32.748Z","duration_sec":36495,"std_minutes":300},{"id":"3bc8becf-2b5e-4391-8c9f-619d63d7281c","job_id":"J02-dc56","name":"Dismantle: Pump, Lines, &amp; Screen","order":3,"status":"done","started_at":"2026-08-10T01:30:32.748Z","completed_at":"2026-08-10T08:27:37.616Z","duration_sec":25024,"std_minutes":240},{"id":"bacf6ce8-8a97-4831-9f38-3010f4d64a9a","job_id":"J02-dc56","name":"Dismantle: Planetary GP","order":4,"status":"done","started_at":"2026-08-10T08:27:37.616Z","completed_at":"2026-08-11T05:36:57.526Z","duration_sec":76159,"std_minutes":900},{"id":"74bc5c28-b84c-4cfa-b429-25198c968f30","job_id":"J02-dc56","name":"Dismantle: Directional &amp; Idler gear","order":5,"status":"done","started_at":"2026-08-11T05:36:57.526Z","completed_at":"2026-08-11T14:50:26.762Z","duration_sec":33209,"std_minutes":300},{"id":"c3ce574f-16e3-4ce2-815e-10a842f608de","job_id":"J02-dc56","name":"Dismantle: Clean up Housing 2ea","order":6,"status":"done","started_at":"2026-08-11T14:50:26.763Z","completed_at":"2026-08-12T14:25:17.931Z","duration_sec":84891,"std_minutes":120},{"id":"b57a5afd-0b62-47a8-a149-df57cdbec92f","job_id":"J02-dc56","name":"Dismantle: Part list &amp; Tear Down","order":7,"status":"in_progress","started_at":"","completed_at":"","duration_sec":215,"std_minutes":240},{"id":"ef67991d-4f1b-4929-b4b9-3bd70d1c1a8b","job_id":"J02-dc56","name":"Assemble: Directional &amp; Idler gear","order":8,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"19689610-ed31-4c36-959c-6233ef31d9cc","job_id":"J02-dc56","name":"Assemble: Planetary GP","order":9,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"572f712a-0376-495f-a98f-9ee71ead12b3","job_id":"J02-dc56","name":"Assemble: CV 2EA","order":10,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"033a6b1b-8daf-46cc-a1e1-292ad2451d5f","job_id":"J02-dc56","name":"Assemble: Pump, Lines, &amp; Screen","order":11,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"f52cc000-4714-474d-a6c4-a3f41408fbb7","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Set up","order":12,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"a9b889d6-b2f7-4421-a27a-fcd6a2fde9f9","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Test","order":13,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"3edd89d2-41a4-4856-976b-cbc716dc3788","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Release","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"4d87b720-179e-4dbd-bf95-3d44c356f29e","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300}],"assignees":[{"id":"e39218a1-186b-46ca-b35a-d999eac3307c","job_id":"J02-dc56","technician_id":"T-37cadb58","assigned_at":"2026-08-11T14:56:11.247Z","is_lead":"1"},{"id":"56cff857-6f11-4d4f-889c-272de87907ef","job_id":"J02-dc56","technician_id":"T-e4a06545","assigned_at":"2026-08-11T14:56:11.247Z","is_lead":"0"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-37cadb58","status":"busy","current_job_id":"J02-dc56"},{"id":"T-e4a06545","status":"busy","current_job_id":"J02-dc56"}]}</t>
-  </si>
-  <si>
-    <t>e8d9c702-a95b-4a30-a427-3ac25f8ccf29</t>
-  </si>
-  <si>
-    <t>2026-08-12T14:28:56.726Z</t>
-  </si>
-  <si>
-    <t>{"job":{"id":"J02-dc56","title":"Recondition Transmission 16H,G","unit":"E448 — D10T","unit_id":"a5c2144b-1b29-40f7-9b5c-cfbbc03c3387","description":"Job recondition Transmission 16H,G (time frame standar).","status":"in_progress","technician_id":"T-37cadb58","template_id":"ne-transmission-16h-g","created_at":"2026-08-09T14:29:20.672Z","started_at":"2026-08-09T15:02:48.075Z","completed_at":"","paused_at":"","total_paused_sec":92,"estimated_minutes":5340},"steps":[{"id":"91804ed8-5ad4-4ffd-aaad-beba64eb9cb2","job_id":"J02-dc56","name":"Dismantle: Washing Transmission gp","order":1,"status":"done","started_at":"2026-08-09T15:02:48.075Z","completed_at":"2026-08-09T15:20:47.571Z","duration_sec":1079,"std_minutes":240},{"id":"a127f857-f092-4b21-b197-3e3c8a02d549","job_id":"J02-dc56","name":"Dismantle: Control Valve 2EA","order":2,"status":"done","started_at":"2026-08-10T01:30:25.210Z","completed_at":"2026-08-10T01:30:32.748Z","duration_sec":36495,"std_minutes":300},{"id":"3bc8becf-2b5e-4391-8c9f-619d63d7281c","job_id":"J02-dc56","name":"Dismantle: Pump, Lines, &amp; Screen","order":3,"status":"done","started_at":"2026-08-10T01:30:32.748Z","completed_at":"2026-08-10T08:27:37.616Z","duration_sec":25024,"std_minutes":240},{"id":"bacf6ce8-8a97-4831-9f38-3010f4d64a9a","job_id":"J02-dc56","name":"Dismantle: Planetary GP","order":4,"status":"done","started_at":"2026-08-10T08:27:37.616Z","completed_at":"2026-08-11T05:36:57.526Z","duration_sec":76159,"std_minutes":900},{"id":"74bc5c28-b84c-4cfa-b429-25198c968f30","job_id":"J02-dc56","name":"Dismantle: Directional &amp; Idler gear","order":5,"status":"done","started_at":"2026-08-11T05:36:57.526Z","completed_at":"2026-08-11T14:50:26.762Z","duration_sec":33209,"std_minutes":300},{"id":"c3ce574f-16e3-4ce2-815e-10a842f608de","job_id":"J02-dc56","name":"Dismantle: Clean up Housing 2ea","order":6,"status":"done","started_at":"2026-08-11T14:50:26.763Z","completed_at":"2026-08-12T14:25:17.931Z","duration_sec":84891,"std_minutes":120},{"id":"b57a5afd-0b62-47a8-a149-df57cdbec92f","job_id":"J02-dc56","name":"Dismantle: Part list &amp; Tear Down","order":7,"status":"in_progress","started_at":"2026-08-12T14:28:56.705Z","completed_at":"","duration_sec":215,"std_minutes":240},{"id":"ef67991d-4f1b-4929-b4b9-3bd70d1c1a8b","job_id":"J02-dc56","name":"Assemble: Directional &amp; Idler gear","order":8,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"19689610-ed31-4c36-959c-6233ef31d9cc","job_id":"J02-dc56","name":"Assemble: Planetary GP","order":9,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"572f712a-0376-495f-a98f-9ee71ead12b3","job_id":"J02-dc56","name":"Assemble: CV 2EA","order":10,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"033a6b1b-8daf-46cc-a1e1-292ad2451d5f","job_id":"J02-dc56","name":"Assemble: Pump, Lines, &amp; Screen","order":11,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"f52cc000-4714-474d-a6c4-a3f41408fbb7","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Set up","order":12,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"a9b889d6-b2f7-4421-a27a-fcd6a2fde9f9","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Test","order":13,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"3edd89d2-41a4-4856-976b-cbc716dc3788","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Release","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"4d87b720-179e-4dbd-bf95-3d44c356f29e","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300}],"assignees":[{"id":"e39218a1-186b-46ca-b35a-d999eac3307c","job_id":"J02-dc56","technician_id":"T-37cadb58","assigned_at":"2026-08-11T14:56:11.247Z","is_lead":"1"},{"id":"56cff857-6f11-4d4f-889c-272de87907ef","job_id":"J02-dc56","technician_id":"T-e4a06545","assigned_at":"2026-08-11T14:56:11.247Z","is_lead":"0"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-37cadb58","status":"busy","current_job_id":"J02-dc56"},{"id":"T-e4a06545","status":"busy","current_job_id":"J02-dc56"}]}</t>
+    <t>1c0ae08a-4944-424c-930a-e6540e1b4e9d</t>
+  </si>
+  <si>
+    <t>2026-08-11T15:28:01.344Z</t>
+  </si>
+  <si>
+    <t>{"job":{"id":"J02-dc56","title":"Recondition Transmission 16H,G","unit":"E448 — D10T","unit_id":"a5c2144b-1b29-40f7-9b5c-cfbbc03c3387","description":"Job recondition Transmission 16H,G (time frame standar).","status":"in_progress","technician_id":"T-37cadb58","template_id":"ne-transmission-16h-g","created_at":"2026-08-09T14:29:20.672Z","started_at":"2026-08-09T15:02:48.075Z","completed_at":"","paused_at":"","total_paused_sec":89,"estimated_minutes":5340},"steps":[{"id":"91804ed8-5ad4-4ffd-aaad-beba64eb9cb2","job_id":"J02-dc56","name":"Dismantle: Washing Transmission gp","order":1,"status":"done","started_at":"2026-08-09T15:02:48.075Z","completed_at":"2026-08-09T15:20:47.571Z","duration_sec":1079,"std_minutes":240},{"id":"a127f857-f092-4b21-b197-3e3c8a02d549","job_id":"J02-dc56","name":"Dismantle: Control Valve 2EA","order":2,"status":"done","started_at":"2026-08-10T01:30:25.210Z","completed_at":"2026-08-10T01:30:32.748Z","duration_sec":36495,"std_minutes":300},{"id":"3bc8becf-2b5e-4391-8c9f-619d63d7281c","job_id":"J02-dc56","name":"Dismantle: Pump, Lines, &amp; Screen","order":3,"status":"done","started_at":"2026-08-10T01:30:32.748Z","completed_at":"2026-08-10T08:27:37.616Z","duration_sec":25024,"std_minutes":240},{"id":"bacf6ce8-8a97-4831-9f38-3010f4d64a9a","job_id":"J02-dc56","name":"Dismantle: Planetary GP","order":4,"status":"done","started_at":"2026-08-10T08:27:37.616Z","completed_at":"2026-08-11T05:36:57.526Z","duration_sec":76159,"std_minutes":900},{"id":"74bc5c28-b84c-4cfa-b429-25198c968f30","job_id":"J02-dc56","name":"Dismantle: Directional &amp; Idler gear","order":5,"status":"done","started_at":"2026-08-11T05:36:57.526Z","completed_at":"2026-08-11T14:50:26.762Z","duration_sec":33209,"std_minutes":300},{"id":"c3ce574f-16e3-4ce2-815e-10a842f608de","job_id":"J02-dc56","name":"Dismantle: Clean up Housing 2ea","order":6,"status":"done","started_at":"2026-08-11T14:50:26.763Z","completed_at":"2026-08-11T15:28:01.298Z","duration_sec":2254,"std_minutes":120},{"id":"b57a5afd-0b62-47a8-a149-df57cdbec92f","job_id":"J02-dc56","name":"Dismantle: Part list &amp; Tear Down","order":7,"status":"in_progress","started_at":"2026-08-11T15:28:01.298Z","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"ef67991d-4f1b-4929-b4b9-3bd70d1c1a8b","job_id":"J02-dc56","name":"Assemble: Directional &amp; Idler gear","order":8,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"19689610-ed31-4c36-959c-6233ef31d9cc","job_id":"J02-dc56","name":"Assemble: Planetary GP","order":9,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"572f712a-0376-495f-a98f-9ee71ead12b3","job_id":"J02-dc56","name":"Assemble: CV 2EA","order":10,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"033a6b1b-8daf-46cc-a1e1-292ad2451d5f","job_id":"J02-dc56","name":"Assemble: Pump, Lines, &amp; Screen","order":11,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"f52cc000-4714-474d-a6c4-a3f41408fbb7","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Set up","order":12,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"a9b889d6-b2f7-4421-a27a-fcd6a2fde9f9","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Test","order":13,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"3edd89d2-41a4-4856-976b-cbc716dc3788","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Release","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"4d87b720-179e-4dbd-bf95-3d44c356f29e","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300}],"assignees":[{"id":"e39218a1-186b-46ca-b35a-d999eac3307c","job_id":"J02-dc56","technician_id":"T-37cadb58","assigned_at":"2026-08-11T14:56:11.247Z","is_lead":"1"},{"id":"56cff857-6f11-4d4f-889c-272de87907ef","job_id":"J02-dc56","technician_id":"T-e4a06545","assigned_at":"2026-08-11T14:56:11.247Z","is_lead":"0"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-37cadb58","status":"busy","current_job_id":"J02-dc56"},{"id":"T-e4a06545","status":"busy","current_job_id":"J02-dc56"}]}</t>
+  </si>
+  <si>
+    <t>2cab4c84-d9c7-4c5f-839b-2d53b02e759b</t>
+  </si>
+  <si>
+    <t>2026-08-11T15:28:10.913Z</t>
+  </si>
+  <si>
+    <t>{"job":{"id":"J03-c0e2","title":"Recondition Transmission D10T,R","unit":"E448 — D10T","unit_id":"a5c2144b-1b29-40f7-9b5c-cfbbc03c3387","description":"Job recondition Transmission D10T,R (time frame standar).","status":"in_progress","technician_id":"T-533ca22c","template_id":"ne-transmission-d10t-r","created_at":"2026-08-10T08:22:13.799Z","started_at":"2026-08-10T08:23:20.053Z","completed_at":"","paused_at":"","total_paused_sec":3,"estimated_minutes":5820},"steps":[{"id":"7609ebf3-f1eb-4d9d-9591-f21d853034e1","job_id":"J03-c0e2","name":"Dismantle: Washing Transmission","order":1,"status":"done","started_at":"2026-08-10T08:23:20.053Z","completed_at":"2026-08-10T08:24:03.692Z","duration_sec":43,"std_minutes":60},{"id":"a3923555-21a4-4b60-9959-c48d814bf136","job_id":"J03-c0e2","name":"Dismantle: Trans Gear","order":2,"status":"done","started_at":"2026-08-10T08:23:32.872Z","completed_at":"2026-08-10T08:24:06.672Z","duration_sec":33,"std_minutes":600},{"id":"39c70957-da00-4dc8-a988-36ee41ef9841","job_id":"J03-c0e2","name":"Dismantle: CV, Harness, &amp; Sensor","order":3,"status":"done","started_at":"2026-08-10T08:24:08.700Z","completed_at":"2026-08-10T08:24:14.772Z","duration_sec":6,"std_minutes":300},{"id":"6feb4f63-8277-4c8a-a4cf-8d8a3d660682","job_id":"J03-c0e2","name":"Dismantle: Clutch 5","order":4,"status":"done","started_at":"2026-08-10T08:23:32.872Z","completed_at":"2026-08-10T08:24:08.700Z","duration_sec":35,"std_minutes":180},{"id":"179574f5-b3d7-43e4-a065-977ebd015bfc","job_id":"J03-c0e2","name":"Dismantle: Clutch 4","order":5,"status":"done","started_at":"2026-08-10T08:24:14.772Z","completed_at":"2026-08-10T10:10:28.558Z","duration_sec":6373,"std_minutes":180},{"id":"8aff0e07-0f40-4945-a9dc-7a8867ffccf4","job_id":"J03-c0e2","name":"Dismantle: Clutch 3","order":6,"status":"done","started_at":"2026-08-11T05:33:18.994Z","completed_at":"2026-08-11T05:33:34.800Z","duration_sec":69782,"std_minutes":180},{"id":"82415ef2-23b1-4eb2-b027-a268df0f4189","job_id":"J03-c0e2","name":"Dismantle: Clutch 2","order":7,"status":"done","started_at":"2026-08-11T05:33:34.800Z","completed_at":"2026-08-11T05:33:47.115Z","duration_sec":12,"std_minutes":180},{"id":"f7c8bcdc-e2d1-4856-aea1-f577d25b0550","job_id":"J03-c0e2","name":"Dismantle: Clutch 1","order":8,"status":"done","started_at":"2026-08-11T05:33:47.115Z","completed_at":"2026-08-11T15:28:10.891Z","duration_sec":35663,"std_minutes":180},{"id":"4391d523-f1d0-4922-95fb-d3827a21b813","job_id":"J03-c0e2","name":"Dismantle: Planetary &amp; Shaft","order":9,"status":"in_progress","started_at":"2026-08-11T15:28:10.891Z","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"bdcc79ae-9f46-46e2-963d-fd2ba3d40a2e","job_id":"J03-c0e2","name":"Dismantle: Part list &amp; Tear Down","order":10,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"0670c5ee-3df9-46ba-a7e5-790a2591233a","job_id":"J03-c0e2","name":"Assemble: Planetary &amp; Shaft In-Out","order":11,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"7276104d-e8c7-4ea6-aac7-6cd975141c45","job_id":"J03-c0e2","name":"Assemble: Clutch 1","order":12,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"1781ebaa-7fb0-4896-b642-71d33b8c4878","job_id":"J03-c0e2","name":"Assemble: Clutch 2","order":13,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"5532b99d-a7fd-4b7d-a752-796f7bc5daff","job_id":"J03-c0e2","name":"Assemble: Clutch 3","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"ff0ed73f-27d1-4b0a-a4f2-7818d3cfbc7e","job_id":"J03-c0e2","name":"Assemble: Clutch 4","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"970a35a3-a96b-48b4-9f04-a2b921b013f0","job_id":"J03-c0e2","name":"Assemble: Clutch 5","order":16,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"698b11d9-e1a3-451f-8a47-ccabcc5718c6","job_id":"J03-c0e2","name":"Assemble: CV, Harness &amp; Sensor","order":17,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"0620fee8-23da-434a-85e6-6354dee830d7","job_id":"J03-c0e2","name":"Assemble: Trans Gear","order":18,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":900},{"id":"ca31c8c2-4542-42f7-be4e-86974a63447b","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Set up","order":19,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"ba2d158c-a9f5-4d98-aea1-fd1f7983c4eb","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Test","order":20,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"d2f96316-8f95-487c-a7ee-94ba19ef4354","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Release","order":21,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"050b2cfc-5ea2-4926-b9c1-c7bdfe6bbd49","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":22,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240}],"assignees":[{"id":"5ece1c51-c36b-46e5-a9d2-f9106a729470","job_id":"J03-c0e2","technician_id":"T-533ca22c","assigned_at":"2026-08-10T08:23:08.120Z","is_lead":"1"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-533ca22c","status":"busy","current_job_id":"J03-c0e2"}]}</t>
+  </si>
+  <si>
+    <t>6fa9cd04-f169-415b-aced-24370a121cf6</t>
+  </si>
+  <si>
+    <t>2026-08-11T23:52:32.637Z</t>
+  </si>
+  <si>
+    <t>{"job":{"id":"J03-1833","title":"Recondition Transmission 16H,G","unit":"E448 — D10T","unit_id":"a5c2144b-1b29-40f7-9b5c-cfbbc03c3387","description":"Job recondition Transmission 16H,G (time frame standar).","status":"in_progress","technician_id":"T-c23ed9a4","template_id":"ne-transmission-16h-g","created_at":"2026-08-11T05:30:21.056Z","started_at":"2026-08-11T05:32:14.074Z","completed_at":"","paused_at":"","total_paused_sec":0,"estimated_minutes":5340},"steps":[{"id":"e21019ab-05cb-4d4f-8f8f-fb85fa9004da","job_id":"J03-1833","name":"Dismantle: Washing Transmission gp","order":1,"status":"in_progress","started_at":"2026-08-11T05:32:14.074Z","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"5ceecb87-2473-4297-a2a0-db873217f383","job_id":"J03-1833","name":"Dismantle: Control Valve 2EA","order":2,"status":"done","started_at":"2026-08-11T05:32:33.253Z","completed_at":"2026-08-11T23:52:32.616Z","duration_sec":65999,"std_minutes":300},{"id":"11997f0b-4cc8-4b54-8bdd-db3614b948c1","job_id":"J03-1833","name":"Dismantle: Pump, Lines, &amp; Screen","order":3,"status":"in_progress","started_at":"2026-08-11T05:32:33.253Z","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"6c426149-ef7a-48c2-9585-5909fe86eca9","job_id":"J03-1833","name":"Dismantle: Planetary GP","order":4,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":900},{"id":"5d3baced-8d6d-491b-9df4-09eaef47f6b9","job_id":"J03-1833","name":"Dismantle: Directional &amp; Idler gear","order":5,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"0feaac14-da1a-4360-98f3-a99ad7b2fd45","job_id":"J03-1833","name":"Dismantle: Clean up Housing 2ea","order":6,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":120},{"id":"5b00b8bb-18f9-4ef9-ac8c-5d5f25f11170","job_id":"J03-1833","name":"Dismantle: Part list &amp; Tear Down","order":7,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"c536fdc6-3459-4ab5-a588-3454f07f08c7","job_id":"J03-1833","name":"Assemble: Directional &amp; Idler gear","order":8,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"89d1ae15-daf2-4871-9bc0-5940279c96f6","job_id":"J03-1833","name":"Assemble: Planetary GP","order":9,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"1197b5dd-9928-4565-ae50-91f382e2beb0","job_id":"J03-1833","name":"Assemble: CV 2EA","order":10,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"6a936f7e-e97a-47f4-9e03-24e38ef315fc","job_id":"J03-1833","name":"Assemble: Pump, Lines, &amp; Screen","order":11,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"80894723-ea93-40ff-aa35-420c027d3f95","job_id":"J03-1833","name":"Test Bench &amp; Completed: Set up","order":12,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"acf6bd0c-0d96-40b6-8b9e-ee8c27ee1625","job_id":"J03-1833","name":"Test Bench &amp; Completed: Test","order":13,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"81692dde-b76a-433d-9b5d-3476cf3cd7f6","job_id":"J03-1833","name":"Test Bench &amp; Completed: Release","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"b69b87c3-9d4b-450e-8c0e-162eb755ff75","job_id":"J03-1833","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300}],"assignees":[{"id":"a58e3fbd-80eb-4c64-bd6b-bb7196830ed8","job_id":"J03-1833","technician_id":"T-c23ed9a4","assigned_at":"2026-08-11T05:31:58.767Z","is_lead":"1"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-c23ed9a4","status":"busy","current_job_id":"J03-1833"}]}</t>
+  </si>
+  <si>
+    <t>1419bbc0-bf9c-49f9-ace6-ac52c5620a1e</t>
+  </si>
+  <si>
+    <t>2026-08-11T23:52:49.576Z</t>
+  </si>
+  <si>
+    <t>{"job":{"id":"J03-1833","title":"Recondition Transmission 16H,G","unit":"E448 — D10T","unit_id":"a5c2144b-1b29-40f7-9b5c-cfbbc03c3387","description":"Job recondition Transmission 16H,G (time frame standar).","status":"in_progress","technician_id":"T-c23ed9a4","template_id":"ne-transmission-16h-g","created_at":"2026-08-11T05:30:21.056Z","started_at":"2026-08-11T05:32:14.074Z","completed_at":"","paused_at":"","total_paused_sec":0,"estimated_minutes":5340},"steps":[{"id":"e21019ab-05cb-4d4f-8f8f-fb85fa9004da","job_id":"J03-1833","name":"Dismantle: Washing Transmission gp","order":1,"status":"done","started_at":"2026-08-11T05:32:14.074Z","completed_at":"2026-08-11T23:52:49.552Z","duration_sec":66035,"std_minutes":240},{"id":"5ceecb87-2473-4297-a2a0-db873217f383","job_id":"J03-1833","name":"Dismantle: Control Valve 2EA","order":2,"status":"done","started_at":"2026-08-11T05:32:33.253Z","completed_at":"2026-08-11T23:52:32.616Z","duration_sec":65999,"std_minutes":300},{"id":"11997f0b-4cc8-4b54-8bdd-db3614b948c1","job_id":"J03-1833","name":"Dismantle: Pump, Lines, &amp; Screen","order":3,"status":"in_progress","started_at":"2026-08-11T05:32:33.253Z","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"6c426149-ef7a-48c2-9585-5909fe86eca9","job_id":"J03-1833","name":"Dismantle: Planetary GP","order":4,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":900},{"id":"5d3baced-8d6d-491b-9df4-09eaef47f6b9","job_id":"J03-1833","name":"Dismantle: Directional &amp; Idler gear","order":5,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"0feaac14-da1a-4360-98f3-a99ad7b2fd45","job_id":"J03-1833","name":"Dismantle: Clean up Housing 2ea","order":6,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":120},{"id":"5b00b8bb-18f9-4ef9-ac8c-5d5f25f11170","job_id":"J03-1833","name":"Dismantle: Part list &amp; Tear Down","order":7,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"c536fdc6-3459-4ab5-a588-3454f07f08c7","job_id":"J03-1833","name":"Assemble: Directional &amp; Idler gear","order":8,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"89d1ae15-daf2-4871-9bc0-5940279c96f6","job_id":"J03-1833","name":"Assemble: Planetary GP","order":9,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"1197b5dd-9928-4565-ae50-91f382e2beb0","job_id":"J03-1833","name":"Assemble: CV 2EA","order":10,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"6a936f7e-e97a-47f4-9e03-24e38ef315fc","job_id":"J03-1833","name":"Assemble: Pump, Lines, &amp; Screen","order":11,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"80894723-ea93-40ff-aa35-420c027d3f95","job_id":"J03-1833","name":"Test Bench &amp; Completed: Set up","order":12,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"acf6bd0c-0d96-40b6-8b9e-ee8c27ee1625","job_id":"J03-1833","name":"Test Bench &amp; Completed: Test","order":13,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"81692dde-b76a-433d-9b5d-3476cf3cd7f6","job_id":"J03-1833","name":"Test Bench &amp; Completed: Release","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"b69b87c3-9d4b-450e-8c0e-162eb755ff75","job_id":"J03-1833","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300}],"assignees":[{"id":"a58e3fbd-80eb-4c64-bd6b-bb7196830ed8","job_id":"J03-1833","technician_id":"T-c23ed9a4","assigned_at":"2026-08-11T05:31:58.767Z","is_lead":"1"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-c23ed9a4","status":"busy","current_job_id":"J03-1833"}]}</t>
+  </si>
+  <si>
+    <t>7cd47ea4-bfb7-42bd-8d8e-908412787f65</t>
+  </si>
+  <si>
+    <t>2026-08-11T23:52:51.833Z</t>
+  </si>
+  <si>
+    <t>{"job":{"id":"J03-1833","title":"Recondition Transmission 16H,G","unit":"E448 — D10T","unit_id":"a5c2144b-1b29-40f7-9b5c-cfbbc03c3387","description":"Job recondition Transmission 16H,G (time frame standar).","status":"in_progress","technician_id":"T-c23ed9a4","template_id":"ne-transmission-16h-g","created_at":"2026-08-11T05:30:21.056Z","started_at":"2026-08-11T05:32:14.074Z","completed_at":"","paused_at":"","total_paused_sec":0,"estimated_minutes":5340},"steps":[{"id":"e21019ab-05cb-4d4f-8f8f-fb85fa9004da","job_id":"J03-1833","name":"Dismantle: Washing Transmission gp","order":1,"status":"done","started_at":"2026-08-11T05:32:14.074Z","completed_at":"2026-08-11T23:52:49.552Z","duration_sec":66035,"std_minutes":240},{"id":"5ceecb87-2473-4297-a2a0-db873217f383","job_id":"J03-1833","name":"Dismantle: Control Valve 2EA","order":2,"status":"done","started_at":"2026-08-11T05:32:33.253Z","completed_at":"2026-08-11T23:52:32.616Z","duration_sec":65999,"std_minutes":300},{"id":"11997f0b-4cc8-4b54-8bdd-db3614b948c1","job_id":"J03-1833","name":"Dismantle: Pump, Lines, &amp; Screen","order":3,"status":"done","started_at":"2026-08-11T05:32:33.253Z","completed_at":"2026-08-11T23:52:51.817Z","duration_sec":66018,"std_minutes":240},{"id":"6c426149-ef7a-48c2-9585-5909fe86eca9","job_id":"J03-1833","name":"Dismantle: Planetary GP","order":4,"status":"in_progress","started_at":"2026-08-11T23:52:51.817Z","completed_at":"","duration_sec":0,"std_minutes":900},{"id":"5d3baced-8d6d-491b-9df4-09eaef47f6b9","job_id":"J03-1833","name":"Dismantle: Directional &amp; Idler gear","order":5,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"0feaac14-da1a-4360-98f3-a99ad7b2fd45","job_id":"J03-1833","name":"Dismantle: Clean up Housing 2ea","order":6,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":120},{"id":"5b00b8bb-18f9-4ef9-ac8c-5d5f25f11170","job_id":"J03-1833","name":"Dismantle: Part list &amp; Tear Down","order":7,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"c536fdc6-3459-4ab5-a588-3454f07f08c7","job_id":"J03-1833","name":"Assemble: Directional &amp; Idler gear","order":8,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"89d1ae15-daf2-4871-9bc0-5940279c96f6","job_id":"J03-1833","name":"Assemble: Planetary GP","order":9,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"1197b5dd-9928-4565-ae50-91f382e2beb0","job_id":"J03-1833","name":"Assemble: CV 2EA","order":10,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"6a936f7e-e97a-47f4-9e03-24e38ef315fc","job_id":"J03-1833","name":"Assemble: Pump, Lines, &amp; Screen","order":11,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"80894723-ea93-40ff-aa35-420c027d3f95","job_id":"J03-1833","name":"Test Bench &amp; Completed: Set up","order":12,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"acf6bd0c-0d96-40b6-8b9e-ee8c27ee1625","job_id":"J03-1833","name":"Test Bench &amp; Completed: Test","order":13,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"81692dde-b76a-433d-9b5d-3476cf3cd7f6","job_id":"J03-1833","name":"Test Bench &amp; Completed: Release","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"b69b87c3-9d4b-450e-8c0e-162eb755ff75","job_id":"J03-1833","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300}],"assignees":[{"id":"a58e3fbd-80eb-4c64-bd6b-bb7196830ed8","job_id":"J03-1833","technician_id":"T-c23ed9a4","assigned_at":"2026-08-11T05:31:58.767Z","is_lead":"1"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-c23ed9a4","status":"busy","current_job_id":"J03-1833"}]}</t>
+  </si>
+  <si>
+    <t>7704b641-b5ad-455c-aa06-2cca203190cc</t>
+  </si>
+  <si>
+    <t>2026-08-11T23:53:02.252Z</t>
+  </si>
+  <si>
+    <t>{"job":{"id":"J03-c0e2","title":"Recondition Transmission D10T,R","unit":"E448 — D10T","unit_id":"a5c2144b-1b29-40f7-9b5c-cfbbc03c3387","description":"Job recondition Transmission D10T,R (time frame standar).","status":"in_progress","technician_id":"T-533ca22c","template_id":"ne-transmission-d10t-r","created_at":"2026-08-10T08:22:13.799Z","started_at":"2026-08-10T08:23:20.053Z","completed_at":"","paused_at":"","total_paused_sec":3,"estimated_minutes":5820},"steps":[{"id":"7609ebf3-f1eb-4d9d-9591-f21d853034e1","job_id":"J03-c0e2","name":"Dismantle: Washing Transmission","order":1,"status":"done","started_at":"2026-08-10T08:23:20.053Z","completed_at":"2026-08-10T08:24:03.692Z","duration_sec":43,"std_minutes":60},{"id":"a3923555-21a4-4b60-9959-c48d814bf136","job_id":"J03-c0e2","name":"Dismantle: Trans Gear","order":2,"status":"done","started_at":"2026-08-10T08:23:32.872Z","completed_at":"2026-08-10T08:24:06.672Z","duration_sec":33,"std_minutes":600},{"id":"39c70957-da00-4dc8-a988-36ee41ef9841","job_id":"J03-c0e2","name":"Dismantle: CV, Harness, &amp; Sensor","order":3,"status":"done","started_at":"2026-08-10T08:24:08.700Z","completed_at":"2026-08-10T08:24:14.772Z","duration_sec":6,"std_minutes":300},{"id":"6feb4f63-8277-4c8a-a4cf-8d8a3d660682","job_id":"J03-c0e2","name":"Dismantle: Clutch 5","order":4,"status":"done","started_at":"2026-08-10T08:23:32.872Z","completed_at":"2026-08-10T08:24:08.700Z","duration_sec":35,"std_minutes":180},{"id":"179574f5-b3d7-43e4-a065-977ebd015bfc","job_id":"J03-c0e2","name":"Dismantle: Clutch 4","order":5,"status":"done","started_at":"2026-08-10T08:24:14.772Z","completed_at":"2026-08-10T10:10:28.558Z","duration_sec":6373,"std_minutes":180},{"id":"8aff0e07-0f40-4945-a9dc-7a8867ffccf4","job_id":"J03-c0e2","name":"Dismantle: Clutch 3","order":6,"status":"done","started_at":"2026-08-11T05:33:18.994Z","completed_at":"2026-08-11T05:33:34.800Z","duration_sec":69782,"std_minutes":180},{"id":"82415ef2-23b1-4eb2-b027-a268df0f4189","job_id":"J03-c0e2","name":"Dismantle: Clutch 2","order":7,"status":"done","started_at":"2026-08-11T05:33:34.800Z","completed_at":"2026-08-11T05:33:47.115Z","duration_sec":12,"std_minutes":180},{"id":"f7c8bcdc-e2d1-4856-aea1-f577d25b0550","job_id":"J03-c0e2","name":"Dismantle: Clutch 1","order":8,"status":"done","started_at":"2026-08-11T05:33:47.115Z","completed_at":"2026-08-11T15:28:10.891Z","duration_sec":35663,"std_minutes":180},{"id":"4391d523-f1d0-4922-95fb-d3827a21b813","job_id":"J03-c0e2","name":"Dismantle: Planetary &amp; Shaft","order":9,"status":"done","started_at":"2026-08-11T15:28:10.891Z","completed_at":"2026-08-11T23:53:02.227Z","duration_sec":30291,"std_minutes":300},{"id":"bdcc79ae-9f46-46e2-963d-fd2ba3d40a2e","job_id":"J03-c0e2","name":"Dismantle: Part list &amp; Tear Down","order":10,"status":"in_progress","started_at":"2026-08-11T23:53:02.227Z","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"0670c5ee-3df9-46ba-a7e5-790a2591233a","job_id":"J03-c0e2","name":"Assemble: Planetary &amp; Shaft In-Out","order":11,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"7276104d-e8c7-4ea6-aac7-6cd975141c45","job_id":"J03-c0e2","name":"Assemble: Clutch 1","order":12,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"1781ebaa-7fb0-4896-b642-71d33b8c4878","job_id":"J03-c0e2","name":"Assemble: Clutch 2","order":13,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"5532b99d-a7fd-4b7d-a752-796f7bc5daff","job_id":"J03-c0e2","name":"Assemble: Clutch 3","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"ff0ed73f-27d1-4b0a-a4f2-7818d3cfbc7e","job_id":"J03-c0e2","name":"Assemble: Clutch 4","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"970a35a3-a96b-48b4-9f04-a2b921b013f0","job_id":"J03-c0e2","name":"Assemble: Clutch 5","order":16,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"698b11d9-e1a3-451f-8a47-ccabcc5718c6","job_id":"J03-c0e2","name":"Assemble: CV, Harness &amp; Sensor","order":17,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"0620fee8-23da-434a-85e6-6354dee830d7","job_id":"J03-c0e2","name":"Assemble: Trans Gear","order":18,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":900},{"id":"ca31c8c2-4542-42f7-be4e-86974a63447b","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Set up","order":19,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"ba2d158c-a9f5-4d98-aea1-fd1f7983c4eb","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Test","order":20,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"d2f96316-8f95-487c-a7ee-94ba19ef4354","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Release","order":21,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"050b2cfc-5ea2-4926-b9c1-c7bdfe6bbd49","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":22,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240}],"assignees":[{"id":"5ece1c51-c36b-46e5-a9d2-f9106a729470","job_id":"J03-c0e2","technician_id":"T-533ca22c","assigned_at":"2026-08-10T08:23:08.120Z","is_lead":"1"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-533ca22c","status":"busy","current_job_id":"J03-c0e2"}]}</t>
+  </si>
+  <si>
+    <t>cdf30bd9-b4cb-4b1a-b2e6-50e28710d072</t>
+  </si>
+  <si>
+    <t>2026-08-12T00:05:46.138Z</t>
+  </si>
+  <si>
+    <t>{"job":{"id":"J02-dc56","title":"Recondition Transmission 16H,G","unit":"E448 — D10T","unit_id":"a5c2144b-1b29-40f7-9b5c-cfbbc03c3387","description":"Job recondition Transmission 16H,G (time frame standar).","status":"in_progress","technician_id":"T-37cadb58","template_id":"ne-transmission-16h-g","created_at":"2026-08-09T14:29:20.672Z","started_at":"2026-08-09T15:02:48.075Z","completed_at":"","paused_at":"","total_paused_sec":89,"estimated_minutes":5340},"steps":[{"id":"91804ed8-5ad4-4ffd-aaad-beba64eb9cb2","job_id":"J02-dc56","name":"Dismantle: Washing Transmission gp","order":1,"status":"done","started_at":"2026-08-09T15:02:48.075Z","completed_at":"2026-08-09T15:20:47.571Z","duration_sec":1079,"std_minutes":240},{"id":"a127f857-f092-4b21-b197-3e3c8a02d549","job_id":"J02-dc56","name":"Dismantle: Control Valve 2EA","order":2,"status":"done","started_at":"2026-08-10T01:30:25.210Z","completed_at":"2026-08-10T01:30:32.748Z","duration_sec":36495,"std_minutes":300},{"id":"3bc8becf-2b5e-4391-8c9f-619d63d7281c","job_id":"J02-dc56","name":"Dismantle: Pump, Lines, &amp; Screen","order":3,"status":"done","started_at":"2026-08-10T01:30:32.748Z","completed_at":"2026-08-10T08:27:37.616Z","duration_sec":25024,"std_minutes":240},{"id":"bacf6ce8-8a97-4831-9f38-3010f4d64a9a","job_id":"J02-dc56","name":"Dismantle: Planetary GP","order":4,"status":"done","started_at":"2026-08-10T08:27:37.616Z","completed_at":"2026-08-11T05:36:57.526Z","duration_sec":76159,"std_minutes":900},{"id":"74bc5c28-b84c-4cfa-b429-25198c968f30","job_id":"J02-dc56","name":"Dismantle: Directional &amp; Idler gear","order":5,"status":"done","started_at":"2026-08-11T05:36:57.526Z","completed_at":"2026-08-11T14:50:26.762Z","duration_sec":33209,"std_minutes":300},{"id":"c3ce574f-16e3-4ce2-815e-10a842f608de","job_id":"J02-dc56","name":"Dismantle: Clean up Housing 2ea","order":6,"status":"done","started_at":"2026-08-11T14:50:26.763Z","completed_at":"2026-08-11T15:28:01.298Z","duration_sec":2254,"std_minutes":120},{"id":"b57a5afd-0b62-47a8-a149-df57cdbec92f","job_id":"J02-dc56","name":"Dismantle: Part list &amp; Tear Down","order":7,"status":"done","started_at":"2026-08-11T15:28:01.298Z","completed_at":"2026-08-12T00:05:46.117Z","duration_sec":31064,"std_minutes":240},{"id":"ef67991d-4f1b-4929-b4b9-3bd70d1c1a8b","job_id":"J02-dc56","name":"Assemble: Directional &amp; Idler gear","order":8,"status":"in_progress","started_at":"2026-08-12T00:05:46.117Z","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"19689610-ed31-4c36-959c-6233ef31d9cc","job_id":"J02-dc56","name":"Assemble: Planetary GP","order":9,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"572f712a-0376-495f-a98f-9ee71ead12b3","job_id":"J02-dc56","name":"Assemble: CV 2EA","order":10,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"033a6b1b-8daf-46cc-a1e1-292ad2451d5f","job_id":"J02-dc56","name":"Assemble: Pump, Lines, &amp; Screen","order":11,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"f52cc000-4714-474d-a6c4-a3f41408fbb7","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Set up","order":12,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"a9b889d6-b2f7-4421-a27a-fcd6a2fde9f9","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Test","order":13,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"3edd89d2-41a4-4856-976b-cbc716dc3788","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Release","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"4d87b720-179e-4dbd-bf95-3d44c356f29e","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300}],"assignees":[{"id":"e39218a1-186b-46ca-b35a-d999eac3307c","job_id":"J02-dc56","technician_id":"T-37cadb58","assigned_at":"2026-08-11T14:56:11.247Z","is_lead":"1"},{"id":"56cff857-6f11-4d4f-889c-272de87907ef","job_id":"J02-dc56","technician_id":"T-e4a06545","assigned_at":"2026-08-11T14:56:11.247Z","is_lead":"0"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-37cadb58","status":"busy","current_job_id":"J02-dc56"},{"id":"T-e4a06545","status":"busy","current_job_id":"J02-dc56"}]}</t>
+  </si>
+  <si>
+    <t>0cb3efc0-ad07-40f7-8d75-f2b7ab2aee74</t>
+  </si>
+  <si>
+    <t>2026-08-12T03:13:34.811Z</t>
+  </si>
+  <si>
+    <t>{"job":{"id":"J03-c0e2","title":"Recondition Transmission D10T,R","unit":"E448 — D10T","unit_id":"a5c2144b-1b29-40f7-9b5c-cfbbc03c3387","description":"Job recondition Transmission D10T,R (time frame standar).","status":"in_progress","technician_id":"T-533ca22c","template_id":"ne-transmission-d10t-r","created_at":"2026-08-10T08:22:13.799Z","started_at":"2026-08-10T08:23:20.053Z","completed_at":"","paused_at":"","total_paused_sec":3,"estimated_minutes":5820},"steps":[{"id":"7609ebf3-f1eb-4d9d-9591-f21d853034e1","job_id":"J03-c0e2","name":"Dismantle: Washing Transmission","order":1,"status":"done","started_at":"2026-08-10T08:23:20.053Z","completed_at":"2026-08-10T08:24:03.692Z","duration_sec":43,"std_minutes":60},{"id":"a3923555-21a4-4b60-9959-c48d814bf136","job_id":"J03-c0e2","name":"Dismantle: Trans Gear","order":2,"status":"done","started_at":"2026-08-10T08:23:32.872Z","completed_at":"2026-08-10T08:24:06.672Z","duration_sec":33,"std_minutes":600},{"id":"39c70957-da00-4dc8-a988-36ee41ef9841","job_id":"J03-c0e2","name":"Dismantle: CV, Harness, &amp; Sensor","order":3,"status":"done","started_at":"2026-08-10T08:24:08.700Z","completed_at":"2026-08-10T08:24:14.772Z","duration_sec":6,"std_minutes":300},{"id":"6feb4f63-8277-4c8a-a4cf-8d8a3d660682","job_id":"J03-c0e2","name":"Dismantle: Clutch 5","order":4,"status":"done","started_at":"2026-08-10T08:23:32.872Z","completed_at":"2026-08-10T08:24:08.700Z","duration_sec":35,"std_minutes":180},{"id":"179574f5-b3d7-43e4-a065-977ebd015bfc","job_id":"J03-c0e2","name":"Dismantle: Clutch 4","order":5,"status":"done","started_at":"2026-08-10T08:24:14.772Z","completed_at":"2026-08-10T10:10:28.558Z","duration_sec":6373,"std_minutes":180},{"id":"8aff0e07-0f40-4945-a9dc-7a8867ffccf4","job_id":"J03-c0e2","name":"Dismantle: Clutch 3","order":6,"status":"done","started_at":"2026-08-11T05:33:18.994Z","completed_at":"2026-08-11T05:33:34.800Z","duration_sec":69782,"std_minutes":180},{"id":"82415ef2-23b1-4eb2-b027-a268df0f4189","job_id":"J03-c0e2","name":"Dismantle: Clutch 2","order":7,"status":"done","started_at":"2026-08-11T05:33:34.800Z","completed_at":"2026-08-11T05:33:47.115Z","duration_sec":12,"std_minutes":180},{"id":"f7c8bcdc-e2d1-4856-aea1-f577d25b0550","job_id":"J03-c0e2","name":"Dismantle: Clutch 1","order":8,"status":"done","started_at":"2026-08-11T05:33:47.115Z","completed_at":"2026-08-11T15:28:10.891Z","duration_sec":35663,"std_minutes":180},{"id":"4391d523-f1d0-4922-95fb-d3827a21b813","job_id":"J03-c0e2","name":"Dismantle: Planetary &amp; Shaft","order":9,"status":"done","started_at":"2026-08-11T15:28:10.891Z","completed_at":"2026-08-11T23:53:02.227Z","duration_sec":30291,"std_minutes":300},{"id":"bdcc79ae-9f46-46e2-963d-fd2ba3d40a2e","job_id":"J03-c0e2","name":"Dismantle: Part list &amp; Tear Down","order":10,"status":"done","started_at":"2026-08-11T23:53:02.227Z","completed_at":"2026-08-12T03:13:34.783Z","duration_sec":12032,"std_minutes":240},{"id":"0670c5ee-3df9-46ba-a7e5-790a2591233a","job_id":"J03-c0e2","name":"Assemble: Planetary &amp; Shaft In-Out","order":11,"status":"in_progress","started_at":"2026-08-12T03:13:34.783Z","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"7276104d-e8c7-4ea6-aac7-6cd975141c45","job_id":"J03-c0e2","name":"Assemble: Clutch 1","order":12,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"1781ebaa-7fb0-4896-b642-71d33b8c4878","job_id":"J03-c0e2","name":"Assemble: Clutch 2","order":13,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"5532b99d-a7fd-4b7d-a752-796f7bc5daff","job_id":"J03-c0e2","name":"Assemble: Clutch 3","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"ff0ed73f-27d1-4b0a-a4f2-7818d3cfbc7e","job_id":"J03-c0e2","name":"Assemble: Clutch 4","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"970a35a3-a96b-48b4-9f04-a2b921b013f0","job_id":"J03-c0e2","name":"Assemble: Clutch 5","order":16,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"698b11d9-e1a3-451f-8a47-ccabcc5718c6","job_id":"J03-c0e2","name":"Assemble: CV, Harness &amp; Sensor","order":17,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"0620fee8-23da-434a-85e6-6354dee830d7","job_id":"J03-c0e2","name":"Assemble: Trans Gear","order":18,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":900},{"id":"ca31c8c2-4542-42f7-be4e-86974a63447b","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Set up","order":19,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"ba2d158c-a9f5-4d98-aea1-fd1f7983c4eb","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Test","order":20,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"d2f96316-8f95-487c-a7ee-94ba19ef4354","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Release","order":21,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"050b2cfc-5ea2-4926-b9c1-c7bdfe6bbd49","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":22,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240}],"assignees":[{"id":"5ece1c51-c36b-46e5-a9d2-f9106a729470","job_id":"J03-c0e2","technician_id":"T-533ca22c","assigned_at":"2026-08-10T08:23:08.120Z","is_lead":"1"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-533ca22c","status":"busy","current_job_id":"J03-c0e2"}]}</t>
+  </si>
+  <si>
+    <t>9df41070-a700-4aea-bba9-c1a2ad1a1498</t>
+  </si>
+  <si>
+    <t>2026-08-12T03:47:41.240Z</t>
+  </si>
+  <si>
+    <t>{"job":{"id":"J02-dc56","title":"Recondition Transmission 16H,G","unit":"E448 — D10T","unit_id":"a5c2144b-1b29-40f7-9b5c-cfbbc03c3387","description":"Job recondition Transmission 16H,G (time frame standar).","status":"in_progress","technician_id":"T-37cadb58","template_id":"ne-transmission-16h-g","created_at":"2026-08-09T14:29:20.672Z","started_at":"2026-08-09T15:02:48.075Z","completed_at":"","paused_at":"","total_paused_sec":89,"estimated_minutes":5340},"steps":[{"id":"91804ed8-5ad4-4ffd-aaad-beba64eb9cb2","job_id":"J02-dc56","name":"Dismantle: Washing Transmission gp","order":1,"status":"done","started_at":"2026-08-09T15:02:48.075Z","completed_at":"2026-08-09T15:20:47.571Z","duration_sec":1079,"std_minutes":240},{"id":"a127f857-f092-4b21-b197-3e3c8a02d549","job_id":"J02-dc56","name":"Dismantle: Control Valve 2EA","order":2,"status":"done","started_at":"2026-08-10T01:30:25.210Z","completed_at":"2026-08-10T01:30:32.748Z","duration_sec":36495,"std_minutes":300},{"id":"3bc8becf-2b5e-4391-8c9f-619d63d7281c","job_id":"J02-dc56","name":"Dismantle: Pump, Lines, &amp; Screen","order":3,"status":"done","started_at":"2026-08-10T01:30:32.748Z","completed_at":"2026-08-10T08:27:37.616Z","duration_sec":25024,"std_minutes":240},{"id":"bacf6ce8-8a97-4831-9f38-3010f4d64a9a","job_id":"J02-dc56","name":"Dismantle: Planetary GP","order":4,"status":"done","started_at":"2026-08-10T08:27:37.616Z","completed_at":"2026-08-11T05:36:57.526Z","duration_sec":76159,"std_minutes":900},{"id":"74bc5c28-b84c-4cfa-b429-25198c968f30","job_id":"J02-dc56","name":"Dismantle: Directional &amp; Idler gear","order":5,"status":"done","started_at":"2026-08-11T05:36:57.526Z","completed_at":"2026-08-11T14:50:26.762Z","duration_sec":33209,"std_minutes":300},{"id":"c3ce574f-16e3-4ce2-815e-10a842f608de","job_id":"J02-dc56","name":"Dismantle: Clean up Housing 2ea","order":6,"status":"done","started_at":"2026-08-11T14:50:26.763Z","completed_at":"2026-08-11T15:28:01.298Z","duration_sec":2254,"std_minutes":120},{"id":"b57a5afd-0b62-47a8-a149-df57cdbec92f","job_id":"J02-dc56","name":"Dismantle: Part list &amp; Tear Down","order":7,"status":"done","started_at":"2026-08-11T15:28:01.298Z","completed_at":"2026-08-12T00:05:46.117Z","duration_sec":31064,"std_minutes":240},{"id":"ef67991d-4f1b-4929-b4b9-3bd70d1c1a8b","job_id":"J02-dc56","name":"Assemble: Directional &amp; Idler gear","order":8,"status":"done","started_at":"2026-08-12T00:05:46.117Z","completed_at":"2026-08-12T03:47:41.223Z","duration_sec":13315,"std_minutes":600},{"id":"19689610-ed31-4c36-959c-6233ef31d9cc","job_id":"J02-dc56","name":"Assemble: Planetary GP","order":9,"status":"in_progress","started_at":"2026-08-12T03:47:41.223Z","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"572f712a-0376-495f-a98f-9ee71ead12b3","job_id":"J02-dc56","name":"Assemble: CV 2EA","order":10,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"033a6b1b-8daf-46cc-a1e1-292ad2451d5f","job_id":"J02-dc56","name":"Assemble: Pump, Lines, &amp; Screen","order":11,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"f52cc000-4714-474d-a6c4-a3f41408fbb7","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Set up","order":12,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"a9b889d6-b2f7-4421-a27a-fcd6a2fde9f9","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Test","order":13,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"3edd89d2-41a4-4856-976b-cbc716dc3788","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Release","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"4d87b720-179e-4dbd-bf95-3d44c356f29e","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300}],"assignees":[{"id":"e39218a1-186b-46ca-b35a-d999eac3307c","job_id":"J02-dc56","technician_id":"T-37cadb58","assigned_at":"2026-08-11T14:56:11.247Z","is_lead":"1"},{"id":"56cff857-6f11-4d4f-889c-272de87907ef","job_id":"J02-dc56","technician_id":"T-e4a06545","assigned_at":"2026-08-11T14:56:11.247Z","is_lead":"0"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-37cadb58","status":"busy","current_job_id":"J02-dc56"},{"id":"T-e4a06545","status":"busy","current_job_id":"J02-dc56"}]}</t>
+  </si>
+  <si>
+    <t>04d4850b-ea0f-4065-b74b-58d197464edc</t>
+  </si>
+  <si>
+    <t>2026-08-12T09:25:37.982Z</t>
+  </si>
+  <si>
+    <t>{"job":{"id":"J02-dc56","title":"Recondition Transmission 16H,G","unit":"E448 — D10T","unit_id":"a5c2144b-1b29-40f7-9b5c-cfbbc03c3387","description":"Job recondition Transmission 16H,G (time frame standar).","status":"in_progress","technician_id":"T-37cadb58","template_id":"ne-transmission-16h-g","created_at":"2026-08-09T14:29:20.672Z","started_at":"2026-08-09T15:02:48.075Z","completed_at":"","paused_at":"","total_paused_sec":89,"estimated_minutes":5340},"steps":[{"id":"91804ed8-5ad4-4ffd-aaad-beba64eb9cb2","job_id":"J02-dc56","name":"Dismantle: Washing Transmission gp","order":1,"status":"done","started_at":"2026-08-09T15:02:48.075Z","completed_at":"2026-08-09T15:20:47.571Z","duration_sec":1079,"std_minutes":240},{"id":"a127f857-f092-4b21-b197-3e3c8a02d549","job_id":"J02-dc56","name":"Dismantle: Control Valve 2EA","order":2,"status":"done","started_at":"2026-08-10T01:30:25.210Z","completed_at":"2026-08-10T01:30:32.748Z","duration_sec":36495,"std_minutes":300},{"id":"3bc8becf-2b5e-4391-8c9f-619d63d7281c","job_id":"J02-dc56","name":"Dismantle: Pump, Lines, &amp; Screen","order":3,"status":"done","started_at":"2026-08-10T01:30:32.748Z","completed_at":"2026-08-10T08:27:37.616Z","duration_sec":25024,"std_minutes":240},{"id":"bacf6ce8-8a97-4831-9f38-3010f4d64a9a","job_id":"J02-dc56","name":"Dismantle: Planetary GP","order":4,"status":"done","started_at":"2026-08-10T08:27:37.616Z","completed_at":"2026-08-11T05:36:57.526Z","duration_sec":76159,"std_minutes":900},{"id":"74bc5c28-b84c-4cfa-b429-25198c968f30","job_id":"J02-dc56","name":"Dismantle: Directional &amp; Idler gear","order":5,"status":"done","started_at":"2026-08-11T05:36:57.526Z","completed_at":"2026-08-11T14:50:26.762Z","duration_sec":33209,"std_minutes":300},{"id":"c3ce574f-16e3-4ce2-815e-10a842f608de","job_id":"J02-dc56","name":"Dismantle: Clean up Housing 2ea","order":6,"status":"done","started_at":"2026-08-11T14:50:26.763Z","completed_at":"2026-08-11T15:28:01.298Z","duration_sec":2254,"std_minutes":120},{"id":"b57a5afd-0b62-47a8-a149-df57cdbec92f","job_id":"J02-dc56","name":"Dismantle: Part list &amp; Tear Down","order":7,"status":"done","started_at":"2026-08-11T15:28:01.298Z","completed_at":"2026-08-12T00:05:46.117Z","duration_sec":31064,"std_minutes":240},{"id":"ef67991d-4f1b-4929-b4b9-3bd70d1c1a8b","job_id":"J02-dc56","name":"Assemble: Directional &amp; Idler gear","order":8,"status":"done","started_at":"2026-08-12T00:05:46.117Z","completed_at":"2026-08-12T03:47:41.223Z","duration_sec":13315,"std_minutes":600},{"id":"19689610-ed31-4c36-959c-6233ef31d9cc","job_id":"J02-dc56","name":"Assemble: Planetary GP","order":9,"status":"done","started_at":"2026-08-12T03:47:41.223Z","completed_at":"2026-08-12T09:25:37.962Z","duration_sec":20276,"std_minutes":600},{"id":"572f712a-0376-495f-a98f-9ee71ead12b3","job_id":"J02-dc56","name":"Assemble: CV 2EA","order":10,"status":"in_progress","started_at":"2026-08-12T09:25:37.962Z","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"033a6b1b-8daf-46cc-a1e1-292ad2451d5f","job_id":"J02-dc56","name":"Assemble: Pump, Lines, &amp; Screen","order":11,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"f52cc000-4714-474d-a6c4-a3f41408fbb7","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Set up","order":12,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"a9b889d6-b2f7-4421-a27a-fcd6a2fde9f9","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Test","order":13,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"3edd89d2-41a4-4856-976b-cbc716dc3788","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Release","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"4d87b720-179e-4dbd-bf95-3d44c356f29e","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300}],"assignees":[{"id":"e39218a1-186b-46ca-b35a-d999eac3307c","job_id":"J02-dc56","technician_id":"T-37cadb58","assigned_at":"2026-08-11T14:56:11.247Z","is_lead":"1"},{"id":"56cff857-6f11-4d4f-889c-272de87907ef","job_id":"J02-dc56","technician_id":"T-e4a06545","assigned_at":"2026-08-11T14:56:11.247Z","is_lead":"0"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-37cadb58","status":"busy","current_job_id":"J02-dc56"},{"id":"T-e4a06545","status":"busy","current_job_id":"J02-dc56"}]}</t>
   </si>
 </sst>
 </file>
@@ -933,7 +915,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q42"/>
+  <dimension ref="A1:Q40"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -2534,13 +2516,13 @@
         <v>147</v>
       </c>
       <c r="C31" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="D31" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="E31" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="F31" t="s">
         <v>32</v>
@@ -2549,16 +2531,16 @@
         <v>23</v>
       </c>
       <c r="H31" t="s">
-        <v>107</v>
+        <v>24</v>
       </c>
       <c r="I31" t="s">
-        <v>107</v>
+        <v>24</v>
       </c>
       <c r="J31" t="s">
         <v>33</v>
       </c>
       <c r="K31" t="s">
-        <v>121</v>
+        <v>145</v>
       </c>
       <c r="L31" t="s">
         <v>148</v>
@@ -2587,13 +2569,13 @@
         <v>150</v>
       </c>
       <c r="C32" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="D32" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="E32" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="F32" t="s">
         <v>32</v>
@@ -2602,16 +2584,16 @@
         <v>23</v>
       </c>
       <c r="H32" t="s">
-        <v>107</v>
+        <v>55</v>
       </c>
       <c r="I32" t="s">
-        <v>107</v>
+        <v>55</v>
       </c>
       <c r="J32" t="s">
-        <v>33</v>
+        <v>88</v>
       </c>
       <c r="K32" t="s">
-        <v>148</v>
+        <v>135</v>
       </c>
       <c r="L32" t="s">
         <v>151</v>
@@ -2640,13 +2622,13 @@
         <v>153</v>
       </c>
       <c r="C33" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="D33" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="E33" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="F33" t="s">
         <v>32</v>
@@ -2664,7 +2646,7 @@
         <v>33</v>
       </c>
       <c r="K33" t="s">
-        <v>151</v>
+        <v>121</v>
       </c>
       <c r="L33" t="s">
         <v>154</v>
@@ -2693,16 +2675,16 @@
         <v>156</v>
       </c>
       <c r="C34" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="D34" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="E34" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="F34" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="G34" t="s">
         <v>23</v>
@@ -2714,7 +2696,7 @@
         <v>107</v>
       </c>
       <c r="J34" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="K34" t="s">
         <v>154</v>
@@ -2746,16 +2728,16 @@
         <v>159</v>
       </c>
       <c r="C35" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="D35" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="E35" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="F35" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="G35" t="s">
         <v>23</v>
@@ -2767,7 +2749,7 @@
         <v>107</v>
       </c>
       <c r="J35" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="K35" t="s">
         <v>157</v>
@@ -2799,13 +2781,13 @@
         <v>162</v>
       </c>
       <c r="C36" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="D36" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="E36" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="F36" t="s">
         <v>32</v>
@@ -2814,16 +2796,16 @@
         <v>23</v>
       </c>
       <c r="H36" t="s">
-        <v>107</v>
+        <v>55</v>
       </c>
       <c r="I36" t="s">
-        <v>107</v>
+        <v>55</v>
       </c>
       <c r="J36" t="s">
-        <v>33</v>
+        <v>88</v>
       </c>
       <c r="K36" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="L36" t="s">
         <v>163</v>
@@ -2867,16 +2849,16 @@
         <v>23</v>
       </c>
       <c r="H37" t="s">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="I37" t="s">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="J37" t="s">
-        <v>88</v>
+        <v>33</v>
       </c>
       <c r="K37" t="s">
-        <v>135</v>
+        <v>148</v>
       </c>
       <c r="L37" t="s">
         <v>166</v>
@@ -2905,13 +2887,13 @@
         <v>168</v>
       </c>
       <c r="C38" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="D38" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="E38" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="F38" t="s">
         <v>32</v>
@@ -2920,16 +2902,16 @@
         <v>23</v>
       </c>
       <c r="H38" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="I38" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="J38" t="s">
-        <v>33</v>
+        <v>88</v>
       </c>
       <c r="K38" t="s">
-        <v>145</v>
+        <v>163</v>
       </c>
       <c r="L38" t="s">
         <v>169</v>
@@ -2958,31 +2940,31 @@
         <v>171</v>
       </c>
       <c r="C39" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="D39" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="E39" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="F39" t="s">
-        <v>83</v>
+        <v>32</v>
       </c>
       <c r="G39" t="s">
         <v>23</v>
       </c>
       <c r="H39" t="s">
-        <v>107</v>
+        <v>24</v>
       </c>
       <c r="I39" t="s">
-        <v>107</v>
+        <v>24</v>
       </c>
       <c r="J39" t="s">
-        <v>120</v>
+        <v>33</v>
       </c>
       <c r="K39" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="L39" t="s">
         <v>172</v>
@@ -3011,13 +2993,13 @@
         <v>174</v>
       </c>
       <c r="C40" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="D40" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="E40" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="F40" t="s">
         <v>32</v>
@@ -3026,16 +3008,16 @@
         <v>23</v>
       </c>
       <c r="H40" t="s">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="I40" t="s">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="J40" t="s">
-        <v>88</v>
+        <v>33</v>
       </c>
       <c r="K40" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="L40" t="s">
         <v>175</v>
@@ -3053,112 +3035,6 @@
         <v>36</v>
       </c>
       <c r="Q40" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>176</v>
-      </c>
-      <c r="B41" t="s">
-        <v>177</v>
-      </c>
-      <c r="C41" t="s">
-        <v>19</v>
-      </c>
-      <c r="D41" t="s">
-        <v>20</v>
-      </c>
-      <c r="E41" t="s">
-        <v>21</v>
-      </c>
-      <c r="F41" t="s">
-        <v>41</v>
-      </c>
-      <c r="G41" t="s">
-        <v>23</v>
-      </c>
-      <c r="H41" t="s">
-        <v>24</v>
-      </c>
-      <c r="I41" t="s">
-        <v>24</v>
-      </c>
-      <c r="J41" t="s">
-        <v>42</v>
-      </c>
-      <c r="K41" t="s">
-        <v>169</v>
-      </c>
-      <c r="L41" t="s">
-        <v>178</v>
-      </c>
-      <c r="M41" t="s">
-        <v>35</v>
-      </c>
-      <c r="N41" t="s">
-        <v>36</v>
-      </c>
-      <c r="O41" t="s">
-        <v>36</v>
-      </c>
-      <c r="P41" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q41" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>179</v>
-      </c>
-      <c r="B42" t="s">
-        <v>180</v>
-      </c>
-      <c r="C42" t="s">
-        <v>19</v>
-      </c>
-      <c r="D42" t="s">
-        <v>20</v>
-      </c>
-      <c r="E42" t="s">
-        <v>21</v>
-      </c>
-      <c r="F42" t="s">
-        <v>46</v>
-      </c>
-      <c r="G42" t="s">
-        <v>23</v>
-      </c>
-      <c r="H42" t="s">
-        <v>24</v>
-      </c>
-      <c r="I42" t="s">
-        <v>24</v>
-      </c>
-      <c r="J42" t="s">
-        <v>47</v>
-      </c>
-      <c r="K42" t="s">
-        <v>178</v>
-      </c>
-      <c r="L42" t="s">
-        <v>181</v>
-      </c>
-      <c r="M42" t="s">
-        <v>35</v>
-      </c>
-      <c r="N42" t="s">
-        <v>36</v>
-      </c>
-      <c r="O42" t="s">
-        <v>36</v>
-      </c>
-      <c r="P42" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q42" t="s">
         <v>36</v>
       </c>
     </row>

--- a/data/backup-jobs.xlsx
+++ b/data/backup-jobs.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="680" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="748" uniqueCount="188">
   <si>
     <t>id</t>
   </si>
@@ -539,6 +539,42 @@
   </si>
   <si>
     <t>{"job":{"id":"J02-dc56","title":"Recondition Transmission 16H,G","unit":"E448 — D10T","unit_id":"a5c2144b-1b29-40f7-9b5c-cfbbc03c3387","description":"Job recondition Transmission 16H,G (time frame standar).","status":"in_progress","technician_id":"T-37cadb58","template_id":"ne-transmission-16h-g","created_at":"2026-08-09T14:29:20.672Z","started_at":"2026-08-09T15:02:48.075Z","completed_at":"","paused_at":"","total_paused_sec":89,"estimated_minutes":5340},"steps":[{"id":"91804ed8-5ad4-4ffd-aaad-beba64eb9cb2","job_id":"J02-dc56","name":"Dismantle: Washing Transmission gp","order":1,"status":"done","started_at":"2026-08-09T15:02:48.075Z","completed_at":"2026-08-09T15:20:47.571Z","duration_sec":1079,"std_minutes":240},{"id":"a127f857-f092-4b21-b197-3e3c8a02d549","job_id":"J02-dc56","name":"Dismantle: Control Valve 2EA","order":2,"status":"done","started_at":"2026-08-10T01:30:25.210Z","completed_at":"2026-08-10T01:30:32.748Z","duration_sec":36495,"std_minutes":300},{"id":"3bc8becf-2b5e-4391-8c9f-619d63d7281c","job_id":"J02-dc56","name":"Dismantle: Pump, Lines, &amp; Screen","order":3,"status":"done","started_at":"2026-08-10T01:30:32.748Z","completed_at":"2026-08-10T08:27:37.616Z","duration_sec":25024,"std_minutes":240},{"id":"bacf6ce8-8a97-4831-9f38-3010f4d64a9a","job_id":"J02-dc56","name":"Dismantle: Planetary GP","order":4,"status":"done","started_at":"2026-08-10T08:27:37.616Z","completed_at":"2026-08-11T05:36:57.526Z","duration_sec":76159,"std_minutes":900},{"id":"74bc5c28-b84c-4cfa-b429-25198c968f30","job_id":"J02-dc56","name":"Dismantle: Directional &amp; Idler gear","order":5,"status":"done","started_at":"2026-08-11T05:36:57.526Z","completed_at":"2026-08-11T14:50:26.762Z","duration_sec":33209,"std_minutes":300},{"id":"c3ce574f-16e3-4ce2-815e-10a842f608de","job_id":"J02-dc56","name":"Dismantle: Clean up Housing 2ea","order":6,"status":"done","started_at":"2026-08-11T14:50:26.763Z","completed_at":"2026-08-11T15:28:01.298Z","duration_sec":2254,"std_minutes":120},{"id":"b57a5afd-0b62-47a8-a149-df57cdbec92f","job_id":"J02-dc56","name":"Dismantle: Part list &amp; Tear Down","order":7,"status":"done","started_at":"2026-08-11T15:28:01.298Z","completed_at":"2026-08-12T00:05:46.117Z","duration_sec":31064,"std_minutes":240},{"id":"ef67991d-4f1b-4929-b4b9-3bd70d1c1a8b","job_id":"J02-dc56","name":"Assemble: Directional &amp; Idler gear","order":8,"status":"done","started_at":"2026-08-12T00:05:46.117Z","completed_at":"2026-08-12T03:47:41.223Z","duration_sec":13315,"std_minutes":600},{"id":"19689610-ed31-4c36-959c-6233ef31d9cc","job_id":"J02-dc56","name":"Assemble: Planetary GP","order":9,"status":"done","started_at":"2026-08-12T03:47:41.223Z","completed_at":"2026-08-12T09:25:37.962Z","duration_sec":20276,"std_minutes":600},{"id":"572f712a-0376-495f-a98f-9ee71ead12b3","job_id":"J02-dc56","name":"Assemble: CV 2EA","order":10,"status":"in_progress","started_at":"2026-08-12T09:25:37.962Z","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"033a6b1b-8daf-46cc-a1e1-292ad2451d5f","job_id":"J02-dc56","name":"Assemble: Pump, Lines, &amp; Screen","order":11,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"f52cc000-4714-474d-a6c4-a3f41408fbb7","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Set up","order":12,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"a9b889d6-b2f7-4421-a27a-fcd6a2fde9f9","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Test","order":13,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"3edd89d2-41a4-4856-976b-cbc716dc3788","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Release","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"4d87b720-179e-4dbd-bf95-3d44c356f29e","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300}],"assignees":[{"id":"e39218a1-186b-46ca-b35a-d999eac3307c","job_id":"J02-dc56","technician_id":"T-37cadb58","assigned_at":"2026-08-11T14:56:11.247Z","is_lead":"1"},{"id":"56cff857-6f11-4d4f-889c-272de87907ef","job_id":"J02-dc56","technician_id":"T-e4a06545","assigned_at":"2026-08-11T14:56:11.247Z","is_lead":"0"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-37cadb58","status":"busy","current_job_id":"J02-dc56"},{"id":"T-e4a06545","status":"busy","current_job_id":"J02-dc56"}]}</t>
+  </si>
+  <si>
+    <t>79bd2fb4-a466-49af-bac4-4acca3b71982</t>
+  </si>
+  <si>
+    <t>2026-08-13T03:13:58.634Z</t>
+  </si>
+  <si>
+    <t>{"job":{"id":"J02-dc56","title":"Recondition Transmission 16H,G","unit":"E448 — D10T","unit_id":"a5c2144b-1b29-40f7-9b5c-cfbbc03c3387","description":"Job recondition Transmission 16H,G (time frame standar).","status":"in_progress","technician_id":"T-37cadb58","template_id":"ne-transmission-16h-g","created_at":"2026-08-09T14:29:20.672Z","started_at":"2026-08-09T15:02:48.075Z","completed_at":"","paused_at":"","total_paused_sec":89,"estimated_minutes":5340},"steps":[{"id":"91804ed8-5ad4-4ffd-aaad-beba64eb9cb2","job_id":"J02-dc56","name":"Dismantle: Washing Transmission gp","order":1,"status":"done","started_at":"2026-08-09T15:02:48.075Z","completed_at":"2026-08-09T15:20:47.571Z","duration_sec":1079,"std_minutes":240},{"id":"a127f857-f092-4b21-b197-3e3c8a02d549","job_id":"J02-dc56","name":"Dismantle: Control Valve 2EA","order":2,"status":"done","started_at":"2026-08-10T01:30:25.210Z","completed_at":"2026-08-10T01:30:32.748Z","duration_sec":36495,"std_minutes":300},{"id":"3bc8becf-2b5e-4391-8c9f-619d63d7281c","job_id":"J02-dc56","name":"Dismantle: Pump, Lines, &amp; Screen","order":3,"status":"done","started_at":"2026-08-10T01:30:32.748Z","completed_at":"2026-08-10T08:27:37.616Z","duration_sec":25024,"std_minutes":240},{"id":"bacf6ce8-8a97-4831-9f38-3010f4d64a9a","job_id":"J02-dc56","name":"Dismantle: Planetary GP","order":4,"status":"done","started_at":"2026-08-10T08:27:37.616Z","completed_at":"2026-08-11T05:36:57.526Z","duration_sec":76159,"std_minutes":900},{"id":"74bc5c28-b84c-4cfa-b429-25198c968f30","job_id":"J02-dc56","name":"Dismantle: Directional &amp; Idler gear","order":5,"status":"done","started_at":"2026-08-11T05:36:57.526Z","completed_at":"2026-08-11T14:50:26.762Z","duration_sec":33209,"std_minutes":300},{"id":"c3ce574f-16e3-4ce2-815e-10a842f608de","job_id":"J02-dc56","name":"Dismantle: Clean up Housing 2ea","order":6,"status":"done","started_at":"2026-08-11T14:50:26.763Z","completed_at":"2026-08-11T15:28:01.298Z","duration_sec":2254,"std_minutes":120},{"id":"b57a5afd-0b62-47a8-a149-df57cdbec92f","job_id":"J02-dc56","name":"Dismantle: Part list &amp; Tear Down","order":7,"status":"done","started_at":"2026-08-11T15:28:01.298Z","completed_at":"2026-08-12T00:05:46.117Z","duration_sec":31064,"std_minutes":240},{"id":"ef67991d-4f1b-4929-b4b9-3bd70d1c1a8b","job_id":"J02-dc56","name":"Assemble: Directional &amp; Idler gear","order":8,"status":"done","started_at":"2026-08-12T00:05:46.117Z","completed_at":"2026-08-12T03:47:41.223Z","duration_sec":13315,"std_minutes":600},{"id":"19689610-ed31-4c36-959c-6233ef31d9cc","job_id":"J02-dc56","name":"Assemble: Planetary GP","order":9,"status":"done","started_at":"2026-08-12T03:47:41.223Z","completed_at":"2026-08-12T09:25:37.962Z","duration_sec":20276,"std_minutes":600},{"id":"572f712a-0376-495f-a98f-9ee71ead12b3","job_id":"J02-dc56","name":"Assemble: CV 2EA","order":10,"status":"done","started_at":"2026-08-12T09:25:37.962Z","completed_at":"2026-08-13T03:13:58.520Z","duration_sec":64100,"std_minutes":300},{"id":"033a6b1b-8daf-46cc-a1e1-292ad2451d5f","job_id":"J02-dc56","name":"Assemble: Pump, Lines, &amp; Screen","order":11,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"f52cc000-4714-474d-a6c4-a3f41408fbb7","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Set up","order":12,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"a9b889d6-b2f7-4421-a27a-fcd6a2fde9f9","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Test","order":13,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"3edd89d2-41a4-4856-976b-cbc716dc3788","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Release","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"4d87b720-179e-4dbd-bf95-3d44c356f29e","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300}],"assignees":[{"id":"e39218a1-186b-46ca-b35a-d999eac3307c","job_id":"J02-dc56","technician_id":"T-37cadb58","assigned_at":"2026-08-11T14:56:11.247Z","is_lead":"1"},{"id":"56cff857-6f11-4d4f-889c-272de87907ef","job_id":"J02-dc56","technician_id":"T-e4a06545","assigned_at":"2026-08-11T14:56:11.247Z","is_lead":"0"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-37cadb58","status":"busy","current_job_id":"J02-dc56"},{"id":"T-e4a06545","status":"busy","current_job_id":"J02-dc56"}]}</t>
+  </si>
+  <si>
+    <t>f1a2d14b-2971-4935-afc8-a17e56dd9e4a</t>
+  </si>
+  <si>
+    <t>2026-08-13T03:14:06.440Z</t>
+  </si>
+  <si>
+    <t>{"job":{"id":"J02-dc56","title":"Recondition Transmission 16H,G","unit":"E448 — D10T","unit_id":"a5c2144b-1b29-40f7-9b5c-cfbbc03c3387","description":"Job recondition Transmission 16H,G (time frame standar).","status":"in_progress","technician_id":"T-37cadb58","template_id":"ne-transmission-16h-g","created_at":"2026-08-09T14:29:20.672Z","started_at":"2026-08-09T15:02:48.075Z","completed_at":"","paused_at":"","total_paused_sec":89,"estimated_minutes":5340},"steps":[{"id":"91804ed8-5ad4-4ffd-aaad-beba64eb9cb2","job_id":"J02-dc56","name":"Dismantle: Washing Transmission gp","order":1,"status":"done","started_at":"2026-08-09T15:02:48.075Z","completed_at":"2026-08-09T15:20:47.571Z","duration_sec":1079,"std_minutes":240},{"id":"a127f857-f092-4b21-b197-3e3c8a02d549","job_id":"J02-dc56","name":"Dismantle: Control Valve 2EA","order":2,"status":"done","started_at":"2026-08-10T01:30:25.210Z","completed_at":"2026-08-10T01:30:32.748Z","duration_sec":36495,"std_minutes":300},{"id":"3bc8becf-2b5e-4391-8c9f-619d63d7281c","job_id":"J02-dc56","name":"Dismantle: Pump, Lines, &amp; Screen","order":3,"status":"done","started_at":"2026-08-10T01:30:32.748Z","completed_at":"2026-08-10T08:27:37.616Z","duration_sec":25024,"std_minutes":240},{"id":"bacf6ce8-8a97-4831-9f38-3010f4d64a9a","job_id":"J02-dc56","name":"Dismantle: Planetary GP","order":4,"status":"done","started_at":"2026-08-10T08:27:37.616Z","completed_at":"2026-08-11T05:36:57.526Z","duration_sec":76159,"std_minutes":900},{"id":"74bc5c28-b84c-4cfa-b429-25198c968f30","job_id":"J02-dc56","name":"Dismantle: Directional &amp; Idler gear","order":5,"status":"done","started_at":"2026-08-11T05:36:57.526Z","completed_at":"2026-08-11T14:50:26.762Z","duration_sec":33209,"std_minutes":300},{"id":"c3ce574f-16e3-4ce2-815e-10a842f608de","job_id":"J02-dc56","name":"Dismantle: Clean up Housing 2ea","order":6,"status":"done","started_at":"2026-08-11T14:50:26.763Z","completed_at":"2026-08-11T15:28:01.298Z","duration_sec":2254,"std_minutes":120},{"id":"b57a5afd-0b62-47a8-a149-df57cdbec92f","job_id":"J02-dc56","name":"Dismantle: Part list &amp; Tear Down","order":7,"status":"done","started_at":"2026-08-11T15:28:01.298Z","completed_at":"2026-08-12T00:05:46.117Z","duration_sec":31064,"std_minutes":240},{"id":"ef67991d-4f1b-4929-b4b9-3bd70d1c1a8b","job_id":"J02-dc56","name":"Assemble: Directional &amp; Idler gear","order":8,"status":"done","started_at":"2026-08-12T00:05:46.117Z","completed_at":"2026-08-12T03:47:41.223Z","duration_sec":13315,"std_minutes":600},{"id":"19689610-ed31-4c36-959c-6233ef31d9cc","job_id":"J02-dc56","name":"Assemble: Planetary GP","order":9,"status":"done","started_at":"2026-08-12T03:47:41.223Z","completed_at":"2026-08-12T09:25:37.962Z","duration_sec":20276,"std_minutes":600},{"id":"572f712a-0376-495f-a98f-9ee71ead12b3","job_id":"J02-dc56","name":"Assemble: CV 2EA","order":10,"status":"done","started_at":"2026-08-12T09:25:37.962Z","completed_at":"2026-08-13T03:13:58.520Z","duration_sec":64100,"std_minutes":300},{"id":"033a6b1b-8daf-46cc-a1e1-292ad2451d5f","job_id":"J02-dc56","name":"Assemble: Pump, Lines, &amp; Screen","order":11,"status":"in_progress","started_at":"2026-08-13T03:14:06.385Z","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"f52cc000-4714-474d-a6c4-a3f41408fbb7","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Set up","order":12,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"a9b889d6-b2f7-4421-a27a-fcd6a2fde9f9","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Test","order":13,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"3edd89d2-41a4-4856-976b-cbc716dc3788","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Release","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"4d87b720-179e-4dbd-bf95-3d44c356f29e","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300}],"assignees":[{"id":"e39218a1-186b-46ca-b35a-d999eac3307c","job_id":"J02-dc56","technician_id":"T-37cadb58","assigned_at":"2026-08-11T14:56:11.247Z","is_lead":"1"},{"id":"56cff857-6f11-4d4f-889c-272de87907ef","job_id":"J02-dc56","technician_id":"T-e4a06545","assigned_at":"2026-08-11T14:56:11.247Z","is_lead":"0"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-37cadb58","status":"busy","current_job_id":"J02-dc56"},{"id":"T-e4a06545","status":"busy","current_job_id":"J02-dc56"}]}</t>
+  </si>
+  <si>
+    <t>e64b0648-651e-45ff-9c67-6d77099684ef</t>
+  </si>
+  <si>
+    <t>2026-08-13T11:13:02.603Z</t>
+  </si>
+  <si>
+    <t>{"job":{"id":"J02-dc56","title":"Recondition Transmission 16H,G","unit":"E448 — D10T","unit_id":"a5c2144b-1b29-40f7-9b5c-cfbbc03c3387","description":"Job recondition Transmission 16H,G (time frame standar).","status":"paused","technician_id":"T-37cadb58","template_id":"ne-transmission-16h-g","created_at":"2026-08-09T14:29:20.672Z","started_at":"2026-08-09T15:02:48.075Z","completed_at":"","paused_at":"2026-08-13T11:13:02.526Z","total_paused_sec":89,"estimated_minutes":5340},"steps":[{"id":"91804ed8-5ad4-4ffd-aaad-beba64eb9cb2","job_id":"J02-dc56","name":"Dismantle: Washing Transmission gp","order":1,"status":"done","started_at":"2026-08-09T15:02:48.075Z","completed_at":"2026-08-09T15:20:47.571Z","duration_sec":1079,"std_minutes":240},{"id":"a127f857-f092-4b21-b197-3e3c8a02d549","job_id":"J02-dc56","name":"Dismantle: Control Valve 2EA","order":2,"status":"done","started_at":"2026-08-10T01:30:25.210Z","completed_at":"2026-08-10T01:30:32.748Z","duration_sec":36495,"std_minutes":300},{"id":"3bc8becf-2b5e-4391-8c9f-619d63d7281c","job_id":"J02-dc56","name":"Dismantle: Pump, Lines, &amp; Screen","order":3,"status":"done","started_at":"2026-08-10T01:30:32.748Z","completed_at":"2026-08-10T08:27:37.616Z","duration_sec":25024,"std_minutes":240},{"id":"bacf6ce8-8a97-4831-9f38-3010f4d64a9a","job_id":"J02-dc56","name":"Dismantle: Planetary GP","order":4,"status":"done","started_at":"2026-08-10T08:27:37.616Z","completed_at":"2026-08-11T05:36:57.526Z","duration_sec":76159,"std_minutes":900},{"id":"74bc5c28-b84c-4cfa-b429-25198c968f30","job_id":"J02-dc56","name":"Dismantle: Directional &amp; Idler gear","order":5,"status":"done","started_at":"2026-08-11T05:36:57.526Z","completed_at":"2026-08-11T14:50:26.762Z","duration_sec":33209,"std_minutes":300},{"id":"c3ce574f-16e3-4ce2-815e-10a842f608de","job_id":"J02-dc56","name":"Dismantle: Clean up Housing 2ea","order":6,"status":"done","started_at":"2026-08-11T14:50:26.763Z","completed_at":"2026-08-11T15:28:01.298Z","duration_sec":2254,"std_minutes":120},{"id":"b57a5afd-0b62-47a8-a149-df57cdbec92f","job_id":"J02-dc56","name":"Dismantle: Part list &amp; Tear Down","order":7,"status":"done","started_at":"2026-08-11T15:28:01.298Z","completed_at":"2026-08-12T00:05:46.117Z","duration_sec":31064,"std_minutes":240},{"id":"ef67991d-4f1b-4929-b4b9-3bd70d1c1a8b","job_id":"J02-dc56","name":"Assemble: Directional &amp; Idler gear","order":8,"status":"done","started_at":"2026-08-12T00:05:46.117Z","completed_at":"2026-08-12T03:47:41.223Z","duration_sec":13315,"std_minutes":600},{"id":"19689610-ed31-4c36-959c-6233ef31d9cc","job_id":"J02-dc56","name":"Assemble: Planetary GP","order":9,"status":"done","started_at":"2026-08-12T03:47:41.223Z","completed_at":"2026-08-12T09:25:37.962Z","duration_sec":20276,"std_minutes":600},{"id":"572f712a-0376-495f-a98f-9ee71ead12b3","job_id":"J02-dc56","name":"Assemble: CV 2EA","order":10,"status":"done","started_at":"2026-08-12T09:25:37.962Z","completed_at":"2026-08-13T03:13:58.520Z","duration_sec":64100,"std_minutes":300},{"id":"033a6b1b-8daf-46cc-a1e1-292ad2451d5f","job_id":"J02-dc56","name":"Assemble: Pump, Lines, &amp; Screen","order":11,"status":"in_progress","started_at":"","completed_at":"","duration_sec":28736,"std_minutes":300},{"id":"f52cc000-4714-474d-a6c4-a3f41408fbb7","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Set up","order":12,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"a9b889d6-b2f7-4421-a27a-fcd6a2fde9f9","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Test","order":13,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"3edd89d2-41a4-4856-976b-cbc716dc3788","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Release","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"4d87b720-179e-4dbd-bf95-3d44c356f29e","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300}],"assignees":[{"id":"e39218a1-186b-46ca-b35a-d999eac3307c","job_id":"J02-dc56","technician_id":"T-37cadb58","assigned_at":"2026-08-11T14:56:11.247Z","is_lead":"1"},{"id":"56cff857-6f11-4d4f-889c-272de87907ef","job_id":"J02-dc56","technician_id":"T-e4a06545","assigned_at":"2026-08-11T14:56:11.247Z","is_lead":"0"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-37cadb58","status":"busy","current_job_id":"J02-dc56"},{"id":"T-e4a06545","status":"busy","current_job_id":"J02-dc56"}]}</t>
+  </si>
+  <si>
+    <t>66dc7a3e-1610-4aa1-af56-59f7cfb92c5c</t>
+  </si>
+  <si>
+    <t>2026-08-13T11:13:08.471Z</t>
+  </si>
+  <si>
+    <t>{"job":{"id":"J02-dc56","title":"Recondition Transmission 16H,G","unit":"E448 — D10T","unit_id":"a5c2144b-1b29-40f7-9b5c-cfbbc03c3387","description":"Job recondition Transmission 16H,G (time frame standar).","status":"in_progress","technician_id":"T-37cadb58","template_id":"ne-transmission-16h-g","created_at":"2026-08-09T14:29:20.672Z","started_at":"2026-08-09T15:02:48.075Z","completed_at":"","paused_at":"","total_paused_sec":94,"estimated_minutes":5340},"steps":[{"id":"91804ed8-5ad4-4ffd-aaad-beba64eb9cb2","job_id":"J02-dc56","name":"Dismantle: Washing Transmission gp","order":1,"status":"done","started_at":"2026-08-09T15:02:48.075Z","completed_at":"2026-08-09T15:20:47.571Z","duration_sec":1079,"std_minutes":240},{"id":"a127f857-f092-4b21-b197-3e3c8a02d549","job_id":"J02-dc56","name":"Dismantle: Control Valve 2EA","order":2,"status":"done","started_at":"2026-08-10T01:30:25.210Z","completed_at":"2026-08-10T01:30:32.748Z","duration_sec":36495,"std_minutes":300},{"id":"3bc8becf-2b5e-4391-8c9f-619d63d7281c","job_id":"J02-dc56","name":"Dismantle: Pump, Lines, &amp; Screen","order":3,"status":"done","started_at":"2026-08-10T01:30:32.748Z","completed_at":"2026-08-10T08:27:37.616Z","duration_sec":25024,"std_minutes":240},{"id":"bacf6ce8-8a97-4831-9f38-3010f4d64a9a","job_id":"J02-dc56","name":"Dismantle: Planetary GP","order":4,"status":"done","started_at":"2026-08-10T08:27:37.616Z","completed_at":"2026-08-11T05:36:57.526Z","duration_sec":76159,"std_minutes":900},{"id":"74bc5c28-b84c-4cfa-b429-25198c968f30","job_id":"J02-dc56","name":"Dismantle: Directional &amp; Idler gear","order":5,"status":"done","started_at":"2026-08-11T05:36:57.526Z","completed_at":"2026-08-11T14:50:26.762Z","duration_sec":33209,"std_minutes":300},{"id":"c3ce574f-16e3-4ce2-815e-10a842f608de","job_id":"J02-dc56","name":"Dismantle: Clean up Housing 2ea","order":6,"status":"done","started_at":"2026-08-11T14:50:26.763Z","completed_at":"2026-08-11T15:28:01.298Z","duration_sec":2254,"std_minutes":120},{"id":"b57a5afd-0b62-47a8-a149-df57cdbec92f","job_id":"J02-dc56","name":"Dismantle: Part list &amp; Tear Down","order":7,"status":"done","started_at":"2026-08-11T15:28:01.298Z","completed_at":"2026-08-12T00:05:46.117Z","duration_sec":31064,"std_minutes":240},{"id":"ef67991d-4f1b-4929-b4b9-3bd70d1c1a8b","job_id":"J02-dc56","name":"Assemble: Directional &amp; Idler gear","order":8,"status":"done","started_at":"2026-08-12T00:05:46.117Z","completed_at":"2026-08-12T03:47:41.223Z","duration_sec":13315,"std_minutes":600},{"id":"19689610-ed31-4c36-959c-6233ef31d9cc","job_id":"J02-dc56","name":"Assemble: Planetary GP","order":9,"status":"done","started_at":"2026-08-12T03:47:41.223Z","completed_at":"2026-08-12T09:25:37.962Z","duration_sec":20276,"std_minutes":600},{"id":"572f712a-0376-495f-a98f-9ee71ead12b3","job_id":"J02-dc56","name":"Assemble: CV 2EA","order":10,"status":"done","started_at":"2026-08-12T09:25:37.962Z","completed_at":"2026-08-13T03:13:58.520Z","duration_sec":64100,"std_minutes":300},{"id":"033a6b1b-8daf-46cc-a1e1-292ad2451d5f","job_id":"J02-dc56","name":"Assemble: Pump, Lines, &amp; Screen","order":11,"status":"in_progress","started_at":"2026-08-13T11:13:08.442Z","completed_at":"","duration_sec":28736,"std_minutes":300},{"id":"f52cc000-4714-474d-a6c4-a3f41408fbb7","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Set up","order":12,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"a9b889d6-b2f7-4421-a27a-fcd6a2fde9f9","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Test","order":13,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"3edd89d2-41a4-4856-976b-cbc716dc3788","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Release","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"4d87b720-179e-4dbd-bf95-3d44c356f29e","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300}],"assignees":[{"id":"e39218a1-186b-46ca-b35a-d999eac3307c","job_id":"J02-dc56","technician_id":"T-37cadb58","assigned_at":"2026-08-11T14:56:11.247Z","is_lead":"1"},{"id":"56cff857-6f11-4d4f-889c-272de87907ef","job_id":"J02-dc56","technician_id":"T-e4a06545","assigned_at":"2026-08-11T14:56:11.247Z","is_lead":"0"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-37cadb58","status":"busy","current_job_id":"J02-dc56"},{"id":"T-e4a06545","status":"busy","current_job_id":"J02-dc56"}]}</t>
   </si>
 </sst>
 </file>
@@ -915,7 +951,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q40"/>
+  <dimension ref="A1:Q44"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -3038,6 +3074,218 @@
         <v>36</v>
       </c>
     </row>
+    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>176</v>
+      </c>
+      <c r="B41" t="s">
+        <v>177</v>
+      </c>
+      <c r="C41" t="s">
+        <v>19</v>
+      </c>
+      <c r="D41" t="s">
+        <v>20</v>
+      </c>
+      <c r="E41" t="s">
+        <v>21</v>
+      </c>
+      <c r="F41" t="s">
+        <v>32</v>
+      </c>
+      <c r="G41" t="s">
+        <v>23</v>
+      </c>
+      <c r="H41" t="s">
+        <v>24</v>
+      </c>
+      <c r="I41" t="s">
+        <v>24</v>
+      </c>
+      <c r="J41" t="s">
+        <v>33</v>
+      </c>
+      <c r="K41" t="s">
+        <v>175</v>
+      </c>
+      <c r="L41" t="s">
+        <v>178</v>
+      </c>
+      <c r="M41" t="s">
+        <v>35</v>
+      </c>
+      <c r="N41" t="s">
+        <v>36</v>
+      </c>
+      <c r="O41" t="s">
+        <v>36</v>
+      </c>
+      <c r="P41" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>179</v>
+      </c>
+      <c r="B42" t="s">
+        <v>180</v>
+      </c>
+      <c r="C42" t="s">
+        <v>19</v>
+      </c>
+      <c r="D42" t="s">
+        <v>20</v>
+      </c>
+      <c r="E42" t="s">
+        <v>21</v>
+      </c>
+      <c r="F42" t="s">
+        <v>83</v>
+      </c>
+      <c r="G42" t="s">
+        <v>23</v>
+      </c>
+      <c r="H42" t="s">
+        <v>24</v>
+      </c>
+      <c r="I42" t="s">
+        <v>24</v>
+      </c>
+      <c r="J42" t="s">
+        <v>120</v>
+      </c>
+      <c r="K42" t="s">
+        <v>178</v>
+      </c>
+      <c r="L42" t="s">
+        <v>181</v>
+      </c>
+      <c r="M42" t="s">
+        <v>35</v>
+      </c>
+      <c r="N42" t="s">
+        <v>36</v>
+      </c>
+      <c r="O42" t="s">
+        <v>36</v>
+      </c>
+      <c r="P42" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>182</v>
+      </c>
+      <c r="B43" t="s">
+        <v>183</v>
+      </c>
+      <c r="C43" t="s">
+        <v>19</v>
+      </c>
+      <c r="D43" t="s">
+        <v>20</v>
+      </c>
+      <c r="E43" t="s">
+        <v>21</v>
+      </c>
+      <c r="F43" t="s">
+        <v>41</v>
+      </c>
+      <c r="G43" t="s">
+        <v>23</v>
+      </c>
+      <c r="H43" t="s">
+        <v>24</v>
+      </c>
+      <c r="I43" t="s">
+        <v>24</v>
+      </c>
+      <c r="J43" t="s">
+        <v>42</v>
+      </c>
+      <c r="K43" t="s">
+        <v>181</v>
+      </c>
+      <c r="L43" t="s">
+        <v>184</v>
+      </c>
+      <c r="M43" t="s">
+        <v>35</v>
+      </c>
+      <c r="N43" t="s">
+        <v>36</v>
+      </c>
+      <c r="O43" t="s">
+        <v>36</v>
+      </c>
+      <c r="P43" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>185</v>
+      </c>
+      <c r="B44" t="s">
+        <v>186</v>
+      </c>
+      <c r="C44" t="s">
+        <v>19</v>
+      </c>
+      <c r="D44" t="s">
+        <v>20</v>
+      </c>
+      <c r="E44" t="s">
+        <v>21</v>
+      </c>
+      <c r="F44" t="s">
+        <v>46</v>
+      </c>
+      <c r="G44" t="s">
+        <v>23</v>
+      </c>
+      <c r="H44" t="s">
+        <v>24</v>
+      </c>
+      <c r="I44" t="s">
+        <v>24</v>
+      </c>
+      <c r="J44" t="s">
+        <v>47</v>
+      </c>
+      <c r="K44" t="s">
+        <v>184</v>
+      </c>
+      <c r="L44" t="s">
+        <v>187</v>
+      </c>
+      <c r="M44" t="s">
+        <v>35</v>
+      </c>
+      <c r="N44" t="s">
+        <v>36</v>
+      </c>
+      <c r="O44" t="s">
+        <v>36</v>
+      </c>
+      <c r="P44" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>36</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/data/backup-jobs.xlsx
+++ b/data/backup-jobs.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="748" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1428" uniqueCount="308">
   <si>
     <t>id</t>
   </si>
@@ -575,6 +575,366 @@
   </si>
   <si>
     <t>{"job":{"id":"J02-dc56","title":"Recondition Transmission 16H,G","unit":"E448 — D10T","unit_id":"a5c2144b-1b29-40f7-9b5c-cfbbc03c3387","description":"Job recondition Transmission 16H,G (time frame standar).","status":"in_progress","technician_id":"T-37cadb58","template_id":"ne-transmission-16h-g","created_at":"2026-08-09T14:29:20.672Z","started_at":"2026-08-09T15:02:48.075Z","completed_at":"","paused_at":"","total_paused_sec":94,"estimated_minutes":5340},"steps":[{"id":"91804ed8-5ad4-4ffd-aaad-beba64eb9cb2","job_id":"J02-dc56","name":"Dismantle: Washing Transmission gp","order":1,"status":"done","started_at":"2026-08-09T15:02:48.075Z","completed_at":"2026-08-09T15:20:47.571Z","duration_sec":1079,"std_minutes":240},{"id":"a127f857-f092-4b21-b197-3e3c8a02d549","job_id":"J02-dc56","name":"Dismantle: Control Valve 2EA","order":2,"status":"done","started_at":"2026-08-10T01:30:25.210Z","completed_at":"2026-08-10T01:30:32.748Z","duration_sec":36495,"std_minutes":300},{"id":"3bc8becf-2b5e-4391-8c9f-619d63d7281c","job_id":"J02-dc56","name":"Dismantle: Pump, Lines, &amp; Screen","order":3,"status":"done","started_at":"2026-08-10T01:30:32.748Z","completed_at":"2026-08-10T08:27:37.616Z","duration_sec":25024,"std_minutes":240},{"id":"bacf6ce8-8a97-4831-9f38-3010f4d64a9a","job_id":"J02-dc56","name":"Dismantle: Planetary GP","order":4,"status":"done","started_at":"2026-08-10T08:27:37.616Z","completed_at":"2026-08-11T05:36:57.526Z","duration_sec":76159,"std_minutes":900},{"id":"74bc5c28-b84c-4cfa-b429-25198c968f30","job_id":"J02-dc56","name":"Dismantle: Directional &amp; Idler gear","order":5,"status":"done","started_at":"2026-08-11T05:36:57.526Z","completed_at":"2026-08-11T14:50:26.762Z","duration_sec":33209,"std_minutes":300},{"id":"c3ce574f-16e3-4ce2-815e-10a842f608de","job_id":"J02-dc56","name":"Dismantle: Clean up Housing 2ea","order":6,"status":"done","started_at":"2026-08-11T14:50:26.763Z","completed_at":"2026-08-11T15:28:01.298Z","duration_sec":2254,"std_minutes":120},{"id":"b57a5afd-0b62-47a8-a149-df57cdbec92f","job_id":"J02-dc56","name":"Dismantle: Part list &amp; Tear Down","order":7,"status":"done","started_at":"2026-08-11T15:28:01.298Z","completed_at":"2026-08-12T00:05:46.117Z","duration_sec":31064,"std_minutes":240},{"id":"ef67991d-4f1b-4929-b4b9-3bd70d1c1a8b","job_id":"J02-dc56","name":"Assemble: Directional &amp; Idler gear","order":8,"status":"done","started_at":"2026-08-12T00:05:46.117Z","completed_at":"2026-08-12T03:47:41.223Z","duration_sec":13315,"std_minutes":600},{"id":"19689610-ed31-4c36-959c-6233ef31d9cc","job_id":"J02-dc56","name":"Assemble: Planetary GP","order":9,"status":"done","started_at":"2026-08-12T03:47:41.223Z","completed_at":"2026-08-12T09:25:37.962Z","duration_sec":20276,"std_minutes":600},{"id":"572f712a-0376-495f-a98f-9ee71ead12b3","job_id":"J02-dc56","name":"Assemble: CV 2EA","order":10,"status":"done","started_at":"2026-08-12T09:25:37.962Z","completed_at":"2026-08-13T03:13:58.520Z","duration_sec":64100,"std_minutes":300},{"id":"033a6b1b-8daf-46cc-a1e1-292ad2451d5f","job_id":"J02-dc56","name":"Assemble: Pump, Lines, &amp; Screen","order":11,"status":"in_progress","started_at":"2026-08-13T11:13:08.442Z","completed_at":"","duration_sec":28736,"std_minutes":300},{"id":"f52cc000-4714-474d-a6c4-a3f41408fbb7","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Set up","order":12,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"a9b889d6-b2f7-4421-a27a-fcd6a2fde9f9","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Test","order":13,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"3edd89d2-41a4-4856-976b-cbc716dc3788","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Release","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"4d87b720-179e-4dbd-bf95-3d44c356f29e","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300}],"assignees":[{"id":"e39218a1-186b-46ca-b35a-d999eac3307c","job_id":"J02-dc56","technician_id":"T-37cadb58","assigned_at":"2026-08-11T14:56:11.247Z","is_lead":"1"},{"id":"56cff857-6f11-4d4f-889c-272de87907ef","job_id":"J02-dc56","technician_id":"T-e4a06545","assigned_at":"2026-08-11T14:56:11.247Z","is_lead":"0"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-37cadb58","status":"busy","current_job_id":"J02-dc56"},{"id":"T-e4a06545","status":"busy","current_job_id":"J02-dc56"}]}</t>
+  </si>
+  <si>
+    <t>c545076b-108f-44bd-b1da-d5926441f392</t>
+  </si>
+  <si>
+    <t>2026-08-13T11:59:07.351Z</t>
+  </si>
+  <si>
+    <t>{"job":{"id":"J02-dc56","title":"Recondition Transmission 16H,G","unit":"E448 — D10T","unit_id":"a5c2144b-1b29-40f7-9b5c-cfbbc03c3387","description":"Job recondition Transmission 16H,G (time frame standar).","status":"in_progress","technician_id":"T-37cadb58","template_id":"ne-transmission-16h-g","created_at":"2026-08-09T14:29:20.672Z","started_at":"2026-08-09T15:02:48.075Z","completed_at":"","paused_at":"","total_paused_sec":94,"estimated_minutes":5340},"steps":[{"id":"91804ed8-5ad4-4ffd-aaad-beba64eb9cb2","job_id":"J02-dc56","name":"Dismantle: Washing Transmission gp","order":1,"status":"done","started_at":"2026-08-09T15:02:48.075Z","completed_at":"2026-08-09T15:20:47.571Z","duration_sec":1079,"std_minutes":240},{"id":"a127f857-f092-4b21-b197-3e3c8a02d549","job_id":"J02-dc56","name":"Dismantle: Control Valve 2EA","order":2,"status":"done","started_at":"2026-08-10T01:30:25.210Z","completed_at":"2026-08-10T01:30:32.748Z","duration_sec":36495,"std_minutes":300},{"id":"3bc8becf-2b5e-4391-8c9f-619d63d7281c","job_id":"J02-dc56","name":"Dismantle: Pump, Lines, &amp; Screen","order":3,"status":"done","started_at":"2026-08-10T01:30:32.748Z","completed_at":"2026-08-10T08:27:37.616Z","duration_sec":25024,"std_minutes":240},{"id":"bacf6ce8-8a97-4831-9f38-3010f4d64a9a","job_id":"J02-dc56","name":"Dismantle: Planetary GP","order":4,"status":"done","started_at":"2026-08-10T08:27:37.616Z","completed_at":"2026-08-11T05:36:57.526Z","duration_sec":76159,"std_minutes":900},{"id":"74bc5c28-b84c-4cfa-b429-25198c968f30","job_id":"J02-dc56","name":"Dismantle: Directional &amp; Idler gear","order":5,"status":"done","started_at":"2026-08-11T05:36:57.526Z","completed_at":"2026-08-11T14:50:26.762Z","duration_sec":33209,"std_minutes":300},{"id":"c3ce574f-16e3-4ce2-815e-10a842f608de","job_id":"J02-dc56","name":"Dismantle: Clean up Housing 2ea","order":6,"status":"done","started_at":"2026-08-11T14:50:26.763Z","completed_at":"2026-08-11T15:28:01.298Z","duration_sec":2254,"std_minutes":120},{"id":"b57a5afd-0b62-47a8-a149-df57cdbec92f","job_id":"J02-dc56","name":"Dismantle: Part list &amp; Tear Down","order":7,"status":"done","started_at":"2026-08-11T15:28:01.298Z","completed_at":"2026-08-12T00:05:46.117Z","duration_sec":31064,"std_minutes":240},{"id":"ef67991d-4f1b-4929-b4b9-3bd70d1c1a8b","job_id":"J02-dc56","name":"Assemble: Directional &amp; Idler gear","order":8,"status":"done","started_at":"2026-08-12T00:05:46.117Z","completed_at":"2026-08-12T03:47:41.223Z","duration_sec":13315,"std_minutes":600},{"id":"19689610-ed31-4c36-959c-6233ef31d9cc","job_id":"J02-dc56","name":"Assemble: Planetary GP","order":9,"status":"done","started_at":"2026-08-12T03:47:41.223Z","completed_at":"2026-08-12T09:25:37.962Z","duration_sec":20276,"std_minutes":600},{"id":"572f712a-0376-495f-a98f-9ee71ead12b3","job_id":"J02-dc56","name":"Assemble: CV 2EA","order":10,"status":"done","started_at":"2026-08-12T09:25:37.962Z","completed_at":"2026-08-13T03:13:58.520Z","duration_sec":64100,"std_minutes":300},{"id":"033a6b1b-8daf-46cc-a1e1-292ad2451d5f","job_id":"J02-dc56","name":"Assemble: Pump, Lines, &amp; Screen","order":11,"status":"in_progress","started_at":"2026-08-13T11:13:08.442Z","completed_at":"","duration_sec":28736,"std_minutes":300},{"id":"f52cc000-4714-474d-a6c4-a3f41408fbb7","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Set up","order":12,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"a9b889d6-b2f7-4421-a27a-fcd6a2fde9f9","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Test","order":13,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"3edd89d2-41a4-4856-976b-cbc716dc3788","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Release","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"4d87b720-179e-4dbd-bf95-3d44c356f29e","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300}],"assignees":[{"id":"807d403b-7225-4728-9297-8411e1a7b87a","job_id":"J02-dc56","technician_id":"T-37cadb58","assigned_at":"2026-08-13T11:59:07.300Z","is_lead":"1"},{"id":"48b8ecbd-f351-4775-8a9e-02e76692d919","job_id":"J02-dc56","technician_id":"T-e4a06545","assigned_at":"2026-08-13T11:59:07.300Z","is_lead":"0"},{"id":"31170e28-57e5-4fee-825a-bde2b4f6e4d1","job_id":"J02-dc56","technician_id":"T-d32c7e65","assigned_at":"2026-08-13T11:59:07.300Z","is_lead":"0"},{"id":"dbdf3fae-bfda-48fe-a926-ec835948b663","job_id":"J02-dc56","technician_id":"T-d6375327","assigned_at":"2026-08-13T11:59:07.300Z","is_lead":"0"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-37cadb58","status":"busy","current_job_id":"J02-dc56"},{"id":"T-e4a06545","status":"busy","current_job_id":"J02-dc56"},{"id":"T-d32c7e65","status":"busy","current_job_id":"J02-dc56"},{"id":"T-d6375327","status":"busy","current_job_id":"J02-dc56"}]}</t>
+  </si>
+  <si>
+    <t>311bc47d-2ae6-4718-b8d4-caa195f16340</t>
+  </si>
+  <si>
+    <t>2026-08-13T11:59:07.817Z</t>
+  </si>
+  <si>
+    <t>{"job":{"id":"J02-dc56","title":"Recondition Transmission 16H,G","unit":"E448 — D10T","unit_id":"a5c2144b-1b29-40f7-9b5c-cfbbc03c3387","description":"Job recondition Transmission 16H,G (time frame standar).","status":"in_progress","technician_id":"T-37cadb58","template_id":"ne-transmission-16h-g","created_at":"2026-08-09T14:29:20.672Z","started_at":"2026-08-09T15:02:48.075Z","completed_at":"","paused_at":"","total_paused_sec":94,"estimated_minutes":5340},"steps":[{"id":"91804ed8-5ad4-4ffd-aaad-beba64eb9cb2","job_id":"J02-dc56","name":"Dismantle: Washing Transmission gp","order":1,"status":"done","started_at":"2026-08-09T15:02:48.075Z","completed_at":"2026-08-09T15:20:47.571Z","duration_sec":1079,"std_minutes":240},{"id":"a127f857-f092-4b21-b197-3e3c8a02d549","job_id":"J02-dc56","name":"Dismantle: Control Valve 2EA","order":2,"status":"done","started_at":"2026-08-10T01:30:25.210Z","completed_at":"2026-08-10T01:30:32.748Z","duration_sec":36495,"std_minutes":300},{"id":"3bc8becf-2b5e-4391-8c9f-619d63d7281c","job_id":"J02-dc56","name":"Dismantle: Pump, Lines, &amp; Screen","order":3,"status":"done","started_at":"2026-08-10T01:30:32.748Z","completed_at":"2026-08-10T08:27:37.616Z","duration_sec":25024,"std_minutes":240},{"id":"bacf6ce8-8a97-4831-9f38-3010f4d64a9a","job_id":"J02-dc56","name":"Dismantle: Planetary GP","order":4,"status":"done","started_at":"2026-08-10T08:27:37.616Z","completed_at":"2026-08-11T05:36:57.526Z","duration_sec":76159,"std_minutes":900},{"id":"74bc5c28-b84c-4cfa-b429-25198c968f30","job_id":"J02-dc56","name":"Dismantle: Directional &amp; Idler gear","order":5,"status":"done","started_at":"2026-08-11T05:36:57.526Z","completed_at":"2026-08-11T14:50:26.762Z","duration_sec":33209,"std_minutes":300},{"id":"c3ce574f-16e3-4ce2-815e-10a842f608de","job_id":"J02-dc56","name":"Dismantle: Clean up Housing 2ea","order":6,"status":"done","started_at":"2026-08-11T14:50:26.763Z","completed_at":"2026-08-11T15:28:01.298Z","duration_sec":2254,"std_minutes":120},{"id":"b57a5afd-0b62-47a8-a149-df57cdbec92f","job_id":"J02-dc56","name":"Dismantle: Part list &amp; Tear Down","order":7,"status":"done","started_at":"2026-08-11T15:28:01.298Z","completed_at":"2026-08-12T00:05:46.117Z","duration_sec":31064,"std_minutes":240},{"id":"ef67991d-4f1b-4929-b4b9-3bd70d1c1a8b","job_id":"J02-dc56","name":"Assemble: Directional &amp; Idler gear","order":8,"status":"done","started_at":"2026-08-12T00:05:46.117Z","completed_at":"2026-08-12T03:47:41.223Z","duration_sec":13315,"std_minutes":600},{"id":"19689610-ed31-4c36-959c-6233ef31d9cc","job_id":"J02-dc56","name":"Assemble: Planetary GP","order":9,"status":"done","started_at":"2026-08-12T03:47:41.223Z","completed_at":"2026-08-12T09:25:37.962Z","duration_sec":20276,"std_minutes":600},{"id":"572f712a-0376-495f-a98f-9ee71ead12b3","job_id":"J02-dc56","name":"Assemble: CV 2EA","order":10,"status":"done","started_at":"2026-08-12T09:25:37.962Z","completed_at":"2026-08-13T03:13:58.520Z","duration_sec":64100,"std_minutes":300},{"id":"033a6b1b-8daf-46cc-a1e1-292ad2451d5f","job_id":"J02-dc56","name":"Assemble: Pump, Lines, &amp; Screen","order":11,"status":"in_progress","started_at":"2026-08-13T11:13:08.442Z","completed_at":"","duration_sec":28736,"std_minutes":300},{"id":"f52cc000-4714-474d-a6c4-a3f41408fbb7","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Set up","order":12,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"a9b889d6-b2f7-4421-a27a-fcd6a2fde9f9","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Test","order":13,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"3edd89d2-41a4-4856-976b-cbc716dc3788","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Release","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"4d87b720-179e-4dbd-bf95-3d44c356f29e","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300}],"assignees":[{"id":"d2b36c98-f910-4833-af11-5d3d51619ece","job_id":"J02-dc56","technician_id":"T-37cadb58","assigned_at":"2026-08-13T11:59:07.784Z","is_lead":"1"},{"id":"7b49e353-ba78-4d75-8514-489b128b1f03","job_id":"J02-dc56","technician_id":"T-e4a06545","assigned_at":"2026-08-13T11:59:07.784Z","is_lead":"0"},{"id":"b576d662-f2ff-48ce-ae67-ffd489aa3d6a","job_id":"J02-dc56","technician_id":"T-d32c7e65","assigned_at":"2026-08-13T11:59:07.784Z","is_lead":"0"},{"id":"efd7a7fe-13ab-4f0b-8e1d-477e0fd9d726","job_id":"J02-dc56","technician_id":"T-d6375327","assigned_at":"2026-08-13T11:59:07.784Z","is_lead":"0"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-37cadb58","status":"busy","current_job_id":"J02-dc56"},{"id":"T-e4a06545","status":"busy","current_job_id":"J02-dc56"},{"id":"T-d32c7e65","status":"busy","current_job_id":"J02-dc56"},{"id":"T-d6375327","status":"busy","current_job_id":"J02-dc56"}]}</t>
+  </si>
+  <si>
+    <t>18d924ec-14cd-425a-94dd-11e5f170ed51</t>
+  </si>
+  <si>
+    <t>2026-08-13T11:59:31.386Z</t>
+  </si>
+  <si>
+    <t>{"job":{"id":"J02-dc56","title":"Recondition Transmission 16H,G","unit":"E448 — D10T","unit_id":"a5c2144b-1b29-40f7-9b5c-cfbbc03c3387","description":"Job recondition Transmission 16H,G (time frame standar).","status":"in_progress","technician_id":"T-37cadb58","template_id":"ne-transmission-16h-g","created_at":"2026-08-09T14:29:20.672Z","started_at":"2026-08-09T15:02:48.075Z","completed_at":"","paused_at":"","total_paused_sec":94,"estimated_minutes":5340},"steps":[{"id":"91804ed8-5ad4-4ffd-aaad-beba64eb9cb2","job_id":"J02-dc56","name":"Dismantle: Washing Transmission gp","order":1,"status":"done","started_at":"2026-08-09T15:02:48.075Z","completed_at":"2026-08-09T15:20:47.571Z","duration_sec":1079,"std_minutes":240},{"id":"a127f857-f092-4b21-b197-3e3c8a02d549","job_id":"J02-dc56","name":"Dismantle: Control Valve 2EA","order":2,"status":"done","started_at":"2026-08-10T01:30:25.210Z","completed_at":"2026-08-10T01:30:32.748Z","duration_sec":36495,"std_minutes":300},{"id":"3bc8becf-2b5e-4391-8c9f-619d63d7281c","job_id":"J02-dc56","name":"Dismantle: Pump, Lines, &amp; Screen","order":3,"status":"done","started_at":"2026-08-10T01:30:32.748Z","completed_at":"2026-08-10T08:27:37.616Z","duration_sec":25024,"std_minutes":240},{"id":"bacf6ce8-8a97-4831-9f38-3010f4d64a9a","job_id":"J02-dc56","name":"Dismantle: Planetary GP","order":4,"status":"done","started_at":"2026-08-10T08:27:37.616Z","completed_at":"2026-08-11T05:36:57.526Z","duration_sec":76159,"std_minutes":900},{"id":"74bc5c28-b84c-4cfa-b429-25198c968f30","job_id":"J02-dc56","name":"Dismantle: Directional &amp; Idler gear","order":5,"status":"done","started_at":"2026-08-11T05:36:57.526Z","completed_at":"2026-08-11T14:50:26.762Z","duration_sec":33209,"std_minutes":300},{"id":"c3ce574f-16e3-4ce2-815e-10a842f608de","job_id":"J02-dc56","name":"Dismantle: Clean up Housing 2ea","order":6,"status":"done","started_at":"2026-08-11T14:50:26.763Z","completed_at":"2026-08-11T15:28:01.298Z","duration_sec":2254,"std_minutes":120},{"id":"b57a5afd-0b62-47a8-a149-df57cdbec92f","job_id":"J02-dc56","name":"Dismantle: Part list &amp; Tear Down","order":7,"status":"done","started_at":"2026-08-11T15:28:01.298Z","completed_at":"2026-08-12T00:05:46.117Z","duration_sec":31064,"std_minutes":240},{"id":"ef67991d-4f1b-4929-b4b9-3bd70d1c1a8b","job_id":"J02-dc56","name":"Assemble: Directional &amp; Idler gear","order":8,"status":"done","started_at":"2026-08-12T00:05:46.117Z","completed_at":"2026-08-12T03:47:41.223Z","duration_sec":13315,"std_minutes":600},{"id":"19689610-ed31-4c36-959c-6233ef31d9cc","job_id":"J02-dc56","name":"Assemble: Planetary GP","order":9,"status":"done","started_at":"2026-08-12T03:47:41.223Z","completed_at":"2026-08-12T09:25:37.962Z","duration_sec":20276,"std_minutes":600},{"id":"572f712a-0376-495f-a98f-9ee71ead12b3","job_id":"J02-dc56","name":"Assemble: CV 2EA","order":10,"status":"done","started_at":"2026-08-12T09:25:37.962Z","completed_at":"2026-08-13T03:13:58.520Z","duration_sec":64100,"std_minutes":300},{"id":"033a6b1b-8daf-46cc-a1e1-292ad2451d5f","job_id":"J02-dc56","name":"Assemble: Pump, Lines, &amp; Screen","order":11,"status":"in_progress","started_at":"2026-08-13T11:13:08.442Z","completed_at":"","duration_sec":28736,"std_minutes":300},{"id":"f52cc000-4714-474d-a6c4-a3f41408fbb7","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Set up","order":12,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"a9b889d6-b2f7-4421-a27a-fcd6a2fde9f9","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Test","order":13,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"3edd89d2-41a4-4856-976b-cbc716dc3788","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Release","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"4d87b720-179e-4dbd-bf95-3d44c356f29e","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300}],"assignees":[{"id":"af60aef2-03e8-45ce-b903-4a262fc9a44d","job_id":"J02-dc56","technician_id":"T-37cadb58","assigned_at":"2026-08-13T11:59:31.336Z","is_lead":"1"},{"id":"379e760d-855f-4581-b3cd-0150eb021108","job_id":"J02-dc56","technician_id":"T-e4a06545","assigned_at":"2026-08-13T11:59:31.336Z","is_lead":"0"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-37cadb58","status":"busy","current_job_id":"J02-dc56"},{"id":"T-e4a06545","status":"busy","current_job_id":"J02-dc56"}]}</t>
+  </si>
+  <si>
+    <t>35aebcb3-2c21-43a2-9f91-9b6a301ac088</t>
+  </si>
+  <si>
+    <t>2026-08-13T12:00:53.645Z</t>
+  </si>
+  <si>
+    <t>{"job":{"id":"J02-dc56","title":"Recondition Transmission 16H,G","unit":"E448 — D10T","unit_id":"a5c2144b-1b29-40f7-9b5c-cfbbc03c3387","description":"Job recondition Transmission 16H,G (time frame standar).","status":"in_progress","technician_id":"T-37cadb58","template_id":"ne-transmission-16h-g","created_at":"2026-08-09T14:29:20.672Z","started_at":"2026-08-09T15:02:48.075Z","completed_at":"","paused_at":"","total_paused_sec":94,"estimated_minutes":5340},"steps":[{"id":"91804ed8-5ad4-4ffd-aaad-beba64eb9cb2","job_id":"J02-dc56","name":"Dismantle: Washing Transmission gp","order":1,"status":"done","started_at":"2026-08-09T15:02:48.075Z","completed_at":"2026-08-09T15:20:47.571Z","duration_sec":1079,"std_minutes":240},{"id":"a127f857-f092-4b21-b197-3e3c8a02d549","job_id":"J02-dc56","name":"Dismantle: Control Valve 2EA","order":2,"status":"done","started_at":"2026-08-10T01:30:25.210Z","completed_at":"2026-08-10T01:30:32.748Z","duration_sec":36495,"std_minutes":300},{"id":"3bc8becf-2b5e-4391-8c9f-619d63d7281c","job_id":"J02-dc56","name":"Dismantle: Pump, Lines, &amp; Screen","order":3,"status":"done","started_at":"2026-08-10T01:30:32.748Z","completed_at":"2026-08-10T08:27:37.616Z","duration_sec":25024,"std_minutes":240},{"id":"bacf6ce8-8a97-4831-9f38-3010f4d64a9a","job_id":"J02-dc56","name":"Dismantle: Planetary GP","order":4,"status":"done","started_at":"2026-08-10T08:27:37.616Z","completed_at":"2026-08-11T05:36:57.526Z","duration_sec":76159,"std_minutes":900},{"id":"74bc5c28-b84c-4cfa-b429-25198c968f30","job_id":"J02-dc56","name":"Dismantle: Directional &amp; Idler gear","order":5,"status":"done","started_at":"2026-08-11T05:36:57.526Z","completed_at":"2026-08-11T14:50:26.762Z","duration_sec":33209,"std_minutes":300},{"id":"c3ce574f-16e3-4ce2-815e-10a842f608de","job_id":"J02-dc56","name":"Dismantle: Clean up Housing 2ea","order":6,"status":"done","started_at":"2026-08-11T14:50:26.763Z","completed_at":"2026-08-11T15:28:01.298Z","duration_sec":2254,"std_minutes":120},{"id":"b57a5afd-0b62-47a8-a149-df57cdbec92f","job_id":"J02-dc56","name":"Dismantle: Part list &amp; Tear Down","order":7,"status":"done","started_at":"2026-08-11T15:28:01.298Z","completed_at":"2026-08-12T00:05:46.117Z","duration_sec":31064,"std_minutes":240},{"id":"ef67991d-4f1b-4929-b4b9-3bd70d1c1a8b","job_id":"J02-dc56","name":"Assemble: Directional &amp; Idler gear","order":8,"status":"done","started_at":"2026-08-12T00:05:46.117Z","completed_at":"2026-08-12T03:47:41.223Z","duration_sec":13315,"std_minutes":600},{"id":"19689610-ed31-4c36-959c-6233ef31d9cc","job_id":"J02-dc56","name":"Assemble: Planetary GP","order":9,"status":"done","started_at":"2026-08-12T03:47:41.223Z","completed_at":"2026-08-12T09:25:37.962Z","duration_sec":20276,"std_minutes":600},{"id":"572f712a-0376-495f-a98f-9ee71ead12b3","job_id":"J02-dc56","name":"Assemble: CV 2EA","order":10,"status":"done","started_at":"2026-08-12T09:25:37.962Z","completed_at":"2026-08-13T03:13:58.520Z","duration_sec":64100,"std_minutes":300},{"id":"033a6b1b-8daf-46cc-a1e1-292ad2451d5f","job_id":"J02-dc56","name":"Assemble: Pump, Lines, &amp; Screen","order":11,"status":"in_progress","started_at":"2026-08-13T11:13:08.442Z","completed_at":"","duration_sec":28736,"std_minutes":300},{"id":"f52cc000-4714-474d-a6c4-a3f41408fbb7","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Set up","order":12,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"a9b889d6-b2f7-4421-a27a-fcd6a2fde9f9","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Test","order":13,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"3edd89d2-41a4-4856-976b-cbc716dc3788","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Release","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"4d87b720-179e-4dbd-bf95-3d44c356f29e","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300}],"assignees":[{"id":"1f5f6d88-234a-4820-9829-8c09dd563f03","job_id":"J02-dc56","technician_id":"T-37cadb58","assigned_at":"2026-08-13T12:00:53.597Z","is_lead":"1"},{"id":"c12465b9-579c-4d48-9722-ef3e29c74786","job_id":"J02-dc56","technician_id":"T-e4a06545","assigned_at":"2026-08-13T12:00:53.597Z","is_lead":"0"},{"id":"72fc4a70-4fe3-4950-b9a8-c9f8dd984ed5","job_id":"J02-dc56","technician_id":"T-d32c7e65","assigned_at":"2026-08-13T12:00:53.597Z","is_lead":"0"},{"id":"7cd80765-921d-4b4c-8ce8-63d9a64950a2","job_id":"J02-dc56","technician_id":"T-3d0a3937","assigned_at":"2026-08-13T12:00:53.597Z","is_lead":"0"},{"id":"e5c9330c-6e82-47d7-afb9-499ee4580d8b","job_id":"J02-dc56","technician_id":"T-d6375327","assigned_at":"2026-08-13T12:00:53.597Z","is_lead":"0"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-37cadb58","status":"busy","current_job_id":"J02-dc56"},{"id":"T-e4a06545","status":"busy","current_job_id":"J02-dc56"},{"id":"T-d32c7e65","status":"busy","current_job_id":"J02-dc56"},{"id":"T-d6375327","status":"busy","current_job_id":"J02-dc56"},{"id":"T-3d0a3937","status":"busy","current_job_id":"J02-dc56"}]}</t>
+  </si>
+  <si>
+    <t>1f0508b1-19e1-4f93-81b6-4940a8a69f4f</t>
+  </si>
+  <si>
+    <t>2026-08-13T12:00:54.348Z</t>
+  </si>
+  <si>
+    <t>{"job":{"id":"J02-dc56","title":"Recondition Transmission 16H,G","unit":"E448 — D10T","unit_id":"a5c2144b-1b29-40f7-9b5c-cfbbc03c3387","description":"Job recondition Transmission 16H,G (time frame standar).","status":"in_progress","technician_id":"T-37cadb58","template_id":"ne-transmission-16h-g","created_at":"2026-08-09T14:29:20.672Z","started_at":"2026-08-09T15:02:48.075Z","completed_at":"","paused_at":"","total_paused_sec":94,"estimated_minutes":5340},"steps":[{"id":"91804ed8-5ad4-4ffd-aaad-beba64eb9cb2","job_id":"J02-dc56","name":"Dismantle: Washing Transmission gp","order":1,"status":"done","started_at":"2026-08-09T15:02:48.075Z","completed_at":"2026-08-09T15:20:47.571Z","duration_sec":1079,"std_minutes":240},{"id":"a127f857-f092-4b21-b197-3e3c8a02d549","job_id":"J02-dc56","name":"Dismantle: Control Valve 2EA","order":2,"status":"done","started_at":"2026-08-10T01:30:25.210Z","completed_at":"2026-08-10T01:30:32.748Z","duration_sec":36495,"std_minutes":300},{"id":"3bc8becf-2b5e-4391-8c9f-619d63d7281c","job_id":"J02-dc56","name":"Dismantle: Pump, Lines, &amp; Screen","order":3,"status":"done","started_at":"2026-08-10T01:30:32.748Z","completed_at":"2026-08-10T08:27:37.616Z","duration_sec":25024,"std_minutes":240},{"id":"bacf6ce8-8a97-4831-9f38-3010f4d64a9a","job_id":"J02-dc56","name":"Dismantle: Planetary GP","order":4,"status":"done","started_at":"2026-08-10T08:27:37.616Z","completed_at":"2026-08-11T05:36:57.526Z","duration_sec":76159,"std_minutes":900},{"id":"74bc5c28-b84c-4cfa-b429-25198c968f30","job_id":"J02-dc56","name":"Dismantle: Directional &amp; Idler gear","order":5,"status":"done","started_at":"2026-08-11T05:36:57.526Z","completed_at":"2026-08-11T14:50:26.762Z","duration_sec":33209,"std_minutes":300},{"id":"c3ce574f-16e3-4ce2-815e-10a842f608de","job_id":"J02-dc56","name":"Dismantle: Clean up Housing 2ea","order":6,"status":"done","started_at":"2026-08-11T14:50:26.763Z","completed_at":"2026-08-11T15:28:01.298Z","duration_sec":2254,"std_minutes":120},{"id":"b57a5afd-0b62-47a8-a149-df57cdbec92f","job_id":"J02-dc56","name":"Dismantle: Part list &amp; Tear Down","order":7,"status":"done","started_at":"2026-08-11T15:28:01.298Z","completed_at":"2026-08-12T00:05:46.117Z","duration_sec":31064,"std_minutes":240},{"id":"ef67991d-4f1b-4929-b4b9-3bd70d1c1a8b","job_id":"J02-dc56","name":"Assemble: Directional &amp; Idler gear","order":8,"status":"done","started_at":"2026-08-12T00:05:46.117Z","completed_at":"2026-08-12T03:47:41.223Z","duration_sec":13315,"std_minutes":600},{"id":"19689610-ed31-4c36-959c-6233ef31d9cc","job_id":"J02-dc56","name":"Assemble: Planetary GP","order":9,"status":"done","started_at":"2026-08-12T03:47:41.223Z","completed_at":"2026-08-12T09:25:37.962Z","duration_sec":20276,"std_minutes":600},{"id":"572f712a-0376-495f-a98f-9ee71ead12b3","job_id":"J02-dc56","name":"Assemble: CV 2EA","order":10,"status":"done","started_at":"2026-08-12T09:25:37.962Z","completed_at":"2026-08-13T03:13:58.520Z","duration_sec":64100,"std_minutes":300},{"id":"033a6b1b-8daf-46cc-a1e1-292ad2451d5f","job_id":"J02-dc56","name":"Assemble: Pump, Lines, &amp; Screen","order":11,"status":"done","started_at":"2026-08-13T11:13:08.442Z","completed_at":"2026-08-13T12:00:54.248Z","duration_sec":31601,"std_minutes":300},{"id":"f52cc000-4714-474d-a6c4-a3f41408fbb7","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Set up","order":12,"status":"in_progress","started_at":"2026-08-13T12:00:54.248Z","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"a9b889d6-b2f7-4421-a27a-fcd6a2fde9f9","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Test","order":13,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"3edd89d2-41a4-4856-976b-cbc716dc3788","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Release","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"4d87b720-179e-4dbd-bf95-3d44c356f29e","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300}],"assignees":[{"id":"1f5f6d88-234a-4820-9829-8c09dd563f03","job_id":"J02-dc56","technician_id":"T-37cadb58","assigned_at":"2026-08-13T12:00:53.597Z","is_lead":"1"},{"id":"c12465b9-579c-4d48-9722-ef3e29c74786","job_id":"J02-dc56","technician_id":"T-e4a06545","assigned_at":"2026-08-13T12:00:53.597Z","is_lead":"0"},{"id":"72fc4a70-4fe3-4950-b9a8-c9f8dd984ed5","job_id":"J02-dc56","technician_id":"T-d32c7e65","assigned_at":"2026-08-13T12:00:53.597Z","is_lead":"0"},{"id":"7cd80765-921d-4b4c-8ce8-63d9a64950a2","job_id":"J02-dc56","technician_id":"T-3d0a3937","assigned_at":"2026-08-13T12:00:53.597Z","is_lead":"0"},{"id":"e5c9330c-6e82-47d7-afb9-499ee4580d8b","job_id":"J02-dc56","technician_id":"T-d6375327","assigned_at":"2026-08-13T12:00:53.597Z","is_lead":"0"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-37cadb58","status":"busy","current_job_id":"J02-dc56"},{"id":"T-e4a06545","status":"busy","current_job_id":"J02-dc56"},{"id":"T-d32c7e65","status":"busy","current_job_id":"J02-dc56"},{"id":"T-d6375327","status":"busy","current_job_id":"J02-dc56"},{"id":"T-3d0a3937","status":"busy","current_job_id":"J02-dc56"}]}</t>
+  </si>
+  <si>
+    <t>4a0c1d62-9a61-4366-9e37-9b9500330303</t>
+  </si>
+  <si>
+    <t>2026-08-13T12:00:54.943Z</t>
+  </si>
+  <si>
+    <t>{"job":{"id":"J02-dc56","title":"Recondition Transmission 16H,G","unit":"E448 — D10T","unit_id":"a5c2144b-1b29-40f7-9b5c-cfbbc03c3387","description":"Job recondition Transmission 16H,G (time frame standar).","status":"in_progress","technician_id":"T-37cadb58","template_id":"ne-transmission-16h-g","created_at":"2026-08-09T14:29:20.672Z","started_at":"2026-08-09T15:02:48.075Z","completed_at":"","paused_at":"","total_paused_sec":94,"estimated_minutes":5340},"steps":[{"id":"91804ed8-5ad4-4ffd-aaad-beba64eb9cb2","job_id":"J02-dc56","name":"Dismantle: Washing Transmission gp","order":1,"status":"done","started_at":"2026-08-09T15:02:48.075Z","completed_at":"2026-08-09T15:20:47.571Z","duration_sec":1079,"std_minutes":240},{"id":"a127f857-f092-4b21-b197-3e3c8a02d549","job_id":"J02-dc56","name":"Dismantle: Control Valve 2EA","order":2,"status":"done","started_at":"2026-08-10T01:30:25.210Z","completed_at":"2026-08-10T01:30:32.748Z","duration_sec":36495,"std_minutes":300},{"id":"3bc8becf-2b5e-4391-8c9f-619d63d7281c","job_id":"J02-dc56","name":"Dismantle: Pump, Lines, &amp; Screen","order":3,"status":"done","started_at":"2026-08-10T01:30:32.748Z","completed_at":"2026-08-10T08:27:37.616Z","duration_sec":25024,"std_minutes":240},{"id":"bacf6ce8-8a97-4831-9f38-3010f4d64a9a","job_id":"J02-dc56","name":"Dismantle: Planetary GP","order":4,"status":"done","started_at":"2026-08-10T08:27:37.616Z","completed_at":"2026-08-11T05:36:57.526Z","duration_sec":76159,"std_minutes":900},{"id":"74bc5c28-b84c-4cfa-b429-25198c968f30","job_id":"J02-dc56","name":"Dismantle: Directional &amp; Idler gear","order":5,"status":"done","started_at":"2026-08-11T05:36:57.526Z","completed_at":"2026-08-11T14:50:26.762Z","duration_sec":33209,"std_minutes":300},{"id":"c3ce574f-16e3-4ce2-815e-10a842f608de","job_id":"J02-dc56","name":"Dismantle: Clean up Housing 2ea","order":6,"status":"done","started_at":"2026-08-11T14:50:26.763Z","completed_at":"2026-08-11T15:28:01.298Z","duration_sec":2254,"std_minutes":120},{"id":"b57a5afd-0b62-47a8-a149-df57cdbec92f","job_id":"J02-dc56","name":"Dismantle: Part list &amp; Tear Down","order":7,"status":"done","started_at":"2026-08-11T15:28:01.298Z","completed_at":"2026-08-12T00:05:46.117Z","duration_sec":31064,"std_minutes":240},{"id":"ef67991d-4f1b-4929-b4b9-3bd70d1c1a8b","job_id":"J02-dc56","name":"Assemble: Directional &amp; Idler gear","order":8,"status":"done","started_at":"2026-08-12T00:05:46.117Z","completed_at":"2026-08-12T03:47:41.223Z","duration_sec":13315,"std_minutes":600},{"id":"19689610-ed31-4c36-959c-6233ef31d9cc","job_id":"J02-dc56","name":"Assemble: Planetary GP","order":9,"status":"done","started_at":"2026-08-12T03:47:41.223Z","completed_at":"2026-08-12T09:25:37.962Z","duration_sec":20276,"std_minutes":600},{"id":"572f712a-0376-495f-a98f-9ee71ead12b3","job_id":"J02-dc56","name":"Assemble: CV 2EA","order":10,"status":"done","started_at":"2026-08-12T09:25:37.962Z","completed_at":"2026-08-13T03:13:58.520Z","duration_sec":64100,"std_minutes":300},{"id":"033a6b1b-8daf-46cc-a1e1-292ad2451d5f","job_id":"J02-dc56","name":"Assemble: Pump, Lines, &amp; Screen","order":11,"status":"done","started_at":"2026-08-13T11:13:08.442Z","completed_at":"2026-08-13T12:00:54.248Z","duration_sec":31601,"std_minutes":300},{"id":"f52cc000-4714-474d-a6c4-a3f41408fbb7","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Set up","order":12,"status":"done","started_at":"2026-08-13T12:00:54.248Z","completed_at":"2026-08-13T12:00:54.894Z","duration_sec":0,"std_minutes":300},{"id":"a9b889d6-b2f7-4421-a27a-fcd6a2fde9f9","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Test","order":13,"status":"in_progress","started_at":"2026-08-13T12:00:54.894Z","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"3edd89d2-41a4-4856-976b-cbc716dc3788","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Release","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"4d87b720-179e-4dbd-bf95-3d44c356f29e","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300}],"assignees":[{"id":"1f5f6d88-234a-4820-9829-8c09dd563f03","job_id":"J02-dc56","technician_id":"T-37cadb58","assigned_at":"2026-08-13T12:00:53.597Z","is_lead":"1"},{"id":"c12465b9-579c-4d48-9722-ef3e29c74786","job_id":"J02-dc56","technician_id":"T-e4a06545","assigned_at":"2026-08-13T12:00:53.597Z","is_lead":"0"},{"id":"72fc4a70-4fe3-4950-b9a8-c9f8dd984ed5","job_id":"J02-dc56","technician_id":"T-d32c7e65","assigned_at":"2026-08-13T12:00:53.597Z","is_lead":"0"},{"id":"7cd80765-921d-4b4c-8ce8-63d9a64950a2","job_id":"J02-dc56","technician_id":"T-3d0a3937","assigned_at":"2026-08-13T12:00:53.597Z","is_lead":"0"},{"id":"e5c9330c-6e82-47d7-afb9-499ee4580d8b","job_id":"J02-dc56","technician_id":"T-d6375327","assigned_at":"2026-08-13T12:00:53.597Z","is_lead":"0"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-37cadb58","status":"busy","current_job_id":"J02-dc56"},{"id":"T-e4a06545","status":"busy","current_job_id":"J02-dc56"},{"id":"T-d32c7e65","status":"busy","current_job_id":"J02-dc56"},{"id":"T-d6375327","status":"busy","current_job_id":"J02-dc56"},{"id":"T-3d0a3937","status":"busy","current_job_id":"J02-dc56"}]}</t>
+  </si>
+  <si>
+    <t>8eb7dcfb-baa7-41fc-bd0c-01e73139cc4b</t>
+  </si>
+  <si>
+    <t>2026-08-13T12:03:07.744Z</t>
+  </si>
+  <si>
+    <t>{"job":{"id":"J03-c0e2","title":"Recondition Transmission D10T,R","unit":"E448 — D10T","unit_id":"a5c2144b-1b29-40f7-9b5c-cfbbc03c3387","description":"Job recondition Transmission D10T,R (time frame standar).","status":"in_progress","technician_id":"T-533ca22c","template_id":"ne-transmission-d10t-r","created_at":"2026-08-10T08:22:13.799Z","started_at":"2026-08-10T08:23:20.053Z","completed_at":"","paused_at":"","total_paused_sec":3,"estimated_minutes":5820},"steps":[{"id":"7609ebf3-f1eb-4d9d-9591-f21d853034e1","job_id":"J03-c0e2","name":"Dismantle: Washing Transmission","order":1,"status":"done","started_at":"2026-08-10T08:23:20.053Z","completed_at":"2026-08-10T08:24:03.692Z","duration_sec":43,"std_minutes":60},{"id":"a3923555-21a4-4b60-9959-c48d814bf136","job_id":"J03-c0e2","name":"Dismantle: Trans Gear","order":2,"status":"done","started_at":"2026-08-10T08:23:32.872Z","completed_at":"2026-08-10T08:24:06.672Z","duration_sec":33,"std_minutes":600},{"id":"39c70957-da00-4dc8-a988-36ee41ef9841","job_id":"J03-c0e2","name":"Dismantle: CV, Harness, &amp; Sensor","order":3,"status":"done","started_at":"2026-08-10T08:24:08.700Z","completed_at":"2026-08-10T08:24:14.772Z","duration_sec":6,"std_minutes":300},{"id":"6feb4f63-8277-4c8a-a4cf-8d8a3d660682","job_id":"J03-c0e2","name":"Dismantle: Clutch 5","order":4,"status":"done","started_at":"2026-08-10T08:23:32.872Z","completed_at":"2026-08-10T08:24:08.700Z","duration_sec":35,"std_minutes":180},{"id":"179574f5-b3d7-43e4-a065-977ebd015bfc","job_id":"J03-c0e2","name":"Dismantle: Clutch 4","order":5,"status":"done","started_at":"2026-08-10T08:24:14.772Z","completed_at":"2026-08-10T10:10:28.558Z","duration_sec":6373,"std_minutes":180},{"id":"8aff0e07-0f40-4945-a9dc-7a8867ffccf4","job_id":"J03-c0e2","name":"Dismantle: Clutch 3","order":6,"status":"done","started_at":"2026-08-11T05:33:18.994Z","completed_at":"2026-08-11T05:33:34.800Z","duration_sec":69782,"std_minutes":180},{"id":"82415ef2-23b1-4eb2-b027-a268df0f4189","job_id":"J03-c0e2","name":"Dismantle: Clutch 2","order":7,"status":"done","started_at":"2026-08-11T05:33:34.800Z","completed_at":"2026-08-11T05:33:47.115Z","duration_sec":12,"std_minutes":180},{"id":"f7c8bcdc-e2d1-4856-aea1-f577d25b0550","job_id":"J03-c0e2","name":"Dismantle: Clutch 1","order":8,"status":"done","started_at":"2026-08-11T05:33:47.115Z","completed_at":"2026-08-11T15:28:10.891Z","duration_sec":35663,"std_minutes":180},{"id":"4391d523-f1d0-4922-95fb-d3827a21b813","job_id":"J03-c0e2","name":"Dismantle: Planetary &amp; Shaft","order":9,"status":"done","started_at":"2026-08-11T15:28:10.891Z","completed_at":"2026-08-11T23:53:02.227Z","duration_sec":30291,"std_minutes":300},{"id":"bdcc79ae-9f46-46e2-963d-fd2ba3d40a2e","job_id":"J03-c0e2","name":"Dismantle: Part list &amp; Tear Down","order":10,"status":"done","started_at":"2026-08-11T23:53:02.227Z","completed_at":"2026-08-12T03:13:34.783Z","duration_sec":12032,"std_minutes":240},{"id":"0670c5ee-3df9-46ba-a7e5-790a2591233a","job_id":"J03-c0e2","name":"Assemble: Planetary &amp; Shaft In-Out","order":11,"status":"done","started_at":"2026-08-12T03:13:34.783Z","completed_at":"2026-08-13T12:03:07.679Z","duration_sec":118172,"std_minutes":300},{"id":"7276104d-e8c7-4ea6-aac7-6cd975141c45","job_id":"J03-c0e2","name":"Assemble: Clutch 1","order":12,"status":"in_progress","started_at":"2026-08-13T12:03:07.680Z","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"1781ebaa-7fb0-4896-b642-71d33b8c4878","job_id":"J03-c0e2","name":"Assemble: Clutch 2","order":13,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"5532b99d-a7fd-4b7d-a752-796f7bc5daff","job_id":"J03-c0e2","name":"Assemble: Clutch 3","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"ff0ed73f-27d1-4b0a-a4f2-7818d3cfbc7e","job_id":"J03-c0e2","name":"Assemble: Clutch 4","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"970a35a3-a96b-48b4-9f04-a2b921b013f0","job_id":"J03-c0e2","name":"Assemble: Clutch 5","order":16,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"698b11d9-e1a3-451f-8a47-ccabcc5718c6","job_id":"J03-c0e2","name":"Assemble: CV, Harness &amp; Sensor","order":17,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"0620fee8-23da-434a-85e6-6354dee830d7","job_id":"J03-c0e2","name":"Assemble: Trans Gear","order":18,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":900},{"id":"ca31c8c2-4542-42f7-be4e-86974a63447b","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Set up","order":19,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"ba2d158c-a9f5-4d98-aea1-fd1f7983c4eb","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Test","order":20,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"d2f96316-8f95-487c-a7ee-94ba19ef4354","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Release","order":21,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"050b2cfc-5ea2-4926-b9c1-c7bdfe6bbd49","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":22,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240}],"assignees":[{"id":"5ece1c51-c36b-46e5-a9d2-f9106a729470","job_id":"J03-c0e2","technician_id":"T-533ca22c","assigned_at":"2026-08-10T08:23:08.120Z","is_lead":"1"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-533ca22c","status":"busy","current_job_id":"J03-c0e2"}]}</t>
+  </si>
+  <si>
+    <t>b17baf0f-1f67-497f-af6f-60cd88e78ee8</t>
+  </si>
+  <si>
+    <t>2026-08-13T12:06:24.618Z</t>
+  </si>
+  <si>
+    <t>{"job":{"id":"J02-dc56","title":"Recondition Transmission 16H,G","unit":"E448 — D10T","unit_id":"a5c2144b-1b29-40f7-9b5c-cfbbc03c3387","description":"Job recondition Transmission 16H,G (time frame standar).","status":"in_progress","technician_id":"T-37cadb58","template_id":"ne-transmission-16h-g","created_at":"2026-08-09T14:29:20.672Z","started_at":"2026-08-09T15:02:48.075Z","completed_at":"","paused_at":"","total_paused_sec":94,"estimated_minutes":5340},"steps":[{"id":"91804ed8-5ad4-4ffd-aaad-beba64eb9cb2","job_id":"J02-dc56","name":"Dismantle: Washing Transmission gp","order":1,"status":"done","started_at":"2026-08-09T15:02:48.075Z","completed_at":"2026-08-09T15:20:47.571Z","duration_sec":1079,"std_minutes":240},{"id":"a127f857-f092-4b21-b197-3e3c8a02d549","job_id":"J02-dc56","name":"Dismantle: Control Valve 2EA","order":2,"status":"done","started_at":"2026-08-10T01:30:25.210Z","completed_at":"2026-08-10T01:30:32.748Z","duration_sec":36495,"std_minutes":300},{"id":"3bc8becf-2b5e-4391-8c9f-619d63d7281c","job_id":"J02-dc56","name":"Dismantle: Pump, Lines, &amp; Screen","order":3,"status":"done","started_at":"2026-08-10T01:30:32.748Z","completed_at":"2026-08-10T08:27:37.616Z","duration_sec":25024,"std_minutes":240},{"id":"bacf6ce8-8a97-4831-9f38-3010f4d64a9a","job_id":"J02-dc56","name":"Dismantle: Planetary GP","order":4,"status":"done","started_at":"2026-08-10T08:27:37.616Z","completed_at":"2026-08-11T05:36:57.526Z","duration_sec":76159,"std_minutes":900},{"id":"74bc5c28-b84c-4cfa-b429-25198c968f30","job_id":"J02-dc56","name":"Dismantle: Directional &amp; Idler gear","order":5,"status":"done","started_at":"2026-08-11T05:36:57.526Z","completed_at":"2026-08-11T14:50:26.762Z","duration_sec":33209,"std_minutes":300},{"id":"c3ce574f-16e3-4ce2-815e-10a842f608de","job_id":"J02-dc56","name":"Dismantle: Clean up Housing 2ea","order":6,"status":"done","started_at":"2026-08-11T14:50:26.763Z","completed_at":"2026-08-11T15:28:01.298Z","duration_sec":2254,"std_minutes":120},{"id":"b57a5afd-0b62-47a8-a149-df57cdbec92f","job_id":"J02-dc56","name":"Dismantle: Part list &amp; Tear Down","order":7,"status":"done","started_at":"2026-08-11T15:28:01.298Z","completed_at":"2026-08-12T00:05:46.117Z","duration_sec":31064,"std_minutes":240},{"id":"ef67991d-4f1b-4929-b4b9-3bd70d1c1a8b","job_id":"J02-dc56","name":"Assemble: Directional &amp; Idler gear","order":8,"status":"done","started_at":"2026-08-12T00:05:46.117Z","completed_at":"2026-08-12T03:47:41.223Z","duration_sec":13315,"std_minutes":600},{"id":"19689610-ed31-4c36-959c-6233ef31d9cc","job_id":"J02-dc56","name":"Assemble: Planetary GP","order":9,"status":"done","started_at":"2026-08-12T03:47:41.223Z","completed_at":"2026-08-12T09:25:37.962Z","duration_sec":20276,"std_minutes":600},{"id":"572f712a-0376-495f-a98f-9ee71ead12b3","job_id":"J02-dc56","name":"Assemble: CV 2EA","order":10,"status":"done","started_at":"2026-08-12T09:25:37.962Z","completed_at":"2026-08-13T03:13:58.520Z","duration_sec":64100,"std_minutes":300},{"id":"033a6b1b-8daf-46cc-a1e1-292ad2451d5f","job_id":"J02-dc56","name":"Assemble: Pump, Lines, &amp; Screen","order":11,"status":"done","started_at":"2026-08-13T11:13:08.442Z","completed_at":"2026-08-13T12:00:54.248Z","duration_sec":31601,"std_minutes":300},{"id":"f52cc000-4714-474d-a6c4-a3f41408fbb7","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Set up","order":12,"status":"done","started_at":"2026-08-13T12:00:54.248Z","completed_at":"2026-08-13T12:00:54.894Z","duration_sec":0,"std_minutes":300},{"id":"a9b889d6-b2f7-4421-a27a-fcd6a2fde9f9","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Test","order":13,"status":"in_progress","started_at":"2026-08-13T12:00:54.894Z","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"3edd89d2-41a4-4856-976b-cbc716dc3788","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Release","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"4d87b720-179e-4dbd-bf95-3d44c356f29e","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300}],"assignees":[{"id":"683f5458-078c-4cc6-8d96-56a5a4920650","job_id":"J02-dc56","technician_id":"T-37cadb58","assigned_at":"2026-08-13T12:06:24.563Z","is_lead":"1"},{"id":"17cd8abf-0ccd-4318-a58e-ef6aebec0f43","job_id":"J02-dc56","technician_id":"T-e4a06545","assigned_at":"2026-08-13T12:06:24.563Z","is_lead":"0"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-37cadb58","status":"busy","current_job_id":"J02-dc56"},{"id":"T-e4a06545","status":"busy","current_job_id":"J02-dc56"}]}</t>
+  </si>
+  <si>
+    <t>9977ceeb-e9e7-4aa4-8b1f-2cff971b7c49</t>
+  </si>
+  <si>
+    <t>2026-08-13T12:09:10.741Z</t>
+  </si>
+  <si>
+    <t>{"job":{"id":"J03-1833","title":"Recondition Transmission 16H,G","unit":"E448 — D10T","unit_id":"a5c2144b-1b29-40f7-9b5c-cfbbc03c3387","description":"Job recondition Transmission 16H,G (time frame standar).","status":"in_progress","technician_id":"T-c23ed9a4","template_id":"ne-transmission-16h-g","created_at":"2026-08-11T05:30:21.056Z","started_at":"2026-08-11T05:32:14.074Z","completed_at":"","paused_at":"","total_paused_sec":0,"estimated_minutes":5340},"steps":[{"id":"e21019ab-05cb-4d4f-8f8f-fb85fa9004da","job_id":"J03-1833","name":"Dismantle: Washing Transmission gp","order":1,"status":"done","started_at":"2026-08-11T05:32:14.074Z","completed_at":"2026-08-11T23:52:49.552Z","duration_sec":66035,"std_minutes":240},{"id":"5ceecb87-2473-4297-a2a0-db873217f383","job_id":"J03-1833","name":"Dismantle: Control Valve 2EA","order":2,"status":"done","started_at":"2026-08-11T05:32:33.253Z","completed_at":"2026-08-11T23:52:32.616Z","duration_sec":65999,"std_minutes":300},{"id":"11997f0b-4cc8-4b54-8bdd-db3614b948c1","job_id":"J03-1833","name":"Dismantle: Pump, Lines, &amp; Screen","order":3,"status":"done","started_at":"2026-08-11T05:32:33.253Z","completed_at":"2026-08-11T23:52:51.817Z","duration_sec":66018,"std_minutes":240},{"id":"6c426149-ef7a-48c2-9585-5909fe86eca9","job_id":"J03-1833","name":"Dismantle: Planetary GP","order":4,"status":"done","started_at":"2026-08-11T23:52:51.817Z","completed_at":"2026-08-13T12:08:28.871Z","duration_sec":130537,"std_minutes":900},{"id":"5d3baced-8d6d-491b-9df4-09eaef47f6b9","job_id":"J03-1833","name":"Dismantle: Directional &amp; Idler gear","order":5,"status":"in_progress","started_at":"2026-08-13T12:09:10.701Z","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"0feaac14-da1a-4360-98f3-a99ad7b2fd45","job_id":"J03-1833","name":"Dismantle: Clean up Housing 2ea","order":6,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":120},{"id":"5b00b8bb-18f9-4ef9-ac8c-5d5f25f11170","job_id":"J03-1833","name":"Dismantle: Part list &amp; Tear Down","order":7,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"c536fdc6-3459-4ab5-a588-3454f07f08c7","job_id":"J03-1833","name":"Assemble: Directional &amp; Idler gear","order":8,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"89d1ae15-daf2-4871-9bc0-5940279c96f6","job_id":"J03-1833","name":"Assemble: Planetary GP","order":9,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"1197b5dd-9928-4565-ae50-91f382e2beb0","job_id":"J03-1833","name":"Assemble: CV 2EA","order":10,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"6a936f7e-e97a-47f4-9e03-24e38ef315fc","job_id":"J03-1833","name":"Assemble: Pump, Lines, &amp; Screen","order":11,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"80894723-ea93-40ff-aa35-420c027d3f95","job_id":"J03-1833","name":"Test Bench &amp; Completed: Set up","order":12,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"acf6bd0c-0d96-40b6-8b9e-ee8c27ee1625","job_id":"J03-1833","name":"Test Bench &amp; Completed: Test","order":13,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"81692dde-b76a-433d-9b5d-3476cf3cd7f6","job_id":"J03-1833","name":"Test Bench &amp; Completed: Release","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"b69b87c3-9d4b-450e-8c0e-162eb755ff75","job_id":"J03-1833","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300}],"assignees":[{"id":"a58e3fbd-80eb-4c64-bd6b-bb7196830ed8","job_id":"J03-1833","technician_id":"T-c23ed9a4","assigned_at":"2026-08-11T05:31:58.767Z","is_lead":"1"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-c23ed9a4","status":"busy","current_job_id":"J03-1833"}]}</t>
+  </si>
+  <si>
+    <t>2bf3c5a6-5a3b-403f-bce9-aaeae58da781</t>
+  </si>
+  <si>
+    <t>2026-08-13T12:09:11.271Z</t>
+  </si>
+  <si>
+    <t>{"job":{"id":"J03-1833","title":"Recondition Transmission 16H,G","unit":"E448 — D10T","unit_id":"a5c2144b-1b29-40f7-9b5c-cfbbc03c3387","description":"Job recondition Transmission 16H,G (time frame standar).","status":"in_progress","technician_id":"T-c23ed9a4","template_id":"ne-transmission-16h-g","created_at":"2026-08-11T05:30:21.056Z","started_at":"2026-08-11T05:32:14.074Z","completed_at":"","paused_at":"","total_paused_sec":0,"estimated_minutes":5340},"steps":[{"id":"e21019ab-05cb-4d4f-8f8f-fb85fa9004da","job_id":"J03-1833","name":"Dismantle: Washing Transmission gp","order":1,"status":"done","started_at":"2026-08-11T05:32:14.074Z","completed_at":"2026-08-11T23:52:49.552Z","duration_sec":66035,"std_minutes":240},{"id":"5ceecb87-2473-4297-a2a0-db873217f383","job_id":"J03-1833","name":"Dismantle: Control Valve 2EA","order":2,"status":"done","started_at":"2026-08-11T05:32:33.253Z","completed_at":"2026-08-11T23:52:32.616Z","duration_sec":65999,"std_minutes":300},{"id":"11997f0b-4cc8-4b54-8bdd-db3614b948c1","job_id":"J03-1833","name":"Dismantle: Pump, Lines, &amp; Screen","order":3,"status":"done","started_at":"2026-08-11T05:32:33.253Z","completed_at":"2026-08-11T23:52:51.817Z","duration_sec":66018,"std_minutes":240},{"id":"6c426149-ef7a-48c2-9585-5909fe86eca9","job_id":"J03-1833","name":"Dismantle: Planetary GP","order":4,"status":"done","started_at":"2026-08-11T23:52:51.817Z","completed_at":"2026-08-13T12:08:28.871Z","duration_sec":130537,"std_minutes":900},{"id":"5d3baced-8d6d-491b-9df4-09eaef47f6b9","job_id":"J03-1833","name":"Dismantle: Directional &amp; Idler gear","order":5,"status":"done","started_at":"2026-08-13T12:08:28.871Z","completed_at":"2026-08-13T12:08:40.688Z","duration_sec":11,"std_minutes":300},{"id":"0feaac14-da1a-4360-98f3-a99ad7b2fd45","job_id":"J03-1833","name":"Dismantle: Clean up Housing 2ea","order":6,"status":"in_progress","started_at":"2026-08-13T12:09:11.234Z","completed_at":"","duration_sec":0,"std_minutes":120},{"id":"5b00b8bb-18f9-4ef9-ac8c-5d5f25f11170","job_id":"J03-1833","name":"Dismantle: Part list &amp; Tear Down","order":7,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"c536fdc6-3459-4ab5-a588-3454f07f08c7","job_id":"J03-1833","name":"Assemble: Directional &amp; Idler gear","order":8,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"89d1ae15-daf2-4871-9bc0-5940279c96f6","job_id":"J03-1833","name":"Assemble: Planetary GP","order":9,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"1197b5dd-9928-4565-ae50-91f382e2beb0","job_id":"J03-1833","name":"Assemble: CV 2EA","order":10,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"6a936f7e-e97a-47f4-9e03-24e38ef315fc","job_id":"J03-1833","name":"Assemble: Pump, Lines, &amp; Screen","order":11,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"80894723-ea93-40ff-aa35-420c027d3f95","job_id":"J03-1833","name":"Test Bench &amp; Completed: Set up","order":12,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"acf6bd0c-0d96-40b6-8b9e-ee8c27ee1625","job_id":"J03-1833","name":"Test Bench &amp; Completed: Test","order":13,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"81692dde-b76a-433d-9b5d-3476cf3cd7f6","job_id":"J03-1833","name":"Test Bench &amp; Completed: Release","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"b69b87c3-9d4b-450e-8c0e-162eb755ff75","job_id":"J03-1833","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300}],"assignees":[{"id":"a58e3fbd-80eb-4c64-bd6b-bb7196830ed8","job_id":"J03-1833","technician_id":"T-c23ed9a4","assigned_at":"2026-08-11T05:31:58.767Z","is_lead":"1"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-c23ed9a4","status":"busy","current_job_id":"J03-1833"}]}</t>
+  </si>
+  <si>
+    <t>eea060a1-ddb9-48fb-b15e-fc724ed7207c</t>
+  </si>
+  <si>
+    <t>2026-08-13T12:10:35.004Z</t>
+  </si>
+  <si>
+    <t>{"job":{"id":"J02-dc56","title":"Recondition Transmission 16H,G","unit":"E448 — D10T","unit_id":"a5c2144b-1b29-40f7-9b5c-cfbbc03c3387","description":"Job recondition Transmission 16H,G (time frame standar).","status":"in_progress","technician_id":"T-37cadb58","template_id":"ne-transmission-16h-g","created_at":"2026-08-09T14:29:20.672Z","started_at":"2026-08-09T15:02:48.075Z","completed_at":"","paused_at":"","total_paused_sec":94,"estimated_minutes":5340},"steps":[{"id":"91804ed8-5ad4-4ffd-aaad-beba64eb9cb2","job_id":"J02-dc56","name":"Dismantle: Washing Transmission gp","order":1,"status":"done","started_at":"2026-08-09T15:02:48.075Z","completed_at":"2026-08-09T15:20:47.571Z","duration_sec":1079,"std_minutes":240},{"id":"a127f857-f092-4b21-b197-3e3c8a02d549","job_id":"J02-dc56","name":"Dismantle: Control Valve 2EA","order":2,"status":"done","started_at":"2026-08-10T01:30:25.210Z","completed_at":"2026-08-10T01:30:32.748Z","duration_sec":36495,"std_minutes":300},{"id":"3bc8becf-2b5e-4391-8c9f-619d63d7281c","job_id":"J02-dc56","name":"Dismantle: Pump, Lines, &amp; Screen","order":3,"status":"done","started_at":"2026-08-10T01:30:32.748Z","completed_at":"2026-08-10T08:27:37.616Z","duration_sec":25024,"std_minutes":240},{"id":"bacf6ce8-8a97-4831-9f38-3010f4d64a9a","job_id":"J02-dc56","name":"Dismantle: Planetary GP","order":4,"status":"done","started_at":"2026-08-10T08:27:37.616Z","completed_at":"2026-08-11T05:36:57.526Z","duration_sec":76159,"std_minutes":900},{"id":"74bc5c28-b84c-4cfa-b429-25198c968f30","job_id":"J02-dc56","name":"Dismantle: Directional &amp; Idler gear","order":5,"status":"done","started_at":"2026-08-11T05:36:57.526Z","completed_at":"2026-08-11T14:50:26.762Z","duration_sec":33209,"std_minutes":300},{"id":"c3ce574f-16e3-4ce2-815e-10a842f608de","job_id":"J02-dc56","name":"Dismantle: Clean up Housing 2ea","order":6,"status":"done","started_at":"2026-08-11T14:50:26.763Z","completed_at":"2026-08-11T15:28:01.298Z","duration_sec":2254,"std_minutes":120},{"id":"b57a5afd-0b62-47a8-a149-df57cdbec92f","job_id":"J02-dc56","name":"Dismantle: Part list &amp; Tear Down","order":7,"status":"done","started_at":"2026-08-11T15:28:01.298Z","completed_at":"2026-08-12T00:05:46.117Z","duration_sec":31064,"std_minutes":240},{"id":"ef67991d-4f1b-4929-b4b9-3bd70d1c1a8b","job_id":"J02-dc56","name":"Assemble: Directional &amp; Idler gear","order":8,"status":"done","started_at":"2026-08-12T00:05:46.117Z","completed_at":"2026-08-12T03:47:41.223Z","duration_sec":13315,"std_minutes":600},{"id":"19689610-ed31-4c36-959c-6233ef31d9cc","job_id":"J02-dc56","name":"Assemble: Planetary GP","order":9,"status":"done","started_at":"2026-08-12T03:47:41.223Z","completed_at":"2026-08-12T09:25:37.962Z","duration_sec":20276,"std_minutes":600},{"id":"572f712a-0376-495f-a98f-9ee71ead12b3","job_id":"J02-dc56","name":"Assemble: CV 2EA","order":10,"status":"done","started_at":"2026-08-12T09:25:37.962Z","completed_at":"2026-08-13T03:13:58.520Z","duration_sec":64100,"std_minutes":300},{"id":"033a6b1b-8daf-46cc-a1e1-292ad2451d5f","job_id":"J02-dc56","name":"Assemble: Pump, Lines, &amp; Screen","order":11,"status":"done","started_at":"2026-08-13T11:13:08.442Z","completed_at":"2026-08-13T12:00:54.248Z","duration_sec":31601,"std_minutes":300},{"id":"f52cc000-4714-474d-a6c4-a3f41408fbb7","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Set up","order":12,"status":"done","started_at":"2026-08-13T12:00:54.248Z","completed_at":"2026-08-13T12:00:54.894Z","duration_sec":0,"std_minutes":300},{"id":"a9b889d6-b2f7-4421-a27a-fcd6a2fde9f9","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Test","order":13,"status":"in_progress","started_at":"2026-08-13T12:00:54.894Z","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"3edd89d2-41a4-4856-976b-cbc716dc3788","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Release","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"4d87b720-179e-4dbd-bf95-3d44c356f29e","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300}],"assignees":[{"id":"be4e949d-d820-4b28-b15a-054abe52834e","job_id":"J02-dc56","technician_id":"T-37cadb58","assigned_at":"2026-08-13T12:10:34.946Z","is_lead":"1"},{"id":"f54a99f1-4255-448e-98a9-4621ace561ec","job_id":"J02-dc56","technician_id":"T-e4a06545","assigned_at":"2026-08-13T12:10:34.946Z","is_lead":"0"},{"id":"9641f9a5-abbe-471b-bbec-4a731f535ee5","job_id":"J02-dc56","technician_id":"T-d32c7e65","assigned_at":"2026-08-13T12:10:34.946Z","is_lead":"0"},{"id":"9e67f933-012e-4980-a3f0-2c40b4043bb6","job_id":"J02-dc56","technician_id":"T-d6375327","assigned_at":"2026-08-13T12:10:34.946Z","is_lead":"0"},{"id":"545377eb-7418-420b-8d2a-a86555fa4b6e","job_id":"J02-dc56","technician_id":"T-3d0a3937","assigned_at":"2026-08-13T12:10:34.946Z","is_lead":"0"},{"id":"c422779f-8029-4bff-b90e-348b11aa6ea3","job_id":"J02-dc56","technician_id":"T-103b0d90","assigned_at":"2026-08-13T12:10:34.946Z","is_lead":"0"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-37cadb58","status":"busy","current_job_id":"J02-dc56"},{"id":"T-e4a06545","status":"busy","current_job_id":"J02-dc56"},{"id":"T-d32c7e65","status":"busy","current_job_id":"J02-dc56"},{"id":"T-d6375327","status":"busy","current_job_id":"J02-dc56"},{"id":"T-3d0a3937","status":"busy","current_job_id":"J02-dc56"},{"id":"T-103b0d90","status":"busy","current_job_id":"J02-dc56"}]}</t>
+  </si>
+  <si>
+    <t>0f4183dd-d09f-4d2e-98e2-798953a0d8ff</t>
+  </si>
+  <si>
+    <t>2026-08-13T12:10:35.432Z</t>
+  </si>
+  <si>
+    <t>{"job":{"id":"J03-1833","title":"Recondition Transmission 16H,G","unit":"E448 — D10T","unit_id":"a5c2144b-1b29-40f7-9b5c-cfbbc03c3387","description":"Job recondition Transmission 16H,G (time frame standar).","status":"paused","technician_id":"T-c23ed9a4","template_id":"ne-transmission-16h-g","created_at":"2026-08-11T05:30:21.056Z","started_at":"2026-08-11T05:32:14.074Z","completed_at":"","paused_at":"2026-08-13T12:10:35.384Z","total_paused_sec":0,"estimated_minutes":5340},"steps":[{"id":"e21019ab-05cb-4d4f-8f8f-fb85fa9004da","job_id":"J03-1833","name":"Dismantle: Washing Transmission gp","order":1,"status":"done","started_at":"2026-08-11T05:32:14.074Z","completed_at":"2026-08-11T23:52:49.552Z","duration_sec":66035,"std_minutes":240},{"id":"5ceecb87-2473-4297-a2a0-db873217f383","job_id":"J03-1833","name":"Dismantle: Control Valve 2EA","order":2,"status":"done","started_at":"2026-08-11T05:32:33.253Z","completed_at":"2026-08-11T23:52:32.616Z","duration_sec":65999,"std_minutes":300},{"id":"11997f0b-4cc8-4b54-8bdd-db3614b948c1","job_id":"J03-1833","name":"Dismantle: Pump, Lines, &amp; Screen","order":3,"status":"done","started_at":"2026-08-11T05:32:33.253Z","completed_at":"2026-08-11T23:52:51.817Z","duration_sec":66018,"std_minutes":240},{"id":"6c426149-ef7a-48c2-9585-5909fe86eca9","job_id":"J03-1833","name":"Dismantle: Planetary GP","order":4,"status":"done","started_at":"2026-08-11T23:52:51.817Z","completed_at":"2026-08-13T12:08:28.871Z","duration_sec":130537,"std_minutes":900},{"id":"5d3baced-8d6d-491b-9df4-09eaef47f6b9","job_id":"J03-1833","name":"Dismantle: Directional &amp; Idler gear","order":5,"status":"done","started_at":"2026-08-13T12:08:28.871Z","completed_at":"2026-08-13T12:08:40.688Z","duration_sec":11,"std_minutes":300},{"id":"0feaac14-da1a-4360-98f3-a99ad7b2fd45","job_id":"J03-1833","name":"Dismantle: Clean up Housing 2ea","order":6,"status":"in_progress","started_at":"","completed_at":"","duration_sec":84,"std_minutes":120},{"id":"5b00b8bb-18f9-4ef9-ac8c-5d5f25f11170","job_id":"J03-1833","name":"Dismantle: Part list &amp; Tear Down","order":7,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"c536fdc6-3459-4ab5-a588-3454f07f08c7","job_id":"J03-1833","name":"Assemble: Directional &amp; Idler gear","order":8,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"89d1ae15-daf2-4871-9bc0-5940279c96f6","job_id":"J03-1833","name":"Assemble: Planetary GP","order":9,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"1197b5dd-9928-4565-ae50-91f382e2beb0","job_id":"J03-1833","name":"Assemble: CV 2EA","order":10,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"6a936f7e-e97a-47f4-9e03-24e38ef315fc","job_id":"J03-1833","name":"Assemble: Pump, Lines, &amp; Screen","order":11,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"80894723-ea93-40ff-aa35-420c027d3f95","job_id":"J03-1833","name":"Test Bench &amp; Completed: Set up","order":12,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"acf6bd0c-0d96-40b6-8b9e-ee8c27ee1625","job_id":"J03-1833","name":"Test Bench &amp; Completed: Test","order":13,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"81692dde-b76a-433d-9b5d-3476cf3cd7f6","job_id":"J03-1833","name":"Test Bench &amp; Completed: Release","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"b69b87c3-9d4b-450e-8c0e-162eb755ff75","job_id":"J03-1833","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300}],"assignees":[{"id":"a58e3fbd-80eb-4c64-bd6b-bb7196830ed8","job_id":"J03-1833","technician_id":"T-c23ed9a4","assigned_at":"2026-08-11T05:31:58.767Z","is_lead":"1"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-c23ed9a4","status":"busy","current_job_id":"J03-1833"}]}</t>
+  </si>
+  <si>
+    <t>c50c58a0-a807-41d5-bc52-a12b68aed3c0</t>
+  </si>
+  <si>
+    <t>2026-08-13T12:11:38.866Z</t>
+  </si>
+  <si>
+    <t>{"job":{"id":"J03-1833","title":"Recondition Transmission 16H,G","unit":"E448 — D10T","unit_id":"a5c2144b-1b29-40f7-9b5c-cfbbc03c3387","description":"Job recondition Transmission 16H,G (time frame standar).","status":"in_progress","technician_id":"T-c23ed9a4","template_id":"ne-transmission-16h-g","created_at":"2026-08-11T05:30:21.056Z","started_at":"2026-08-11T05:32:14.074Z","completed_at":"","paused_at":"","total_paused_sec":63,"estimated_minutes":5340},"steps":[{"id":"e21019ab-05cb-4d4f-8f8f-fb85fa9004da","job_id":"J03-1833","name":"Dismantle: Washing Transmission gp","order":1,"status":"done","started_at":"2026-08-11T05:32:14.074Z","completed_at":"2026-08-11T23:52:49.552Z","duration_sec":66035,"std_minutes":240},{"id":"5ceecb87-2473-4297-a2a0-db873217f383","job_id":"J03-1833","name":"Dismantle: Control Valve 2EA","order":2,"status":"done","started_at":"2026-08-11T05:32:33.253Z","completed_at":"2026-08-11T23:52:32.616Z","duration_sec":65999,"std_minutes":300},{"id":"11997f0b-4cc8-4b54-8bdd-db3614b948c1","job_id":"J03-1833","name":"Dismantle: Pump, Lines, &amp; Screen","order":3,"status":"done","started_at":"2026-08-11T05:32:33.253Z","completed_at":"2026-08-11T23:52:51.817Z","duration_sec":66018,"std_minutes":240},{"id":"6c426149-ef7a-48c2-9585-5909fe86eca9","job_id":"J03-1833","name":"Dismantle: Planetary GP","order":4,"status":"done","started_at":"2026-08-11T23:52:51.817Z","completed_at":"2026-08-13T12:08:28.871Z","duration_sec":130537,"std_minutes":900},{"id":"5d3baced-8d6d-491b-9df4-09eaef47f6b9","job_id":"J03-1833","name":"Dismantle: Directional &amp; Idler gear","order":5,"status":"done","started_at":"2026-08-13T12:08:28.871Z","completed_at":"2026-08-13T12:08:40.688Z","duration_sec":11,"std_minutes":300},{"id":"0feaac14-da1a-4360-98f3-a99ad7b2fd45","job_id":"J03-1833","name":"Dismantle: Clean up Housing 2ea","order":6,"status":"in_progress","started_at":"2026-08-13T12:11:38.761Z","completed_at":"","duration_sec":84,"std_minutes":120},{"id":"5b00b8bb-18f9-4ef9-ac8c-5d5f25f11170","job_id":"J03-1833","name":"Dismantle: Part list &amp; Tear Down","order":7,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"c536fdc6-3459-4ab5-a588-3454f07f08c7","job_id":"J03-1833","name":"Assemble: Directional &amp; Idler gear","order":8,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"89d1ae15-daf2-4871-9bc0-5940279c96f6","job_id":"J03-1833","name":"Assemble: Planetary GP","order":9,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"1197b5dd-9928-4565-ae50-91f382e2beb0","job_id":"J03-1833","name":"Assemble: CV 2EA","order":10,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"6a936f7e-e97a-47f4-9e03-24e38ef315fc","job_id":"J03-1833","name":"Assemble: Pump, Lines, &amp; Screen","order":11,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"80894723-ea93-40ff-aa35-420c027d3f95","job_id":"J03-1833","name":"Test Bench &amp; Completed: Set up","order":12,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"acf6bd0c-0d96-40b6-8b9e-ee8c27ee1625","job_id":"J03-1833","name":"Test Bench &amp; Completed: Test","order":13,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"81692dde-b76a-433d-9b5d-3476cf3cd7f6","job_id":"J03-1833","name":"Test Bench &amp; Completed: Release","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"b69b87c3-9d4b-450e-8c0e-162eb755ff75","job_id":"J03-1833","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300}],"assignees":[{"id":"a58e3fbd-80eb-4c64-bd6b-bb7196830ed8","job_id":"J03-1833","technician_id":"T-c23ed9a4","assigned_at":"2026-08-11T05:31:58.767Z","is_lead":"1"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-c23ed9a4","status":"busy","current_job_id":"J03-1833"}]}</t>
+  </si>
+  <si>
+    <t>4b92b44f-c952-4fb8-a229-bc9049b85577</t>
+  </si>
+  <si>
+    <t>2026-08-13T12:11:48.298Z</t>
+  </si>
+  <si>
+    <t>{"job":{"id":"J03-1833","title":"Recondition Transmission 16H,G","unit":"E448 — D10T","unit_id":"a5c2144b-1b29-40f7-9b5c-cfbbc03c3387","description":"Job recondition Transmission 16H,G (time frame standar).","status":"paused","technician_id":"T-c23ed9a4","template_id":"ne-transmission-16h-g","created_at":"2026-08-11T05:30:21.056Z","started_at":"2026-08-11T05:32:14.074Z","completed_at":"","paused_at":"2026-08-13T12:11:47.982Z","total_paused_sec":63,"estimated_minutes":5340},"steps":[{"id":"e21019ab-05cb-4d4f-8f8f-fb85fa9004da","job_id":"J03-1833","name":"Dismantle: Washing Transmission gp","order":1,"status":"done","started_at":"2026-08-11T05:32:14.074Z","completed_at":"2026-08-11T23:52:49.552Z","duration_sec":66035,"std_minutes":240},{"id":"5ceecb87-2473-4297-a2a0-db873217f383","job_id":"J03-1833","name":"Dismantle: Control Valve 2EA","order":2,"status":"done","started_at":"2026-08-11T05:32:33.253Z","completed_at":"2026-08-11T23:52:32.616Z","duration_sec":65999,"std_minutes":300},{"id":"11997f0b-4cc8-4b54-8bdd-db3614b948c1","job_id":"J03-1833","name":"Dismantle: Pump, Lines, &amp; Screen","order":3,"status":"done","started_at":"2026-08-11T05:32:33.253Z","completed_at":"2026-08-11T23:52:51.817Z","duration_sec":66018,"std_minutes":240},{"id":"6c426149-ef7a-48c2-9585-5909fe86eca9","job_id":"J03-1833","name":"Dismantle: Planetary GP","order":4,"status":"done","started_at":"2026-08-11T23:52:51.817Z","completed_at":"2026-08-13T12:08:28.871Z","duration_sec":130537,"std_minutes":900},{"id":"5d3baced-8d6d-491b-9df4-09eaef47f6b9","job_id":"J03-1833","name":"Dismantle: Directional &amp; Idler gear","order":5,"status":"done","started_at":"2026-08-13T12:08:28.871Z","completed_at":"2026-08-13T12:08:40.688Z","duration_sec":11,"std_minutes":300},{"id":"0feaac14-da1a-4360-98f3-a99ad7b2fd45","job_id":"J03-1833","name":"Dismantle: Clean up Housing 2ea","order":6,"status":"in_progress","started_at":"","completed_at":"","duration_sec":93,"std_minutes":120},{"id":"5b00b8bb-18f9-4ef9-ac8c-5d5f25f11170","job_id":"J03-1833","name":"Dismantle: Part list &amp; Tear Down","order":7,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"c536fdc6-3459-4ab5-a588-3454f07f08c7","job_id":"J03-1833","name":"Assemble: Directional &amp; Idler gear","order":8,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"89d1ae15-daf2-4871-9bc0-5940279c96f6","job_id":"J03-1833","name":"Assemble: Planetary GP","order":9,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"1197b5dd-9928-4565-ae50-91f382e2beb0","job_id":"J03-1833","name":"Assemble: CV 2EA","order":10,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"6a936f7e-e97a-47f4-9e03-24e38ef315fc","job_id":"J03-1833","name":"Assemble: Pump, Lines, &amp; Screen","order":11,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"80894723-ea93-40ff-aa35-420c027d3f95","job_id":"J03-1833","name":"Test Bench &amp; Completed: Set up","order":12,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"acf6bd0c-0d96-40b6-8b9e-ee8c27ee1625","job_id":"J03-1833","name":"Test Bench &amp; Completed: Test","order":13,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"81692dde-b76a-433d-9b5d-3476cf3cd7f6","job_id":"J03-1833","name":"Test Bench &amp; Completed: Release","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"b69b87c3-9d4b-450e-8c0e-162eb755ff75","job_id":"J03-1833","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300}],"assignees":[{"id":"a58e3fbd-80eb-4c64-bd6b-bb7196830ed8","job_id":"J03-1833","technician_id":"T-c23ed9a4","assigned_at":"2026-08-11T05:31:58.767Z","is_lead":"1"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-c23ed9a4","status":"busy","current_job_id":"J03-1833"}]}</t>
+  </si>
+  <si>
+    <t>17b867f0-8944-49db-94f1-f9662d074ab7</t>
+  </si>
+  <si>
+    <t>2026-08-13T12:11:54.729Z</t>
+  </si>
+  <si>
+    <t>{"job":{"id":"J03-1833","title":"Recondition Transmission 16H,G","unit":"E448 — D10T","unit_id":"a5c2144b-1b29-40f7-9b5c-cfbbc03c3387","description":"Job recondition Transmission 16H,G (time frame standar).","status":"in_progress","technician_id":"T-c23ed9a4","template_id":"ne-transmission-16h-g","created_at":"2026-08-11T05:30:21.056Z","started_at":"2026-08-11T05:32:14.074Z","completed_at":"","paused_at":"","total_paused_sec":69,"estimated_minutes":5340},"steps":[{"id":"e21019ab-05cb-4d4f-8f8f-fb85fa9004da","job_id":"J03-1833","name":"Dismantle: Washing Transmission gp","order":1,"status":"done","started_at":"2026-08-11T05:32:14.074Z","completed_at":"2026-08-11T23:52:49.552Z","duration_sec":66035,"std_minutes":240},{"id":"5ceecb87-2473-4297-a2a0-db873217f383","job_id":"J03-1833","name":"Dismantle: Control Valve 2EA","order":2,"status":"done","started_at":"2026-08-11T05:32:33.253Z","completed_at":"2026-08-11T23:52:32.616Z","duration_sec":65999,"std_minutes":300},{"id":"11997f0b-4cc8-4b54-8bdd-db3614b948c1","job_id":"J03-1833","name":"Dismantle: Pump, Lines, &amp; Screen","order":3,"status":"done","started_at":"2026-08-11T05:32:33.253Z","completed_at":"2026-08-11T23:52:51.817Z","duration_sec":66018,"std_minutes":240},{"id":"6c426149-ef7a-48c2-9585-5909fe86eca9","job_id":"J03-1833","name":"Dismantle: Planetary GP","order":4,"status":"done","started_at":"2026-08-11T23:52:51.817Z","completed_at":"2026-08-13T12:08:28.871Z","duration_sec":130537,"std_minutes":900},{"id":"5d3baced-8d6d-491b-9df4-09eaef47f6b9","job_id":"J03-1833","name":"Dismantle: Directional &amp; Idler gear","order":5,"status":"done","started_at":"2026-08-13T12:08:28.871Z","completed_at":"2026-08-13T12:08:40.688Z","duration_sec":11,"std_minutes":300},{"id":"0feaac14-da1a-4360-98f3-a99ad7b2fd45","job_id":"J03-1833","name":"Dismantle: Clean up Housing 2ea","order":6,"status":"in_progress","started_at":"2026-08-13T12:11:54.696Z","completed_at":"","duration_sec":93,"std_minutes":120},{"id":"5b00b8bb-18f9-4ef9-ac8c-5d5f25f11170","job_id":"J03-1833","name":"Dismantle: Part list &amp; Tear Down","order":7,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"c536fdc6-3459-4ab5-a588-3454f07f08c7","job_id":"J03-1833","name":"Assemble: Directional &amp; Idler gear","order":8,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"89d1ae15-daf2-4871-9bc0-5940279c96f6","job_id":"J03-1833","name":"Assemble: Planetary GP","order":9,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"1197b5dd-9928-4565-ae50-91f382e2beb0","job_id":"J03-1833","name":"Assemble: CV 2EA","order":10,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"6a936f7e-e97a-47f4-9e03-24e38ef315fc","job_id":"J03-1833","name":"Assemble: Pump, Lines, &amp; Screen","order":11,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"80894723-ea93-40ff-aa35-420c027d3f95","job_id":"J03-1833","name":"Test Bench &amp; Completed: Set up","order":12,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"acf6bd0c-0d96-40b6-8b9e-ee8c27ee1625","job_id":"J03-1833","name":"Test Bench &amp; Completed: Test","order":13,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"81692dde-b76a-433d-9b5d-3476cf3cd7f6","job_id":"J03-1833","name":"Test Bench &amp; Completed: Release","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"b69b87c3-9d4b-450e-8c0e-162eb755ff75","job_id":"J03-1833","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300}],"assignees":[{"id":"a58e3fbd-80eb-4c64-bd6b-bb7196830ed8","job_id":"J03-1833","technician_id":"T-c23ed9a4","assigned_at":"2026-08-11T05:31:58.767Z","is_lead":"1"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-c23ed9a4","status":"busy","current_job_id":"J03-1833"}]}</t>
+  </si>
+  <si>
+    <t>434a501a-880c-48b7-8893-0cdea2b7c471</t>
+  </si>
+  <si>
+    <t>2026-08-13T12:11:59.299Z</t>
+  </si>
+  <si>
+    <t>{"job":{"id":"J03-1833","title":"Recondition Transmission 16H,G","unit":"E448 — D10T","unit_id":"a5c2144b-1b29-40f7-9b5c-cfbbc03c3387","description":"Job recondition Transmission 16H,G (time frame standar).","status":"paused","technician_id":"T-c23ed9a4","template_id":"ne-transmission-16h-g","created_at":"2026-08-11T05:30:21.056Z","started_at":"2026-08-11T05:32:14.074Z","completed_at":"","paused_at":"2026-08-13T12:11:59.103Z","total_paused_sec":69,"estimated_minutes":5340},"steps":[{"id":"e21019ab-05cb-4d4f-8f8f-fb85fa9004da","job_id":"J03-1833","name":"Dismantle: Washing Transmission gp","order":1,"status":"done","started_at":"2026-08-11T05:32:14.074Z","completed_at":"2026-08-11T23:52:49.552Z","duration_sec":66035,"std_minutes":240},{"id":"5ceecb87-2473-4297-a2a0-db873217f383","job_id":"J03-1833","name":"Dismantle: Control Valve 2EA","order":2,"status":"done","started_at":"2026-08-11T05:32:33.253Z","completed_at":"2026-08-11T23:52:32.616Z","duration_sec":65999,"std_minutes":300},{"id":"11997f0b-4cc8-4b54-8bdd-db3614b948c1","job_id":"J03-1833","name":"Dismantle: Pump, Lines, &amp; Screen","order":3,"status":"done","started_at":"2026-08-11T05:32:33.253Z","completed_at":"2026-08-11T23:52:51.817Z","duration_sec":66018,"std_minutes":240},{"id":"6c426149-ef7a-48c2-9585-5909fe86eca9","job_id":"J03-1833","name":"Dismantle: Planetary GP","order":4,"status":"done","started_at":"2026-08-11T23:52:51.817Z","completed_at":"2026-08-13T12:08:28.871Z","duration_sec":130537,"std_minutes":900},{"id":"5d3baced-8d6d-491b-9df4-09eaef47f6b9","job_id":"J03-1833","name":"Dismantle: Directional &amp; Idler gear","order":5,"status":"done","started_at":"2026-08-13T12:08:28.871Z","completed_at":"2026-08-13T12:08:40.688Z","duration_sec":11,"std_minutes":300},{"id":"0feaac14-da1a-4360-98f3-a99ad7b2fd45","job_id":"J03-1833","name":"Dismantle: Clean up Housing 2ea","order":6,"status":"in_progress","started_at":"","completed_at":"","duration_sec":97,"std_minutes":120},{"id":"5b00b8bb-18f9-4ef9-ac8c-5d5f25f11170","job_id":"J03-1833","name":"Dismantle: Part list &amp; Tear Down","order":7,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"c536fdc6-3459-4ab5-a588-3454f07f08c7","job_id":"J03-1833","name":"Assemble: Directional &amp; Idler gear","order":8,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"89d1ae15-daf2-4871-9bc0-5940279c96f6","job_id":"J03-1833","name":"Assemble: Planetary GP","order":9,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"1197b5dd-9928-4565-ae50-91f382e2beb0","job_id":"J03-1833","name":"Assemble: CV 2EA","order":10,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"6a936f7e-e97a-47f4-9e03-24e38ef315fc","job_id":"J03-1833","name":"Assemble: Pump, Lines, &amp; Screen","order":11,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"80894723-ea93-40ff-aa35-420c027d3f95","job_id":"J03-1833","name":"Test Bench &amp; Completed: Set up","order":12,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"acf6bd0c-0d96-40b6-8b9e-ee8c27ee1625","job_id":"J03-1833","name":"Test Bench &amp; Completed: Test","order":13,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"81692dde-b76a-433d-9b5d-3476cf3cd7f6","job_id":"J03-1833","name":"Test Bench &amp; Completed: Release","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"b69b87c3-9d4b-450e-8c0e-162eb755ff75","job_id":"J03-1833","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300}],"assignees":[{"id":"a58e3fbd-80eb-4c64-bd6b-bb7196830ed8","job_id":"J03-1833","technician_id":"T-c23ed9a4","assigned_at":"2026-08-11T05:31:58.767Z","is_lead":"1"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-c23ed9a4","status":"busy","current_job_id":"J03-1833"}]}</t>
+  </si>
+  <si>
+    <t>e9a85d8a-6905-402e-a8a2-b4f5f0a72f63</t>
+  </si>
+  <si>
+    <t>2026-08-13T12:12:19.635Z</t>
+  </si>
+  <si>
+    <t>{"job":{"id":"J03-1833","title":"Recondition Transmission 16H,G","unit":"E448 — D10T","unit_id":"a5c2144b-1b29-40f7-9b5c-cfbbc03c3387","description":"Job recondition Transmission 16H,G (time frame standar).","status":"in_progress","technician_id":"T-c23ed9a4","template_id":"ne-transmission-16h-g","created_at":"2026-08-11T05:30:21.056Z","started_at":"2026-08-11T05:32:14.074Z","completed_at":"","paused_at":"","total_paused_sec":89,"estimated_minutes":5340},"steps":[{"id":"e21019ab-05cb-4d4f-8f8f-fb85fa9004da","job_id":"J03-1833","name":"Dismantle: Washing Transmission gp","order":1,"status":"done","started_at":"2026-08-11T05:32:14.074Z","completed_at":"2026-08-11T23:52:49.552Z","duration_sec":66035,"std_minutes":240},{"id":"5ceecb87-2473-4297-a2a0-db873217f383","job_id":"J03-1833","name":"Dismantle: Control Valve 2EA","order":2,"status":"done","started_at":"2026-08-11T05:32:33.253Z","completed_at":"2026-08-11T23:52:32.616Z","duration_sec":65999,"std_minutes":300},{"id":"11997f0b-4cc8-4b54-8bdd-db3614b948c1","job_id":"J03-1833","name":"Dismantle: Pump, Lines, &amp; Screen","order":3,"status":"done","started_at":"2026-08-11T05:32:33.253Z","completed_at":"2026-08-11T23:52:51.817Z","duration_sec":66018,"std_minutes":240},{"id":"6c426149-ef7a-48c2-9585-5909fe86eca9","job_id":"J03-1833","name":"Dismantle: Planetary GP","order":4,"status":"done","started_at":"2026-08-11T23:52:51.817Z","completed_at":"2026-08-13T12:08:28.871Z","duration_sec":130537,"std_minutes":900},{"id":"5d3baced-8d6d-491b-9df4-09eaef47f6b9","job_id":"J03-1833","name":"Dismantle: Directional &amp; Idler gear","order":5,"status":"done","started_at":"2026-08-13T12:08:28.871Z","completed_at":"2026-08-13T12:08:40.688Z","duration_sec":11,"std_minutes":300},{"id":"0feaac14-da1a-4360-98f3-a99ad7b2fd45","job_id":"J03-1833","name":"Dismantle: Clean up Housing 2ea","order":6,"status":"in_progress","started_at":"2026-08-13T12:12:19.584Z","completed_at":"","duration_sec":97,"std_minutes":120},{"id":"5b00b8bb-18f9-4ef9-ac8c-5d5f25f11170","job_id":"J03-1833","name":"Dismantle: Part list &amp; Tear Down","order":7,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"c536fdc6-3459-4ab5-a588-3454f07f08c7","job_id":"J03-1833","name":"Assemble: Directional &amp; Idler gear","order":8,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"89d1ae15-daf2-4871-9bc0-5940279c96f6","job_id":"J03-1833","name":"Assemble: Planetary GP","order":9,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"1197b5dd-9928-4565-ae50-91f382e2beb0","job_id":"J03-1833","name":"Assemble: CV 2EA","order":10,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"6a936f7e-e97a-47f4-9e03-24e38ef315fc","job_id":"J03-1833","name":"Assemble: Pump, Lines, &amp; Screen","order":11,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"80894723-ea93-40ff-aa35-420c027d3f95","job_id":"J03-1833","name":"Test Bench &amp; Completed: Set up","order":12,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"acf6bd0c-0d96-40b6-8b9e-ee8c27ee1625","job_id":"J03-1833","name":"Test Bench &amp; Completed: Test","order":13,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"81692dde-b76a-433d-9b5d-3476cf3cd7f6","job_id":"J03-1833","name":"Test Bench &amp; Completed: Release","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"b69b87c3-9d4b-450e-8c0e-162eb755ff75","job_id":"J03-1833","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300}],"assignees":[{"id":"a58e3fbd-80eb-4c64-bd6b-bb7196830ed8","job_id":"J03-1833","technician_id":"T-c23ed9a4","assigned_at":"2026-08-11T05:31:58.767Z","is_lead":"1"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-c23ed9a4","status":"busy","current_job_id":"J03-1833"}]}</t>
+  </si>
+  <si>
+    <t>4672333f-1401-4348-9bd4-013540605001</t>
+  </si>
+  <si>
+    <t>2026-08-13T12:17:45.343Z</t>
+  </si>
+  <si>
+    <t>{"job":{"id":"J03-1833","title":"Recondition Transmission 16H,G","unit":"E448 — D10T","unit_id":"a5c2144b-1b29-40f7-9b5c-cfbbc03c3387","description":"Job recondition Transmission 16H,G (time frame standar).","status":"paused","technician_id":"T-c23ed9a4","template_id":"ne-transmission-16h-g","created_at":"2026-08-11T05:30:21.056Z","started_at":"2026-08-11T05:32:14.074Z","completed_at":"","paused_at":"2026-08-13T12:12:37.225Z","total_paused_sec":89,"estimated_minutes":5340},"steps":[{"id":"e21019ab-05cb-4d4f-8f8f-fb85fa9004da","job_id":"J03-1833","name":"Dismantle: Washing Transmission gp","order":1,"status":"done","started_at":"2026-08-11T05:32:14.074Z","completed_at":"2026-08-11T23:52:49.552Z","duration_sec":66035,"std_minutes":240},{"id":"5ceecb87-2473-4297-a2a0-db873217f383","job_id":"J03-1833","name":"Dismantle: Control Valve 2EA","order":2,"status":"done","started_at":"2026-08-11T05:32:33.253Z","completed_at":"2026-08-11T23:52:32.616Z","duration_sec":65999,"std_minutes":300},{"id":"11997f0b-4cc8-4b54-8bdd-db3614b948c1","job_id":"J03-1833","name":"Dismantle: Pump, Lines, &amp; Screen","order":3,"status":"done","started_at":"2026-08-11T05:32:33.253Z","completed_at":"2026-08-11T23:52:51.817Z","duration_sec":66018,"std_minutes":240},{"id":"6c426149-ef7a-48c2-9585-5909fe86eca9","job_id":"J03-1833","name":"Dismantle: Planetary GP","order":4,"status":"done","started_at":"2026-08-11T23:52:51.817Z","completed_at":"2026-08-13T12:08:28.871Z","duration_sec":130537,"std_minutes":900},{"id":"5d3baced-8d6d-491b-9df4-09eaef47f6b9","job_id":"J03-1833","name":"Dismantle: Directional &amp; Idler gear","order":5,"status":"done","started_at":"2026-08-13T12:08:28.871Z","completed_at":"2026-08-13T12:08:40.688Z","duration_sec":11,"std_minutes":300},{"id":"0feaac14-da1a-4360-98f3-a99ad7b2fd45","job_id":"J03-1833","name":"Dismantle: Clean up Housing 2ea","order":6,"status":"in_progress","started_at":"","completed_at":"","duration_sec":114,"std_minutes":120},{"id":"5b00b8bb-18f9-4ef9-ac8c-5d5f25f11170","job_id":"J03-1833","name":"Dismantle: Part list &amp; Tear Down","order":7,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"c536fdc6-3459-4ab5-a588-3454f07f08c7","job_id":"J03-1833","name":"Assemble: Directional &amp; Idler gear","order":8,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"89d1ae15-daf2-4871-9bc0-5940279c96f6","job_id":"J03-1833","name":"Assemble: Planetary GP","order":9,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"1197b5dd-9928-4565-ae50-91f382e2beb0","job_id":"J03-1833","name":"Assemble: CV 2EA","order":10,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"6a936f7e-e97a-47f4-9e03-24e38ef315fc","job_id":"J03-1833","name":"Assemble: Pump, Lines, &amp; Screen","order":11,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"80894723-ea93-40ff-aa35-420c027d3f95","job_id":"J03-1833","name":"Test Bench &amp; Completed: Set up","order":12,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"acf6bd0c-0d96-40b6-8b9e-ee8c27ee1625","job_id":"J03-1833","name":"Test Bench &amp; Completed: Test","order":13,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"81692dde-b76a-433d-9b5d-3476cf3cd7f6","job_id":"J03-1833","name":"Test Bench &amp; Completed: Release","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"b69b87c3-9d4b-450e-8c0e-162eb755ff75","job_id":"J03-1833","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300}],"assignees":[{"id":"a58e3fbd-80eb-4c64-bd6b-bb7196830ed8","job_id":"J03-1833","technician_id":"T-c23ed9a4","assigned_at":"2026-08-11T05:31:58.767Z","is_lead":"1"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-c23ed9a4","status":"busy","current_job_id":"J03-1833"}]}</t>
+  </si>
+  <si>
+    <t>7e5c7760-ef4e-44e0-b689-bbe012939c4f</t>
+  </si>
+  <si>
+    <t>2026-08-13T12:17:46.050Z</t>
+  </si>
+  <si>
+    <t>{"job":{"id":"J03-1833","title":"Recondition Transmission 16H,G","unit":"E448 — D10T","unit_id":"a5c2144b-1b29-40f7-9b5c-cfbbc03c3387","description":"Job recondition Transmission 16H,G (time frame standar).","status":"in_progress","technician_id":"T-c23ed9a4","template_id":"ne-transmission-16h-g","created_at":"2026-08-11T05:30:21.056Z","started_at":"2026-08-11T05:32:14.074Z","completed_at":"","paused_at":"","total_paused_sec":397,"estimated_minutes":5340},"steps":[{"id":"e21019ab-05cb-4d4f-8f8f-fb85fa9004da","job_id":"J03-1833","name":"Dismantle: Washing Transmission gp","order":1,"status":"done","started_at":"2026-08-11T05:32:14.074Z","completed_at":"2026-08-11T23:52:49.552Z","duration_sec":66035,"std_minutes":240},{"id":"5ceecb87-2473-4297-a2a0-db873217f383","job_id":"J03-1833","name":"Dismantle: Control Valve 2EA","order":2,"status":"done","started_at":"2026-08-11T05:32:33.253Z","completed_at":"2026-08-11T23:52:32.616Z","duration_sec":65999,"std_minutes":300},{"id":"11997f0b-4cc8-4b54-8bdd-db3614b948c1","job_id":"J03-1833","name":"Dismantle: Pump, Lines, &amp; Screen","order":3,"status":"done","started_at":"2026-08-11T05:32:33.253Z","completed_at":"2026-08-11T23:52:51.817Z","duration_sec":66018,"std_minutes":240},{"id":"6c426149-ef7a-48c2-9585-5909fe86eca9","job_id":"J03-1833","name":"Dismantle: Planetary GP","order":4,"status":"done","started_at":"2026-08-11T23:52:51.817Z","completed_at":"2026-08-13T12:08:28.871Z","duration_sec":130537,"std_minutes":900},{"id":"5d3baced-8d6d-491b-9df4-09eaef47f6b9","job_id":"J03-1833","name":"Dismantle: Directional &amp; Idler gear","order":5,"status":"done","started_at":"2026-08-13T12:08:28.871Z","completed_at":"2026-08-13T12:08:40.688Z","duration_sec":11,"std_minutes":300},{"id":"0feaac14-da1a-4360-98f3-a99ad7b2fd45","job_id":"J03-1833","name":"Dismantle: Clean up Housing 2ea","order":6,"status":"in_progress","started_at":"2026-08-13T12:17:45.958Z","completed_at":"","duration_sec":114,"std_minutes":120},{"id":"5b00b8bb-18f9-4ef9-ac8c-5d5f25f11170","job_id":"J03-1833","name":"Dismantle: Part list &amp; Tear Down","order":7,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"c536fdc6-3459-4ab5-a588-3454f07f08c7","job_id":"J03-1833","name":"Assemble: Directional &amp; Idler gear","order":8,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"89d1ae15-daf2-4871-9bc0-5940279c96f6","job_id":"J03-1833","name":"Assemble: Planetary GP","order":9,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"1197b5dd-9928-4565-ae50-91f382e2beb0","job_id":"J03-1833","name":"Assemble: CV 2EA","order":10,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"6a936f7e-e97a-47f4-9e03-24e38ef315fc","job_id":"J03-1833","name":"Assemble: Pump, Lines, &amp; Screen","order":11,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"80894723-ea93-40ff-aa35-420c027d3f95","job_id":"J03-1833","name":"Test Bench &amp; Completed: Set up","order":12,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"acf6bd0c-0d96-40b6-8b9e-ee8c27ee1625","job_id":"J03-1833","name":"Test Bench &amp; Completed: Test","order":13,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"81692dde-b76a-433d-9b5d-3476cf3cd7f6","job_id":"J03-1833","name":"Test Bench &amp; Completed: Release","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"b69b87c3-9d4b-450e-8c0e-162eb755ff75","job_id":"J03-1833","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300}],"assignees":[{"id":"a58e3fbd-80eb-4c64-bd6b-bb7196830ed8","job_id":"J03-1833","technician_id":"T-c23ed9a4","assigned_at":"2026-08-11T05:31:58.767Z","is_lead":"1"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-c23ed9a4","status":"busy","current_job_id":"J03-1833"}]}</t>
+  </si>
+  <si>
+    <t>efe1cdde-c1ab-4ee1-9b6b-49c500f00394</t>
+  </si>
+  <si>
+    <t>2026-08-13T12:17:46.520Z</t>
+  </si>
+  <si>
+    <t>{"job":{"id":"J03-1833","title":"Recondition Transmission 16H,G","unit":"E448 — D10T","unit_id":"a5c2144b-1b29-40f7-9b5c-cfbbc03c3387","description":"Job recondition Transmission 16H,G (time frame standar).","status":"paused","technician_id":"T-c23ed9a4","template_id":"ne-transmission-16h-g","created_at":"2026-08-11T05:30:21.056Z","started_at":"2026-08-11T05:32:14.074Z","completed_at":"","paused_at":"2026-08-13T12:13:30.204Z","total_paused_sec":397,"estimated_minutes":5340},"steps":[{"id":"e21019ab-05cb-4d4f-8f8f-fb85fa9004da","job_id":"J03-1833","name":"Dismantle: Washing Transmission gp","order":1,"status":"done","started_at":"2026-08-11T05:32:14.074Z","completed_at":"2026-08-11T23:52:49.552Z","duration_sec":66035,"std_minutes":240},{"id":"5ceecb87-2473-4297-a2a0-db873217f383","job_id":"J03-1833","name":"Dismantle: Control Valve 2EA","order":2,"status":"done","started_at":"2026-08-11T05:32:33.253Z","completed_at":"2026-08-11T23:52:32.616Z","duration_sec":65999,"std_minutes":300},{"id":"11997f0b-4cc8-4b54-8bdd-db3614b948c1","job_id":"J03-1833","name":"Dismantle: Pump, Lines, &amp; Screen","order":3,"status":"done","started_at":"2026-08-11T05:32:33.253Z","completed_at":"2026-08-11T23:52:51.817Z","duration_sec":66018,"std_minutes":240},{"id":"6c426149-ef7a-48c2-9585-5909fe86eca9","job_id":"J03-1833","name":"Dismantle: Planetary GP","order":4,"status":"done","started_at":"2026-08-11T23:52:51.817Z","completed_at":"2026-08-13T12:08:28.871Z","duration_sec":130537,"std_minutes":900},{"id":"5d3baced-8d6d-491b-9df4-09eaef47f6b9","job_id":"J03-1833","name":"Dismantle: Directional &amp; Idler gear","order":5,"status":"done","started_at":"2026-08-13T12:08:28.871Z","completed_at":"2026-08-13T12:08:40.688Z","duration_sec":11,"std_minutes":300},{"id":"0feaac14-da1a-4360-98f3-a99ad7b2fd45","job_id":"J03-1833","name":"Dismantle: Clean up Housing 2ea","order":6,"status":"in_progress","started_at":"","completed_at":"","duration_sec":131,"std_minutes":120},{"id":"5b00b8bb-18f9-4ef9-ac8c-5d5f25f11170","job_id":"J03-1833","name":"Dismantle: Part list &amp; Tear Down","order":7,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"c536fdc6-3459-4ab5-a588-3454f07f08c7","job_id":"J03-1833","name":"Assemble: Directional &amp; Idler gear","order":8,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"89d1ae15-daf2-4871-9bc0-5940279c96f6","job_id":"J03-1833","name":"Assemble: Planetary GP","order":9,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"1197b5dd-9928-4565-ae50-91f382e2beb0","job_id":"J03-1833","name":"Assemble: CV 2EA","order":10,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"6a936f7e-e97a-47f4-9e03-24e38ef315fc","job_id":"J03-1833","name":"Assemble: Pump, Lines, &amp; Screen","order":11,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"80894723-ea93-40ff-aa35-420c027d3f95","job_id":"J03-1833","name":"Test Bench &amp; Completed: Set up","order":12,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"acf6bd0c-0d96-40b6-8b9e-ee8c27ee1625","job_id":"J03-1833","name":"Test Bench &amp; Completed: Test","order":13,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"81692dde-b76a-433d-9b5d-3476cf3cd7f6","job_id":"J03-1833","name":"Test Bench &amp; Completed: Release","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"b69b87c3-9d4b-450e-8c0e-162eb755ff75","job_id":"J03-1833","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300}],"assignees":[{"id":"a58e3fbd-80eb-4c64-bd6b-bb7196830ed8","job_id":"J03-1833","technician_id":"T-c23ed9a4","assigned_at":"2026-08-11T05:31:58.767Z","is_lead":"1"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-c23ed9a4","status":"busy","current_job_id":"J03-1833"}]}</t>
+  </si>
+  <si>
+    <t>36b7697a-07aa-4814-bc83-59d8e9eb9f4f</t>
+  </si>
+  <si>
+    <t>2026-08-13T12:17:46.849Z</t>
+  </si>
+  <si>
+    <t>{"job":{"id":"J03-1833","title":"Recondition Transmission 16H,G","unit":"E448 — D10T","unit_id":"a5c2144b-1b29-40f7-9b5c-cfbbc03c3387","description":"Job recondition Transmission 16H,G (time frame standar).","status":"in_progress","technician_id":"T-c23ed9a4","template_id":"ne-transmission-16h-g","created_at":"2026-08-11T05:30:21.056Z","started_at":"2026-08-11T05:32:14.074Z","completed_at":"","paused_at":"","total_paused_sec":653,"estimated_minutes":5340},"steps":[{"id":"e21019ab-05cb-4d4f-8f8f-fb85fa9004da","job_id":"J03-1833","name":"Dismantle: Washing Transmission gp","order":1,"status":"done","started_at":"2026-08-11T05:32:14.074Z","completed_at":"2026-08-11T23:52:49.552Z","duration_sec":66035,"std_minutes":240},{"id":"5ceecb87-2473-4297-a2a0-db873217f383","job_id":"J03-1833","name":"Dismantle: Control Valve 2EA","order":2,"status":"done","started_at":"2026-08-11T05:32:33.253Z","completed_at":"2026-08-11T23:52:32.616Z","duration_sec":65999,"std_minutes":300},{"id":"11997f0b-4cc8-4b54-8bdd-db3614b948c1","job_id":"J03-1833","name":"Dismantle: Pump, Lines, &amp; Screen","order":3,"status":"done","started_at":"2026-08-11T05:32:33.253Z","completed_at":"2026-08-11T23:52:51.817Z","duration_sec":66018,"std_minutes":240},{"id":"6c426149-ef7a-48c2-9585-5909fe86eca9","job_id":"J03-1833","name":"Dismantle: Planetary GP","order":4,"status":"done","started_at":"2026-08-11T23:52:51.817Z","completed_at":"2026-08-13T12:08:28.871Z","duration_sec":130537,"std_minutes":900},{"id":"5d3baced-8d6d-491b-9df4-09eaef47f6b9","job_id":"J03-1833","name":"Dismantle: Directional &amp; Idler gear","order":5,"status":"done","started_at":"2026-08-13T12:08:28.871Z","completed_at":"2026-08-13T12:08:40.688Z","duration_sec":11,"std_minutes":300},{"id":"0feaac14-da1a-4360-98f3-a99ad7b2fd45","job_id":"J03-1833","name":"Dismantle: Clean up Housing 2ea","order":6,"status":"in_progress","started_at":"2026-08-13T12:17:46.813Z","completed_at":"","duration_sec":131,"std_minutes":120},{"id":"5b00b8bb-18f9-4ef9-ac8c-5d5f25f11170","job_id":"J03-1833","name":"Dismantle: Part list &amp; Tear Down","order":7,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"c536fdc6-3459-4ab5-a588-3454f07f08c7","job_id":"J03-1833","name":"Assemble: Directional &amp; Idler gear","order":8,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"89d1ae15-daf2-4871-9bc0-5940279c96f6","job_id":"J03-1833","name":"Assemble: Planetary GP","order":9,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"1197b5dd-9928-4565-ae50-91f382e2beb0","job_id":"J03-1833","name":"Assemble: CV 2EA","order":10,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"6a936f7e-e97a-47f4-9e03-24e38ef315fc","job_id":"J03-1833","name":"Assemble: Pump, Lines, &amp; Screen","order":11,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"80894723-ea93-40ff-aa35-420c027d3f95","job_id":"J03-1833","name":"Test Bench &amp; Completed: Set up","order":12,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"acf6bd0c-0d96-40b6-8b9e-ee8c27ee1625","job_id":"J03-1833","name":"Test Bench &amp; Completed: Test","order":13,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"81692dde-b76a-433d-9b5d-3476cf3cd7f6","job_id":"J03-1833","name":"Test Bench &amp; Completed: Release","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"b69b87c3-9d4b-450e-8c0e-162eb755ff75","job_id":"J03-1833","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300}],"assignees":[{"id":"a58e3fbd-80eb-4c64-bd6b-bb7196830ed8","job_id":"J03-1833","technician_id":"T-c23ed9a4","assigned_at":"2026-08-11T05:31:58.767Z","is_lead":"1"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-c23ed9a4","status":"busy","current_job_id":"J03-1833"}]}</t>
+  </si>
+  <si>
+    <t>343bc287-7dd4-4dc0-b695-9b5d367c7f6f</t>
+  </si>
+  <si>
+    <t>2026-08-13T12:17:47.260Z</t>
+  </si>
+  <si>
+    <t>{"job":{"id":"J03-1833","title":"Recondition Transmission 16H,G","unit":"E448 — D10T","unit_id":"a5c2144b-1b29-40f7-9b5c-cfbbc03c3387","description":"Job recondition Transmission 16H,G (time frame standar).","status":"paused","technician_id":"T-c23ed9a4","template_id":"ne-transmission-16h-g","created_at":"2026-08-11T05:30:21.056Z","started_at":"2026-08-11T05:32:14.074Z","completed_at":"","paused_at":"2026-08-13T12:13:51.777Z","total_paused_sec":653,"estimated_minutes":5340},"steps":[{"id":"e21019ab-05cb-4d4f-8f8f-fb85fa9004da","job_id":"J03-1833","name":"Dismantle: Washing Transmission gp","order":1,"status":"done","started_at":"2026-08-11T05:32:14.074Z","completed_at":"2026-08-11T23:52:49.552Z","duration_sec":66035,"std_minutes":240},{"id":"5ceecb87-2473-4297-a2a0-db873217f383","job_id":"J03-1833","name":"Dismantle: Control Valve 2EA","order":2,"status":"done","started_at":"2026-08-11T05:32:33.253Z","completed_at":"2026-08-11T23:52:32.616Z","duration_sec":65999,"std_minutes":300},{"id":"11997f0b-4cc8-4b54-8bdd-db3614b948c1","job_id":"J03-1833","name":"Dismantle: Pump, Lines, &amp; Screen","order":3,"status":"done","started_at":"2026-08-11T05:32:33.253Z","completed_at":"2026-08-11T23:52:51.817Z","duration_sec":66018,"std_minutes":240},{"id":"6c426149-ef7a-48c2-9585-5909fe86eca9","job_id":"J03-1833","name":"Dismantle: Planetary GP","order":4,"status":"done","started_at":"2026-08-11T23:52:51.817Z","completed_at":"2026-08-13T12:08:28.871Z","duration_sec":130537,"std_minutes":900},{"id":"5d3baced-8d6d-491b-9df4-09eaef47f6b9","job_id":"J03-1833","name":"Dismantle: Directional &amp; Idler gear","order":5,"status":"done","started_at":"2026-08-13T12:08:28.871Z","completed_at":"2026-08-13T12:08:40.688Z","duration_sec":11,"std_minutes":300},{"id":"0feaac14-da1a-4360-98f3-a99ad7b2fd45","job_id":"J03-1833","name":"Dismantle: Clean up Housing 2ea","order":6,"status":"in_progress","started_at":"","completed_at":"","duration_sec":136,"std_minutes":120},{"id":"5b00b8bb-18f9-4ef9-ac8c-5d5f25f11170","job_id":"J03-1833","name":"Dismantle: Part list &amp; Tear Down","order":7,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"c536fdc6-3459-4ab5-a588-3454f07f08c7","job_id":"J03-1833","name":"Assemble: Directional &amp; Idler gear","order":8,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"89d1ae15-daf2-4871-9bc0-5940279c96f6","job_id":"J03-1833","name":"Assemble: Planetary GP","order":9,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"1197b5dd-9928-4565-ae50-91f382e2beb0","job_id":"J03-1833","name":"Assemble: CV 2EA","order":10,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"6a936f7e-e97a-47f4-9e03-24e38ef315fc","job_id":"J03-1833","name":"Assemble: Pump, Lines, &amp; Screen","order":11,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"80894723-ea93-40ff-aa35-420c027d3f95","job_id":"J03-1833","name":"Test Bench &amp; Completed: Set up","order":12,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"acf6bd0c-0d96-40b6-8b9e-ee8c27ee1625","job_id":"J03-1833","name":"Test Bench &amp; Completed: Test","order":13,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"81692dde-b76a-433d-9b5d-3476cf3cd7f6","job_id":"J03-1833","name":"Test Bench &amp; Completed: Release","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"b69b87c3-9d4b-450e-8c0e-162eb755ff75","job_id":"J03-1833","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300}],"assignees":[{"id":"a58e3fbd-80eb-4c64-bd6b-bb7196830ed8","job_id":"J03-1833","technician_id":"T-c23ed9a4","assigned_at":"2026-08-11T05:31:58.767Z","is_lead":"1"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-c23ed9a4","status":"busy","current_job_id":"J03-1833"}]}</t>
+  </si>
+  <si>
+    <t>5ff4ea84-4693-4b8f-9a80-0c2496d19fd5</t>
+  </si>
+  <si>
+    <t>2026-08-13T12:24:20.771Z</t>
+  </si>
+  <si>
+    <t>{"job":{"id":"J03-1833","title":"Recondition Transmission 16H,G","unit":"E448 — D10T","unit_id":"a5c2144b-1b29-40f7-9b5c-cfbbc03c3387","description":"Job recondition Transmission 16H,G (time frame standar).","status":"in_progress","technician_id":"T-c23ed9a4","template_id":"ne-transmission-16h-g","created_at":"2026-08-11T05:30:21.056Z","started_at":"2026-08-11T05:32:14.074Z","completed_at":"","paused_at":"","total_paused_sec":1281,"estimated_minutes":5340},"steps":[{"id":"e21019ab-05cb-4d4f-8f8f-fb85fa9004da","job_id":"J03-1833","name":"Dismantle: Washing Transmission gp","order":1,"status":"done","started_at":"2026-08-11T05:32:14.074Z","completed_at":"2026-08-11T23:52:49.552Z","duration_sec":66035,"std_minutes":240},{"id":"5ceecb87-2473-4297-a2a0-db873217f383","job_id":"J03-1833","name":"Dismantle: Control Valve 2EA","order":2,"status":"done","started_at":"2026-08-11T05:32:33.253Z","completed_at":"2026-08-11T23:52:32.616Z","duration_sec":65999,"std_minutes":300},{"id":"11997f0b-4cc8-4b54-8bdd-db3614b948c1","job_id":"J03-1833","name":"Dismantle: Pump, Lines, &amp; Screen","order":3,"status":"done","started_at":"2026-08-11T05:32:33.253Z","completed_at":"2026-08-11T23:52:51.817Z","duration_sec":66018,"std_minutes":240},{"id":"6c426149-ef7a-48c2-9585-5909fe86eca9","job_id":"J03-1833","name":"Dismantle: Planetary GP","order":4,"status":"done","started_at":"2026-08-11T23:52:51.817Z","completed_at":"2026-08-13T12:08:28.871Z","duration_sec":130537,"std_minutes":900},{"id":"5d3baced-8d6d-491b-9df4-09eaef47f6b9","job_id":"J03-1833","name":"Dismantle: Directional &amp; Idler gear","order":5,"status":"done","started_at":"2026-08-13T12:08:28.871Z","completed_at":"2026-08-13T12:08:40.688Z","duration_sec":11,"std_minutes":300},{"id":"0feaac14-da1a-4360-98f3-a99ad7b2fd45","job_id":"J03-1833","name":"Dismantle: Clean up Housing 2ea","order":6,"status":"in_progress","started_at":"2026-08-13T12:24:20.713Z","completed_at":"","duration_sec":136,"std_minutes":120},{"id":"5b00b8bb-18f9-4ef9-ac8c-5d5f25f11170","job_id":"J03-1833","name":"Dismantle: Part list &amp; Tear Down","order":7,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"c536fdc6-3459-4ab5-a588-3454f07f08c7","job_id":"J03-1833","name":"Assemble: Directional &amp; Idler gear","order":8,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"89d1ae15-daf2-4871-9bc0-5940279c96f6","job_id":"J03-1833","name":"Assemble: Planetary GP","order":9,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"1197b5dd-9928-4565-ae50-91f382e2beb0","job_id":"J03-1833","name":"Assemble: CV 2EA","order":10,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"6a936f7e-e97a-47f4-9e03-24e38ef315fc","job_id":"J03-1833","name":"Assemble: Pump, Lines, &amp; Screen","order":11,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"80894723-ea93-40ff-aa35-420c027d3f95","job_id":"J03-1833","name":"Test Bench &amp; Completed: Set up","order":12,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"acf6bd0c-0d96-40b6-8b9e-ee8c27ee1625","job_id":"J03-1833","name":"Test Bench &amp; Completed: Test","order":13,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"81692dde-b76a-433d-9b5d-3476cf3cd7f6","job_id":"J03-1833","name":"Test Bench &amp; Completed: Release","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"b69b87c3-9d4b-450e-8c0e-162eb755ff75","job_id":"J03-1833","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300}],"assignees":[{"id":"a58e3fbd-80eb-4c64-bd6b-bb7196830ed8","job_id":"J03-1833","technician_id":"T-c23ed9a4","assigned_at":"2026-08-11T05:31:58.767Z","is_lead":"1"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-c23ed9a4","status":"busy","current_job_id":"J03-1833"}]}</t>
+  </si>
+  <si>
+    <t>bc203c6f-c836-43e8-9fd1-7d3a9771ee0a</t>
+  </si>
+  <si>
+    <t>2026-08-13T12:24:21.303Z</t>
+  </si>
+  <si>
+    <t>{"job":{"id":"J03-1833","title":"Recondition Transmission 16H,G","unit":"E448 — D10T","unit_id":"a5c2144b-1b29-40f7-9b5c-cfbbc03c3387","description":"Job recondition Transmission 16H,G (time frame standar).","status":"paused","technician_id":"T-c23ed9a4","template_id":"ne-transmission-16h-g","created_at":"2026-08-11T05:30:21.056Z","started_at":"2026-08-11T05:32:14.074Z","completed_at":"","paused_at":"2026-08-13T12:18:41.540Z","total_paused_sec":1281,"estimated_minutes":5340},"steps":[{"id":"e21019ab-05cb-4d4f-8f8f-fb85fa9004da","job_id":"J03-1833","name":"Dismantle: Washing Transmission gp","order":1,"status":"done","started_at":"2026-08-11T05:32:14.074Z","completed_at":"2026-08-11T23:52:49.552Z","duration_sec":66035,"std_minutes":240},{"id":"5ceecb87-2473-4297-a2a0-db873217f383","job_id":"J03-1833","name":"Dismantle: Control Valve 2EA","order":2,"status":"done","started_at":"2026-08-11T05:32:33.253Z","completed_at":"2026-08-11T23:52:32.616Z","duration_sec":65999,"std_minutes":300},{"id":"11997f0b-4cc8-4b54-8bdd-db3614b948c1","job_id":"J03-1833","name":"Dismantle: Pump, Lines, &amp; Screen","order":3,"status":"done","started_at":"2026-08-11T05:32:33.253Z","completed_at":"2026-08-11T23:52:51.817Z","duration_sec":66018,"std_minutes":240},{"id":"6c426149-ef7a-48c2-9585-5909fe86eca9","job_id":"J03-1833","name":"Dismantle: Planetary GP","order":4,"status":"done","started_at":"2026-08-11T23:52:51.817Z","completed_at":"2026-08-13T12:08:28.871Z","duration_sec":130537,"std_minutes":900},{"id":"5d3baced-8d6d-491b-9df4-09eaef47f6b9","job_id":"J03-1833","name":"Dismantle: Directional &amp; Idler gear","order":5,"status":"done","started_at":"2026-08-13T12:08:28.871Z","completed_at":"2026-08-13T12:08:40.688Z","duration_sec":11,"std_minutes":300},{"id":"0feaac14-da1a-4360-98f3-a99ad7b2fd45","job_id":"J03-1833","name":"Dismantle: Clean up Housing 2ea","order":6,"status":"in_progress","started_at":"","completed_at":"","duration_sec":142,"std_minutes":120},{"id":"5b00b8bb-18f9-4ef9-ac8c-5d5f25f11170","job_id":"J03-1833","name":"Dismantle: Part list &amp; Tear Down","order":7,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"c536fdc6-3459-4ab5-a588-3454f07f08c7","job_id":"J03-1833","name":"Assemble: Directional &amp; Idler gear","order":8,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"89d1ae15-daf2-4871-9bc0-5940279c96f6","job_id":"J03-1833","name":"Assemble: Planetary GP","order":9,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"1197b5dd-9928-4565-ae50-91f382e2beb0","job_id":"J03-1833","name":"Assemble: CV 2EA","order":10,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"6a936f7e-e97a-47f4-9e03-24e38ef315fc","job_id":"J03-1833","name":"Assemble: Pump, Lines, &amp; Screen","order":11,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"80894723-ea93-40ff-aa35-420c027d3f95","job_id":"J03-1833","name":"Test Bench &amp; Completed: Set up","order":12,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"acf6bd0c-0d96-40b6-8b9e-ee8c27ee1625","job_id":"J03-1833","name":"Test Bench &amp; Completed: Test","order":13,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"81692dde-b76a-433d-9b5d-3476cf3cd7f6","job_id":"J03-1833","name":"Test Bench &amp; Completed: Release","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"b69b87c3-9d4b-450e-8c0e-162eb755ff75","job_id":"J03-1833","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300}],"assignees":[{"id":"a58e3fbd-80eb-4c64-bd6b-bb7196830ed8","job_id":"J03-1833","technician_id":"T-c23ed9a4","assigned_at":"2026-08-11T05:31:58.767Z","is_lead":"1"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-c23ed9a4","status":"busy","current_job_id":"J03-1833"}]}</t>
+  </si>
+  <si>
+    <t>d06372d7-b3d1-41b2-980c-bd76aeb2e566</t>
+  </si>
+  <si>
+    <t>2026-08-13T12:24:21.710Z</t>
+  </si>
+  <si>
+    <t>{"job":{"id":"J03-1833","title":"Recondition Transmission 16H,G","unit":"E448 — D10T","unit_id":"a5c2144b-1b29-40f7-9b5c-cfbbc03c3387","description":"Job recondition Transmission 16H,G (time frame standar).","status":"in_progress","technician_id":"T-c23ed9a4","template_id":"ne-transmission-16h-g","created_at":"2026-08-11T05:30:21.056Z","started_at":"2026-08-11T05:32:14.074Z","completed_at":"","paused_at":"","total_paused_sec":1621,"estimated_minutes":5340},"steps":[{"id":"e21019ab-05cb-4d4f-8f8f-fb85fa9004da","job_id":"J03-1833","name":"Dismantle: Washing Transmission gp","order":1,"status":"done","started_at":"2026-08-11T05:32:14.074Z","completed_at":"2026-08-11T23:52:49.552Z","duration_sec":66035,"std_minutes":240},{"id":"5ceecb87-2473-4297-a2a0-db873217f383","job_id":"J03-1833","name":"Dismantle: Control Valve 2EA","order":2,"status":"done","started_at":"2026-08-11T05:32:33.253Z","completed_at":"2026-08-11T23:52:32.616Z","duration_sec":65999,"std_minutes":300},{"id":"11997f0b-4cc8-4b54-8bdd-db3614b948c1","job_id":"J03-1833","name":"Dismantle: Pump, Lines, &amp; Screen","order":3,"status":"done","started_at":"2026-08-11T05:32:33.253Z","completed_at":"2026-08-11T23:52:51.817Z","duration_sec":66018,"std_minutes":240},{"id":"6c426149-ef7a-48c2-9585-5909fe86eca9","job_id":"J03-1833","name":"Dismantle: Planetary GP","order":4,"status":"done","started_at":"2026-08-11T23:52:51.817Z","completed_at":"2026-08-13T12:08:28.871Z","duration_sec":130537,"std_minutes":900},{"id":"5d3baced-8d6d-491b-9df4-09eaef47f6b9","job_id":"J03-1833","name":"Dismantle: Directional &amp; Idler gear","order":5,"status":"done","started_at":"2026-08-13T12:08:28.871Z","completed_at":"2026-08-13T12:08:40.688Z","duration_sec":11,"std_minutes":300},{"id":"0feaac14-da1a-4360-98f3-a99ad7b2fd45","job_id":"J03-1833","name":"Dismantle: Clean up Housing 2ea","order":6,"status":"in_progress","started_at":"2026-08-13T12:24:21.671Z","completed_at":"","duration_sec":142,"std_minutes":120},{"id":"5b00b8bb-18f9-4ef9-ac8c-5d5f25f11170","job_id":"J03-1833","name":"Dismantle: Part list &amp; Tear Down","order":7,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"c536fdc6-3459-4ab5-a588-3454f07f08c7","job_id":"J03-1833","name":"Assemble: Directional &amp; Idler gear","order":8,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"89d1ae15-daf2-4871-9bc0-5940279c96f6","job_id":"J03-1833","name":"Assemble: Planetary GP","order":9,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"1197b5dd-9928-4565-ae50-91f382e2beb0","job_id":"J03-1833","name":"Assemble: CV 2EA","order":10,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"6a936f7e-e97a-47f4-9e03-24e38ef315fc","job_id":"J03-1833","name":"Assemble: Pump, Lines, &amp; Screen","order":11,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"80894723-ea93-40ff-aa35-420c027d3f95","job_id":"J03-1833","name":"Test Bench &amp; Completed: Set up","order":12,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"acf6bd0c-0d96-40b6-8b9e-ee8c27ee1625","job_id":"J03-1833","name":"Test Bench &amp; Completed: Test","order":13,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"81692dde-b76a-433d-9b5d-3476cf3cd7f6","job_id":"J03-1833","name":"Test Bench &amp; Completed: Release","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"b69b87c3-9d4b-450e-8c0e-162eb755ff75","job_id":"J03-1833","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300}],"assignees":[{"id":"a58e3fbd-80eb-4c64-bd6b-bb7196830ed8","job_id":"J03-1833","technician_id":"T-c23ed9a4","assigned_at":"2026-08-11T05:31:58.767Z","is_lead":"1"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-c23ed9a4","status":"busy","current_job_id":"J03-1833"}]}</t>
+  </si>
+  <si>
+    <t>f8aa6294-0c7f-43a8-953a-ae7c34272036</t>
+  </si>
+  <si>
+    <t>2026-08-13T12:24:22.076Z</t>
+  </si>
+  <si>
+    <t>{"job":{"id":"J03-1833","title":"Recondition Transmission 16H,G","unit":"E448 — D10T","unit_id":"a5c2144b-1b29-40f7-9b5c-cfbbc03c3387","description":"Job recondition Transmission 16H,G (time frame standar).","status":"paused","technician_id":"T-c23ed9a4","template_id":"ne-transmission-16h-g","created_at":"2026-08-11T05:30:21.056Z","started_at":"2026-08-11T05:32:14.074Z","completed_at":"","paused_at":"2026-08-13T12:19:15.570Z","total_paused_sec":1621,"estimated_minutes":5340},"steps":[{"id":"e21019ab-05cb-4d4f-8f8f-fb85fa9004da","job_id":"J03-1833","name":"Dismantle: Washing Transmission gp","order":1,"status":"done","started_at":"2026-08-11T05:32:14.074Z","completed_at":"2026-08-11T23:52:49.552Z","duration_sec":66035,"std_minutes":240},{"id":"5ceecb87-2473-4297-a2a0-db873217f383","job_id":"J03-1833","name":"Dismantle: Control Valve 2EA","order":2,"status":"done","started_at":"2026-08-11T05:32:33.253Z","completed_at":"2026-08-11T23:52:32.616Z","duration_sec":65999,"std_minutes":300},{"id":"11997f0b-4cc8-4b54-8bdd-db3614b948c1","job_id":"J03-1833","name":"Dismantle: Pump, Lines, &amp; Screen","order":3,"status":"done","started_at":"2026-08-11T05:32:33.253Z","completed_at":"2026-08-11T23:52:51.817Z","duration_sec":66018,"std_minutes":240},{"id":"6c426149-ef7a-48c2-9585-5909fe86eca9","job_id":"J03-1833","name":"Dismantle: Planetary GP","order":4,"status":"done","started_at":"2026-08-11T23:52:51.817Z","completed_at":"2026-08-13T12:08:28.871Z","duration_sec":130537,"std_minutes":900},{"id":"5d3baced-8d6d-491b-9df4-09eaef47f6b9","job_id":"J03-1833","name":"Dismantle: Directional &amp; Idler gear","order":5,"status":"done","started_at":"2026-08-13T12:08:28.871Z","completed_at":"2026-08-13T12:08:40.688Z","duration_sec":11,"std_minutes":300},{"id":"0feaac14-da1a-4360-98f3-a99ad7b2fd45","job_id":"J03-1833","name":"Dismantle: Clean up Housing 2ea","order":6,"status":"in_progress","started_at":"","completed_at":"","duration_sec":156,"std_minutes":120},{"id":"5b00b8bb-18f9-4ef9-ac8c-5d5f25f11170","job_id":"J03-1833","name":"Dismantle: Part list &amp; Tear Down","order":7,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"c536fdc6-3459-4ab5-a588-3454f07f08c7","job_id":"J03-1833","name":"Assemble: Directional &amp; Idler gear","order":8,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"89d1ae15-daf2-4871-9bc0-5940279c96f6","job_id":"J03-1833","name":"Assemble: Planetary GP","order":9,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"1197b5dd-9928-4565-ae50-91f382e2beb0","job_id":"J03-1833","name":"Assemble: CV 2EA","order":10,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"6a936f7e-e97a-47f4-9e03-24e38ef315fc","job_id":"J03-1833","name":"Assemble: Pump, Lines, &amp; Screen","order":11,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"80894723-ea93-40ff-aa35-420c027d3f95","job_id":"J03-1833","name":"Test Bench &amp; Completed: Set up","order":12,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"acf6bd0c-0d96-40b6-8b9e-ee8c27ee1625","job_id":"J03-1833","name":"Test Bench &amp; Completed: Test","order":13,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"81692dde-b76a-433d-9b5d-3476cf3cd7f6","job_id":"J03-1833","name":"Test Bench &amp; Completed: Release","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"b69b87c3-9d4b-450e-8c0e-162eb755ff75","job_id":"J03-1833","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300}],"assignees":[{"id":"a58e3fbd-80eb-4c64-bd6b-bb7196830ed8","job_id":"J03-1833","technician_id":"T-c23ed9a4","assigned_at":"2026-08-11T05:31:58.767Z","is_lead":"1"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-c23ed9a4","status":"busy","current_job_id":"J03-1833"}]}</t>
+  </si>
+  <si>
+    <t>f6169f65-ad04-41a9-b7a6-86174954d36e</t>
+  </si>
+  <si>
+    <t>2026-08-13T12:24:22.431Z</t>
+  </si>
+  <si>
+    <t>{"job":{"id":"J03-1833","title":"Recondition Transmission 16H,G","unit":"E448 — D10T","unit_id":"a5c2144b-1b29-40f7-9b5c-cfbbc03c3387","description":"Job recondition Transmission 16H,G (time frame standar).","status":"in_progress","technician_id":"T-c23ed9a4","template_id":"ne-transmission-16h-g","created_at":"2026-08-11T05:30:21.056Z","started_at":"2026-08-11T05:32:14.074Z","completed_at":"","paused_at":"","total_paused_sec":1927,"estimated_minutes":5340},"steps":[{"id":"e21019ab-05cb-4d4f-8f8f-fb85fa9004da","job_id":"J03-1833","name":"Dismantle: Washing Transmission gp","order":1,"status":"done","started_at":"2026-08-11T05:32:14.074Z","completed_at":"2026-08-11T23:52:49.552Z","duration_sec":66035,"std_minutes":240},{"id":"5ceecb87-2473-4297-a2a0-db873217f383","job_id":"J03-1833","name":"Dismantle: Control Valve 2EA","order":2,"status":"done","started_at":"2026-08-11T05:32:33.253Z","completed_at":"2026-08-11T23:52:32.616Z","duration_sec":65999,"std_minutes":300},{"id":"11997f0b-4cc8-4b54-8bdd-db3614b948c1","job_id":"J03-1833","name":"Dismantle: Pump, Lines, &amp; Screen","order":3,"status":"done","started_at":"2026-08-11T05:32:33.253Z","completed_at":"2026-08-11T23:52:51.817Z","duration_sec":66018,"std_minutes":240},{"id":"6c426149-ef7a-48c2-9585-5909fe86eca9","job_id":"J03-1833","name":"Dismantle: Planetary GP","order":4,"status":"done","started_at":"2026-08-11T23:52:51.817Z","completed_at":"2026-08-13T12:08:28.871Z","duration_sec":130537,"std_minutes":900},{"id":"5d3baced-8d6d-491b-9df4-09eaef47f6b9","job_id":"J03-1833","name":"Dismantle: Directional &amp; Idler gear","order":5,"status":"done","started_at":"2026-08-13T12:08:28.871Z","completed_at":"2026-08-13T12:08:40.688Z","duration_sec":11,"std_minutes":300},{"id":"0feaac14-da1a-4360-98f3-a99ad7b2fd45","job_id":"J03-1833","name":"Dismantle: Clean up Housing 2ea","order":6,"status":"in_progress","started_at":"2026-08-13T12:24:22.396Z","completed_at":"","duration_sec":156,"std_minutes":120},{"id":"5b00b8bb-18f9-4ef9-ac8c-5d5f25f11170","job_id":"J03-1833","name":"Dismantle: Part list &amp; Tear Down","order":7,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"c536fdc6-3459-4ab5-a588-3454f07f08c7","job_id":"J03-1833","name":"Assemble: Directional &amp; Idler gear","order":8,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"89d1ae15-daf2-4871-9bc0-5940279c96f6","job_id":"J03-1833","name":"Assemble: Planetary GP","order":9,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"1197b5dd-9928-4565-ae50-91f382e2beb0","job_id":"J03-1833","name":"Assemble: CV 2EA","order":10,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"6a936f7e-e97a-47f4-9e03-24e38ef315fc","job_id":"J03-1833","name":"Assemble: Pump, Lines, &amp; Screen","order":11,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"80894723-ea93-40ff-aa35-420c027d3f95","job_id":"J03-1833","name":"Test Bench &amp; Completed: Set up","order":12,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"acf6bd0c-0d96-40b6-8b9e-ee8c27ee1625","job_id":"J03-1833","name":"Test Bench &amp; Completed: Test","order":13,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"81692dde-b76a-433d-9b5d-3476cf3cd7f6","job_id":"J03-1833","name":"Test Bench &amp; Completed: Release","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"b69b87c3-9d4b-450e-8c0e-162eb755ff75","job_id":"J03-1833","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300}],"assignees":[{"id":"a58e3fbd-80eb-4c64-bd6b-bb7196830ed8","job_id":"J03-1833","technician_id":"T-c23ed9a4","assigned_at":"2026-08-11T05:31:58.767Z","is_lead":"1"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-c23ed9a4","status":"busy","current_job_id":"J03-1833"}]}</t>
+  </si>
+  <si>
+    <t>40db843c-1a62-450a-8a01-96069e30221d</t>
+  </si>
+  <si>
+    <t>2026-08-13T12:24:31.835Z</t>
+  </si>
+  <si>
+    <t>{"job":{"id":"J03-c0e2","title":"Recondition Transmission D10T,R","unit":"E448 — D10T","unit_id":"a5c2144b-1b29-40f7-9b5c-cfbbc03c3387","description":"Job recondition Transmission D10T,R (time frame standar).","status":"paused","technician_id":"T-533ca22c","template_id":"ne-transmission-d10t-r","created_at":"2026-08-10T08:22:13.799Z","started_at":"2026-08-10T08:23:20.053Z","completed_at":"","paused_at":"2026-08-13T12:24:31.573Z","total_paused_sec":3,"estimated_minutes":5820},"steps":[{"id":"7609ebf3-f1eb-4d9d-9591-f21d853034e1","job_id":"J03-c0e2","name":"Dismantle: Washing Transmission","order":1,"status":"done","started_at":"2026-08-10T08:23:20.053Z","completed_at":"2026-08-10T08:24:03.692Z","duration_sec":43,"std_minutes":60},{"id":"a3923555-21a4-4b60-9959-c48d814bf136","job_id":"J03-c0e2","name":"Dismantle: Trans Gear","order":2,"status":"done","started_at":"2026-08-10T08:23:32.872Z","completed_at":"2026-08-10T08:24:06.672Z","duration_sec":33,"std_minutes":600},{"id":"39c70957-da00-4dc8-a988-36ee41ef9841","job_id":"J03-c0e2","name":"Dismantle: CV, Harness, &amp; Sensor","order":3,"status":"done","started_at":"2026-08-10T08:24:08.700Z","completed_at":"2026-08-10T08:24:14.772Z","duration_sec":6,"std_minutes":300},{"id":"6feb4f63-8277-4c8a-a4cf-8d8a3d660682","job_id":"J03-c0e2","name":"Dismantle: Clutch 5","order":4,"status":"done","started_at":"2026-08-10T08:23:32.872Z","completed_at":"2026-08-10T08:24:08.700Z","duration_sec":35,"std_minutes":180},{"id":"179574f5-b3d7-43e4-a065-977ebd015bfc","job_id":"J03-c0e2","name":"Dismantle: Clutch 4","order":5,"status":"done","started_at":"2026-08-10T08:24:14.772Z","completed_at":"2026-08-10T10:10:28.558Z","duration_sec":6373,"std_minutes":180},{"id":"8aff0e07-0f40-4945-a9dc-7a8867ffccf4","job_id":"J03-c0e2","name":"Dismantle: Clutch 3","order":6,"status":"done","started_at":"2026-08-11T05:33:18.994Z","completed_at":"2026-08-11T05:33:34.800Z","duration_sec":69782,"std_minutes":180},{"id":"82415ef2-23b1-4eb2-b027-a268df0f4189","job_id":"J03-c0e2","name":"Dismantle: Clutch 2","order":7,"status":"done","started_at":"2026-08-11T05:33:34.800Z","completed_at":"2026-08-11T05:33:47.115Z","duration_sec":12,"std_minutes":180},{"id":"f7c8bcdc-e2d1-4856-aea1-f577d25b0550","job_id":"J03-c0e2","name":"Dismantle: Clutch 1","order":8,"status":"done","started_at":"2026-08-11T05:33:47.115Z","completed_at":"2026-08-11T15:28:10.891Z","duration_sec":35663,"std_minutes":180},{"id":"4391d523-f1d0-4922-95fb-d3827a21b813","job_id":"J03-c0e2","name":"Dismantle: Planetary &amp; Shaft","order":9,"status":"done","started_at":"2026-08-11T15:28:10.891Z","completed_at":"2026-08-11T23:53:02.227Z","duration_sec":30291,"std_minutes":300},{"id":"bdcc79ae-9f46-46e2-963d-fd2ba3d40a2e","job_id":"J03-c0e2","name":"Dismantle: Part list &amp; Tear Down","order":10,"status":"done","started_at":"2026-08-11T23:53:02.227Z","completed_at":"2026-08-12T03:13:34.783Z","duration_sec":12032,"std_minutes":240},{"id":"0670c5ee-3df9-46ba-a7e5-790a2591233a","job_id":"J03-c0e2","name":"Assemble: Planetary &amp; Shaft In-Out","order":11,"status":"done","started_at":"2026-08-12T03:13:34.783Z","completed_at":"2026-08-13T12:03:07.679Z","duration_sec":118172,"std_minutes":300},{"id":"7276104d-e8c7-4ea6-aac7-6cd975141c45","job_id":"J03-c0e2","name":"Assemble: Clutch 1","order":12,"status":"in_progress","started_at":"","completed_at":"","duration_sec":1283,"std_minutes":180},{"id":"1781ebaa-7fb0-4896-b642-71d33b8c4878","job_id":"J03-c0e2","name":"Assemble: Clutch 2","order":13,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"5532b99d-a7fd-4b7d-a752-796f7bc5daff","job_id":"J03-c0e2","name":"Assemble: Clutch 3","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"ff0ed73f-27d1-4b0a-a4f2-7818d3cfbc7e","job_id":"J03-c0e2","name":"Assemble: Clutch 4","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"970a35a3-a96b-48b4-9f04-a2b921b013f0","job_id":"J03-c0e2","name":"Assemble: Clutch 5","order":16,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"698b11d9-e1a3-451f-8a47-ccabcc5718c6","job_id":"J03-c0e2","name":"Assemble: CV, Harness &amp; Sensor","order":17,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"0620fee8-23da-434a-85e6-6354dee830d7","job_id":"J03-c0e2","name":"Assemble: Trans Gear","order":18,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":900},{"id":"ca31c8c2-4542-42f7-be4e-86974a63447b","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Set up","order":19,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"ba2d158c-a9f5-4d98-aea1-fd1f7983c4eb","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Test","order":20,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"d2f96316-8f95-487c-a7ee-94ba19ef4354","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Release","order":21,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"050b2cfc-5ea2-4926-b9c1-c7bdfe6bbd49","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":22,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240}],"assignees":[{"id":"5ece1c51-c36b-46e5-a9d2-f9106a729470","job_id":"J03-c0e2","technician_id":"T-533ca22c","assigned_at":"2026-08-10T08:23:08.120Z","is_lead":"1"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-533ca22c","status":"busy","current_job_id":"J03-c0e2"}]}</t>
+  </si>
+  <si>
+    <t>ea0e48af-f876-42d8-88e7-3e1b7056e0ea</t>
+  </si>
+  <si>
+    <t>2026-08-13T12:24:45.852Z</t>
+  </si>
+  <si>
+    <t>{"job":{"id":"J03-c0e2","title":"Recondition Transmission D10T,R","unit":"E448 — D10T","unit_id":"a5c2144b-1b29-40f7-9b5c-cfbbc03c3387","description":"Job recondition Transmission D10T,R (time frame standar).","status":"in_progress","technician_id":"T-533ca22c","template_id":"ne-transmission-d10t-r","created_at":"2026-08-10T08:22:13.799Z","started_at":"2026-08-10T08:23:20.053Z","completed_at":"","paused_at":"","total_paused_sec":17,"estimated_minutes":5820},"steps":[{"id":"7609ebf3-f1eb-4d9d-9591-f21d853034e1","job_id":"J03-c0e2","name":"Dismantle: Washing Transmission","order":1,"status":"done","started_at":"2026-08-10T08:23:20.053Z","completed_at":"2026-08-10T08:24:03.692Z","duration_sec":43,"std_minutes":60},{"id":"a3923555-21a4-4b60-9959-c48d814bf136","job_id":"J03-c0e2","name":"Dismantle: Trans Gear","order":2,"status":"done","started_at":"2026-08-10T08:23:32.872Z","completed_at":"2026-08-10T08:24:06.672Z","duration_sec":33,"std_minutes":600},{"id":"39c70957-da00-4dc8-a988-36ee41ef9841","job_id":"J03-c0e2","name":"Dismantle: CV, Harness, &amp; Sensor","order":3,"status":"done","started_at":"2026-08-10T08:24:08.700Z","completed_at":"2026-08-10T08:24:14.772Z","duration_sec":6,"std_minutes":300},{"id":"6feb4f63-8277-4c8a-a4cf-8d8a3d660682","job_id":"J03-c0e2","name":"Dismantle: Clutch 5","order":4,"status":"done","started_at":"2026-08-10T08:23:32.872Z","completed_at":"2026-08-10T08:24:08.700Z","duration_sec":35,"std_minutes":180},{"id":"179574f5-b3d7-43e4-a065-977ebd015bfc","job_id":"J03-c0e2","name":"Dismantle: Clutch 4","order":5,"status":"done","started_at":"2026-08-10T08:24:14.772Z","completed_at":"2026-08-10T10:10:28.558Z","duration_sec":6373,"std_minutes":180},{"id":"8aff0e07-0f40-4945-a9dc-7a8867ffccf4","job_id":"J03-c0e2","name":"Dismantle: Clutch 3","order":6,"status":"done","started_at":"2026-08-11T05:33:18.994Z","completed_at":"2026-08-11T05:33:34.800Z","duration_sec":69782,"std_minutes":180},{"id":"82415ef2-23b1-4eb2-b027-a268df0f4189","job_id":"J03-c0e2","name":"Dismantle: Clutch 2","order":7,"status":"done","started_at":"2026-08-11T05:33:34.800Z","completed_at":"2026-08-11T05:33:47.115Z","duration_sec":12,"std_minutes":180},{"id":"f7c8bcdc-e2d1-4856-aea1-f577d25b0550","job_id":"J03-c0e2","name":"Dismantle: Clutch 1","order":8,"status":"done","started_at":"2026-08-11T05:33:47.115Z","completed_at":"2026-08-11T15:28:10.891Z","duration_sec":35663,"std_minutes":180},{"id":"4391d523-f1d0-4922-95fb-d3827a21b813","job_id":"J03-c0e2","name":"Dismantle: Planetary &amp; Shaft","order":9,"status":"done","started_at":"2026-08-11T15:28:10.891Z","completed_at":"2026-08-11T23:53:02.227Z","duration_sec":30291,"std_minutes":300},{"id":"bdcc79ae-9f46-46e2-963d-fd2ba3d40a2e","job_id":"J03-c0e2","name":"Dismantle: Part list &amp; Tear Down","order":10,"status":"done","started_at":"2026-08-11T23:53:02.227Z","completed_at":"2026-08-12T03:13:34.783Z","duration_sec":12032,"std_minutes":240},{"id":"0670c5ee-3df9-46ba-a7e5-790a2591233a","job_id":"J03-c0e2","name":"Assemble: Planetary &amp; Shaft In-Out","order":11,"status":"done","started_at":"2026-08-12T03:13:34.783Z","completed_at":"2026-08-13T12:03:07.679Z","duration_sec":118172,"std_minutes":300},{"id":"7276104d-e8c7-4ea6-aac7-6cd975141c45","job_id":"J03-c0e2","name":"Assemble: Clutch 1","order":12,"status":"in_progress","started_at":"2026-08-13T12:24:45.819Z","completed_at":"","duration_sec":1283,"std_minutes":180},{"id":"1781ebaa-7fb0-4896-b642-71d33b8c4878","job_id":"J03-c0e2","name":"Assemble: Clutch 2","order":13,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"5532b99d-a7fd-4b7d-a752-796f7bc5daff","job_id":"J03-c0e2","name":"Assemble: Clutch 3","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"ff0ed73f-27d1-4b0a-a4f2-7818d3cfbc7e","job_id":"J03-c0e2","name":"Assemble: Clutch 4","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"970a35a3-a96b-48b4-9f04-a2b921b013f0","job_id":"J03-c0e2","name":"Assemble: Clutch 5","order":16,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"698b11d9-e1a3-451f-8a47-ccabcc5718c6","job_id":"J03-c0e2","name":"Assemble: CV, Harness &amp; Sensor","order":17,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"0620fee8-23da-434a-85e6-6354dee830d7","job_id":"J03-c0e2","name":"Assemble: Trans Gear","order":18,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":900},{"id":"ca31c8c2-4542-42f7-be4e-86974a63447b","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Set up","order":19,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"ba2d158c-a9f5-4d98-aea1-fd1f7983c4eb","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Test","order":20,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"d2f96316-8f95-487c-a7ee-94ba19ef4354","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Release","order":21,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"050b2cfc-5ea2-4926-b9c1-c7bdfe6bbd49","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":22,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240}],"assignees":[{"id":"5ece1c51-c36b-46e5-a9d2-f9106a729470","job_id":"J03-c0e2","technician_id":"T-533ca22c","assigned_at":"2026-08-10T08:23:08.120Z","is_lead":"1"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-533ca22c","status":"busy","current_job_id":"J03-c0e2"}]}</t>
+  </si>
+  <si>
+    <t>f16870ab-3070-401f-9ba8-37d2401712c1</t>
+  </si>
+  <si>
+    <t>2026-08-13T12:26:33.285Z</t>
+  </si>
+  <si>
+    <t>{"job":{"id":"J03-c0e2","title":"Recondition Transmission D10T,R","unit":"E448 — D10T","unit_id":"a5c2144b-1b29-40f7-9b5c-cfbbc03c3387","description":"Job recondition Transmission D10T,R (time frame standar).","status":"paused","technician_id":"T-533ca22c","template_id":"ne-transmission-d10t-r","created_at":"2026-08-10T08:22:13.799Z","started_at":"2026-08-10T08:23:20.053Z","completed_at":"","paused_at":"2026-08-13T12:25:15.005Z","total_paused_sec":17,"estimated_minutes":5820},"steps":[{"id":"7609ebf3-f1eb-4d9d-9591-f21d853034e1","job_id":"J03-c0e2","name":"Dismantle: Washing Transmission","order":1,"status":"done","started_at":"2026-08-10T08:23:20.053Z","completed_at":"2026-08-10T08:24:03.692Z","duration_sec":43,"std_minutes":60},{"id":"a3923555-21a4-4b60-9959-c48d814bf136","job_id":"J03-c0e2","name":"Dismantle: Trans Gear","order":2,"status":"done","started_at":"2026-08-10T08:23:32.872Z","completed_at":"2026-08-10T08:24:06.672Z","duration_sec":33,"std_minutes":600},{"id":"39c70957-da00-4dc8-a988-36ee41ef9841","job_id":"J03-c0e2","name":"Dismantle: CV, Harness, &amp; Sensor","order":3,"status":"done","started_at":"2026-08-10T08:24:08.700Z","completed_at":"2026-08-10T08:24:14.772Z","duration_sec":6,"std_minutes":300},{"id":"6feb4f63-8277-4c8a-a4cf-8d8a3d660682","job_id":"J03-c0e2","name":"Dismantle: Clutch 5","order":4,"status":"done","started_at":"2026-08-10T08:23:32.872Z","completed_at":"2026-08-10T08:24:08.700Z","duration_sec":35,"std_minutes":180},{"id":"179574f5-b3d7-43e4-a065-977ebd015bfc","job_id":"J03-c0e2","name":"Dismantle: Clutch 4","order":5,"status":"done","started_at":"2026-08-10T08:24:14.772Z","completed_at":"2026-08-10T10:10:28.558Z","duration_sec":6373,"std_minutes":180},{"id":"8aff0e07-0f40-4945-a9dc-7a8867ffccf4","job_id":"J03-c0e2","name":"Dismantle: Clutch 3","order":6,"status":"done","started_at":"2026-08-11T05:33:18.994Z","completed_at":"2026-08-11T05:33:34.800Z","duration_sec":69782,"std_minutes":180},{"id":"82415ef2-23b1-4eb2-b027-a268df0f4189","job_id":"J03-c0e2","name":"Dismantle: Clutch 2","order":7,"status":"done","started_at":"2026-08-11T05:33:34.800Z","completed_at":"2026-08-11T05:33:47.115Z","duration_sec":12,"std_minutes":180},{"id":"f7c8bcdc-e2d1-4856-aea1-f577d25b0550","job_id":"J03-c0e2","name":"Dismantle: Clutch 1","order":8,"status":"done","started_at":"2026-08-11T05:33:47.115Z","completed_at":"2026-08-11T15:28:10.891Z","duration_sec":35663,"std_minutes":180},{"id":"4391d523-f1d0-4922-95fb-d3827a21b813","job_id":"J03-c0e2","name":"Dismantle: Planetary &amp; Shaft","order":9,"status":"done","started_at":"2026-08-11T15:28:10.891Z","completed_at":"2026-08-11T23:53:02.227Z","duration_sec":30291,"std_minutes":300},{"id":"bdcc79ae-9f46-46e2-963d-fd2ba3d40a2e","job_id":"J03-c0e2","name":"Dismantle: Part list &amp; Tear Down","order":10,"status":"done","started_at":"2026-08-11T23:53:02.227Z","completed_at":"2026-08-12T03:13:34.783Z","duration_sec":12032,"std_minutes":240},{"id":"0670c5ee-3df9-46ba-a7e5-790a2591233a","job_id":"J03-c0e2","name":"Assemble: Planetary &amp; Shaft In-Out","order":11,"status":"done","started_at":"2026-08-12T03:13:34.783Z","completed_at":"2026-08-13T12:03:07.679Z","duration_sec":118172,"std_minutes":300},{"id":"7276104d-e8c7-4ea6-aac7-6cd975141c45","job_id":"J03-c0e2","name":"Assemble: Clutch 1","order":12,"status":"in_progress","started_at":"","completed_at":"","duration_sec":1312,"std_minutes":180},{"id":"1781ebaa-7fb0-4896-b642-71d33b8c4878","job_id":"J03-c0e2","name":"Assemble: Clutch 2","order":13,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"5532b99d-a7fd-4b7d-a752-796f7bc5daff","job_id":"J03-c0e2","name":"Assemble: Clutch 3","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"ff0ed73f-27d1-4b0a-a4f2-7818d3cfbc7e","job_id":"J03-c0e2","name":"Assemble: Clutch 4","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"970a35a3-a96b-48b4-9f04-a2b921b013f0","job_id":"J03-c0e2","name":"Assemble: Clutch 5","order":16,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"698b11d9-e1a3-451f-8a47-ccabcc5718c6","job_id":"J03-c0e2","name":"Assemble: CV, Harness &amp; Sensor","order":17,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"0620fee8-23da-434a-85e6-6354dee830d7","job_id":"J03-c0e2","name":"Assemble: Trans Gear","order":18,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":900},{"id":"ca31c8c2-4542-42f7-be4e-86974a63447b","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Set up","order":19,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"ba2d158c-a9f5-4d98-aea1-fd1f7983c4eb","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Test","order":20,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"d2f96316-8f95-487c-a7ee-94ba19ef4354","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Release","order":21,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"050b2cfc-5ea2-4926-b9c1-c7bdfe6bbd49","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":22,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240}],"assignees":[{"id":"5ece1c51-c36b-46e5-a9d2-f9106a729470","job_id":"J03-c0e2","technician_id":"T-533ca22c","assigned_at":"2026-08-10T08:23:08.120Z","is_lead":"1"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-533ca22c","status":"busy","current_job_id":"J03-c0e2"}]}</t>
+  </si>
+  <si>
+    <t>9c70e4b9-448a-4030-977d-0b493a4ae75e</t>
+  </si>
+  <si>
+    <t>2026-08-13T12:26:33.860Z</t>
+  </si>
+  <si>
+    <t>{"job":{"id":"J03-c0e2","title":"Recondition Transmission D10T,R","unit":"E448 — D10T","unit_id":"a5c2144b-1b29-40f7-9b5c-cfbbc03c3387","description":"Job recondition Transmission D10T,R (time frame standar).","status":"in_progress","technician_id":"T-533ca22c","template_id":"ne-transmission-d10t-r","created_at":"2026-08-10T08:22:13.799Z","started_at":"2026-08-10T08:23:20.053Z","completed_at":"","paused_at":"","total_paused_sec":95,"estimated_minutes":5820},"steps":[{"id":"7609ebf3-f1eb-4d9d-9591-f21d853034e1","job_id":"J03-c0e2","name":"Dismantle: Washing Transmission","order":1,"status":"done","started_at":"2026-08-10T08:23:20.053Z","completed_at":"2026-08-10T08:24:03.692Z","duration_sec":43,"std_minutes":60},{"id":"a3923555-21a4-4b60-9959-c48d814bf136","job_id":"J03-c0e2","name":"Dismantle: Trans Gear","order":2,"status":"done","started_at":"2026-08-10T08:23:32.872Z","completed_at":"2026-08-10T08:24:06.672Z","duration_sec":33,"std_minutes":600},{"id":"39c70957-da00-4dc8-a988-36ee41ef9841","job_id":"J03-c0e2","name":"Dismantle: CV, Harness, &amp; Sensor","order":3,"status":"done","started_at":"2026-08-10T08:24:08.700Z","completed_at":"2026-08-10T08:24:14.772Z","duration_sec":6,"std_minutes":300},{"id":"6feb4f63-8277-4c8a-a4cf-8d8a3d660682","job_id":"J03-c0e2","name":"Dismantle: Clutch 5","order":4,"status":"done","started_at":"2026-08-10T08:23:32.872Z","completed_at":"2026-08-10T08:24:08.700Z","duration_sec":35,"std_minutes":180},{"id":"179574f5-b3d7-43e4-a065-977ebd015bfc","job_id":"J03-c0e2","name":"Dismantle: Clutch 4","order":5,"status":"done","started_at":"2026-08-10T08:24:14.772Z","completed_at":"2026-08-10T10:10:28.558Z","duration_sec":6373,"std_minutes":180},{"id":"8aff0e07-0f40-4945-a9dc-7a8867ffccf4","job_id":"J03-c0e2","name":"Dismantle: Clutch 3","order":6,"status":"done","started_at":"2026-08-11T05:33:18.994Z","completed_at":"2026-08-11T05:33:34.800Z","duration_sec":69782,"std_minutes":180},{"id":"82415ef2-23b1-4eb2-b027-a268df0f4189","job_id":"J03-c0e2","name":"Dismantle: Clutch 2","order":7,"status":"done","started_at":"2026-08-11T05:33:34.800Z","completed_at":"2026-08-11T05:33:47.115Z","duration_sec":12,"std_minutes":180},{"id":"f7c8bcdc-e2d1-4856-aea1-f577d25b0550","job_id":"J03-c0e2","name":"Dismantle: Clutch 1","order":8,"status":"done","started_at":"2026-08-11T05:33:47.115Z","completed_at":"2026-08-11T15:28:10.891Z","duration_sec":35663,"std_minutes":180},{"id":"4391d523-f1d0-4922-95fb-d3827a21b813","job_id":"J03-c0e2","name":"Dismantle: Planetary &amp; Shaft","order":9,"status":"done","started_at":"2026-08-11T15:28:10.891Z","completed_at":"2026-08-11T23:53:02.227Z","duration_sec":30291,"std_minutes":300},{"id":"bdcc79ae-9f46-46e2-963d-fd2ba3d40a2e","job_id":"J03-c0e2","name":"Dismantle: Part list &amp; Tear Down","order":10,"status":"done","started_at":"2026-08-11T23:53:02.227Z","completed_at":"2026-08-12T03:13:34.783Z","duration_sec":12032,"std_minutes":240},{"id":"0670c5ee-3df9-46ba-a7e5-790a2591233a","job_id":"J03-c0e2","name":"Assemble: Planetary &amp; Shaft In-Out","order":11,"status":"done","started_at":"2026-08-12T03:13:34.783Z","completed_at":"2026-08-13T12:03:07.679Z","duration_sec":118172,"std_minutes":300},{"id":"7276104d-e8c7-4ea6-aac7-6cd975141c45","job_id":"J03-c0e2","name":"Assemble: Clutch 1","order":12,"status":"in_progress","started_at":"2026-08-13T12:26:33.816Z","completed_at":"","duration_sec":1312,"std_minutes":180},{"id":"1781ebaa-7fb0-4896-b642-71d33b8c4878","job_id":"J03-c0e2","name":"Assemble: Clutch 2","order":13,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"5532b99d-a7fd-4b7d-a752-796f7bc5daff","job_id":"J03-c0e2","name":"Assemble: Clutch 3","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"ff0ed73f-27d1-4b0a-a4f2-7818d3cfbc7e","job_id":"J03-c0e2","name":"Assemble: Clutch 4","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"970a35a3-a96b-48b4-9f04-a2b921b013f0","job_id":"J03-c0e2","name":"Assemble: Clutch 5","order":16,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"698b11d9-e1a3-451f-8a47-ccabcc5718c6","job_id":"J03-c0e2","name":"Assemble: CV, Harness &amp; Sensor","order":17,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"0620fee8-23da-434a-85e6-6354dee830d7","job_id":"J03-c0e2","name":"Assemble: Trans Gear","order":18,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":900},{"id":"ca31c8c2-4542-42f7-be4e-86974a63447b","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Set up","order":19,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"ba2d158c-a9f5-4d98-aea1-fd1f7983c4eb","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Test","order":20,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"d2f96316-8f95-487c-a7ee-94ba19ef4354","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Release","order":21,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"050b2cfc-5ea2-4926-b9c1-c7bdfe6bbd49","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":22,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240}],"assignees":[{"id":"5ece1c51-c36b-46e5-a9d2-f9106a729470","job_id":"J03-c0e2","technician_id":"T-533ca22c","assigned_at":"2026-08-10T08:23:08.120Z","is_lead":"1"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-533ca22c","status":"busy","current_job_id":"J03-c0e2"}]}</t>
+  </si>
+  <si>
+    <t>9aa610f4-4e23-4f70-8bf1-7e9a8bd7ce99</t>
+  </si>
+  <si>
+    <t>2026-08-13T12:26:34.247Z</t>
+  </si>
+  <si>
+    <t>{"job":{"id":"J03-c0e2","title":"Recondition Transmission D10T,R","unit":"E448 — D10T","unit_id":"a5c2144b-1b29-40f7-9b5c-cfbbc03c3387","description":"Job recondition Transmission D10T,R (time frame standar).","status":"paused","technician_id":"T-533ca22c","template_id":"ne-transmission-d10t-r","created_at":"2026-08-10T08:22:13.799Z","started_at":"2026-08-10T08:23:20.053Z","completed_at":"","paused_at":"2026-08-13T12:26:10.267Z","total_paused_sec":95,"estimated_minutes":5820},"steps":[{"id":"7609ebf3-f1eb-4d9d-9591-f21d853034e1","job_id":"J03-c0e2","name":"Dismantle: Washing Transmission","order":1,"status":"done","started_at":"2026-08-10T08:23:20.053Z","completed_at":"2026-08-10T08:24:03.692Z","duration_sec":43,"std_minutes":60},{"id":"a3923555-21a4-4b60-9959-c48d814bf136","job_id":"J03-c0e2","name":"Dismantle: Trans Gear","order":2,"status":"done","started_at":"2026-08-10T08:23:32.872Z","completed_at":"2026-08-10T08:24:06.672Z","duration_sec":33,"std_minutes":600},{"id":"39c70957-da00-4dc8-a988-36ee41ef9841","job_id":"J03-c0e2","name":"Dismantle: CV, Harness, &amp; Sensor","order":3,"status":"done","started_at":"2026-08-10T08:24:08.700Z","completed_at":"2026-08-10T08:24:14.772Z","duration_sec":6,"std_minutes":300},{"id":"6feb4f63-8277-4c8a-a4cf-8d8a3d660682","job_id":"J03-c0e2","name":"Dismantle: Clutch 5","order":4,"status":"done","started_at":"2026-08-10T08:23:32.872Z","completed_at":"2026-08-10T08:24:08.700Z","duration_sec":35,"std_minutes":180},{"id":"179574f5-b3d7-43e4-a065-977ebd015bfc","job_id":"J03-c0e2","name":"Dismantle: Clutch 4","order":5,"status":"done","started_at":"2026-08-10T08:24:14.772Z","completed_at":"2026-08-10T10:10:28.558Z","duration_sec":6373,"std_minutes":180},{"id":"8aff0e07-0f40-4945-a9dc-7a8867ffccf4","job_id":"J03-c0e2","name":"Dismantle: Clutch 3","order":6,"status":"done","started_at":"2026-08-11T05:33:18.994Z","completed_at":"2026-08-11T05:33:34.800Z","duration_sec":69782,"std_minutes":180},{"id":"82415ef2-23b1-4eb2-b027-a268df0f4189","job_id":"J03-c0e2","name":"Dismantle: Clutch 2","order":7,"status":"done","started_at":"2026-08-11T05:33:34.800Z","completed_at":"2026-08-11T05:33:47.115Z","duration_sec":12,"std_minutes":180},{"id":"f7c8bcdc-e2d1-4856-aea1-f577d25b0550","job_id":"J03-c0e2","name":"Dismantle: Clutch 1","order":8,"status":"done","started_at":"2026-08-11T05:33:47.115Z","completed_at":"2026-08-11T15:28:10.891Z","duration_sec":35663,"std_minutes":180},{"id":"4391d523-f1d0-4922-95fb-d3827a21b813","job_id":"J03-c0e2","name":"Dismantle: Planetary &amp; Shaft","order":9,"status":"done","started_at":"2026-08-11T15:28:10.891Z","completed_at":"2026-08-11T23:53:02.227Z","duration_sec":30291,"std_minutes":300},{"id":"bdcc79ae-9f46-46e2-963d-fd2ba3d40a2e","job_id":"J03-c0e2","name":"Dismantle: Part list &amp; Tear Down","order":10,"status":"done","started_at":"2026-08-11T23:53:02.227Z","completed_at":"2026-08-12T03:13:34.783Z","duration_sec":12032,"std_minutes":240},{"id":"0670c5ee-3df9-46ba-a7e5-790a2591233a","job_id":"J03-c0e2","name":"Assemble: Planetary &amp; Shaft In-Out","order":11,"status":"done","started_at":"2026-08-12T03:13:34.783Z","completed_at":"2026-08-13T12:03:07.679Z","duration_sec":118172,"std_minutes":300},{"id":"7276104d-e8c7-4ea6-aac7-6cd975141c45","job_id":"J03-c0e2","name":"Assemble: Clutch 1","order":12,"status":"in_progress","started_at":"","completed_at":"","duration_sec":1352,"std_minutes":180},{"id":"1781ebaa-7fb0-4896-b642-71d33b8c4878","job_id":"J03-c0e2","name":"Assemble: Clutch 2","order":13,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"5532b99d-a7fd-4b7d-a752-796f7bc5daff","job_id":"J03-c0e2","name":"Assemble: Clutch 3","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"ff0ed73f-27d1-4b0a-a4f2-7818d3cfbc7e","job_id":"J03-c0e2","name":"Assemble: Clutch 4","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"970a35a3-a96b-48b4-9f04-a2b921b013f0","job_id":"J03-c0e2","name":"Assemble: Clutch 5","order":16,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"698b11d9-e1a3-451f-8a47-ccabcc5718c6","job_id":"J03-c0e2","name":"Assemble: CV, Harness &amp; Sensor","order":17,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"0620fee8-23da-434a-85e6-6354dee830d7","job_id":"J03-c0e2","name":"Assemble: Trans Gear","order":18,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":900},{"id":"ca31c8c2-4542-42f7-be4e-86974a63447b","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Set up","order":19,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"ba2d158c-a9f5-4d98-aea1-fd1f7983c4eb","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Test","order":20,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"d2f96316-8f95-487c-a7ee-94ba19ef4354","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Release","order":21,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"050b2cfc-5ea2-4926-b9c1-c7bdfe6bbd49","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":22,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240}],"assignees":[{"id":"5ece1c51-c36b-46e5-a9d2-f9106a729470","job_id":"J03-c0e2","technician_id":"T-533ca22c","assigned_at":"2026-08-10T08:23:08.120Z","is_lead":"1"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-533ca22c","status":"busy","current_job_id":"J03-c0e2"}]}</t>
+  </si>
+  <si>
+    <t>9517480c-7cdf-4922-b671-f64c246268d3</t>
+  </si>
+  <si>
+    <t>2026-08-13T12:27:08.704Z</t>
+  </si>
+  <si>
+    <t>{"job":{"id":"J03-c0e2","title":"Recondition Transmission D10T,R","unit":"E448 — D10T","unit_id":"a5c2144b-1b29-40f7-9b5c-cfbbc03c3387","description":"Job recondition Transmission D10T,R (time frame standar).","status":"in_progress","technician_id":"T-533ca22c","template_id":"ne-transmission-d10t-r","created_at":"2026-08-10T08:22:13.799Z","started_at":"2026-08-10T08:23:20.053Z","completed_at":"","paused_at":"","total_paused_sec":153,"estimated_minutes":5820},"steps":[{"id":"7609ebf3-f1eb-4d9d-9591-f21d853034e1","job_id":"J03-c0e2","name":"Dismantle: Washing Transmission","order":1,"status":"done","started_at":"2026-08-10T08:23:20.053Z","completed_at":"2026-08-10T08:24:03.692Z","duration_sec":43,"std_minutes":60},{"id":"a3923555-21a4-4b60-9959-c48d814bf136","job_id":"J03-c0e2","name":"Dismantle: Trans Gear","order":2,"status":"done","started_at":"2026-08-10T08:23:32.872Z","completed_at":"2026-08-10T08:24:06.672Z","duration_sec":33,"std_minutes":600},{"id":"39c70957-da00-4dc8-a988-36ee41ef9841","job_id":"J03-c0e2","name":"Dismantle: CV, Harness, &amp; Sensor","order":3,"status":"done","started_at":"2026-08-10T08:24:08.700Z","completed_at":"2026-08-10T08:24:14.772Z","duration_sec":6,"std_minutes":300},{"id":"6feb4f63-8277-4c8a-a4cf-8d8a3d660682","job_id":"J03-c0e2","name":"Dismantle: Clutch 5","order":4,"status":"done","started_at":"2026-08-10T08:23:32.872Z","completed_at":"2026-08-10T08:24:08.700Z","duration_sec":35,"std_minutes":180},{"id":"179574f5-b3d7-43e4-a065-977ebd015bfc","job_id":"J03-c0e2","name":"Dismantle: Clutch 4","order":5,"status":"done","started_at":"2026-08-10T08:24:14.772Z","completed_at":"2026-08-10T10:10:28.558Z","duration_sec":6373,"std_minutes":180},{"id":"8aff0e07-0f40-4945-a9dc-7a8867ffccf4","job_id":"J03-c0e2","name":"Dismantle: Clutch 3","order":6,"status":"done","started_at":"2026-08-11T05:33:18.994Z","completed_at":"2026-08-11T05:33:34.800Z","duration_sec":69782,"std_minutes":180},{"id":"82415ef2-23b1-4eb2-b027-a268df0f4189","job_id":"J03-c0e2","name":"Dismantle: Clutch 2","order":7,"status":"done","started_at":"2026-08-11T05:33:34.800Z","completed_at":"2026-08-11T05:33:47.115Z","duration_sec":12,"std_minutes":180},{"id":"f7c8bcdc-e2d1-4856-aea1-f577d25b0550","job_id":"J03-c0e2","name":"Dismantle: Clutch 1","order":8,"status":"done","started_at":"2026-08-11T05:33:47.115Z","completed_at":"2026-08-11T15:28:10.891Z","duration_sec":35663,"std_minutes":180},{"id":"4391d523-f1d0-4922-95fb-d3827a21b813","job_id":"J03-c0e2","name":"Dismantle: Planetary &amp; Shaft","order":9,"status":"done","started_at":"2026-08-11T15:28:10.891Z","completed_at":"2026-08-11T23:53:02.227Z","duration_sec":30291,"std_minutes":300},{"id":"bdcc79ae-9f46-46e2-963d-fd2ba3d40a2e","job_id":"J03-c0e2","name":"Dismantle: Part list &amp; Tear Down","order":10,"status":"done","started_at":"2026-08-11T23:53:02.227Z","completed_at":"2026-08-12T03:13:34.783Z","duration_sec":12032,"std_minutes":240},{"id":"0670c5ee-3df9-46ba-a7e5-790a2591233a","job_id":"J03-c0e2","name":"Assemble: Planetary &amp; Shaft In-Out","order":11,"status":"done","started_at":"2026-08-12T03:13:34.783Z","completed_at":"2026-08-13T12:03:07.679Z","duration_sec":118172,"std_minutes":300},{"id":"7276104d-e8c7-4ea6-aac7-6cd975141c45","job_id":"J03-c0e2","name":"Assemble: Clutch 1","order":12,"status":"in_progress","started_at":"2026-08-13T12:27:08.437Z","completed_at":"","duration_sec":1352,"std_minutes":180},{"id":"1781ebaa-7fb0-4896-b642-71d33b8c4878","job_id":"J03-c0e2","name":"Assemble: Clutch 2","order":13,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"5532b99d-a7fd-4b7d-a752-796f7bc5daff","job_id":"J03-c0e2","name":"Assemble: Clutch 3","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"ff0ed73f-27d1-4b0a-a4f2-7818d3cfbc7e","job_id":"J03-c0e2","name":"Assemble: Clutch 4","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"970a35a3-a96b-48b4-9f04-a2b921b013f0","job_id":"J03-c0e2","name":"Assemble: Clutch 5","order":16,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"698b11d9-e1a3-451f-8a47-ccabcc5718c6","job_id":"J03-c0e2","name":"Assemble: CV, Harness &amp; Sensor","order":17,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"0620fee8-23da-434a-85e6-6354dee830d7","job_id":"J03-c0e2","name":"Assemble: Trans Gear","order":18,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":900},{"id":"ca31c8c2-4542-42f7-be4e-86974a63447b","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Set up","order":19,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"ba2d158c-a9f5-4d98-aea1-fd1f7983c4eb","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Test","order":20,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"d2f96316-8f95-487c-a7ee-94ba19ef4354","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Release","order":21,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"050b2cfc-5ea2-4926-b9c1-c7bdfe6bbd49","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":22,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240}],"assignees":[{"id":"5ece1c51-c36b-46e5-a9d2-f9106a729470","job_id":"J03-c0e2","technician_id":"T-533ca22c","assigned_at":"2026-08-10T08:23:08.120Z","is_lead":"1"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-533ca22c","status":"busy","current_job_id":"J03-c0e2"}]}</t>
+  </si>
+  <si>
+    <t>2fc0d07b-9569-4ae8-a314-cc92c1ed6caf</t>
+  </si>
+  <si>
+    <t>2026-08-13T12:29:10.920Z</t>
+  </si>
+  <si>
+    <t>{"job":{"id":"J03-c0e2","title":"Recondition Transmission D10T,R","unit":"E448 — D10T","unit_id":"a5c2144b-1b29-40f7-9b5c-cfbbc03c3387","description":"Job recondition Transmission D10T,R (time frame standar).","status":"paused","technician_id":"T-533ca22c","template_id":"ne-transmission-d10t-r","created_at":"2026-08-10T08:22:13.799Z","started_at":"2026-08-10T08:23:20.053Z","completed_at":"","paused_at":"2026-08-13T12:27:18.614Z","total_paused_sec":153,"estimated_minutes":5820},"steps":[{"id":"7609ebf3-f1eb-4d9d-9591-f21d853034e1","job_id":"J03-c0e2","name":"Dismantle: Washing Transmission","order":1,"status":"done","started_at":"2026-08-10T08:23:20.053Z","completed_at":"2026-08-10T08:24:03.692Z","duration_sec":43,"std_minutes":60},{"id":"a3923555-21a4-4b60-9959-c48d814bf136","job_id":"J03-c0e2","name":"Dismantle: Trans Gear","order":2,"status":"done","started_at":"2026-08-10T08:23:32.872Z","completed_at":"2026-08-10T08:24:06.672Z","duration_sec":33,"std_minutes":600},{"id":"39c70957-da00-4dc8-a988-36ee41ef9841","job_id":"J03-c0e2","name":"Dismantle: CV, Harness, &amp; Sensor","order":3,"status":"done","started_at":"2026-08-10T08:24:08.700Z","completed_at":"2026-08-10T08:24:14.772Z","duration_sec":6,"std_minutes":300},{"id":"6feb4f63-8277-4c8a-a4cf-8d8a3d660682","job_id":"J03-c0e2","name":"Dismantle: Clutch 5","order":4,"status":"done","started_at":"2026-08-10T08:23:32.872Z","completed_at":"2026-08-10T08:24:08.700Z","duration_sec":35,"std_minutes":180},{"id":"179574f5-b3d7-43e4-a065-977ebd015bfc","job_id":"J03-c0e2","name":"Dismantle: Clutch 4","order":5,"status":"done","started_at":"2026-08-10T08:24:14.772Z","completed_at":"2026-08-10T10:10:28.558Z","duration_sec":6373,"std_minutes":180},{"id":"8aff0e07-0f40-4945-a9dc-7a8867ffccf4","job_id":"J03-c0e2","name":"Dismantle: Clutch 3","order":6,"status":"done","started_at":"2026-08-11T05:33:18.994Z","completed_at":"2026-08-11T05:33:34.800Z","duration_sec":69782,"std_minutes":180},{"id":"82415ef2-23b1-4eb2-b027-a268df0f4189","job_id":"J03-c0e2","name":"Dismantle: Clutch 2","order":7,"status":"done","started_at":"2026-08-11T05:33:34.800Z","completed_at":"2026-08-11T05:33:47.115Z","duration_sec":12,"std_minutes":180},{"id":"f7c8bcdc-e2d1-4856-aea1-f577d25b0550","job_id":"J03-c0e2","name":"Dismantle: Clutch 1","order":8,"status":"done","started_at":"2026-08-11T05:33:47.115Z","completed_at":"2026-08-11T15:28:10.891Z","duration_sec":35663,"std_minutes":180},{"id":"4391d523-f1d0-4922-95fb-d3827a21b813","job_id":"J03-c0e2","name":"Dismantle: Planetary &amp; Shaft","order":9,"status":"done","started_at":"2026-08-11T15:28:10.891Z","completed_at":"2026-08-11T23:53:02.227Z","duration_sec":30291,"std_minutes":300},{"id":"bdcc79ae-9f46-46e2-963d-fd2ba3d40a2e","job_id":"J03-c0e2","name":"Dismantle: Part list &amp; Tear Down","order":10,"status":"done","started_at":"2026-08-11T23:53:02.227Z","completed_at":"2026-08-12T03:13:34.783Z","duration_sec":12032,"std_minutes":240},{"id":"0670c5ee-3df9-46ba-a7e5-790a2591233a","job_id":"J03-c0e2","name":"Assemble: Planetary &amp; Shaft In-Out","order":11,"status":"done","started_at":"2026-08-12T03:13:34.783Z","completed_at":"2026-08-13T12:03:07.679Z","duration_sec":118172,"std_minutes":300},{"id":"7276104d-e8c7-4ea6-aac7-6cd975141c45","job_id":"J03-c0e2","name":"Assemble: Clutch 1","order":12,"status":"in_progress","started_at":"","completed_at":"","duration_sec":1362,"std_minutes":180},{"id":"1781ebaa-7fb0-4896-b642-71d33b8c4878","job_id":"J03-c0e2","name":"Assemble: Clutch 2","order":13,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"5532b99d-a7fd-4b7d-a752-796f7bc5daff","job_id":"J03-c0e2","name":"Assemble: Clutch 3","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"ff0ed73f-27d1-4b0a-a4f2-7818d3cfbc7e","job_id":"J03-c0e2","name":"Assemble: Clutch 4","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"970a35a3-a96b-48b4-9f04-a2b921b013f0","job_id":"J03-c0e2","name":"Assemble: Clutch 5","order":16,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"698b11d9-e1a3-451f-8a47-ccabcc5718c6","job_id":"J03-c0e2","name":"Assemble: CV, Harness &amp; Sensor","order":17,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"0620fee8-23da-434a-85e6-6354dee830d7","job_id":"J03-c0e2","name":"Assemble: Trans Gear","order":18,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":900},{"id":"ca31c8c2-4542-42f7-be4e-86974a63447b","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Set up","order":19,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"ba2d158c-a9f5-4d98-aea1-fd1f7983c4eb","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Test","order":20,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"d2f96316-8f95-487c-a7ee-94ba19ef4354","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Release","order":21,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"050b2cfc-5ea2-4926-b9c1-c7bdfe6bbd49","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":22,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240}],"assignees":[{"id":"5ece1c51-c36b-46e5-a9d2-f9106a729470","job_id":"J03-c0e2","technician_id":"T-533ca22c","assigned_at":"2026-08-10T08:23:08.120Z","is_lead":"1"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-533ca22c","status":"busy","current_job_id":"J03-c0e2"}]}</t>
+  </si>
+  <si>
+    <t>46151d01-37c8-4385-9693-3106e8674f9f</t>
+  </si>
+  <si>
+    <t>2026-08-13T12:29:11.354Z</t>
+  </si>
+  <si>
+    <t>{"job":{"id":"J03-c0e2","title":"Recondition Transmission D10T,R","unit":"E448 — D10T","unit_id":"a5c2144b-1b29-40f7-9b5c-cfbbc03c3387","description":"Job recondition Transmission D10T,R (time frame standar).","status":"in_progress","technician_id":"T-533ca22c","template_id":"ne-transmission-d10t-r","created_at":"2026-08-10T08:22:13.799Z","started_at":"2026-08-10T08:23:20.053Z","completed_at":"","paused_at":"","total_paused_sec":178,"estimated_minutes":5820},"steps":[{"id":"7609ebf3-f1eb-4d9d-9591-f21d853034e1","job_id":"J03-c0e2","name":"Dismantle: Washing Transmission","order":1,"status":"done","started_at":"2026-08-10T08:23:20.053Z","completed_at":"2026-08-10T08:24:03.692Z","duration_sec":43,"std_minutes":60},{"id":"a3923555-21a4-4b60-9959-c48d814bf136","job_id":"J03-c0e2","name":"Dismantle: Trans Gear","order":2,"status":"done","started_at":"2026-08-10T08:23:32.872Z","completed_at":"2026-08-10T08:24:06.672Z","duration_sec":33,"std_minutes":600},{"id":"39c70957-da00-4dc8-a988-36ee41ef9841","job_id":"J03-c0e2","name":"Dismantle: CV, Harness, &amp; Sensor","order":3,"status":"done","started_at":"2026-08-10T08:24:08.700Z","completed_at":"2026-08-10T08:24:14.772Z","duration_sec":6,"std_minutes":300},{"id":"6feb4f63-8277-4c8a-a4cf-8d8a3d660682","job_id":"J03-c0e2","name":"Dismantle: Clutch 5","order":4,"status":"done","started_at":"2026-08-10T08:23:32.872Z","completed_at":"2026-08-10T08:24:08.700Z","duration_sec":35,"std_minutes":180},{"id":"179574f5-b3d7-43e4-a065-977ebd015bfc","job_id":"J03-c0e2","name":"Dismantle: Clutch 4","order":5,"status":"done","started_at":"2026-08-10T08:24:14.772Z","completed_at":"2026-08-10T10:10:28.558Z","duration_sec":6373,"std_minutes":180},{"id":"8aff0e07-0f40-4945-a9dc-7a8867ffccf4","job_id":"J03-c0e2","name":"Dismantle: Clutch 3","order":6,"status":"done","started_at":"2026-08-11T05:33:18.994Z","completed_at":"2026-08-11T05:33:34.800Z","duration_sec":69782,"std_minutes":180},{"id":"82415ef2-23b1-4eb2-b027-a268df0f4189","job_id":"J03-c0e2","name":"Dismantle: Clutch 2","order":7,"status":"done","started_at":"2026-08-11T05:33:34.800Z","completed_at":"2026-08-11T05:33:47.115Z","duration_sec":12,"std_minutes":180},{"id":"f7c8bcdc-e2d1-4856-aea1-f577d25b0550","job_id":"J03-c0e2","name":"Dismantle: Clutch 1","order":8,"status":"done","started_at":"2026-08-11T05:33:47.115Z","completed_at":"2026-08-11T15:28:10.891Z","duration_sec":35663,"std_minutes":180},{"id":"4391d523-f1d0-4922-95fb-d3827a21b813","job_id":"J03-c0e2","name":"Dismantle: Planetary &amp; Shaft","order":9,"status":"done","started_at":"2026-08-11T15:28:10.891Z","completed_at":"2026-08-11T23:53:02.227Z","duration_sec":30291,"std_minutes":300},{"id":"bdcc79ae-9f46-46e2-963d-fd2ba3d40a2e","job_id":"J03-c0e2","name":"Dismantle: Part list &amp; Tear Down","order":10,"status":"done","started_at":"2026-08-11T23:53:02.227Z","completed_at":"2026-08-12T03:13:34.783Z","duration_sec":12032,"std_minutes":240},{"id":"0670c5ee-3df9-46ba-a7e5-790a2591233a","job_id":"J03-c0e2","name":"Assemble: Planetary &amp; Shaft In-Out","order":11,"status":"done","started_at":"2026-08-12T03:13:34.783Z","completed_at":"2026-08-13T12:03:07.679Z","duration_sec":118172,"std_minutes":300},{"id":"7276104d-e8c7-4ea6-aac7-6cd975141c45","job_id":"J03-c0e2","name":"Assemble: Clutch 1","order":12,"status":"in_progress","started_at":"2026-08-13T12:27:44.119Z","completed_at":"","duration_sec":1362,"std_minutes":180},{"id":"1781ebaa-7fb0-4896-b642-71d33b8c4878","job_id":"J03-c0e2","name":"Assemble: Clutch 2","order":13,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"5532b99d-a7fd-4b7d-a752-796f7bc5daff","job_id":"J03-c0e2","name":"Assemble: Clutch 3","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"ff0ed73f-27d1-4b0a-a4f2-7818d3cfbc7e","job_id":"J03-c0e2","name":"Assemble: Clutch 4","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"970a35a3-a96b-48b4-9f04-a2b921b013f0","job_id":"J03-c0e2","name":"Assemble: Clutch 5","order":16,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"698b11d9-e1a3-451f-8a47-ccabcc5718c6","job_id":"J03-c0e2","name":"Assemble: CV, Harness &amp; Sensor","order":17,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"0620fee8-23da-434a-85e6-6354dee830d7","job_id":"J03-c0e2","name":"Assemble: Trans Gear","order":18,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":900},{"id":"ca31c8c2-4542-42f7-be4e-86974a63447b","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Set up","order":19,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"ba2d158c-a9f5-4d98-aea1-fd1f7983c4eb","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Test","order":20,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"d2f96316-8f95-487c-a7ee-94ba19ef4354","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Release","order":21,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"050b2cfc-5ea2-4926-b9c1-c7bdfe6bbd49","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":22,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240}],"assignees":[{"id":"5ece1c51-c36b-46e5-a9d2-f9106a729470","job_id":"J03-c0e2","technician_id":"T-533ca22c","assigned_at":"2026-08-10T08:23:08.120Z","is_lead":"1"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-533ca22c","status":"busy","current_job_id":"J03-c0e2"}]}</t>
+  </si>
+  <si>
+    <t>8db2df75-c2fc-4ab8-b0b2-be912e841db8</t>
+  </si>
+  <si>
+    <t>2026-08-13T12:29:11.767Z</t>
+  </si>
+  <si>
+    <t>{"job":{"id":"J03-c0e2","title":"Recondition Transmission D10T,R","unit":"E448 — D10T","unit_id":"a5c2144b-1b29-40f7-9b5c-cfbbc03c3387","description":"Job recondition Transmission D10T,R (time frame standar).","status":"paused","technician_id":"T-533ca22c","template_id":"ne-transmission-d10t-r","created_at":"2026-08-10T08:22:13.799Z","started_at":"2026-08-10T08:23:20.053Z","completed_at":"","paused_at":"2026-08-13T12:28:06.669Z","total_paused_sec":178,"estimated_minutes":5820},"steps":[{"id":"7609ebf3-f1eb-4d9d-9591-f21d853034e1","job_id":"J03-c0e2","name":"Dismantle: Washing Transmission","order":1,"status":"done","started_at":"2026-08-10T08:23:20.053Z","completed_at":"2026-08-10T08:24:03.692Z","duration_sec":43,"std_minutes":60},{"id":"a3923555-21a4-4b60-9959-c48d814bf136","job_id":"J03-c0e2","name":"Dismantle: Trans Gear","order":2,"status":"done","started_at":"2026-08-10T08:23:32.872Z","completed_at":"2026-08-10T08:24:06.672Z","duration_sec":33,"std_minutes":600},{"id":"39c70957-da00-4dc8-a988-36ee41ef9841","job_id":"J03-c0e2","name":"Dismantle: CV, Harness, &amp; Sensor","order":3,"status":"done","started_at":"2026-08-10T08:24:08.700Z","completed_at":"2026-08-10T08:24:14.772Z","duration_sec":6,"std_minutes":300},{"id":"6feb4f63-8277-4c8a-a4cf-8d8a3d660682","job_id":"J03-c0e2","name":"Dismantle: Clutch 5","order":4,"status":"done","started_at":"2026-08-10T08:23:32.872Z","completed_at":"2026-08-10T08:24:08.700Z","duration_sec":35,"std_minutes":180},{"id":"179574f5-b3d7-43e4-a065-977ebd015bfc","job_id":"J03-c0e2","name":"Dismantle: Clutch 4","order":5,"status":"done","started_at":"2026-08-10T08:24:14.772Z","completed_at":"2026-08-10T10:10:28.558Z","duration_sec":6373,"std_minutes":180},{"id":"8aff0e07-0f40-4945-a9dc-7a8867ffccf4","job_id":"J03-c0e2","name":"Dismantle: Clutch 3","order":6,"status":"done","started_at":"2026-08-11T05:33:18.994Z","completed_at":"2026-08-11T05:33:34.800Z","duration_sec":69782,"std_minutes":180},{"id":"82415ef2-23b1-4eb2-b027-a268df0f4189","job_id":"J03-c0e2","name":"Dismantle: Clutch 2","order":7,"status":"done","started_at":"2026-08-11T05:33:34.800Z","completed_at":"2026-08-11T05:33:47.115Z","duration_sec":12,"std_minutes":180},{"id":"f7c8bcdc-e2d1-4856-aea1-f577d25b0550","job_id":"J03-c0e2","name":"Dismantle: Clutch 1","order":8,"status":"done","started_at":"2026-08-11T05:33:47.115Z","completed_at":"2026-08-11T15:28:10.891Z","duration_sec":35663,"std_minutes":180},{"id":"4391d523-f1d0-4922-95fb-d3827a21b813","job_id":"J03-c0e2","name":"Dismantle: Planetary &amp; Shaft","order":9,"status":"done","started_at":"2026-08-11T15:28:10.891Z","completed_at":"2026-08-11T23:53:02.227Z","duration_sec":30291,"std_minutes":300},{"id":"bdcc79ae-9f46-46e2-963d-fd2ba3d40a2e","job_id":"J03-c0e2","name":"Dismantle: Part list &amp; Tear Down","order":10,"status":"done","started_at":"2026-08-11T23:53:02.227Z","completed_at":"2026-08-12T03:13:34.783Z","duration_sec":12032,"std_minutes":240},{"id":"0670c5ee-3df9-46ba-a7e5-790a2591233a","job_id":"J03-c0e2","name":"Assemble: Planetary &amp; Shaft In-Out","order":11,"status":"done","started_at":"2026-08-12T03:13:34.783Z","completed_at":"2026-08-13T12:03:07.679Z","duration_sec":118172,"std_minutes":300},{"id":"7276104d-e8c7-4ea6-aac7-6cd975141c45","job_id":"J03-c0e2","name":"Assemble: Clutch 1","order":12,"status":"in_progress","started_at":"","completed_at":"","duration_sec":1384,"std_minutes":180},{"id":"1781ebaa-7fb0-4896-b642-71d33b8c4878","job_id":"J03-c0e2","name":"Assemble: Clutch 2","order":13,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"5532b99d-a7fd-4b7d-a752-796f7bc5daff","job_id":"J03-c0e2","name":"Assemble: Clutch 3","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"ff0ed73f-27d1-4b0a-a4f2-7818d3cfbc7e","job_id":"J03-c0e2","name":"Assemble: Clutch 4","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"970a35a3-a96b-48b4-9f04-a2b921b013f0","job_id":"J03-c0e2","name":"Assemble: Clutch 5","order":16,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"698b11d9-e1a3-451f-8a47-ccabcc5718c6","job_id":"J03-c0e2","name":"Assemble: CV, Harness &amp; Sensor","order":17,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"0620fee8-23da-434a-85e6-6354dee830d7","job_id":"J03-c0e2","name":"Assemble: Trans Gear","order":18,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":900},{"id":"ca31c8c2-4542-42f7-be4e-86974a63447b","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Set up","order":19,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"ba2d158c-a9f5-4d98-aea1-fd1f7983c4eb","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Test","order":20,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"d2f96316-8f95-487c-a7ee-94ba19ef4354","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Release","order":21,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"050b2cfc-5ea2-4926-b9c1-c7bdfe6bbd49","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":22,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240}],"assignees":[{"id":"5ece1c51-c36b-46e5-a9d2-f9106a729470","job_id":"J03-c0e2","technician_id":"T-533ca22c","assigned_at":"2026-08-10T08:23:08.120Z","is_lead":"1"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-533ca22c","status":"busy","current_job_id":"J03-c0e2"}]}</t>
+  </si>
+  <si>
+    <t>79ca3cec-5426-4aba-ab75-c8c735e620c0</t>
+  </si>
+  <si>
+    <t>2026-08-13T12:29:12.203Z</t>
+  </si>
+  <si>
+    <t>{"job":{"id":"J03-c0e2","title":"Recondition Transmission D10T,R","unit":"E448 — D10T","unit_id":"a5c2144b-1b29-40f7-9b5c-cfbbc03c3387","description":"Job recondition Transmission D10T,R (time frame standar).","status":"in_progress","technician_id":"T-533ca22c","template_id":"ne-transmission-d10t-r","created_at":"2026-08-10T08:22:13.799Z","started_at":"2026-08-10T08:23:20.053Z","completed_at":"","paused_at":"","total_paused_sec":216,"estimated_minutes":5820},"steps":[{"id":"7609ebf3-f1eb-4d9d-9591-f21d853034e1","job_id":"J03-c0e2","name":"Dismantle: Washing Transmission","order":1,"status":"done","started_at":"2026-08-10T08:23:20.053Z","completed_at":"2026-08-10T08:24:03.692Z","duration_sec":43,"std_minutes":60},{"id":"a3923555-21a4-4b60-9959-c48d814bf136","job_id":"J03-c0e2","name":"Dismantle: Trans Gear","order":2,"status":"done","started_at":"2026-08-10T08:23:32.872Z","completed_at":"2026-08-10T08:24:06.672Z","duration_sec":33,"std_minutes":600},{"id":"39c70957-da00-4dc8-a988-36ee41ef9841","job_id":"J03-c0e2","name":"Dismantle: CV, Harness, &amp; Sensor","order":3,"status":"done","started_at":"2026-08-10T08:24:08.700Z","completed_at":"2026-08-10T08:24:14.772Z","duration_sec":6,"std_minutes":300},{"id":"6feb4f63-8277-4c8a-a4cf-8d8a3d660682","job_id":"J03-c0e2","name":"Dismantle: Clutch 5","order":4,"status":"done","started_at":"2026-08-10T08:23:32.872Z","completed_at":"2026-08-10T08:24:08.700Z","duration_sec":35,"std_minutes":180},{"id":"179574f5-b3d7-43e4-a065-977ebd015bfc","job_id":"J03-c0e2","name":"Dismantle: Clutch 4","order":5,"status":"done","started_at":"2026-08-10T08:24:14.772Z","completed_at":"2026-08-10T10:10:28.558Z","duration_sec":6373,"std_minutes":180},{"id":"8aff0e07-0f40-4945-a9dc-7a8867ffccf4","job_id":"J03-c0e2","name":"Dismantle: Clutch 3","order":6,"status":"done","started_at":"2026-08-11T05:33:18.994Z","completed_at":"2026-08-11T05:33:34.800Z","duration_sec":69782,"std_minutes":180},{"id":"82415ef2-23b1-4eb2-b027-a268df0f4189","job_id":"J03-c0e2","name":"Dismantle: Clutch 2","order":7,"status":"done","started_at":"2026-08-11T05:33:34.800Z","completed_at":"2026-08-11T05:33:47.115Z","duration_sec":12,"std_minutes":180},{"id":"f7c8bcdc-e2d1-4856-aea1-f577d25b0550","job_id":"J03-c0e2","name":"Dismantle: Clutch 1","order":8,"status":"done","started_at":"2026-08-11T05:33:47.115Z","completed_at":"2026-08-11T15:28:10.891Z","duration_sec":35663,"std_minutes":180},{"id":"4391d523-f1d0-4922-95fb-d3827a21b813","job_id":"J03-c0e2","name":"Dismantle: Planetary &amp; Shaft","order":9,"status":"done","started_at":"2026-08-11T15:28:10.891Z","completed_at":"2026-08-11T23:53:02.227Z","duration_sec":30291,"std_minutes":300},{"id":"bdcc79ae-9f46-46e2-963d-fd2ba3d40a2e","job_id":"J03-c0e2","name":"Dismantle: Part list &amp; Tear Down","order":10,"status":"done","started_at":"2026-08-11T23:53:02.227Z","completed_at":"2026-08-12T03:13:34.783Z","duration_sec":12032,"std_minutes":240},{"id":"0670c5ee-3df9-46ba-a7e5-790a2591233a","job_id":"J03-c0e2","name":"Assemble: Planetary &amp; Shaft In-Out","order":11,"status":"done","started_at":"2026-08-12T03:13:34.783Z","completed_at":"2026-08-13T12:03:07.679Z","duration_sec":118172,"std_minutes":300},{"id":"7276104d-e8c7-4ea6-aac7-6cd975141c45","job_id":"J03-c0e2","name":"Assemble: Clutch 1","order":12,"status":"in_progress","started_at":"2026-08-13T12:28:45.256Z","completed_at":"","duration_sec":1384,"std_minutes":180},{"id":"1781ebaa-7fb0-4896-b642-71d33b8c4878","job_id":"J03-c0e2","name":"Assemble: Clutch 2","order":13,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"5532b99d-a7fd-4b7d-a752-796f7bc5daff","job_id":"J03-c0e2","name":"Assemble: Clutch 3","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"ff0ed73f-27d1-4b0a-a4f2-7818d3cfbc7e","job_id":"J03-c0e2","name":"Assemble: Clutch 4","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"970a35a3-a96b-48b4-9f04-a2b921b013f0","job_id":"J03-c0e2","name":"Assemble: Clutch 5","order":16,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"698b11d9-e1a3-451f-8a47-ccabcc5718c6","job_id":"J03-c0e2","name":"Assemble: CV, Harness &amp; Sensor","order":17,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"0620fee8-23da-434a-85e6-6354dee830d7","job_id":"J03-c0e2","name":"Assemble: Trans Gear","order":18,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":900},{"id":"ca31c8c2-4542-42f7-be4e-86974a63447b","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Set up","order":19,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"ba2d158c-a9f5-4d98-aea1-fd1f7983c4eb","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Test","order":20,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"d2f96316-8f95-487c-a7ee-94ba19ef4354","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Release","order":21,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"050b2cfc-5ea2-4926-b9c1-c7bdfe6bbd49","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":22,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240}],"assignees":[{"id":"5ece1c51-c36b-46e5-a9d2-f9106a729470","job_id":"J03-c0e2","technician_id":"T-533ca22c","assigned_at":"2026-08-10T08:23:08.120Z","is_lead":"1"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-533ca22c","status":"busy","current_job_id":"J03-c0e2"}]}</t>
+  </si>
+  <si>
+    <t>c1591f2a-c073-417e-b3ba-a5926ce1bc52</t>
+  </si>
+  <si>
+    <t>2026-08-13T12:29:12.587Z</t>
+  </si>
+  <si>
+    <t>{"job":{"id":"J03-c0e2","title":"Recondition Transmission D10T,R","unit":"E448 — D10T","unit_id":"a5c2144b-1b29-40f7-9b5c-cfbbc03c3387","description":"Job recondition Transmission D10T,R (time frame standar).","status":"paused","technician_id":"T-533ca22c","template_id":"ne-transmission-d10t-r","created_at":"2026-08-10T08:22:13.799Z","started_at":"2026-08-10T08:23:20.053Z","completed_at":"","paused_at":"2026-08-13T12:28:49.608Z","total_paused_sec":216,"estimated_minutes":5820},"steps":[{"id":"7609ebf3-f1eb-4d9d-9591-f21d853034e1","job_id":"J03-c0e2","name":"Dismantle: Washing Transmission","order":1,"status":"done","started_at":"2026-08-10T08:23:20.053Z","completed_at":"2026-08-10T08:24:03.692Z","duration_sec":43,"std_minutes":60},{"id":"a3923555-21a4-4b60-9959-c48d814bf136","job_id":"J03-c0e2","name":"Dismantle: Trans Gear","order":2,"status":"done","started_at":"2026-08-10T08:23:32.872Z","completed_at":"2026-08-10T08:24:06.672Z","duration_sec":33,"std_minutes":600},{"id":"39c70957-da00-4dc8-a988-36ee41ef9841","job_id":"J03-c0e2","name":"Dismantle: CV, Harness, &amp; Sensor","order":3,"status":"done","started_at":"2026-08-10T08:24:08.700Z","completed_at":"2026-08-10T08:24:14.772Z","duration_sec":6,"std_minutes":300},{"id":"6feb4f63-8277-4c8a-a4cf-8d8a3d660682","job_id":"J03-c0e2","name":"Dismantle: Clutch 5","order":4,"status":"done","started_at":"2026-08-10T08:23:32.872Z","completed_at":"2026-08-10T08:24:08.700Z","duration_sec":35,"std_minutes":180},{"id":"179574f5-b3d7-43e4-a065-977ebd015bfc","job_id":"J03-c0e2","name":"Dismantle: Clutch 4","order":5,"status":"done","started_at":"2026-08-10T08:24:14.772Z","completed_at":"2026-08-10T10:10:28.558Z","duration_sec":6373,"std_minutes":180},{"id":"8aff0e07-0f40-4945-a9dc-7a8867ffccf4","job_id":"J03-c0e2","name":"Dismantle: Clutch 3","order":6,"status":"done","started_at":"2026-08-11T05:33:18.994Z","completed_at":"2026-08-11T05:33:34.800Z","duration_sec":69782,"std_minutes":180},{"id":"82415ef2-23b1-4eb2-b027-a268df0f4189","job_id":"J03-c0e2","name":"Dismantle: Clutch 2","order":7,"status":"done","started_at":"2026-08-11T05:33:34.800Z","completed_at":"2026-08-11T05:33:47.115Z","duration_sec":12,"std_minutes":180},{"id":"f7c8bcdc-e2d1-4856-aea1-f577d25b0550","job_id":"J03-c0e2","name":"Dismantle: Clutch 1","order":8,"status":"done","started_at":"2026-08-11T05:33:47.115Z","completed_at":"2026-08-11T15:28:10.891Z","duration_sec":35663,"std_minutes":180},{"id":"4391d523-f1d0-4922-95fb-d3827a21b813","job_id":"J03-c0e2","name":"Dismantle: Planetary &amp; Shaft","order":9,"status":"done","started_at":"2026-08-11T15:28:10.891Z","completed_at":"2026-08-11T23:53:02.227Z","duration_sec":30291,"std_minutes":300},{"id":"bdcc79ae-9f46-46e2-963d-fd2ba3d40a2e","job_id":"J03-c0e2","name":"Dismantle: Part list &amp; Tear Down","order":10,"status":"done","started_at":"2026-08-11T23:53:02.227Z","completed_at":"2026-08-12T03:13:34.783Z","duration_sec":12032,"std_minutes":240},{"id":"0670c5ee-3df9-46ba-a7e5-790a2591233a","job_id":"J03-c0e2","name":"Assemble: Planetary &amp; Shaft In-Out","order":11,"status":"done","started_at":"2026-08-12T03:13:34.783Z","completed_at":"2026-08-13T12:03:07.679Z","duration_sec":118172,"std_minutes":300},{"id":"7276104d-e8c7-4ea6-aac7-6cd975141c45","job_id":"J03-c0e2","name":"Assemble: Clutch 1","order":12,"status":"in_progress","started_at":"","completed_at":"","duration_sec":1388,"std_minutes":180},{"id":"1781ebaa-7fb0-4896-b642-71d33b8c4878","job_id":"J03-c0e2","name":"Assemble: Clutch 2","order":13,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"5532b99d-a7fd-4b7d-a752-796f7bc5daff","job_id":"J03-c0e2","name":"Assemble: Clutch 3","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"ff0ed73f-27d1-4b0a-a4f2-7818d3cfbc7e","job_id":"J03-c0e2","name":"Assemble: Clutch 4","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"970a35a3-a96b-48b4-9f04-a2b921b013f0","job_id":"J03-c0e2","name":"Assemble: Clutch 5","order":16,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"698b11d9-e1a3-451f-8a47-ccabcc5718c6","job_id":"J03-c0e2","name":"Assemble: CV, Harness &amp; Sensor","order":17,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"0620fee8-23da-434a-85e6-6354dee830d7","job_id":"J03-c0e2","name":"Assemble: Trans Gear","order":18,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":900},{"id":"ca31c8c2-4542-42f7-be4e-86974a63447b","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Set up","order":19,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"ba2d158c-a9f5-4d98-aea1-fd1f7983c4eb","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Test","order":20,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"d2f96316-8f95-487c-a7ee-94ba19ef4354","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Release","order":21,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"050b2cfc-5ea2-4926-b9c1-c7bdfe6bbd49","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":22,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240}],"assignees":[{"id":"5ece1c51-c36b-46e5-a9d2-f9106a729470","job_id":"J03-c0e2","technician_id":"T-533ca22c","assigned_at":"2026-08-10T08:23:08.120Z","is_lead":"1"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-533ca22c","status":"busy","current_job_id":"J03-c0e2"}]}</t>
+  </si>
+  <si>
+    <t>6c56b495-582b-4cea-9463-113f87887766</t>
+  </si>
+  <si>
+    <t>2026-08-13T12:29:30.709Z</t>
+  </si>
+  <si>
+    <t>{"job":{"id":"J03-c0e2","title":"Recondition Transmission D10T,R","unit":"E448 — D10T","unit_id":"a5c2144b-1b29-40f7-9b5c-cfbbc03c3387","description":"Job recondition Transmission D10T,R (time frame standar).","status":"in_progress","technician_id":"T-533ca22c","template_id":"ne-transmission-d10t-r","created_at":"2026-08-10T08:22:13.799Z","started_at":"2026-08-10T08:23:20.053Z","completed_at":"","paused_at":"","total_paused_sec":256,"estimated_minutes":5820},"steps":[{"id":"7609ebf3-f1eb-4d9d-9591-f21d853034e1","job_id":"J03-c0e2","name":"Dismantle: Washing Transmission","order":1,"status":"done","started_at":"2026-08-10T08:23:20.053Z","completed_at":"2026-08-10T08:24:03.692Z","duration_sec":43,"std_minutes":60},{"id":"a3923555-21a4-4b60-9959-c48d814bf136","job_id":"J03-c0e2","name":"Dismantle: Trans Gear","order":2,"status":"done","started_at":"2026-08-10T08:23:32.872Z","completed_at":"2026-08-10T08:24:06.672Z","duration_sec":33,"std_minutes":600},{"id":"39c70957-da00-4dc8-a988-36ee41ef9841","job_id":"J03-c0e2","name":"Dismantle: CV, Harness, &amp; Sensor","order":3,"status":"done","started_at":"2026-08-10T08:24:08.700Z","completed_at":"2026-08-10T08:24:14.772Z","duration_sec":6,"std_minutes":300},{"id":"6feb4f63-8277-4c8a-a4cf-8d8a3d660682","job_id":"J03-c0e2","name":"Dismantle: Clutch 5","order":4,"status":"done","started_at":"2026-08-10T08:23:32.872Z","completed_at":"2026-08-10T08:24:08.700Z","duration_sec":35,"std_minutes":180},{"id":"179574f5-b3d7-43e4-a065-977ebd015bfc","job_id":"J03-c0e2","name":"Dismantle: Clutch 4","order":5,"status":"done","started_at":"2026-08-10T08:24:14.772Z","completed_at":"2026-08-10T10:10:28.558Z","duration_sec":6373,"std_minutes":180},{"id":"8aff0e07-0f40-4945-a9dc-7a8867ffccf4","job_id":"J03-c0e2","name":"Dismantle: Clutch 3","order":6,"status":"done","started_at":"2026-08-11T05:33:18.994Z","completed_at":"2026-08-11T05:33:34.800Z","duration_sec":69782,"std_minutes":180},{"id":"82415ef2-23b1-4eb2-b027-a268df0f4189","job_id":"J03-c0e2","name":"Dismantle: Clutch 2","order":7,"status":"done","started_at":"2026-08-11T05:33:34.800Z","completed_at":"2026-08-11T05:33:47.115Z","duration_sec":12,"std_minutes":180},{"id":"f7c8bcdc-e2d1-4856-aea1-f577d25b0550","job_id":"J03-c0e2","name":"Dismantle: Clutch 1","order":8,"status":"done","started_at":"2026-08-11T05:33:47.115Z","completed_at":"2026-08-11T15:28:10.891Z","duration_sec":35663,"std_minutes":180},{"id":"4391d523-f1d0-4922-95fb-d3827a21b813","job_id":"J03-c0e2","name":"Dismantle: Planetary &amp; Shaft","order":9,"status":"done","started_at":"2026-08-11T15:28:10.891Z","completed_at":"2026-08-11T23:53:02.227Z","duration_sec":30291,"std_minutes":300},{"id":"bdcc79ae-9f46-46e2-963d-fd2ba3d40a2e","job_id":"J03-c0e2","name":"Dismantle: Part list &amp; Tear Down","order":10,"status":"done","started_at":"2026-08-11T23:53:02.227Z","completed_at":"2026-08-12T03:13:34.783Z","duration_sec":12032,"std_minutes":240},{"id":"0670c5ee-3df9-46ba-a7e5-790a2591233a","job_id":"J03-c0e2","name":"Assemble: Planetary &amp; Shaft In-Out","order":11,"status":"done","started_at":"2026-08-12T03:13:34.783Z","completed_at":"2026-08-13T12:03:07.679Z","duration_sec":118172,"std_minutes":300},{"id":"7276104d-e8c7-4ea6-aac7-6cd975141c45","job_id":"J03-c0e2","name":"Assemble: Clutch 1","order":12,"status":"in_progress","started_at":"2026-08-13T12:29:30.475Z","completed_at":"","duration_sec":1388,"std_minutes":180},{"id":"1781ebaa-7fb0-4896-b642-71d33b8c4878","job_id":"J03-c0e2","name":"Assemble: Clutch 2","order":13,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"5532b99d-a7fd-4b7d-a752-796f7bc5daff","job_id":"J03-c0e2","name":"Assemble: Clutch 3","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"ff0ed73f-27d1-4b0a-a4f2-7818d3cfbc7e","job_id":"J03-c0e2","name":"Assemble: Clutch 4","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"970a35a3-a96b-48b4-9f04-a2b921b013f0","job_id":"J03-c0e2","name":"Assemble: Clutch 5","order":16,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"698b11d9-e1a3-451f-8a47-ccabcc5718c6","job_id":"J03-c0e2","name":"Assemble: CV, Harness &amp; Sensor","order":17,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"0620fee8-23da-434a-85e6-6354dee830d7","job_id":"J03-c0e2","name":"Assemble: Trans Gear","order":18,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":900},{"id":"ca31c8c2-4542-42f7-be4e-86974a63447b","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Set up","order":19,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"ba2d158c-a9f5-4d98-aea1-fd1f7983c4eb","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Test","order":20,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"d2f96316-8f95-487c-a7ee-94ba19ef4354","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Release","order":21,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"050b2cfc-5ea2-4926-b9c1-c7bdfe6bbd49","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":22,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240}],"assignees":[{"id":"5ece1c51-c36b-46e5-a9d2-f9106a729470","job_id":"J03-c0e2","technician_id":"T-533ca22c","assigned_at":"2026-08-10T08:23:08.120Z","is_lead":"1"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-533ca22c","status":"busy","current_job_id":"J03-c0e2"}]}</t>
+  </si>
+  <si>
+    <t>1b1b1d10-a414-4f70-b75b-b7c790f3fdae</t>
+  </si>
+  <si>
+    <t>2026-08-13T12:42:11.090Z</t>
+  </si>
+  <si>
+    <t>{"job":{"id":"J03-1833","title":"Recondition Transmission 16H,G","unit":"E448 — D10T","unit_id":"a5c2144b-1b29-40f7-9b5c-cfbbc03c3387","description":"Job recondition Transmission 16H,G (time frame standar).","status":"in_progress","technician_id":"T-c23ed9a4","template_id":"ne-transmission-16h-g","created_at":"2026-08-11T05:30:21.056Z","started_at":"2026-08-11T05:32:14.074Z","completed_at":"","paused_at":"","total_paused_sec":1927,"estimated_minutes":5340},"steps":[{"id":"e21019ab-05cb-4d4f-8f8f-fb85fa9004da","job_id":"J03-1833","name":"Dismantle: Washing Transmission gp","order":1,"status":"done","started_at":"2026-08-11T05:32:14.074Z","completed_at":"2026-08-11T23:52:49.552Z","duration_sec":66035,"std_minutes":240},{"id":"5ceecb87-2473-4297-a2a0-db873217f383","job_id":"J03-1833","name":"Dismantle: Control Valve 2EA","order":2,"status":"done","started_at":"2026-08-11T05:32:33.253Z","completed_at":"2026-08-11T23:52:32.616Z","duration_sec":65999,"std_minutes":300},{"id":"11997f0b-4cc8-4b54-8bdd-db3614b948c1","job_id":"J03-1833","name":"Dismantle: Pump, Lines, &amp; Screen","order":3,"status":"done","started_at":"2026-08-11T05:32:33.253Z","completed_at":"2026-08-11T23:52:51.817Z","duration_sec":66018,"std_minutes":240},{"id":"6c426149-ef7a-48c2-9585-5909fe86eca9","job_id":"J03-1833","name":"Dismantle: Planetary GP","order":4,"status":"done","started_at":"2026-08-11T23:52:51.817Z","completed_at":"2026-08-13T12:08:28.871Z","duration_sec":130537,"std_minutes":900},{"id":"5d3baced-8d6d-491b-9df4-09eaef47f6b9","job_id":"J03-1833","name":"Dismantle: Directional &amp; Idler gear","order":5,"status":"done","started_at":"2026-08-13T12:08:28.871Z","completed_at":"2026-08-13T12:08:40.688Z","duration_sec":11,"std_minutes":300},{"id":"0feaac14-da1a-4360-98f3-a99ad7b2fd45","job_id":"J03-1833","name":"Dismantle: Clean up Housing 2ea","order":6,"status":"done","started_at":"2026-08-13T12:24:22.396Z","completed_at":"2026-08-13T12:37:05.549Z","duration_sec":1682,"std_minutes":120},{"id":"5b00b8bb-18f9-4ef9-ac8c-5d5f25f11170","job_id":"J03-1833","name":"Dismantle: Part list &amp; Tear Down","order":7,"status":"in_progress","started_at":"2026-08-13T12:42:11.028Z","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"c536fdc6-3459-4ab5-a588-3454f07f08c7","job_id":"J03-1833","name":"Assemble: Directional &amp; Idler gear","order":8,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"89d1ae15-daf2-4871-9bc0-5940279c96f6","job_id":"J03-1833","name":"Assemble: Planetary GP","order":9,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"1197b5dd-9928-4565-ae50-91f382e2beb0","job_id":"J03-1833","name":"Assemble: CV 2EA","order":10,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"6a936f7e-e97a-47f4-9e03-24e38ef315fc","job_id":"J03-1833","name":"Assemble: Pump, Lines, &amp; Screen","order":11,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"80894723-ea93-40ff-aa35-420c027d3f95","job_id":"J03-1833","name":"Test Bench &amp; Completed: Set up","order":12,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"acf6bd0c-0d96-40b6-8b9e-ee8c27ee1625","job_id":"J03-1833","name":"Test Bench &amp; Completed: Test","order":13,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"81692dde-b76a-433d-9b5d-3476cf3cd7f6","job_id":"J03-1833","name":"Test Bench &amp; Completed: Release","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"b69b87c3-9d4b-450e-8c0e-162eb755ff75","job_id":"J03-1833","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300}],"assignees":[{"id":"a58e3fbd-80eb-4c64-bd6b-bb7196830ed8","job_id":"J03-1833","technician_id":"T-c23ed9a4","assigned_at":"2026-08-11T05:31:58.767Z","is_lead":"1"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-c23ed9a4","status":"busy","current_job_id":"J03-1833"}]}</t>
   </si>
 </sst>
 </file>
@@ -951,7 +1311,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q44"/>
+  <dimension ref="A1:Q84"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -3286,6 +3646,2126 @@
         <v>36</v>
       </c>
     </row>
+    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>188</v>
+      </c>
+      <c r="B45" t="s">
+        <v>189</v>
+      </c>
+      <c r="C45" t="s">
+        <v>19</v>
+      </c>
+      <c r="D45" t="s">
+        <v>20</v>
+      </c>
+      <c r="E45" t="s">
+        <v>21</v>
+      </c>
+      <c r="F45" t="s">
+        <v>73</v>
+      </c>
+      <c r="G45" t="s">
+        <v>23</v>
+      </c>
+      <c r="H45" t="s">
+        <v>24</v>
+      </c>
+      <c r="I45" t="s">
+        <v>24</v>
+      </c>
+      <c r="J45" t="s">
+        <v>144</v>
+      </c>
+      <c r="K45" t="s">
+        <v>187</v>
+      </c>
+      <c r="L45" t="s">
+        <v>190</v>
+      </c>
+      <c r="M45" t="s">
+        <v>35</v>
+      </c>
+      <c r="N45" t="s">
+        <v>36</v>
+      </c>
+      <c r="O45" t="s">
+        <v>36</v>
+      </c>
+      <c r="P45" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>191</v>
+      </c>
+      <c r="B46" t="s">
+        <v>192</v>
+      </c>
+      <c r="C46" t="s">
+        <v>19</v>
+      </c>
+      <c r="D46" t="s">
+        <v>20</v>
+      </c>
+      <c r="E46" t="s">
+        <v>21</v>
+      </c>
+      <c r="F46" t="s">
+        <v>73</v>
+      </c>
+      <c r="G46" t="s">
+        <v>23</v>
+      </c>
+      <c r="H46" t="s">
+        <v>24</v>
+      </c>
+      <c r="I46" t="s">
+        <v>24</v>
+      </c>
+      <c r="J46" t="s">
+        <v>144</v>
+      </c>
+      <c r="K46" t="s">
+        <v>190</v>
+      </c>
+      <c r="L46" t="s">
+        <v>193</v>
+      </c>
+      <c r="M46" t="s">
+        <v>35</v>
+      </c>
+      <c r="N46" t="s">
+        <v>36</v>
+      </c>
+      <c r="O46" t="s">
+        <v>36</v>
+      </c>
+      <c r="P46" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>194</v>
+      </c>
+      <c r="B47" t="s">
+        <v>195</v>
+      </c>
+      <c r="C47" t="s">
+        <v>19</v>
+      </c>
+      <c r="D47" t="s">
+        <v>20</v>
+      </c>
+      <c r="E47" t="s">
+        <v>21</v>
+      </c>
+      <c r="F47" t="s">
+        <v>73</v>
+      </c>
+      <c r="G47" t="s">
+        <v>23</v>
+      </c>
+      <c r="H47" t="s">
+        <v>24</v>
+      </c>
+      <c r="I47" t="s">
+        <v>24</v>
+      </c>
+      <c r="J47" t="s">
+        <v>144</v>
+      </c>
+      <c r="K47" t="s">
+        <v>193</v>
+      </c>
+      <c r="L47" t="s">
+        <v>196</v>
+      </c>
+      <c r="M47" t="s">
+        <v>35</v>
+      </c>
+      <c r="N47" t="s">
+        <v>36</v>
+      </c>
+      <c r="O47" t="s">
+        <v>36</v>
+      </c>
+      <c r="P47" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>197</v>
+      </c>
+      <c r="B48" t="s">
+        <v>198</v>
+      </c>
+      <c r="C48" t="s">
+        <v>19</v>
+      </c>
+      <c r="D48" t="s">
+        <v>20</v>
+      </c>
+      <c r="E48" t="s">
+        <v>21</v>
+      </c>
+      <c r="F48" t="s">
+        <v>73</v>
+      </c>
+      <c r="G48" t="s">
+        <v>23</v>
+      </c>
+      <c r="H48" t="s">
+        <v>24</v>
+      </c>
+      <c r="I48" t="s">
+        <v>24</v>
+      </c>
+      <c r="J48" t="s">
+        <v>144</v>
+      </c>
+      <c r="K48" t="s">
+        <v>196</v>
+      </c>
+      <c r="L48" t="s">
+        <v>199</v>
+      </c>
+      <c r="M48" t="s">
+        <v>35</v>
+      </c>
+      <c r="N48" t="s">
+        <v>36</v>
+      </c>
+      <c r="O48" t="s">
+        <v>36</v>
+      </c>
+      <c r="P48" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>200</v>
+      </c>
+      <c r="B49" t="s">
+        <v>201</v>
+      </c>
+      <c r="C49" t="s">
+        <v>19</v>
+      </c>
+      <c r="D49" t="s">
+        <v>20</v>
+      </c>
+      <c r="E49" t="s">
+        <v>21</v>
+      </c>
+      <c r="F49" t="s">
+        <v>32</v>
+      </c>
+      <c r="G49" t="s">
+        <v>23</v>
+      </c>
+      <c r="H49" t="s">
+        <v>24</v>
+      </c>
+      <c r="I49" t="s">
+        <v>24</v>
+      </c>
+      <c r="J49" t="s">
+        <v>33</v>
+      </c>
+      <c r="K49" t="s">
+        <v>199</v>
+      </c>
+      <c r="L49" t="s">
+        <v>202</v>
+      </c>
+      <c r="M49" t="s">
+        <v>35</v>
+      </c>
+      <c r="N49" t="s">
+        <v>36</v>
+      </c>
+      <c r="O49" t="s">
+        <v>36</v>
+      </c>
+      <c r="P49" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>203</v>
+      </c>
+      <c r="B50" t="s">
+        <v>204</v>
+      </c>
+      <c r="C50" t="s">
+        <v>19</v>
+      </c>
+      <c r="D50" t="s">
+        <v>20</v>
+      </c>
+      <c r="E50" t="s">
+        <v>21</v>
+      </c>
+      <c r="F50" t="s">
+        <v>32</v>
+      </c>
+      <c r="G50" t="s">
+        <v>23</v>
+      </c>
+      <c r="H50" t="s">
+        <v>24</v>
+      </c>
+      <c r="I50" t="s">
+        <v>24</v>
+      </c>
+      <c r="J50" t="s">
+        <v>33</v>
+      </c>
+      <c r="K50" t="s">
+        <v>202</v>
+      </c>
+      <c r="L50" t="s">
+        <v>205</v>
+      </c>
+      <c r="M50" t="s">
+        <v>35</v>
+      </c>
+      <c r="N50" t="s">
+        <v>36</v>
+      </c>
+      <c r="O50" t="s">
+        <v>36</v>
+      </c>
+      <c r="P50" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q50" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>206</v>
+      </c>
+      <c r="B51" t="s">
+        <v>207</v>
+      </c>
+      <c r="C51" t="s">
+        <v>19</v>
+      </c>
+      <c r="D51" t="s">
+        <v>20</v>
+      </c>
+      <c r="E51" t="s">
+        <v>21</v>
+      </c>
+      <c r="F51" t="s">
+        <v>32</v>
+      </c>
+      <c r="G51" t="s">
+        <v>23</v>
+      </c>
+      <c r="H51" t="s">
+        <v>55</v>
+      </c>
+      <c r="I51" t="s">
+        <v>55</v>
+      </c>
+      <c r="J51" t="s">
+        <v>88</v>
+      </c>
+      <c r="K51" t="s">
+        <v>169</v>
+      </c>
+      <c r="L51" t="s">
+        <v>208</v>
+      </c>
+      <c r="M51" t="s">
+        <v>35</v>
+      </c>
+      <c r="N51" t="s">
+        <v>36</v>
+      </c>
+      <c r="O51" t="s">
+        <v>36</v>
+      </c>
+      <c r="P51" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>209</v>
+      </c>
+      <c r="B52" t="s">
+        <v>210</v>
+      </c>
+      <c r="C52" t="s">
+        <v>19</v>
+      </c>
+      <c r="D52" t="s">
+        <v>20</v>
+      </c>
+      <c r="E52" t="s">
+        <v>21</v>
+      </c>
+      <c r="F52" t="s">
+        <v>73</v>
+      </c>
+      <c r="G52" t="s">
+        <v>23</v>
+      </c>
+      <c r="H52" t="s">
+        <v>24</v>
+      </c>
+      <c r="I52" t="s">
+        <v>24</v>
+      </c>
+      <c r="J52" t="s">
+        <v>144</v>
+      </c>
+      <c r="K52" t="s">
+        <v>205</v>
+      </c>
+      <c r="L52" t="s">
+        <v>211</v>
+      </c>
+      <c r="M52" t="s">
+        <v>35</v>
+      </c>
+      <c r="N52" t="s">
+        <v>36</v>
+      </c>
+      <c r="O52" t="s">
+        <v>36</v>
+      </c>
+      <c r="P52" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>212</v>
+      </c>
+      <c r="B53" t="s">
+        <v>213</v>
+      </c>
+      <c r="C53" t="s">
+        <v>19</v>
+      </c>
+      <c r="D53" t="s">
+        <v>20</v>
+      </c>
+      <c r="E53" t="s">
+        <v>21</v>
+      </c>
+      <c r="F53" t="s">
+        <v>32</v>
+      </c>
+      <c r="G53" t="s">
+        <v>23</v>
+      </c>
+      <c r="H53" t="s">
+        <v>107</v>
+      </c>
+      <c r="I53" t="s">
+        <v>107</v>
+      </c>
+      <c r="J53" t="s">
+        <v>33</v>
+      </c>
+      <c r="K53" t="s">
+        <v>160</v>
+      </c>
+      <c r="L53" t="s">
+        <v>214</v>
+      </c>
+      <c r="M53" t="s">
+        <v>35</v>
+      </c>
+      <c r="N53" t="s">
+        <v>36</v>
+      </c>
+      <c r="O53" t="s">
+        <v>36</v>
+      </c>
+      <c r="P53" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q53" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>215</v>
+      </c>
+      <c r="B54" t="s">
+        <v>216</v>
+      </c>
+      <c r="C54" t="s">
+        <v>19</v>
+      </c>
+      <c r="D54" t="s">
+        <v>20</v>
+      </c>
+      <c r="E54" t="s">
+        <v>21</v>
+      </c>
+      <c r="F54" t="s">
+        <v>32</v>
+      </c>
+      <c r="G54" t="s">
+        <v>23</v>
+      </c>
+      <c r="H54" t="s">
+        <v>107</v>
+      </c>
+      <c r="I54" t="s">
+        <v>107</v>
+      </c>
+      <c r="J54" t="s">
+        <v>33</v>
+      </c>
+      <c r="K54" t="s">
+        <v>214</v>
+      </c>
+      <c r="L54" t="s">
+        <v>217</v>
+      </c>
+      <c r="M54" t="s">
+        <v>35</v>
+      </c>
+      <c r="N54" t="s">
+        <v>36</v>
+      </c>
+      <c r="O54" t="s">
+        <v>36</v>
+      </c>
+      <c r="P54" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>218</v>
+      </c>
+      <c r="B55" t="s">
+        <v>219</v>
+      </c>
+      <c r="C55" t="s">
+        <v>19</v>
+      </c>
+      <c r="D55" t="s">
+        <v>20</v>
+      </c>
+      <c r="E55" t="s">
+        <v>21</v>
+      </c>
+      <c r="F55" t="s">
+        <v>73</v>
+      </c>
+      <c r="G55" t="s">
+        <v>23</v>
+      </c>
+      <c r="H55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I55" t="s">
+        <v>24</v>
+      </c>
+      <c r="J55" t="s">
+        <v>144</v>
+      </c>
+      <c r="K55" t="s">
+        <v>211</v>
+      </c>
+      <c r="L55" t="s">
+        <v>220</v>
+      </c>
+      <c r="M55" t="s">
+        <v>35</v>
+      </c>
+      <c r="N55" t="s">
+        <v>36</v>
+      </c>
+      <c r="O55" t="s">
+        <v>36</v>
+      </c>
+      <c r="P55" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q55" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>221</v>
+      </c>
+      <c r="B56" t="s">
+        <v>222</v>
+      </c>
+      <c r="C56" t="s">
+        <v>19</v>
+      </c>
+      <c r="D56" t="s">
+        <v>20</v>
+      </c>
+      <c r="E56" t="s">
+        <v>21</v>
+      </c>
+      <c r="F56" t="s">
+        <v>41</v>
+      </c>
+      <c r="G56" t="s">
+        <v>23</v>
+      </c>
+      <c r="H56" t="s">
+        <v>107</v>
+      </c>
+      <c r="I56" t="s">
+        <v>107</v>
+      </c>
+      <c r="J56" t="s">
+        <v>42</v>
+      </c>
+      <c r="K56" t="s">
+        <v>217</v>
+      </c>
+      <c r="L56" t="s">
+        <v>223</v>
+      </c>
+      <c r="M56" t="s">
+        <v>35</v>
+      </c>
+      <c r="N56" t="s">
+        <v>36</v>
+      </c>
+      <c r="O56" t="s">
+        <v>36</v>
+      </c>
+      <c r="P56" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q56" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>224</v>
+      </c>
+      <c r="B57" t="s">
+        <v>225</v>
+      </c>
+      <c r="C57" t="s">
+        <v>19</v>
+      </c>
+      <c r="D57" t="s">
+        <v>20</v>
+      </c>
+      <c r="E57" t="s">
+        <v>21</v>
+      </c>
+      <c r="F57" t="s">
+        <v>46</v>
+      </c>
+      <c r="G57" t="s">
+        <v>23</v>
+      </c>
+      <c r="H57" t="s">
+        <v>107</v>
+      </c>
+      <c r="I57" t="s">
+        <v>107</v>
+      </c>
+      <c r="J57" t="s">
+        <v>47</v>
+      </c>
+      <c r="K57" t="s">
+        <v>223</v>
+      </c>
+      <c r="L57" t="s">
+        <v>226</v>
+      </c>
+      <c r="M57" t="s">
+        <v>35</v>
+      </c>
+      <c r="N57" t="s">
+        <v>36</v>
+      </c>
+      <c r="O57" t="s">
+        <v>36</v>
+      </c>
+      <c r="P57" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q57" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>227</v>
+      </c>
+      <c r="B58" t="s">
+        <v>228</v>
+      </c>
+      <c r="C58" t="s">
+        <v>19</v>
+      </c>
+      <c r="D58" t="s">
+        <v>20</v>
+      </c>
+      <c r="E58" t="s">
+        <v>21</v>
+      </c>
+      <c r="F58" t="s">
+        <v>41</v>
+      </c>
+      <c r="G58" t="s">
+        <v>23</v>
+      </c>
+      <c r="H58" t="s">
+        <v>107</v>
+      </c>
+      <c r="I58" t="s">
+        <v>107</v>
+      </c>
+      <c r="J58" t="s">
+        <v>42</v>
+      </c>
+      <c r="K58" t="s">
+        <v>226</v>
+      </c>
+      <c r="L58" t="s">
+        <v>229</v>
+      </c>
+      <c r="M58" t="s">
+        <v>35</v>
+      </c>
+      <c r="N58" t="s">
+        <v>36</v>
+      </c>
+      <c r="O58" t="s">
+        <v>36</v>
+      </c>
+      <c r="P58" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q58" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>230</v>
+      </c>
+      <c r="B59" t="s">
+        <v>231</v>
+      </c>
+      <c r="C59" t="s">
+        <v>19</v>
+      </c>
+      <c r="D59" t="s">
+        <v>20</v>
+      </c>
+      <c r="E59" t="s">
+        <v>21</v>
+      </c>
+      <c r="F59" t="s">
+        <v>46</v>
+      </c>
+      <c r="G59" t="s">
+        <v>23</v>
+      </c>
+      <c r="H59" t="s">
+        <v>107</v>
+      </c>
+      <c r="I59" t="s">
+        <v>107</v>
+      </c>
+      <c r="J59" t="s">
+        <v>47</v>
+      </c>
+      <c r="K59" t="s">
+        <v>229</v>
+      </c>
+      <c r="L59" t="s">
+        <v>232</v>
+      </c>
+      <c r="M59" t="s">
+        <v>35</v>
+      </c>
+      <c r="N59" t="s">
+        <v>36</v>
+      </c>
+      <c r="O59" t="s">
+        <v>36</v>
+      </c>
+      <c r="P59" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q59" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>233</v>
+      </c>
+      <c r="B60" t="s">
+        <v>234</v>
+      </c>
+      <c r="C60" t="s">
+        <v>19</v>
+      </c>
+      <c r="D60" t="s">
+        <v>20</v>
+      </c>
+      <c r="E60" t="s">
+        <v>21</v>
+      </c>
+      <c r="F60" t="s">
+        <v>41</v>
+      </c>
+      <c r="G60" t="s">
+        <v>23</v>
+      </c>
+      <c r="H60" t="s">
+        <v>107</v>
+      </c>
+      <c r="I60" t="s">
+        <v>107</v>
+      </c>
+      <c r="J60" t="s">
+        <v>42</v>
+      </c>
+      <c r="K60" t="s">
+        <v>232</v>
+      </c>
+      <c r="L60" t="s">
+        <v>235</v>
+      </c>
+      <c r="M60" t="s">
+        <v>35</v>
+      </c>
+      <c r="N60" t="s">
+        <v>36</v>
+      </c>
+      <c r="O60" t="s">
+        <v>36</v>
+      </c>
+      <c r="P60" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q60" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>236</v>
+      </c>
+      <c r="B61" t="s">
+        <v>237</v>
+      </c>
+      <c r="C61" t="s">
+        <v>19</v>
+      </c>
+      <c r="D61" t="s">
+        <v>20</v>
+      </c>
+      <c r="E61" t="s">
+        <v>21</v>
+      </c>
+      <c r="F61" t="s">
+        <v>46</v>
+      </c>
+      <c r="G61" t="s">
+        <v>23</v>
+      </c>
+      <c r="H61" t="s">
+        <v>107</v>
+      </c>
+      <c r="I61" t="s">
+        <v>107</v>
+      </c>
+      <c r="J61" t="s">
+        <v>47</v>
+      </c>
+      <c r="K61" t="s">
+        <v>235</v>
+      </c>
+      <c r="L61" t="s">
+        <v>238</v>
+      </c>
+      <c r="M61" t="s">
+        <v>35</v>
+      </c>
+      <c r="N61" t="s">
+        <v>36</v>
+      </c>
+      <c r="O61" t="s">
+        <v>36</v>
+      </c>
+      <c r="P61" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q61" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>239</v>
+      </c>
+      <c r="B62" t="s">
+        <v>240</v>
+      </c>
+      <c r="C62" t="s">
+        <v>19</v>
+      </c>
+      <c r="D62" t="s">
+        <v>20</v>
+      </c>
+      <c r="E62" t="s">
+        <v>21</v>
+      </c>
+      <c r="F62" t="s">
+        <v>41</v>
+      </c>
+      <c r="G62" t="s">
+        <v>23</v>
+      </c>
+      <c r="H62" t="s">
+        <v>107</v>
+      </c>
+      <c r="I62" t="s">
+        <v>107</v>
+      </c>
+      <c r="J62" t="s">
+        <v>42</v>
+      </c>
+      <c r="K62" t="s">
+        <v>238</v>
+      </c>
+      <c r="L62" t="s">
+        <v>241</v>
+      </c>
+      <c r="M62" t="s">
+        <v>35</v>
+      </c>
+      <c r="N62" t="s">
+        <v>36</v>
+      </c>
+      <c r="O62" t="s">
+        <v>36</v>
+      </c>
+      <c r="P62" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q62" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>242</v>
+      </c>
+      <c r="B63" t="s">
+        <v>243</v>
+      </c>
+      <c r="C63" t="s">
+        <v>19</v>
+      </c>
+      <c r="D63" t="s">
+        <v>20</v>
+      </c>
+      <c r="E63" t="s">
+        <v>21</v>
+      </c>
+      <c r="F63" t="s">
+        <v>46</v>
+      </c>
+      <c r="G63" t="s">
+        <v>23</v>
+      </c>
+      <c r="H63" t="s">
+        <v>107</v>
+      </c>
+      <c r="I63" t="s">
+        <v>107</v>
+      </c>
+      <c r="J63" t="s">
+        <v>47</v>
+      </c>
+      <c r="K63" t="s">
+        <v>241</v>
+      </c>
+      <c r="L63" t="s">
+        <v>244</v>
+      </c>
+      <c r="M63" t="s">
+        <v>35</v>
+      </c>
+      <c r="N63" t="s">
+        <v>36</v>
+      </c>
+      <c r="O63" t="s">
+        <v>36</v>
+      </c>
+      <c r="P63" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q63" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>245</v>
+      </c>
+      <c r="B64" t="s">
+        <v>246</v>
+      </c>
+      <c r="C64" t="s">
+        <v>19</v>
+      </c>
+      <c r="D64" t="s">
+        <v>20</v>
+      </c>
+      <c r="E64" t="s">
+        <v>21</v>
+      </c>
+      <c r="F64" t="s">
+        <v>41</v>
+      </c>
+      <c r="G64" t="s">
+        <v>23</v>
+      </c>
+      <c r="H64" t="s">
+        <v>107</v>
+      </c>
+      <c r="I64" t="s">
+        <v>107</v>
+      </c>
+      <c r="J64" t="s">
+        <v>42</v>
+      </c>
+      <c r="K64" t="s">
+        <v>244</v>
+      </c>
+      <c r="L64" t="s">
+        <v>247</v>
+      </c>
+      <c r="M64" t="s">
+        <v>35</v>
+      </c>
+      <c r="N64" t="s">
+        <v>36</v>
+      </c>
+      <c r="O64" t="s">
+        <v>36</v>
+      </c>
+      <c r="P64" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q64" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>248</v>
+      </c>
+      <c r="B65" t="s">
+        <v>249</v>
+      </c>
+      <c r="C65" t="s">
+        <v>19</v>
+      </c>
+      <c r="D65" t="s">
+        <v>20</v>
+      </c>
+      <c r="E65" t="s">
+        <v>21</v>
+      </c>
+      <c r="F65" t="s">
+        <v>46</v>
+      </c>
+      <c r="G65" t="s">
+        <v>23</v>
+      </c>
+      <c r="H65" t="s">
+        <v>107</v>
+      </c>
+      <c r="I65" t="s">
+        <v>107</v>
+      </c>
+      <c r="J65" t="s">
+        <v>47</v>
+      </c>
+      <c r="K65" t="s">
+        <v>247</v>
+      </c>
+      <c r="L65" t="s">
+        <v>250</v>
+      </c>
+      <c r="M65" t="s">
+        <v>35</v>
+      </c>
+      <c r="N65" t="s">
+        <v>36</v>
+      </c>
+      <c r="O65" t="s">
+        <v>36</v>
+      </c>
+      <c r="P65" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q65" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>251</v>
+      </c>
+      <c r="B66" t="s">
+        <v>252</v>
+      </c>
+      <c r="C66" t="s">
+        <v>19</v>
+      </c>
+      <c r="D66" t="s">
+        <v>20</v>
+      </c>
+      <c r="E66" t="s">
+        <v>21</v>
+      </c>
+      <c r="F66" t="s">
+        <v>41</v>
+      </c>
+      <c r="G66" t="s">
+        <v>23</v>
+      </c>
+      <c r="H66" t="s">
+        <v>107</v>
+      </c>
+      <c r="I66" t="s">
+        <v>107</v>
+      </c>
+      <c r="J66" t="s">
+        <v>42</v>
+      </c>
+      <c r="K66" t="s">
+        <v>250</v>
+      </c>
+      <c r="L66" t="s">
+        <v>253</v>
+      </c>
+      <c r="M66" t="s">
+        <v>35</v>
+      </c>
+      <c r="N66" t="s">
+        <v>36</v>
+      </c>
+      <c r="O66" t="s">
+        <v>36</v>
+      </c>
+      <c r="P66" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q66" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>254</v>
+      </c>
+      <c r="B67" t="s">
+        <v>255</v>
+      </c>
+      <c r="C67" t="s">
+        <v>19</v>
+      </c>
+      <c r="D67" t="s">
+        <v>20</v>
+      </c>
+      <c r="E67" t="s">
+        <v>21</v>
+      </c>
+      <c r="F67" t="s">
+        <v>46</v>
+      </c>
+      <c r="G67" t="s">
+        <v>23</v>
+      </c>
+      <c r="H67" t="s">
+        <v>107</v>
+      </c>
+      <c r="I67" t="s">
+        <v>107</v>
+      </c>
+      <c r="J67" t="s">
+        <v>47</v>
+      </c>
+      <c r="K67" t="s">
+        <v>253</v>
+      </c>
+      <c r="L67" t="s">
+        <v>256</v>
+      </c>
+      <c r="M67" t="s">
+        <v>35</v>
+      </c>
+      <c r="N67" t="s">
+        <v>36</v>
+      </c>
+      <c r="O67" t="s">
+        <v>36</v>
+      </c>
+      <c r="P67" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q67" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>257</v>
+      </c>
+      <c r="B68" t="s">
+        <v>258</v>
+      </c>
+      <c r="C68" t="s">
+        <v>19</v>
+      </c>
+      <c r="D68" t="s">
+        <v>20</v>
+      </c>
+      <c r="E68" t="s">
+        <v>21</v>
+      </c>
+      <c r="F68" t="s">
+        <v>41</v>
+      </c>
+      <c r="G68" t="s">
+        <v>23</v>
+      </c>
+      <c r="H68" t="s">
+        <v>107</v>
+      </c>
+      <c r="I68" t="s">
+        <v>107</v>
+      </c>
+      <c r="J68" t="s">
+        <v>42</v>
+      </c>
+      <c r="K68" t="s">
+        <v>256</v>
+      </c>
+      <c r="L68" t="s">
+        <v>259</v>
+      </c>
+      <c r="M68" t="s">
+        <v>35</v>
+      </c>
+      <c r="N68" t="s">
+        <v>36</v>
+      </c>
+      <c r="O68" t="s">
+        <v>36</v>
+      </c>
+      <c r="P68" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q68" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>260</v>
+      </c>
+      <c r="B69" t="s">
+        <v>261</v>
+      </c>
+      <c r="C69" t="s">
+        <v>19</v>
+      </c>
+      <c r="D69" t="s">
+        <v>20</v>
+      </c>
+      <c r="E69" t="s">
+        <v>21</v>
+      </c>
+      <c r="F69" t="s">
+        <v>46</v>
+      </c>
+      <c r="G69" t="s">
+        <v>23</v>
+      </c>
+      <c r="H69" t="s">
+        <v>107</v>
+      </c>
+      <c r="I69" t="s">
+        <v>107</v>
+      </c>
+      <c r="J69" t="s">
+        <v>47</v>
+      </c>
+      <c r="K69" t="s">
+        <v>259</v>
+      </c>
+      <c r="L69" t="s">
+        <v>262</v>
+      </c>
+      <c r="M69" t="s">
+        <v>35</v>
+      </c>
+      <c r="N69" t="s">
+        <v>36</v>
+      </c>
+      <c r="O69" t="s">
+        <v>36</v>
+      </c>
+      <c r="P69" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q69" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>263</v>
+      </c>
+      <c r="B70" t="s">
+        <v>264</v>
+      </c>
+      <c r="C70" t="s">
+        <v>19</v>
+      </c>
+      <c r="D70" t="s">
+        <v>20</v>
+      </c>
+      <c r="E70" t="s">
+        <v>21</v>
+      </c>
+      <c r="F70" t="s">
+        <v>41</v>
+      </c>
+      <c r="G70" t="s">
+        <v>23</v>
+      </c>
+      <c r="H70" t="s">
+        <v>107</v>
+      </c>
+      <c r="I70" t="s">
+        <v>107</v>
+      </c>
+      <c r="J70" t="s">
+        <v>42</v>
+      </c>
+      <c r="K70" t="s">
+        <v>262</v>
+      </c>
+      <c r="L70" t="s">
+        <v>265</v>
+      </c>
+      <c r="M70" t="s">
+        <v>35</v>
+      </c>
+      <c r="N70" t="s">
+        <v>36</v>
+      </c>
+      <c r="O70" t="s">
+        <v>36</v>
+      </c>
+      <c r="P70" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q70" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>266</v>
+      </c>
+      <c r="B71" t="s">
+        <v>267</v>
+      </c>
+      <c r="C71" t="s">
+        <v>19</v>
+      </c>
+      <c r="D71" t="s">
+        <v>20</v>
+      </c>
+      <c r="E71" t="s">
+        <v>21</v>
+      </c>
+      <c r="F71" t="s">
+        <v>46</v>
+      </c>
+      <c r="G71" t="s">
+        <v>23</v>
+      </c>
+      <c r="H71" t="s">
+        <v>107</v>
+      </c>
+      <c r="I71" t="s">
+        <v>107</v>
+      </c>
+      <c r="J71" t="s">
+        <v>47</v>
+      </c>
+      <c r="K71" t="s">
+        <v>265</v>
+      </c>
+      <c r="L71" t="s">
+        <v>268</v>
+      </c>
+      <c r="M71" t="s">
+        <v>35</v>
+      </c>
+      <c r="N71" t="s">
+        <v>36</v>
+      </c>
+      <c r="O71" t="s">
+        <v>36</v>
+      </c>
+      <c r="P71" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q71" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>269</v>
+      </c>
+      <c r="B72" t="s">
+        <v>270</v>
+      </c>
+      <c r="C72" t="s">
+        <v>19</v>
+      </c>
+      <c r="D72" t="s">
+        <v>20</v>
+      </c>
+      <c r="E72" t="s">
+        <v>21</v>
+      </c>
+      <c r="F72" t="s">
+        <v>41</v>
+      </c>
+      <c r="G72" t="s">
+        <v>23</v>
+      </c>
+      <c r="H72" t="s">
+        <v>55</v>
+      </c>
+      <c r="I72" t="s">
+        <v>55</v>
+      </c>
+      <c r="J72" t="s">
+        <v>124</v>
+      </c>
+      <c r="K72" t="s">
+        <v>208</v>
+      </c>
+      <c r="L72" t="s">
+        <v>271</v>
+      </c>
+      <c r="M72" t="s">
+        <v>35</v>
+      </c>
+      <c r="N72" t="s">
+        <v>36</v>
+      </c>
+      <c r="O72" t="s">
+        <v>36</v>
+      </c>
+      <c r="P72" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q72" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>272</v>
+      </c>
+      <c r="B73" t="s">
+        <v>273</v>
+      </c>
+      <c r="C73" t="s">
+        <v>19</v>
+      </c>
+      <c r="D73" t="s">
+        <v>20</v>
+      </c>
+      <c r="E73" t="s">
+        <v>21</v>
+      </c>
+      <c r="F73" t="s">
+        <v>46</v>
+      </c>
+      <c r="G73" t="s">
+        <v>23</v>
+      </c>
+      <c r="H73" t="s">
+        <v>55</v>
+      </c>
+      <c r="I73" t="s">
+        <v>55</v>
+      </c>
+      <c r="J73" t="s">
+        <v>128</v>
+      </c>
+      <c r="K73" t="s">
+        <v>271</v>
+      </c>
+      <c r="L73" t="s">
+        <v>274</v>
+      </c>
+      <c r="M73" t="s">
+        <v>35</v>
+      </c>
+      <c r="N73" t="s">
+        <v>36</v>
+      </c>
+      <c r="O73" t="s">
+        <v>36</v>
+      </c>
+      <c r="P73" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q73" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>275</v>
+      </c>
+      <c r="B74" t="s">
+        <v>276</v>
+      </c>
+      <c r="C74" t="s">
+        <v>19</v>
+      </c>
+      <c r="D74" t="s">
+        <v>20</v>
+      </c>
+      <c r="E74" t="s">
+        <v>21</v>
+      </c>
+      <c r="F74" t="s">
+        <v>41</v>
+      </c>
+      <c r="G74" t="s">
+        <v>23</v>
+      </c>
+      <c r="H74" t="s">
+        <v>55</v>
+      </c>
+      <c r="I74" t="s">
+        <v>55</v>
+      </c>
+      <c r="J74" t="s">
+        <v>124</v>
+      </c>
+      <c r="K74" t="s">
+        <v>274</v>
+      </c>
+      <c r="L74" t="s">
+        <v>277</v>
+      </c>
+      <c r="M74" t="s">
+        <v>35</v>
+      </c>
+      <c r="N74" t="s">
+        <v>36</v>
+      </c>
+      <c r="O74" t="s">
+        <v>36</v>
+      </c>
+      <c r="P74" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q74" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>278</v>
+      </c>
+      <c r="B75" t="s">
+        <v>279</v>
+      </c>
+      <c r="C75" t="s">
+        <v>19</v>
+      </c>
+      <c r="D75" t="s">
+        <v>20</v>
+      </c>
+      <c r="E75" t="s">
+        <v>21</v>
+      </c>
+      <c r="F75" t="s">
+        <v>46</v>
+      </c>
+      <c r="G75" t="s">
+        <v>23</v>
+      </c>
+      <c r="H75" t="s">
+        <v>55</v>
+      </c>
+      <c r="I75" t="s">
+        <v>55</v>
+      </c>
+      <c r="J75" t="s">
+        <v>128</v>
+      </c>
+      <c r="K75" t="s">
+        <v>277</v>
+      </c>
+      <c r="L75" t="s">
+        <v>280</v>
+      </c>
+      <c r="M75" t="s">
+        <v>35</v>
+      </c>
+      <c r="N75" t="s">
+        <v>36</v>
+      </c>
+      <c r="O75" t="s">
+        <v>36</v>
+      </c>
+      <c r="P75" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q75" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>281</v>
+      </c>
+      <c r="B76" t="s">
+        <v>282</v>
+      </c>
+      <c r="C76" t="s">
+        <v>19</v>
+      </c>
+      <c r="D76" t="s">
+        <v>20</v>
+      </c>
+      <c r="E76" t="s">
+        <v>21</v>
+      </c>
+      <c r="F76" t="s">
+        <v>41</v>
+      </c>
+      <c r="G76" t="s">
+        <v>23</v>
+      </c>
+      <c r="H76" t="s">
+        <v>55</v>
+      </c>
+      <c r="I76" t="s">
+        <v>55</v>
+      </c>
+      <c r="J76" t="s">
+        <v>124</v>
+      </c>
+      <c r="K76" t="s">
+        <v>280</v>
+      </c>
+      <c r="L76" t="s">
+        <v>283</v>
+      </c>
+      <c r="M76" t="s">
+        <v>35</v>
+      </c>
+      <c r="N76" t="s">
+        <v>36</v>
+      </c>
+      <c r="O76" t="s">
+        <v>36</v>
+      </c>
+      <c r="P76" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q76" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>284</v>
+      </c>
+      <c r="B77" t="s">
+        <v>285</v>
+      </c>
+      <c r="C77" t="s">
+        <v>19</v>
+      </c>
+      <c r="D77" t="s">
+        <v>20</v>
+      </c>
+      <c r="E77" t="s">
+        <v>21</v>
+      </c>
+      <c r="F77" t="s">
+        <v>46</v>
+      </c>
+      <c r="G77" t="s">
+        <v>23</v>
+      </c>
+      <c r="H77" t="s">
+        <v>55</v>
+      </c>
+      <c r="I77" t="s">
+        <v>55</v>
+      </c>
+      <c r="J77" t="s">
+        <v>128</v>
+      </c>
+      <c r="K77" t="s">
+        <v>283</v>
+      </c>
+      <c r="L77" t="s">
+        <v>286</v>
+      </c>
+      <c r="M77" t="s">
+        <v>35</v>
+      </c>
+      <c r="N77" t="s">
+        <v>36</v>
+      </c>
+      <c r="O77" t="s">
+        <v>36</v>
+      </c>
+      <c r="P77" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q77" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>287</v>
+      </c>
+      <c r="B78" t="s">
+        <v>288</v>
+      </c>
+      <c r="C78" t="s">
+        <v>19</v>
+      </c>
+      <c r="D78" t="s">
+        <v>20</v>
+      </c>
+      <c r="E78" t="s">
+        <v>21</v>
+      </c>
+      <c r="F78" t="s">
+        <v>41</v>
+      </c>
+      <c r="G78" t="s">
+        <v>23</v>
+      </c>
+      <c r="H78" t="s">
+        <v>55</v>
+      </c>
+      <c r="I78" t="s">
+        <v>55</v>
+      </c>
+      <c r="J78" t="s">
+        <v>124</v>
+      </c>
+      <c r="K78" t="s">
+        <v>286</v>
+      </c>
+      <c r="L78" t="s">
+        <v>289</v>
+      </c>
+      <c r="M78" t="s">
+        <v>35</v>
+      </c>
+      <c r="N78" t="s">
+        <v>36</v>
+      </c>
+      <c r="O78" t="s">
+        <v>36</v>
+      </c>
+      <c r="P78" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q78" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>290</v>
+      </c>
+      <c r="B79" t="s">
+        <v>291</v>
+      </c>
+      <c r="C79" t="s">
+        <v>19</v>
+      </c>
+      <c r="D79" t="s">
+        <v>20</v>
+      </c>
+      <c r="E79" t="s">
+        <v>21</v>
+      </c>
+      <c r="F79" t="s">
+        <v>46</v>
+      </c>
+      <c r="G79" t="s">
+        <v>23</v>
+      </c>
+      <c r="H79" t="s">
+        <v>55</v>
+      </c>
+      <c r="I79" t="s">
+        <v>55</v>
+      </c>
+      <c r="J79" t="s">
+        <v>128</v>
+      </c>
+      <c r="K79" t="s">
+        <v>289</v>
+      </c>
+      <c r="L79" t="s">
+        <v>292</v>
+      </c>
+      <c r="M79" t="s">
+        <v>35</v>
+      </c>
+      <c r="N79" t="s">
+        <v>36</v>
+      </c>
+      <c r="O79" t="s">
+        <v>36</v>
+      </c>
+      <c r="P79" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q79" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>293</v>
+      </c>
+      <c r="B80" t="s">
+        <v>294</v>
+      </c>
+      <c r="C80" t="s">
+        <v>19</v>
+      </c>
+      <c r="D80" t="s">
+        <v>20</v>
+      </c>
+      <c r="E80" t="s">
+        <v>21</v>
+      </c>
+      <c r="F80" t="s">
+        <v>41</v>
+      </c>
+      <c r="G80" t="s">
+        <v>23</v>
+      </c>
+      <c r="H80" t="s">
+        <v>55</v>
+      </c>
+      <c r="I80" t="s">
+        <v>55</v>
+      </c>
+      <c r="J80" t="s">
+        <v>124</v>
+      </c>
+      <c r="K80" t="s">
+        <v>292</v>
+      </c>
+      <c r="L80" t="s">
+        <v>295</v>
+      </c>
+      <c r="M80" t="s">
+        <v>35</v>
+      </c>
+      <c r="N80" t="s">
+        <v>36</v>
+      </c>
+      <c r="O80" t="s">
+        <v>36</v>
+      </c>
+      <c r="P80" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q80" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>296</v>
+      </c>
+      <c r="B81" t="s">
+        <v>297</v>
+      </c>
+      <c r="C81" t="s">
+        <v>19</v>
+      </c>
+      <c r="D81" t="s">
+        <v>20</v>
+      </c>
+      <c r="E81" t="s">
+        <v>21</v>
+      </c>
+      <c r="F81" t="s">
+        <v>46</v>
+      </c>
+      <c r="G81" t="s">
+        <v>23</v>
+      </c>
+      <c r="H81" t="s">
+        <v>55</v>
+      </c>
+      <c r="I81" t="s">
+        <v>55</v>
+      </c>
+      <c r="J81" t="s">
+        <v>128</v>
+      </c>
+      <c r="K81" t="s">
+        <v>295</v>
+      </c>
+      <c r="L81" t="s">
+        <v>298</v>
+      </c>
+      <c r="M81" t="s">
+        <v>35</v>
+      </c>
+      <c r="N81" t="s">
+        <v>36</v>
+      </c>
+      <c r="O81" t="s">
+        <v>36</v>
+      </c>
+      <c r="P81" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q81" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>299</v>
+      </c>
+      <c r="B82" t="s">
+        <v>300</v>
+      </c>
+      <c r="C82" t="s">
+        <v>19</v>
+      </c>
+      <c r="D82" t="s">
+        <v>20</v>
+      </c>
+      <c r="E82" t="s">
+        <v>21</v>
+      </c>
+      <c r="F82" t="s">
+        <v>41</v>
+      </c>
+      <c r="G82" t="s">
+        <v>23</v>
+      </c>
+      <c r="H82" t="s">
+        <v>55</v>
+      </c>
+      <c r="I82" t="s">
+        <v>55</v>
+      </c>
+      <c r="J82" t="s">
+        <v>124</v>
+      </c>
+      <c r="K82" t="s">
+        <v>298</v>
+      </c>
+      <c r="L82" t="s">
+        <v>301</v>
+      </c>
+      <c r="M82" t="s">
+        <v>35</v>
+      </c>
+      <c r="N82" t="s">
+        <v>36</v>
+      </c>
+      <c r="O82" t="s">
+        <v>36</v>
+      </c>
+      <c r="P82" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q82" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>302</v>
+      </c>
+      <c r="B83" t="s">
+        <v>303</v>
+      </c>
+      <c r="C83" t="s">
+        <v>19</v>
+      </c>
+      <c r="D83" t="s">
+        <v>20</v>
+      </c>
+      <c r="E83" t="s">
+        <v>21</v>
+      </c>
+      <c r="F83" t="s">
+        <v>46</v>
+      </c>
+      <c r="G83" t="s">
+        <v>23</v>
+      </c>
+      <c r="H83" t="s">
+        <v>55</v>
+      </c>
+      <c r="I83" t="s">
+        <v>55</v>
+      </c>
+      <c r="J83" t="s">
+        <v>128</v>
+      </c>
+      <c r="K83" t="s">
+        <v>301</v>
+      </c>
+      <c r="L83" t="s">
+        <v>304</v>
+      </c>
+      <c r="M83" t="s">
+        <v>35</v>
+      </c>
+      <c r="N83" t="s">
+        <v>36</v>
+      </c>
+      <c r="O83" t="s">
+        <v>36</v>
+      </c>
+      <c r="P83" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q83" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>305</v>
+      </c>
+      <c r="B84" t="s">
+        <v>306</v>
+      </c>
+      <c r="C84" t="s">
+        <v>19</v>
+      </c>
+      <c r="D84" t="s">
+        <v>20</v>
+      </c>
+      <c r="E84" t="s">
+        <v>21</v>
+      </c>
+      <c r="F84" t="s">
+        <v>32</v>
+      </c>
+      <c r="G84" t="s">
+        <v>23</v>
+      </c>
+      <c r="H84" t="s">
+        <v>107</v>
+      </c>
+      <c r="I84" t="s">
+        <v>107</v>
+      </c>
+      <c r="J84" t="s">
+        <v>33</v>
+      </c>
+      <c r="K84" t="s">
+        <v>268</v>
+      </c>
+      <c r="L84" t="s">
+        <v>307</v>
+      </c>
+      <c r="M84" t="s">
+        <v>35</v>
+      </c>
+      <c r="N84" t="s">
+        <v>36</v>
+      </c>
+      <c r="O84" t="s">
+        <v>36</v>
+      </c>
+      <c r="P84" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q84" t="s">
+        <v>36</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/data/backup-jobs.xlsx
+++ b/data/backup-jobs.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1428" uniqueCount="308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1683" uniqueCount="360">
   <si>
     <t>id</t>
   </si>
@@ -935,6 +935,162 @@
   </si>
   <si>
     <t>{"job":{"id":"J03-1833","title":"Recondition Transmission 16H,G","unit":"E448 — D10T","unit_id":"a5c2144b-1b29-40f7-9b5c-cfbbc03c3387","description":"Job recondition Transmission 16H,G (time frame standar).","status":"in_progress","technician_id":"T-c23ed9a4","template_id":"ne-transmission-16h-g","created_at":"2026-08-11T05:30:21.056Z","started_at":"2026-08-11T05:32:14.074Z","completed_at":"","paused_at":"","total_paused_sec":1927,"estimated_minutes":5340},"steps":[{"id":"e21019ab-05cb-4d4f-8f8f-fb85fa9004da","job_id":"J03-1833","name":"Dismantle: Washing Transmission gp","order":1,"status":"done","started_at":"2026-08-11T05:32:14.074Z","completed_at":"2026-08-11T23:52:49.552Z","duration_sec":66035,"std_minutes":240},{"id":"5ceecb87-2473-4297-a2a0-db873217f383","job_id":"J03-1833","name":"Dismantle: Control Valve 2EA","order":2,"status":"done","started_at":"2026-08-11T05:32:33.253Z","completed_at":"2026-08-11T23:52:32.616Z","duration_sec":65999,"std_minutes":300},{"id":"11997f0b-4cc8-4b54-8bdd-db3614b948c1","job_id":"J03-1833","name":"Dismantle: Pump, Lines, &amp; Screen","order":3,"status":"done","started_at":"2026-08-11T05:32:33.253Z","completed_at":"2026-08-11T23:52:51.817Z","duration_sec":66018,"std_minutes":240},{"id":"6c426149-ef7a-48c2-9585-5909fe86eca9","job_id":"J03-1833","name":"Dismantle: Planetary GP","order":4,"status":"done","started_at":"2026-08-11T23:52:51.817Z","completed_at":"2026-08-13T12:08:28.871Z","duration_sec":130537,"std_minutes":900},{"id":"5d3baced-8d6d-491b-9df4-09eaef47f6b9","job_id":"J03-1833","name":"Dismantle: Directional &amp; Idler gear","order":5,"status":"done","started_at":"2026-08-13T12:08:28.871Z","completed_at":"2026-08-13T12:08:40.688Z","duration_sec":11,"std_minutes":300},{"id":"0feaac14-da1a-4360-98f3-a99ad7b2fd45","job_id":"J03-1833","name":"Dismantle: Clean up Housing 2ea","order":6,"status":"done","started_at":"2026-08-13T12:24:22.396Z","completed_at":"2026-08-13T12:37:05.549Z","duration_sec":1682,"std_minutes":120},{"id":"5b00b8bb-18f9-4ef9-ac8c-5d5f25f11170","job_id":"J03-1833","name":"Dismantle: Part list &amp; Tear Down","order":7,"status":"in_progress","started_at":"2026-08-13T12:42:11.028Z","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"c536fdc6-3459-4ab5-a588-3454f07f08c7","job_id":"J03-1833","name":"Assemble: Directional &amp; Idler gear","order":8,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"89d1ae15-daf2-4871-9bc0-5940279c96f6","job_id":"J03-1833","name":"Assemble: Planetary GP","order":9,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"1197b5dd-9928-4565-ae50-91f382e2beb0","job_id":"J03-1833","name":"Assemble: CV 2EA","order":10,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"6a936f7e-e97a-47f4-9e03-24e38ef315fc","job_id":"J03-1833","name":"Assemble: Pump, Lines, &amp; Screen","order":11,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"80894723-ea93-40ff-aa35-420c027d3f95","job_id":"J03-1833","name":"Test Bench &amp; Completed: Set up","order":12,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"acf6bd0c-0d96-40b6-8b9e-ee8c27ee1625","job_id":"J03-1833","name":"Test Bench &amp; Completed: Test","order":13,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"81692dde-b76a-433d-9b5d-3476cf3cd7f6","job_id":"J03-1833","name":"Test Bench &amp; Completed: Release","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"b69b87c3-9d4b-450e-8c0e-162eb755ff75","job_id":"J03-1833","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300}],"assignees":[{"id":"a58e3fbd-80eb-4c64-bd6b-bb7196830ed8","job_id":"J03-1833","technician_id":"T-c23ed9a4","assigned_at":"2026-08-11T05:31:58.767Z","is_lead":"1"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-c23ed9a4","status":"busy","current_job_id":"J03-1833"}]}</t>
+  </si>
+  <si>
+    <t>19947b01-2dd6-4090-972f-438d18ec5291</t>
+  </si>
+  <si>
+    <t>2026-08-13T13:13:28.201Z</t>
+  </si>
+  <si>
+    <t>J-f12e75a0a2</t>
+  </si>
+  <si>
+    <t>Buat job Recondition Transmission 24H,M · GR407 — 24H</t>
+  </si>
+  <si>
+    <t>{"job":{"id":"J-f12e75a0a2","title":"Recondition Transmission 24H,M","unit":"GR407 — 24H","unit_id":"U-555bc792","description":"Job recondition Transmission 24H,M (time frame standar).","status":"queued","technician_id":"","template_id":"ne-transmission-24h-m","created_at":"2026-08-13T13:13:28.201Z","started_at":"","completed_at":"","paused_at":"","total_paused_sec":0,"estimated_minutes":7560},"steps":[{"id":"S-62fed7fe57","job_id":"J-f12e75a0a2","name":"Dismantle: Washing Transmission gp","order":1,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"S-bdca34bf9c","job_id":"J-f12e75a0a2","name":"Dismantle: Control Valve","order":2,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"S-198d547e50","job_id":"J-f12e75a0a2","name":"Dismantle: Input Trans Gear","order":3,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-0a2990beeb","job_id":"J-f12e75a0a2","name":"Dismantle: Disconnect Planetary","order":4,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-1b44880146","job_id":"J-f12e75a0a2","name":"Dismantle: Clutch 6 &amp; Housing","order":5,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"S-9f4ccc66c5","job_id":"J-f12e75a0a2","name":"Dismantle: Clutch 5","order":6,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-ebd5f203d4","job_id":"J-f12e75a0a2","name":"Dismantle: Clutch 4","order":7,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-efc0d8adbe","job_id":"J-f12e75a0a2","name":"Dismantle: Clutch 3","order":8,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-74a4e63638","job_id":"J-f12e75a0a2","name":"Dismantle: Clutch 2","order":9,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-4dd2a4b52f","job_id":"J-f12e75a0a2","name":"Dismantle: Clutch 1","order":10,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-1cf61d6445","job_id":"J-f12e75a0a2","name":"Dismantle: Planetary &amp; Shaft In-Out","order":11,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"S-f8a0d4e613","job_id":"J-f12e75a0a2","name":"Dismantle: Output Trans Gear","order":12,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":480},{"id":"S-738f8cdae4","job_id":"J-f12e75a0a2","name":"Dismantle: Part list &amp; Tear Down","order":13,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"S-7e81ce5baf","job_id":"J-f12e75a0a2","name":"Assemble: Output Trans Gear","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"S-aacd67baa7","job_id":"J-f12e75a0a2","name":"Assemble: Planetary &amp; Shaft In-Out","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":420},{"id":"S-2bc1eb8c7a","job_id":"J-f12e75a0a2","name":"Assemble: Clutch 1","order":16,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-6c41013e7e","job_id":"J-f12e75a0a2","name":"Assemble: Clutch 2","order":17,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-5dfc9e18df","job_id":"J-f12e75a0a2","name":"Assemble: Clutch 3","order":18,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-427f687ce7","job_id":"J-f12e75a0a2","name":"Assemble: Clutch 4","order":19,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-a7a64f1028","job_id":"J-f12e75a0a2","name":"Assemble: Clutch 5","order":20,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-4f47d5d7b1","job_id":"J-f12e75a0a2","name":"Assemble: Clutch 6 &amp; Housing","order":21,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"S-f5cd7cfd6b","job_id":"J-f12e75a0a2","name":"Assemble: Input Trans Gear","order":22,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"S-647d82040c","job_id":"J-f12e75a0a2","name":"Assemble: Connect Planetary Gp","order":23,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"S-c0da413e41","job_id":"J-f12e75a0a2","name":"Assemble: Control Valve","order":24,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"S-e696ef645c","job_id":"J-f12e75a0a2","name":"Test Bench &amp; Completed: Set up","order":25,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":420},{"id":"S-7d4f1a859e","job_id":"J-f12e75a0a2","name":"Test Bench &amp; Completed: Test","order":26,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"S-1197155765","job_id":"J-f12e75a0a2","name":"Test Bench &amp; Completed: Release","order":27,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":360},{"id":"S-71f21d6927","job_id":"J-f12e75a0a2","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":28,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300}],"assignees":[],"handovers":[],"part_loans":[],"technicians":[]}</t>
+  </si>
+  <si>
+    <t>4fe31433-d8f2-4be5-96a6-426de993766d</t>
+  </si>
+  <si>
+    <t>2026-08-13T13:13:29.908Z</t>
+  </si>
+  <si>
+    <t>assign · Recondition Transmission 24H,M · status assigned</t>
+  </si>
+  <si>
+    <t>{"job":{"id":"J-f12e75a0a2","title":"Recondition Transmission 24H,M","unit":"GR407 — 24H","unit_id":"U-555bc792","description":"Job recondition Transmission 24H,M (time frame standar).","status":"assigned","technician_id":"T-25b280e7","template_id":"ne-transmission-24h-m","created_at":"2026-08-13T13:13:28.201Z","started_at":"","completed_at":"","paused_at":"","total_paused_sec":0,"estimated_minutes":7560},"steps":[{"id":"S-62fed7fe57","job_id":"J-f12e75a0a2","name":"Dismantle: Washing Transmission gp","order":1,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"S-bdca34bf9c","job_id":"J-f12e75a0a2","name":"Dismantle: Control Valve","order":2,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"S-198d547e50","job_id":"J-f12e75a0a2","name":"Dismantle: Input Trans Gear","order":3,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-0a2990beeb","job_id":"J-f12e75a0a2","name":"Dismantle: Disconnect Planetary","order":4,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-1b44880146","job_id":"J-f12e75a0a2","name":"Dismantle: Clutch 6 &amp; Housing","order":5,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"S-9f4ccc66c5","job_id":"J-f12e75a0a2","name":"Dismantle: Clutch 5","order":6,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-ebd5f203d4","job_id":"J-f12e75a0a2","name":"Dismantle: Clutch 4","order":7,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-efc0d8adbe","job_id":"J-f12e75a0a2","name":"Dismantle: Clutch 3","order":8,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-74a4e63638","job_id":"J-f12e75a0a2","name":"Dismantle: Clutch 2","order":9,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-4dd2a4b52f","job_id":"J-f12e75a0a2","name":"Dismantle: Clutch 1","order":10,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-1cf61d6445","job_id":"J-f12e75a0a2","name":"Dismantle: Planetary &amp; Shaft In-Out","order":11,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"S-f8a0d4e613","job_id":"J-f12e75a0a2","name":"Dismantle: Output Trans Gear","order":12,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":480},{"id":"S-738f8cdae4","job_id":"J-f12e75a0a2","name":"Dismantle: Part list &amp; Tear Down","order":13,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"S-7e81ce5baf","job_id":"J-f12e75a0a2","name":"Assemble: Output Trans Gear","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"S-aacd67baa7","job_id":"J-f12e75a0a2","name":"Assemble: Planetary &amp; Shaft In-Out","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":420},{"id":"S-2bc1eb8c7a","job_id":"J-f12e75a0a2","name":"Assemble: Clutch 1","order":16,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-6c41013e7e","job_id":"J-f12e75a0a2","name":"Assemble: Clutch 2","order":17,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-5dfc9e18df","job_id":"J-f12e75a0a2","name":"Assemble: Clutch 3","order":18,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-427f687ce7","job_id":"J-f12e75a0a2","name":"Assemble: Clutch 4","order":19,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-a7a64f1028","job_id":"J-f12e75a0a2","name":"Assemble: Clutch 5","order":20,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-4f47d5d7b1","job_id":"J-f12e75a0a2","name":"Assemble: Clutch 6 &amp; Housing","order":21,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"S-f5cd7cfd6b","job_id":"J-f12e75a0a2","name":"Assemble: Input Trans Gear","order":22,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"S-647d82040c","job_id":"J-f12e75a0a2","name":"Assemble: Connect Planetary Gp","order":23,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"S-c0da413e41","job_id":"J-f12e75a0a2","name":"Assemble: Control Valve","order":24,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"S-e696ef645c","job_id":"J-f12e75a0a2","name":"Test Bench &amp; Completed: Set up","order":25,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":420},{"id":"S-7d4f1a859e","job_id":"J-f12e75a0a2","name":"Test Bench &amp; Completed: Test","order":26,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"S-1197155765","job_id":"J-f12e75a0a2","name":"Test Bench &amp; Completed: Release","order":27,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":360},{"id":"S-71f21d6927","job_id":"J-f12e75a0a2","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":28,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300}],"assignees":[{"id":"12cf269a-3fcd-4435-af09-3ee3a1e43923","job_id":"J-f12e75a0a2","technician_id":"T-25b280e7","assigned_at":"2026-08-13T13:13:29.838Z","is_lead":"1"},{"id":"1db87a48-9c13-40ac-af3f-256b6b08df59","job_id":"J-f12e75a0a2","technician_id":"T-1c1b3289","assigned_at":"2026-08-13T13:13:29.838Z","is_lead":"0"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-25b280e7","status":"busy","current_job_id":"J-f12e75a0a2"},{"id":"T-1c1b3289","status":"busy","current_job_id":"J-f12e75a0a2"}]}</t>
+  </si>
+  <si>
+    <t>6eeb77b2-9c47-4160-8c30-34ec1099036c</t>
+  </si>
+  <si>
+    <t>2026-08-13T13:16:36.807Z</t>
+  </si>
+  <si>
+    <t>start · Recondition Transmission 24H,M · status in_progress</t>
+  </si>
+  <si>
+    <t>{"job":{"id":"J-f12e75a0a2","title":"Recondition Transmission 24H,M","unit":"GR407 — 24H","unit_id":"U-555bc792","description":"Job recondition Transmission 24H,M (time frame standar).","status":"in_progress","technician_id":"T-25b280e7","template_id":"ne-transmission-24h-m","created_at":"2026-08-13T13:13:28.201Z","started_at":"2026-08-13T13:16:36.692Z","completed_at":"","paused_at":"","total_paused_sec":0,"estimated_minutes":7560},"steps":[{"id":"S-62fed7fe57","job_id":"J-f12e75a0a2","name":"Dismantle: Washing Transmission gp","order":1,"status":"in_progress","started_at":"2026-08-13T13:16:36.692Z","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"S-bdca34bf9c","job_id":"J-f12e75a0a2","name":"Dismantle: Control Valve","order":2,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"S-198d547e50","job_id":"J-f12e75a0a2","name":"Dismantle: Input Trans Gear","order":3,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-0a2990beeb","job_id":"J-f12e75a0a2","name":"Dismantle: Disconnect Planetary","order":4,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-1b44880146","job_id":"J-f12e75a0a2","name":"Dismantle: Clutch 6 &amp; Housing","order":5,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"S-9f4ccc66c5","job_id":"J-f12e75a0a2","name":"Dismantle: Clutch 5","order":6,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-ebd5f203d4","job_id":"J-f12e75a0a2","name":"Dismantle: Clutch 4","order":7,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-efc0d8adbe","job_id":"J-f12e75a0a2","name":"Dismantle: Clutch 3","order":8,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-74a4e63638","job_id":"J-f12e75a0a2","name":"Dismantle: Clutch 2","order":9,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-4dd2a4b52f","job_id":"J-f12e75a0a2","name":"Dismantle: Clutch 1","order":10,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-1cf61d6445","job_id":"J-f12e75a0a2","name":"Dismantle: Planetary &amp; Shaft In-Out","order":11,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"S-f8a0d4e613","job_id":"J-f12e75a0a2","name":"Dismantle: Output Trans Gear","order":12,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":480},{"id":"S-738f8cdae4","job_id":"J-f12e75a0a2","name":"Dismantle: Part list &amp; Tear Down","order":13,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"S-7e81ce5baf","job_id":"J-f12e75a0a2","name":"Assemble: Output Trans Gear","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"S-aacd67baa7","job_id":"J-f12e75a0a2","name":"Assemble: Planetary &amp; Shaft In-Out","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":420},{"id":"S-2bc1eb8c7a","job_id":"J-f12e75a0a2","name":"Assemble: Clutch 1","order":16,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-6c41013e7e","job_id":"J-f12e75a0a2","name":"Assemble: Clutch 2","order":17,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-5dfc9e18df","job_id":"J-f12e75a0a2","name":"Assemble: Clutch 3","order":18,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-427f687ce7","job_id":"J-f12e75a0a2","name":"Assemble: Clutch 4","order":19,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-a7a64f1028","job_id":"J-f12e75a0a2","name":"Assemble: Clutch 5","order":20,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-4f47d5d7b1","job_id":"J-f12e75a0a2","name":"Assemble: Clutch 6 &amp; Housing","order":21,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"S-f5cd7cfd6b","job_id":"J-f12e75a0a2","name":"Assemble: Input Trans Gear","order":22,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"S-647d82040c","job_id":"J-f12e75a0a2","name":"Assemble: Connect Planetary Gp","order":23,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"S-c0da413e41","job_id":"J-f12e75a0a2","name":"Assemble: Control Valve","order":24,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"S-e696ef645c","job_id":"J-f12e75a0a2","name":"Test Bench &amp; Completed: Set up","order":25,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":420},{"id":"S-7d4f1a859e","job_id":"J-f12e75a0a2","name":"Test Bench &amp; Completed: Test","order":26,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"S-1197155765","job_id":"J-f12e75a0a2","name":"Test Bench &amp; Completed: Release","order":27,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":360},{"id":"S-71f21d6927","job_id":"J-f12e75a0a2","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":28,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300}],"assignees":[{"id":"12cf269a-3fcd-4435-af09-3ee3a1e43923","job_id":"J-f12e75a0a2","technician_id":"T-25b280e7","assigned_at":"2026-08-13T13:13:29.838Z","is_lead":"1"},{"id":"1db87a48-9c13-40ac-af3f-256b6b08df59","job_id":"J-f12e75a0a2","technician_id":"T-1c1b3289","assigned_at":"2026-08-13T13:13:29.838Z","is_lead":"0"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-25b280e7","status":"busy","current_job_id":"J-f12e75a0a2"},{"id":"T-1c1b3289","status":"busy","current_job_id":"J-f12e75a0a2"}]}</t>
+  </si>
+  <si>
+    <t>b2e58d4a-3fcb-4592-95db-5fb3d24a727d</t>
+  </si>
+  <si>
+    <t>2026-08-13T13:16:37.530Z</t>
+  </si>
+  <si>
+    <t>complete_step · Recondition Transmission 24H,M · status in_progress</t>
+  </si>
+  <si>
+    <t>{"job":{"id":"J-f12e75a0a2","title":"Recondition Transmission 24H,M","unit":"GR407 — 24H","unit_id":"U-555bc792","description":"Job recondition Transmission 24H,M (time frame standar).","status":"in_progress","technician_id":"T-25b280e7","template_id":"ne-transmission-24h-m","created_at":"2026-08-13T13:13:28.201Z","started_at":"2026-08-13T13:16:36.692Z","completed_at":"","paused_at":"","total_paused_sec":0,"estimated_minutes":7560},"steps":[{"id":"S-62fed7fe57","job_id":"J-f12e75a0a2","name":"Dismantle: Washing Transmission gp","order":1,"status":"done","started_at":"2026-08-13T13:14:01.944Z","completed_at":"2026-08-13T13:15:17.497Z","duration_sec":150,"std_minutes":300},{"id":"S-bdca34bf9c","job_id":"J-f12e75a0a2","name":"Dismantle: Control Valve","order":2,"status":"in_progress","started_at":"2026-08-13T13:16:37.469Z","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"S-198d547e50","job_id":"J-f12e75a0a2","name":"Dismantle: Input Trans Gear","order":3,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-0a2990beeb","job_id":"J-f12e75a0a2","name":"Dismantle: Disconnect Planetary","order":4,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-1b44880146","job_id":"J-f12e75a0a2","name":"Dismantle: Clutch 6 &amp; Housing","order":5,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"S-9f4ccc66c5","job_id":"J-f12e75a0a2","name":"Dismantle: Clutch 5","order":6,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-ebd5f203d4","job_id":"J-f12e75a0a2","name":"Dismantle: Clutch 4","order":7,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-efc0d8adbe","job_id":"J-f12e75a0a2","name":"Dismantle: Clutch 3","order":8,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-74a4e63638","job_id":"J-f12e75a0a2","name":"Dismantle: Clutch 2","order":9,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-4dd2a4b52f","job_id":"J-f12e75a0a2","name":"Dismantle: Clutch 1","order":10,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-1cf61d6445","job_id":"J-f12e75a0a2","name":"Dismantle: Planetary &amp; Shaft In-Out","order":11,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"S-f8a0d4e613","job_id":"J-f12e75a0a2","name":"Dismantle: Output Trans Gear","order":12,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":480},{"id":"S-738f8cdae4","job_id":"J-f12e75a0a2","name":"Dismantle: Part list &amp; Tear Down","order":13,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"S-7e81ce5baf","job_id":"J-f12e75a0a2","name":"Assemble: Output Trans Gear","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"S-aacd67baa7","job_id":"J-f12e75a0a2","name":"Assemble: Planetary &amp; Shaft In-Out","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":420},{"id":"S-2bc1eb8c7a","job_id":"J-f12e75a0a2","name":"Assemble: Clutch 1","order":16,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-6c41013e7e","job_id":"J-f12e75a0a2","name":"Assemble: Clutch 2","order":17,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-5dfc9e18df","job_id":"J-f12e75a0a2","name":"Assemble: Clutch 3","order":18,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-427f687ce7","job_id":"J-f12e75a0a2","name":"Assemble: Clutch 4","order":19,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-a7a64f1028","job_id":"J-f12e75a0a2","name":"Assemble: Clutch 5","order":20,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-4f47d5d7b1","job_id":"J-f12e75a0a2","name":"Assemble: Clutch 6 &amp; Housing","order":21,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"S-f5cd7cfd6b","job_id":"J-f12e75a0a2","name":"Assemble: Input Trans Gear","order":22,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"S-647d82040c","job_id":"J-f12e75a0a2","name":"Assemble: Connect Planetary Gp","order":23,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"S-c0da413e41","job_id":"J-f12e75a0a2","name":"Assemble: Control Valve","order":24,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"S-e696ef645c","job_id":"J-f12e75a0a2","name":"Test Bench &amp; Completed: Set up","order":25,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":420},{"id":"S-7d4f1a859e","job_id":"J-f12e75a0a2","name":"Test Bench &amp; Completed: Test","order":26,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"S-1197155765","job_id":"J-f12e75a0a2","name":"Test Bench &amp; Completed: Release","order":27,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":360},{"id":"S-71f21d6927","job_id":"J-f12e75a0a2","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":28,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300}],"assignees":[{"id":"12cf269a-3fcd-4435-af09-3ee3a1e43923","job_id":"J-f12e75a0a2","technician_id":"T-25b280e7","assigned_at":"2026-08-13T13:13:29.838Z","is_lead":"1"},{"id":"1db87a48-9c13-40ac-af3f-256b6b08df59","job_id":"J-f12e75a0a2","technician_id":"T-1c1b3289","assigned_at":"2026-08-13T13:13:29.838Z","is_lead":"0"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-25b280e7","status":"busy","current_job_id":"J-f12e75a0a2"},{"id":"T-1c1b3289","status":"busy","current_job_id":"J-f12e75a0a2"}]}</t>
+  </si>
+  <si>
+    <t>b444e4ef-d97c-4f52-b935-f96ff8353d3b</t>
+  </si>
+  <si>
+    <t>2026-08-13T13:17:20.334Z</t>
+  </si>
+  <si>
+    <t>pause · Recondition Transmission 24H,M · status paused</t>
+  </si>
+  <si>
+    <t>{"job":{"id":"J-f12e75a0a2","title":"Recondition Transmission 24H,M","unit":"GR407 — 24H","unit_id":"U-555bc792","description":"Job recondition Transmission 24H,M (time frame standar).","status":"paused","technician_id":"T-25b280e7","template_id":"ne-transmission-24h-m","created_at":"2026-08-13T13:13:28.201Z","started_at":"2026-08-13T13:16:36.692Z","completed_at":"","paused_at":"2026-08-13T13:17:20.079Z","total_paused_sec":0,"estimated_minutes":7560},"steps":[{"id":"S-62fed7fe57","job_id":"J-f12e75a0a2","name":"Dismantle: Washing Transmission gp","order":1,"status":"done","started_at":"2026-08-13T13:14:01.944Z","completed_at":"2026-08-13T13:15:17.497Z","duration_sec":150,"std_minutes":300},{"id":"S-bdca34bf9c","job_id":"J-f12e75a0a2","name":"Dismantle: Control Valve","order":2,"status":"in_progress","started_at":"","completed_at":"","duration_sec":42,"std_minutes":300},{"id":"S-198d547e50","job_id":"J-f12e75a0a2","name":"Dismantle: Input Trans Gear","order":3,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-0a2990beeb","job_id":"J-f12e75a0a2","name":"Dismantle: Disconnect Planetary","order":4,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-1b44880146","job_id":"J-f12e75a0a2","name":"Dismantle: Clutch 6 &amp; Housing","order":5,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"S-9f4ccc66c5","job_id":"J-f12e75a0a2","name":"Dismantle: Clutch 5","order":6,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-ebd5f203d4","job_id":"J-f12e75a0a2","name":"Dismantle: Clutch 4","order":7,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-efc0d8adbe","job_id":"J-f12e75a0a2","name":"Dismantle: Clutch 3","order":8,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-74a4e63638","job_id":"J-f12e75a0a2","name":"Dismantle: Clutch 2","order":9,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-4dd2a4b52f","job_id":"J-f12e75a0a2","name":"Dismantle: Clutch 1","order":10,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-1cf61d6445","job_id":"J-f12e75a0a2","name":"Dismantle: Planetary &amp; Shaft In-Out","order":11,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"S-f8a0d4e613","job_id":"J-f12e75a0a2","name":"Dismantle: Output Trans Gear","order":12,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":480},{"id":"S-738f8cdae4","job_id":"J-f12e75a0a2","name":"Dismantle: Part list &amp; Tear Down","order":13,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"S-7e81ce5baf","job_id":"J-f12e75a0a2","name":"Assemble: Output Trans Gear","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"S-aacd67baa7","job_id":"J-f12e75a0a2","name":"Assemble: Planetary &amp; Shaft In-Out","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":420},{"id":"S-2bc1eb8c7a","job_id":"J-f12e75a0a2","name":"Assemble: Clutch 1","order":16,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-6c41013e7e","job_id":"J-f12e75a0a2","name":"Assemble: Clutch 2","order":17,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-5dfc9e18df","job_id":"J-f12e75a0a2","name":"Assemble: Clutch 3","order":18,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-427f687ce7","job_id":"J-f12e75a0a2","name":"Assemble: Clutch 4","order":19,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-a7a64f1028","job_id":"J-f12e75a0a2","name":"Assemble: Clutch 5","order":20,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-4f47d5d7b1","job_id":"J-f12e75a0a2","name":"Assemble: Clutch 6 &amp; Housing","order":21,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"S-f5cd7cfd6b","job_id":"J-f12e75a0a2","name":"Assemble: Input Trans Gear","order":22,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"S-647d82040c","job_id":"J-f12e75a0a2","name":"Assemble: Connect Planetary Gp","order":23,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"S-c0da413e41","job_id":"J-f12e75a0a2","name":"Assemble: Control Valve","order":24,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"S-e696ef645c","job_id":"J-f12e75a0a2","name":"Test Bench &amp; Completed: Set up","order":25,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":420},{"id":"S-7d4f1a859e","job_id":"J-f12e75a0a2","name":"Test Bench &amp; Completed: Test","order":26,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"S-1197155765","job_id":"J-f12e75a0a2","name":"Test Bench &amp; Completed: Release","order":27,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":360},{"id":"S-71f21d6927","job_id":"J-f12e75a0a2","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":28,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300}],"assignees":[{"id":"12cf269a-3fcd-4435-af09-3ee3a1e43923","job_id":"J-f12e75a0a2","technician_id":"T-25b280e7","assigned_at":"2026-08-13T13:13:29.838Z","is_lead":"1"},{"id":"1db87a48-9c13-40ac-af3f-256b6b08df59","job_id":"J-f12e75a0a2","technician_id":"T-1c1b3289","assigned_at":"2026-08-13T13:13:29.838Z","is_lead":"0"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-25b280e7","status":"busy","current_job_id":"J-f12e75a0a2"},{"id":"T-1c1b3289","status":"busy","current_job_id":"J-f12e75a0a2"}]}</t>
+  </si>
+  <si>
+    <t>fca6ec41-a5e1-4a1d-b063-e0974275b4fe</t>
+  </si>
+  <si>
+    <t>2026-08-13T13:21:35.032Z</t>
+  </si>
+  <si>
+    <t>{"job":{"id":"J02-dc56","title":"Recondition Transmission 16H,G","unit":"E448 — D10T","unit_id":"a5c2144b-1b29-40f7-9b5c-cfbbc03c3387","description":"Job recondition Transmission 16H,G (time frame standar).","status":"paused","technician_id":"T-37cadb58","template_id":"ne-transmission-16h-g","created_at":"2026-08-09T14:29:20.672Z","started_at":"2026-08-09T15:02:48.075Z","completed_at":"","paused_at":"2026-08-13T13:19:55.231Z","total_paused_sec":94,"estimated_minutes":5340},"steps":[{"id":"91804ed8-5ad4-4ffd-aaad-beba64eb9cb2","job_id":"J02-dc56","name":"Dismantle: Washing Transmission gp","order":1,"status":"done","started_at":"2026-08-09T15:02:48.075Z","completed_at":"2026-08-09T15:20:47.571Z","duration_sec":1079,"std_minutes":240},{"id":"a127f857-f092-4b21-b197-3e3c8a02d549","job_id":"J02-dc56","name":"Dismantle: Control Valve 2EA","order":2,"status":"done","started_at":"2026-08-10T01:30:25.210Z","completed_at":"2026-08-10T01:30:32.748Z","duration_sec":36495,"std_minutes":300},{"id":"3bc8becf-2b5e-4391-8c9f-619d63d7281c","job_id":"J02-dc56","name":"Dismantle: Pump, Lines, &amp; Screen","order":3,"status":"done","started_at":"2026-08-10T01:30:32.748Z","completed_at":"2026-08-10T08:27:37.616Z","duration_sec":25024,"std_minutes":240},{"id":"bacf6ce8-8a97-4831-9f38-3010f4d64a9a","job_id":"J02-dc56","name":"Dismantle: Planetary GP","order":4,"status":"done","started_at":"2026-08-10T08:27:37.616Z","completed_at":"2026-08-11T05:36:57.526Z","duration_sec":76159,"std_minutes":900},{"id":"74bc5c28-b84c-4cfa-b429-25198c968f30","job_id":"J02-dc56","name":"Dismantle: Directional &amp; Idler gear","order":5,"status":"done","started_at":"2026-08-11T05:36:57.526Z","completed_at":"2026-08-11T14:50:26.762Z","duration_sec":33209,"std_minutes":300},{"id":"c3ce574f-16e3-4ce2-815e-10a842f608de","job_id":"J02-dc56","name":"Dismantle: Clean up Housing 2ea","order":6,"status":"done","started_at":"2026-08-11T14:50:26.763Z","completed_at":"2026-08-11T15:28:01.298Z","duration_sec":2254,"std_minutes":120},{"id":"b57a5afd-0b62-47a8-a149-df57cdbec92f","job_id":"J02-dc56","name":"Dismantle: Part list &amp; Tear Down","order":7,"status":"done","started_at":"2026-08-11T15:28:01.298Z","completed_at":"2026-08-12T00:05:46.117Z","duration_sec":31064,"std_minutes":240},{"id":"ef67991d-4f1b-4929-b4b9-3bd70d1c1a8b","job_id":"J02-dc56","name":"Assemble: Directional &amp; Idler gear","order":8,"status":"done","started_at":"2026-08-12T00:05:46.117Z","completed_at":"2026-08-12T03:47:41.223Z","duration_sec":13315,"std_minutes":600},{"id":"19689610-ed31-4c36-959c-6233ef31d9cc","job_id":"J02-dc56","name":"Assemble: Planetary GP","order":9,"status":"done","started_at":"2026-08-12T03:47:41.223Z","completed_at":"2026-08-12T09:25:37.962Z","duration_sec":20276,"std_minutes":600},{"id":"572f712a-0376-495f-a98f-9ee71ead12b3","job_id":"J02-dc56","name":"Assemble: CV 2EA","order":10,"status":"done","started_at":"2026-08-12T09:25:37.962Z","completed_at":"2026-08-13T03:13:58.520Z","duration_sec":64100,"std_minutes":300},{"id":"033a6b1b-8daf-46cc-a1e1-292ad2451d5f","job_id":"J02-dc56","name":"Assemble: Pump, Lines, &amp; Screen","order":11,"status":"done","started_at":"2026-08-13T11:13:08.442Z","completed_at":"2026-08-13T12:00:54.248Z","duration_sec":31601,"std_minutes":300},{"id":"f52cc000-4714-474d-a6c4-a3f41408fbb7","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Set up","order":12,"status":"done","started_at":"2026-08-13T12:00:54.248Z","completed_at":"2026-08-13T12:00:54.894Z","duration_sec":0,"std_minutes":300},{"id":"a9b889d6-b2f7-4421-a27a-fcd6a2fde9f9","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Test","order":13,"status":"in_progress","started_at":"","completed_at":"","duration_sec":4740,"std_minutes":300},{"id":"3edd89d2-41a4-4856-976b-cbc716dc3788","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Release","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"4d87b720-179e-4dbd-bf95-3d44c356f29e","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300}],"assignees":[{"id":"be4e949d-d820-4b28-b15a-054abe52834e","job_id":"J02-dc56","technician_id":"T-37cadb58","assigned_at":"2026-08-13T12:10:34.946Z","is_lead":"1"},{"id":"f54a99f1-4255-448e-98a9-4621ace561ec","job_id":"J02-dc56","technician_id":"T-e4a06545","assigned_at":"2026-08-13T12:10:34.946Z","is_lead":"0"},{"id":"9641f9a5-abbe-471b-bbec-4a731f535ee5","job_id":"J02-dc56","technician_id":"T-d32c7e65","assigned_at":"2026-08-13T12:10:34.946Z","is_lead":"0"},{"id":"9e67f933-012e-4980-a3f0-2c40b4043bb6","job_id":"J02-dc56","technician_id":"T-d6375327","assigned_at":"2026-08-13T12:10:34.946Z","is_lead":"0"},{"id":"545377eb-7418-420b-8d2a-a86555fa4b6e","job_id":"J02-dc56","technician_id":"T-3d0a3937","assigned_at":"2026-08-13T12:10:34.946Z","is_lead":"0"},{"id":"c422779f-8029-4bff-b90e-348b11aa6ea3","job_id":"J02-dc56","technician_id":"T-103b0d90","assigned_at":"2026-08-13T12:10:34.946Z","is_lead":"0"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-37cadb58","status":"busy","current_job_id":"J02-dc56"},{"id":"T-e4a06545","status":"busy","current_job_id":"J02-dc56"},{"id":"T-d32c7e65","status":"busy","current_job_id":"J02-dc56"},{"id":"T-d6375327","status":"busy","current_job_id":"J02-dc56"},{"id":"T-3d0a3937","status":"busy","current_job_id":"J02-dc56"},{"id":"T-103b0d90","status":"busy","current_job_id":"J02-dc56"}]}</t>
+  </si>
+  <si>
+    <t>a3d74b92-7caa-49bb-95d9-29bb01199c38</t>
+  </si>
+  <si>
+    <t>2026-08-13T13:24:36.355Z</t>
+  </si>
+  <si>
+    <t>{"job":{"id":"J02-dc56","title":"Recondition Transmission 16H,G","unit":"E448 — D10T","unit_id":"a5c2144b-1b29-40f7-9b5c-cfbbc03c3387","description":"Job recondition Transmission 16H,G (time frame standar).","status":"in_progress","technician_id":"T-37cadb58","template_id":"ne-transmission-16h-g","created_at":"2026-08-09T14:29:20.672Z","started_at":"2026-08-09T15:02:48.075Z","completed_at":"","paused_at":"","total_paused_sec":374,"estimated_minutes":5340},"steps":[{"id":"91804ed8-5ad4-4ffd-aaad-beba64eb9cb2","job_id":"J02-dc56","name":"Dismantle: Washing Transmission gp","order":1,"status":"done","started_at":"2026-08-09T15:02:48.075Z","completed_at":"2026-08-09T15:20:47.571Z","duration_sec":1079,"std_minutes":240},{"id":"a127f857-f092-4b21-b197-3e3c8a02d549","job_id":"J02-dc56","name":"Dismantle: Control Valve 2EA","order":2,"status":"done","started_at":"2026-08-10T01:30:25.210Z","completed_at":"2026-08-10T01:30:32.748Z","duration_sec":36495,"std_minutes":300},{"id":"3bc8becf-2b5e-4391-8c9f-619d63d7281c","job_id":"J02-dc56","name":"Dismantle: Pump, Lines, &amp; Screen","order":3,"status":"done","started_at":"2026-08-10T01:30:32.748Z","completed_at":"2026-08-10T08:27:37.616Z","duration_sec":25024,"std_minutes":240},{"id":"bacf6ce8-8a97-4831-9f38-3010f4d64a9a","job_id":"J02-dc56","name":"Dismantle: Planetary GP","order":4,"status":"done","started_at":"2026-08-10T08:27:37.616Z","completed_at":"2026-08-11T05:36:57.526Z","duration_sec":76159,"std_minutes":900},{"id":"74bc5c28-b84c-4cfa-b429-25198c968f30","job_id":"J02-dc56","name":"Dismantle: Directional &amp; Idler gear","order":5,"status":"done","started_at":"2026-08-11T05:36:57.526Z","completed_at":"2026-08-11T14:50:26.762Z","duration_sec":33209,"std_minutes":300},{"id":"c3ce574f-16e3-4ce2-815e-10a842f608de","job_id":"J02-dc56","name":"Dismantle: Clean up Housing 2ea","order":6,"status":"done","started_at":"2026-08-11T14:50:26.763Z","completed_at":"2026-08-11T15:28:01.298Z","duration_sec":2254,"std_minutes":120},{"id":"b57a5afd-0b62-47a8-a149-df57cdbec92f","job_id":"J02-dc56","name":"Dismantle: Part list &amp; Tear Down","order":7,"status":"done","started_at":"2026-08-11T15:28:01.298Z","completed_at":"2026-08-12T00:05:46.117Z","duration_sec":31064,"std_minutes":240},{"id":"ef67991d-4f1b-4929-b4b9-3bd70d1c1a8b","job_id":"J02-dc56","name":"Assemble: Directional &amp; Idler gear","order":8,"status":"done","started_at":"2026-08-12T00:05:46.117Z","completed_at":"2026-08-12T03:47:41.223Z","duration_sec":13315,"std_minutes":600},{"id":"19689610-ed31-4c36-959c-6233ef31d9cc","job_id":"J02-dc56","name":"Assemble: Planetary GP","order":9,"status":"done","started_at":"2026-08-12T03:47:41.223Z","completed_at":"2026-08-12T09:25:37.962Z","duration_sec":20276,"std_minutes":600},{"id":"572f712a-0376-495f-a98f-9ee71ead12b3","job_id":"J02-dc56","name":"Assemble: CV 2EA","order":10,"status":"done","started_at":"2026-08-12T09:25:37.962Z","completed_at":"2026-08-13T03:13:58.520Z","duration_sec":64100,"std_minutes":300},{"id":"033a6b1b-8daf-46cc-a1e1-292ad2451d5f","job_id":"J02-dc56","name":"Assemble: Pump, Lines, &amp; Screen","order":11,"status":"done","started_at":"2026-08-13T11:13:08.442Z","completed_at":"2026-08-13T12:00:54.248Z","duration_sec":31601,"std_minutes":300},{"id":"f52cc000-4714-474d-a6c4-a3f41408fbb7","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Set up","order":12,"status":"done","started_at":"2026-08-13T12:00:54.248Z","completed_at":"2026-08-13T12:00:54.894Z","duration_sec":0,"std_minutes":300},{"id":"a9b889d6-b2f7-4421-a27a-fcd6a2fde9f9","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Test","order":13,"status":"in_progress","started_at":"2026-08-13T13:24:36.082Z","completed_at":"","duration_sec":4740,"std_minutes":300},{"id":"3edd89d2-41a4-4856-976b-cbc716dc3788","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Release","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"4d87b720-179e-4dbd-bf95-3d44c356f29e","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300}],"assignees":[{"id":"be4e949d-d820-4b28-b15a-054abe52834e","job_id":"J02-dc56","technician_id":"T-37cadb58","assigned_at":"2026-08-13T12:10:34.946Z","is_lead":"1"},{"id":"f54a99f1-4255-448e-98a9-4621ace561ec","job_id":"J02-dc56","technician_id":"T-e4a06545","assigned_at":"2026-08-13T12:10:34.946Z","is_lead":"0"},{"id":"9641f9a5-abbe-471b-bbec-4a731f535ee5","job_id":"J02-dc56","technician_id":"T-d32c7e65","assigned_at":"2026-08-13T12:10:34.946Z","is_lead":"0"},{"id":"9e67f933-012e-4980-a3f0-2c40b4043bb6","job_id":"J02-dc56","technician_id":"T-d6375327","assigned_at":"2026-08-13T12:10:34.946Z","is_lead":"0"},{"id":"545377eb-7418-420b-8d2a-a86555fa4b6e","job_id":"J02-dc56","technician_id":"T-3d0a3937","assigned_at":"2026-08-13T12:10:34.946Z","is_lead":"0"},{"id":"c422779f-8029-4bff-b90e-348b11aa6ea3","job_id":"J02-dc56","technician_id":"T-103b0d90","assigned_at":"2026-08-13T12:10:34.946Z","is_lead":"0"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-37cadb58","status":"busy","current_job_id":"J02-dc56"},{"id":"T-e4a06545","status":"busy","current_job_id":"J02-dc56"},{"id":"T-d32c7e65","status":"busy","current_job_id":"J02-dc56"},{"id":"T-d6375327","status":"busy","current_job_id":"J02-dc56"},{"id":"T-3d0a3937","status":"busy","current_job_id":"J02-dc56"},{"id":"T-103b0d90","status":"busy","current_job_id":"J02-dc56"}]}</t>
+  </si>
+  <si>
+    <t>3d717349-d7ab-4181-8471-f0ec3b420688</t>
+  </si>
+  <si>
+    <t>2026-08-13T13:24:37.147Z</t>
+  </si>
+  <si>
+    <t>{"job":{"id":"J02-dc56","title":"Recondition Transmission 16H,G","unit":"E448 — D10T","unit_id":"a5c2144b-1b29-40f7-9b5c-cfbbc03c3387","description":"Job recondition Transmission 16H,G (time frame standar).","status":"paused","technician_id":"T-37cadb58","template_id":"ne-transmission-16h-g","created_at":"2026-08-09T14:29:20.672Z","started_at":"2026-08-09T15:02:48.075Z","completed_at":"","paused_at":"2026-08-13T13:19:55.231Z","total_paused_sec":374,"estimated_minutes":5340},"steps":[{"id":"91804ed8-5ad4-4ffd-aaad-beba64eb9cb2","job_id":"J02-dc56","name":"Dismantle: Washing Transmission gp","order":1,"status":"done","started_at":"2026-08-09T15:02:48.075Z","completed_at":"2026-08-09T15:20:47.571Z","duration_sec":1079,"std_minutes":240},{"id":"a127f857-f092-4b21-b197-3e3c8a02d549","job_id":"J02-dc56","name":"Dismantle: Control Valve 2EA","order":2,"status":"done","started_at":"2026-08-10T01:30:25.210Z","completed_at":"2026-08-10T01:30:32.748Z","duration_sec":36495,"std_minutes":300},{"id":"3bc8becf-2b5e-4391-8c9f-619d63d7281c","job_id":"J02-dc56","name":"Dismantle: Pump, Lines, &amp; Screen","order":3,"status":"done","started_at":"2026-08-10T01:30:32.748Z","completed_at":"2026-08-10T08:27:37.616Z","duration_sec":25024,"std_minutes":240},{"id":"bacf6ce8-8a97-4831-9f38-3010f4d64a9a","job_id":"J02-dc56","name":"Dismantle: Planetary GP","order":4,"status":"done","started_at":"2026-08-10T08:27:37.616Z","completed_at":"2026-08-11T05:36:57.526Z","duration_sec":76159,"std_minutes":900},{"id":"74bc5c28-b84c-4cfa-b429-25198c968f30","job_id":"J02-dc56","name":"Dismantle: Directional &amp; Idler gear","order":5,"status":"done","started_at":"2026-08-11T05:36:57.526Z","completed_at":"2026-08-11T14:50:26.762Z","duration_sec":33209,"std_minutes":300},{"id":"c3ce574f-16e3-4ce2-815e-10a842f608de","job_id":"J02-dc56","name":"Dismantle: Clean up Housing 2ea","order":6,"status":"done","started_at":"2026-08-11T14:50:26.763Z","completed_at":"2026-08-11T15:28:01.298Z","duration_sec":2254,"std_minutes":120},{"id":"b57a5afd-0b62-47a8-a149-df57cdbec92f","job_id":"J02-dc56","name":"Dismantle: Part list &amp; Tear Down","order":7,"status":"done","started_at":"2026-08-11T15:28:01.298Z","completed_at":"2026-08-12T00:05:46.117Z","duration_sec":31064,"std_minutes":240},{"id":"ef67991d-4f1b-4929-b4b9-3bd70d1c1a8b","job_id":"J02-dc56","name":"Assemble: Directional &amp; Idler gear","order":8,"status":"done","started_at":"2026-08-12T00:05:46.117Z","completed_at":"2026-08-12T03:47:41.223Z","duration_sec":13315,"std_minutes":600},{"id":"19689610-ed31-4c36-959c-6233ef31d9cc","job_id":"J02-dc56","name":"Assemble: Planetary GP","order":9,"status":"done","started_at":"2026-08-12T03:47:41.223Z","completed_at":"2026-08-12T09:25:37.962Z","duration_sec":20276,"std_minutes":600},{"id":"572f712a-0376-495f-a98f-9ee71ead12b3","job_id":"J02-dc56","name":"Assemble: CV 2EA","order":10,"status":"done","started_at":"2026-08-12T09:25:37.962Z","completed_at":"2026-08-13T03:13:58.520Z","duration_sec":64100,"std_minutes":300},{"id":"033a6b1b-8daf-46cc-a1e1-292ad2451d5f","job_id":"J02-dc56","name":"Assemble: Pump, Lines, &amp; Screen","order":11,"status":"done","started_at":"2026-08-13T11:13:08.442Z","completed_at":"2026-08-13T12:00:54.248Z","duration_sec":31601,"std_minutes":300},{"id":"f52cc000-4714-474d-a6c4-a3f41408fbb7","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Set up","order":12,"status":"done","started_at":"2026-08-13T12:00:54.248Z","completed_at":"2026-08-13T12:00:54.894Z","duration_sec":0,"std_minutes":300},{"id":"a9b889d6-b2f7-4421-a27a-fcd6a2fde9f9","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Test","order":13,"status":"in_progress","started_at":"","completed_at":"","duration_sec":4740,"std_minutes":300},{"id":"3edd89d2-41a4-4856-976b-cbc716dc3788","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Release","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"4d87b720-179e-4dbd-bf95-3d44c356f29e","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300}],"assignees":[{"id":"be4e949d-d820-4b28-b15a-054abe52834e","job_id":"J02-dc56","technician_id":"T-37cadb58","assigned_at":"2026-08-13T12:10:34.946Z","is_lead":"1"},{"id":"f54a99f1-4255-448e-98a9-4621ace561ec","job_id":"J02-dc56","technician_id":"T-e4a06545","assigned_at":"2026-08-13T12:10:34.946Z","is_lead":"0"},{"id":"9641f9a5-abbe-471b-bbec-4a731f535ee5","job_id":"J02-dc56","technician_id":"T-d32c7e65","assigned_at":"2026-08-13T12:10:34.946Z","is_lead":"0"},{"id":"9e67f933-012e-4980-a3f0-2c40b4043bb6","job_id":"J02-dc56","technician_id":"T-d6375327","assigned_at":"2026-08-13T12:10:34.946Z","is_lead":"0"},{"id":"545377eb-7418-420b-8d2a-a86555fa4b6e","job_id":"J02-dc56","technician_id":"T-3d0a3937","assigned_at":"2026-08-13T12:10:34.946Z","is_lead":"0"},{"id":"c422779f-8029-4bff-b90e-348b11aa6ea3","job_id":"J02-dc56","technician_id":"T-103b0d90","assigned_at":"2026-08-13T12:10:34.946Z","is_lead":"0"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-37cadb58","status":"busy","current_job_id":"J02-dc56"},{"id":"T-e4a06545","status":"busy","current_job_id":"J02-dc56"},{"id":"T-d32c7e65","status":"busy","current_job_id":"J02-dc56"},{"id":"T-d6375327","status":"busy","current_job_id":"J02-dc56"},{"id":"T-3d0a3937","status":"busy","current_job_id":"J02-dc56"},{"id":"T-103b0d90","status":"busy","current_job_id":"J02-dc56"}]}</t>
+  </si>
+  <si>
+    <t>d44ff41c-f0c8-4be3-8960-3fc3e0b3b87a</t>
+  </si>
+  <si>
+    <t>2026-08-13T13:24:37.637Z</t>
+  </si>
+  <si>
+    <t>{"job":{"id":"J02-dc56","title":"Recondition Transmission 16H,G","unit":"E448 — D10T","unit_id":"a5c2144b-1b29-40f7-9b5c-cfbbc03c3387","description":"Job recondition Transmission 16H,G (time frame standar).","status":"in_progress","technician_id":"T-37cadb58","template_id":"ne-transmission-16h-g","created_at":"2026-08-09T14:29:20.672Z","started_at":"2026-08-09T15:02:48.075Z","completed_at":"","paused_at":"","total_paused_sec":103,"estimated_minutes":5340},"steps":[{"id":"91804ed8-5ad4-4ffd-aaad-beba64eb9cb2","job_id":"J02-dc56","name":"Dismantle: Washing Transmission gp","order":1,"status":"done","started_at":"2026-08-09T15:02:48.075Z","completed_at":"2026-08-09T15:20:47.571Z","duration_sec":1079,"std_minutes":240},{"id":"a127f857-f092-4b21-b197-3e3c8a02d549","job_id":"J02-dc56","name":"Dismantle: Control Valve 2EA","order":2,"status":"done","started_at":"2026-08-10T01:30:25.210Z","completed_at":"2026-08-10T01:30:32.748Z","duration_sec":36495,"std_minutes":300},{"id":"3bc8becf-2b5e-4391-8c9f-619d63d7281c","job_id":"J02-dc56","name":"Dismantle: Pump, Lines, &amp; Screen","order":3,"status":"done","started_at":"2026-08-10T01:30:32.748Z","completed_at":"2026-08-10T08:27:37.616Z","duration_sec":25024,"std_minutes":240},{"id":"bacf6ce8-8a97-4831-9f38-3010f4d64a9a","job_id":"J02-dc56","name":"Dismantle: Planetary GP","order":4,"status":"done","started_at":"2026-08-10T08:27:37.616Z","completed_at":"2026-08-11T05:36:57.526Z","duration_sec":76159,"std_minutes":900},{"id":"74bc5c28-b84c-4cfa-b429-25198c968f30","job_id":"J02-dc56","name":"Dismantle: Directional &amp; Idler gear","order":5,"status":"done","started_at":"2026-08-11T05:36:57.526Z","completed_at":"2026-08-11T14:50:26.762Z","duration_sec":33209,"std_minutes":300},{"id":"c3ce574f-16e3-4ce2-815e-10a842f608de","job_id":"J02-dc56","name":"Dismantle: Clean up Housing 2ea","order":6,"status":"done","started_at":"2026-08-11T14:50:26.763Z","completed_at":"2026-08-11T15:28:01.298Z","duration_sec":2254,"std_minutes":120},{"id":"b57a5afd-0b62-47a8-a149-df57cdbec92f","job_id":"J02-dc56","name":"Dismantle: Part list &amp; Tear Down","order":7,"status":"done","started_at":"2026-08-11T15:28:01.298Z","completed_at":"2026-08-12T00:05:46.117Z","duration_sec":31064,"std_minutes":240},{"id":"ef67991d-4f1b-4929-b4b9-3bd70d1c1a8b","job_id":"J02-dc56","name":"Assemble: Directional &amp; Idler gear","order":8,"status":"done","started_at":"2026-08-12T00:05:46.117Z","completed_at":"2026-08-12T03:47:41.223Z","duration_sec":13315,"std_minutes":600},{"id":"19689610-ed31-4c36-959c-6233ef31d9cc","job_id":"J02-dc56","name":"Assemble: Planetary GP","order":9,"status":"done","started_at":"2026-08-12T03:47:41.223Z","completed_at":"2026-08-12T09:25:37.962Z","duration_sec":20276,"std_minutes":600},{"id":"572f712a-0376-495f-a98f-9ee71ead12b3","job_id":"J02-dc56","name":"Assemble: CV 2EA","order":10,"status":"done","started_at":"2026-08-12T09:25:37.962Z","completed_at":"2026-08-13T03:13:58.520Z","duration_sec":64100,"std_minutes":300},{"id":"033a6b1b-8daf-46cc-a1e1-292ad2451d5f","job_id":"J02-dc56","name":"Assemble: Pump, Lines, &amp; Screen","order":11,"status":"done","started_at":"2026-08-13T11:13:08.442Z","completed_at":"2026-08-13T12:00:54.248Z","duration_sec":31601,"std_minutes":300},{"id":"f52cc000-4714-474d-a6c4-a3f41408fbb7","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Set up","order":12,"status":"done","started_at":"2026-08-13T12:00:54.248Z","completed_at":"2026-08-13T12:00:54.894Z","duration_sec":0,"std_minutes":300},{"id":"a9b889d6-b2f7-4421-a27a-fcd6a2fde9f9","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Test","order":13,"status":"in_progress","started_at":"2026-08-13T13:20:04.780Z","completed_at":"","duration_sec":4740,"std_minutes":300},{"id":"3edd89d2-41a4-4856-976b-cbc716dc3788","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Release","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"4d87b720-179e-4dbd-bf95-3d44c356f29e","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300}],"assignees":[{"id":"be4e949d-d820-4b28-b15a-054abe52834e","job_id":"J02-dc56","technician_id":"T-37cadb58","assigned_at":"2026-08-13T12:10:34.946Z","is_lead":"1"},{"id":"f54a99f1-4255-448e-98a9-4621ace561ec","job_id":"J02-dc56","technician_id":"T-e4a06545","assigned_at":"2026-08-13T12:10:34.946Z","is_lead":"0"},{"id":"9641f9a5-abbe-471b-bbec-4a731f535ee5","job_id":"J02-dc56","technician_id":"T-d32c7e65","assigned_at":"2026-08-13T12:10:34.946Z","is_lead":"0"},{"id":"9e67f933-012e-4980-a3f0-2c40b4043bb6","job_id":"J02-dc56","technician_id":"T-d6375327","assigned_at":"2026-08-13T12:10:34.946Z","is_lead":"0"},{"id":"545377eb-7418-420b-8d2a-a86555fa4b6e","job_id":"J02-dc56","technician_id":"T-3d0a3937","assigned_at":"2026-08-13T12:10:34.946Z","is_lead":"0"},{"id":"c422779f-8029-4bff-b90e-348b11aa6ea3","job_id":"J02-dc56","technician_id":"T-103b0d90","assigned_at":"2026-08-13T12:10:34.946Z","is_lead":"0"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-37cadb58","status":"busy","current_job_id":"J02-dc56"},{"id":"T-e4a06545","status":"busy","current_job_id":"J02-dc56"},{"id":"T-d32c7e65","status":"busy","current_job_id":"J02-dc56"},{"id":"T-d6375327","status":"busy","current_job_id":"J02-dc56"},{"id":"T-3d0a3937","status":"busy","current_job_id":"J02-dc56"},{"id":"T-103b0d90","status":"busy","current_job_id":"J02-dc56"}]}</t>
+  </si>
+  <si>
+    <t>28027d28-8a87-45f1-b43e-aceb2b53269e</t>
+  </si>
+  <si>
+    <t>2026-08-13T13:26:25.561Z</t>
+  </si>
+  <si>
+    <t>resume · Recondition Transmission 24H,M · status in_progress</t>
+  </si>
+  <si>
+    <t>{"job":{"id":"J-f12e75a0a2","title":"Recondition Transmission 24H,M","unit":"GR407 — 24H","unit_id":"U-555bc792","description":"Job recondition Transmission 24H,M (time frame standar).","status":"in_progress","technician_id":"T-25b280e7","template_id":"ne-transmission-24h-m","created_at":"2026-08-13T13:13:28.201Z","started_at":"2026-08-13T13:16:36.692Z","completed_at":"","paused_at":"","total_paused_sec":483,"estimated_minutes":7560},"steps":[{"id":"S-62fed7fe57","job_id":"J-f12e75a0a2","name":"Dismantle: Washing Transmission gp","order":1,"status":"done","started_at":"2026-08-13T13:14:01.944Z","completed_at":"2026-08-13T13:15:17.497Z","duration_sec":150,"std_minutes":300},{"id":"S-bdca34bf9c","job_id":"J-f12e75a0a2","name":"Dismantle: Control Valve","order":2,"status":"in_progress","started_at":"2026-08-13T13:25:23.974Z","completed_at":"","duration_sec":42,"std_minutes":300},{"id":"S-198d547e50","job_id":"J-f12e75a0a2","name":"Dismantle: Input Trans Gear","order":3,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-0a2990beeb","job_id":"J-f12e75a0a2","name":"Dismantle: Disconnect Planetary","order":4,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-1b44880146","job_id":"J-f12e75a0a2","name":"Dismantle: Clutch 6 &amp; Housing","order":5,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"S-9f4ccc66c5","job_id":"J-f12e75a0a2","name":"Dismantle: Clutch 5","order":6,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-ebd5f203d4","job_id":"J-f12e75a0a2","name":"Dismantle: Clutch 4","order":7,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-efc0d8adbe","job_id":"J-f12e75a0a2","name":"Dismantle: Clutch 3","order":8,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-74a4e63638","job_id":"J-f12e75a0a2","name":"Dismantle: Clutch 2","order":9,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-4dd2a4b52f","job_id":"J-f12e75a0a2","name":"Dismantle: Clutch 1","order":10,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-1cf61d6445","job_id":"J-f12e75a0a2","name":"Dismantle: Planetary &amp; Shaft In-Out","order":11,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"S-f8a0d4e613","job_id":"J-f12e75a0a2","name":"Dismantle: Output Trans Gear","order":12,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":480},{"id":"S-738f8cdae4","job_id":"J-f12e75a0a2","name":"Dismantle: Part list &amp; Tear Down","order":13,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"S-7e81ce5baf","job_id":"J-f12e75a0a2","name":"Assemble: Output Trans Gear","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"S-aacd67baa7","job_id":"J-f12e75a0a2","name":"Assemble: Planetary &amp; Shaft In-Out","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":420},{"id":"S-2bc1eb8c7a","job_id":"J-f12e75a0a2","name":"Assemble: Clutch 1","order":16,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-6c41013e7e","job_id":"J-f12e75a0a2","name":"Assemble: Clutch 2","order":17,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-5dfc9e18df","job_id":"J-f12e75a0a2","name":"Assemble: Clutch 3","order":18,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-427f687ce7","job_id":"J-f12e75a0a2","name":"Assemble: Clutch 4","order":19,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-a7a64f1028","job_id":"J-f12e75a0a2","name":"Assemble: Clutch 5","order":20,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-4f47d5d7b1","job_id":"J-f12e75a0a2","name":"Assemble: Clutch 6 &amp; Housing","order":21,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"S-f5cd7cfd6b","job_id":"J-f12e75a0a2","name":"Assemble: Input Trans Gear","order":22,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"S-647d82040c","job_id":"J-f12e75a0a2","name":"Assemble: Connect Planetary Gp","order":23,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"S-c0da413e41","job_id":"J-f12e75a0a2","name":"Assemble: Control Valve","order":24,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"S-e696ef645c","job_id":"J-f12e75a0a2","name":"Test Bench &amp; Completed: Set up","order":25,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":420},{"id":"S-7d4f1a859e","job_id":"J-f12e75a0a2","name":"Test Bench &amp; Completed: Test","order":26,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"S-1197155765","job_id":"J-f12e75a0a2","name":"Test Bench &amp; Completed: Release","order":27,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":360},{"id":"S-71f21d6927","job_id":"J-f12e75a0a2","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":28,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300}],"assignees":[{"id":"12cf269a-3fcd-4435-af09-3ee3a1e43923","job_id":"J-f12e75a0a2","technician_id":"T-25b280e7","assigned_at":"2026-08-13T13:13:29.838Z","is_lead":"1"},{"id":"1db87a48-9c13-40ac-af3f-256b6b08df59","job_id":"J-f12e75a0a2","technician_id":"T-1c1b3289","assigned_at":"2026-08-13T13:13:29.838Z","is_lead":"0"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-25b280e7","status":"busy","current_job_id":"J-f12e75a0a2"},{"id":"T-1c1b3289","status":"busy","current_job_id":"J-f12e75a0a2"}]}</t>
+  </si>
+  <si>
+    <t>808f7791-4ab3-4f41-9cd0-722da1b1d079</t>
+  </si>
+  <si>
+    <t>2026-08-13T13:26:26.199Z</t>
+  </si>
+  <si>
+    <t>{"job":{"id":"J-f12e75a0a2","title":"Recondition Transmission 24H,M","unit":"GR407 — 24H","unit_id":"U-555bc792","description":"Job recondition Transmission 24H,M (time frame standar).","status":"in_progress","technician_id":"T-25b280e7","template_id":"ne-transmission-24h-m","created_at":"2026-08-13T13:13:28.201Z","started_at":"2026-08-13T13:16:36.692Z","completed_at":"","paused_at":"","total_paused_sec":483,"estimated_minutes":7560},"steps":[{"id":"S-62fed7fe57","job_id":"J-f12e75a0a2","name":"Dismantle: Washing Transmission gp","order":1,"status":"done","started_at":"2026-08-13T13:14:01.944Z","completed_at":"2026-08-13T13:15:17.497Z","duration_sec":150,"std_minutes":300},{"id":"S-bdca34bf9c","job_id":"J-f12e75a0a2","name":"Dismantle: Control Valve","order":2,"status":"done","started_at":"2026-08-13T13:25:23.973Z","completed_at":"2026-08-13T13:25:34.794Z","duration_sec":62,"std_minutes":300},{"id":"S-198d547e50","job_id":"J-f12e75a0a2","name":"Dismantle: Input Trans Gear","order":3,"status":"in_progress","started_at":"2026-08-13T13:25:34.794Z","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-0a2990beeb","job_id":"J-f12e75a0a2","name":"Dismantle: Disconnect Planetary","order":4,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-1b44880146","job_id":"J-f12e75a0a2","name":"Dismantle: Clutch 6 &amp; Housing","order":5,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"S-9f4ccc66c5","job_id":"J-f12e75a0a2","name":"Dismantle: Clutch 5","order":6,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-ebd5f203d4","job_id":"J-f12e75a0a2","name":"Dismantle: Clutch 4","order":7,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-efc0d8adbe","job_id":"J-f12e75a0a2","name":"Dismantle: Clutch 3","order":8,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-74a4e63638","job_id":"J-f12e75a0a2","name":"Dismantle: Clutch 2","order":9,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-4dd2a4b52f","job_id":"J-f12e75a0a2","name":"Dismantle: Clutch 1","order":10,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-1cf61d6445","job_id":"J-f12e75a0a2","name":"Dismantle: Planetary &amp; Shaft In-Out","order":11,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"S-f8a0d4e613","job_id":"J-f12e75a0a2","name":"Dismantle: Output Trans Gear","order":12,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":480},{"id":"S-738f8cdae4","job_id":"J-f12e75a0a2","name":"Dismantle: Part list &amp; Tear Down","order":13,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"S-7e81ce5baf","job_id":"J-f12e75a0a2","name":"Assemble: Output Trans Gear","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"S-aacd67baa7","job_id":"J-f12e75a0a2","name":"Assemble: Planetary &amp; Shaft In-Out","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":420},{"id":"S-2bc1eb8c7a","job_id":"J-f12e75a0a2","name":"Assemble: Clutch 1","order":16,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-6c41013e7e","job_id":"J-f12e75a0a2","name":"Assemble: Clutch 2","order":17,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-5dfc9e18df","job_id":"J-f12e75a0a2","name":"Assemble: Clutch 3","order":18,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-427f687ce7","job_id":"J-f12e75a0a2","name":"Assemble: Clutch 4","order":19,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-a7a64f1028","job_id":"J-f12e75a0a2","name":"Assemble: Clutch 5","order":20,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-4f47d5d7b1","job_id":"J-f12e75a0a2","name":"Assemble: Clutch 6 &amp; Housing","order":21,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"S-f5cd7cfd6b","job_id":"J-f12e75a0a2","name":"Assemble: Input Trans Gear","order":22,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"S-647d82040c","job_id":"J-f12e75a0a2","name":"Assemble: Connect Planetary Gp","order":23,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"S-c0da413e41","job_id":"J-f12e75a0a2","name":"Assemble: Control Valve","order":24,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"S-e696ef645c","job_id":"J-f12e75a0a2","name":"Test Bench &amp; Completed: Set up","order":25,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":420},{"id":"S-7d4f1a859e","job_id":"J-f12e75a0a2","name":"Test Bench &amp; Completed: Test","order":26,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"S-1197155765","job_id":"J-f12e75a0a2","name":"Test Bench &amp; Completed: Release","order":27,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":360},{"id":"S-71f21d6927","job_id":"J-f12e75a0a2","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":28,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300}],"assignees":[{"id":"12cf269a-3fcd-4435-af09-3ee3a1e43923","job_id":"J-f12e75a0a2","technician_id":"T-25b280e7","assigned_at":"2026-08-13T13:13:29.838Z","is_lead":"1"},{"id":"1db87a48-9c13-40ac-af3f-256b6b08df59","job_id":"J-f12e75a0a2","technician_id":"T-1c1b3289","assigned_at":"2026-08-13T13:13:29.838Z","is_lead":"0"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-25b280e7","status":"busy","current_job_id":"J-f12e75a0a2"},{"id":"T-1c1b3289","status":"busy","current_job_id":"J-f12e75a0a2"}]}</t>
+  </si>
+  <si>
+    <t>62b95fc9-fb46-4f3c-85ac-c8eeaef11968</t>
+  </si>
+  <si>
+    <t>2026-08-13T13:26:26.764Z</t>
+  </si>
+  <si>
+    <t>{"job":{"id":"J-f12e75a0a2","title":"Recondition Transmission 24H,M","unit":"GR407 — 24H","unit_id":"U-555bc792","description":"Job recondition Transmission 24H,M (time frame standar).","status":"paused","technician_id":"T-25b280e7","template_id":"ne-transmission-24h-m","created_at":"2026-08-13T13:13:28.201Z","started_at":"2026-08-13T13:16:36.692Z","completed_at":"","paused_at":"2026-08-13T13:25:46.274Z","total_paused_sec":483,"estimated_minutes":7560},"steps":[{"id":"S-62fed7fe57","job_id":"J-f12e75a0a2","name":"Dismantle: Washing Transmission gp","order":1,"status":"done","started_at":"2026-08-13T13:14:01.944Z","completed_at":"2026-08-13T13:15:17.497Z","duration_sec":150,"std_minutes":300},{"id":"S-bdca34bf9c","job_id":"J-f12e75a0a2","name":"Dismantle: Control Valve","order":2,"status":"done","started_at":"2026-08-13T13:25:23.973Z","completed_at":"2026-08-13T13:25:34.794Z","duration_sec":62,"std_minutes":300},{"id":"S-198d547e50","job_id":"J-f12e75a0a2","name":"Dismantle: Input Trans Gear","order":3,"status":"in_progress","started_at":"","completed_at":"","duration_sec":11,"std_minutes":180},{"id":"S-0a2990beeb","job_id":"J-f12e75a0a2","name":"Dismantle: Disconnect Planetary","order":4,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-1b44880146","job_id":"J-f12e75a0a2","name":"Dismantle: Clutch 6 &amp; Housing","order":5,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"S-9f4ccc66c5","job_id":"J-f12e75a0a2","name":"Dismantle: Clutch 5","order":6,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-ebd5f203d4","job_id":"J-f12e75a0a2","name":"Dismantle: Clutch 4","order":7,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-efc0d8adbe","job_id":"J-f12e75a0a2","name":"Dismantle: Clutch 3","order":8,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-74a4e63638","job_id":"J-f12e75a0a2","name":"Dismantle: Clutch 2","order":9,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-4dd2a4b52f","job_id":"J-f12e75a0a2","name":"Dismantle: Clutch 1","order":10,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-1cf61d6445","job_id":"J-f12e75a0a2","name":"Dismantle: Planetary &amp; Shaft In-Out","order":11,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"S-f8a0d4e613","job_id":"J-f12e75a0a2","name":"Dismantle: Output Trans Gear","order":12,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":480},{"id":"S-738f8cdae4","job_id":"J-f12e75a0a2","name":"Dismantle: Part list &amp; Tear Down","order":13,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"S-7e81ce5baf","job_id":"J-f12e75a0a2","name":"Assemble: Output Trans Gear","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"S-aacd67baa7","job_id":"J-f12e75a0a2","name":"Assemble: Planetary &amp; Shaft In-Out","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":420},{"id":"S-2bc1eb8c7a","job_id":"J-f12e75a0a2","name":"Assemble: Clutch 1","order":16,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-6c41013e7e","job_id":"J-f12e75a0a2","name":"Assemble: Clutch 2","order":17,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-5dfc9e18df","job_id":"J-f12e75a0a2","name":"Assemble: Clutch 3","order":18,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-427f687ce7","job_id":"J-f12e75a0a2","name":"Assemble: Clutch 4","order":19,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-a7a64f1028","job_id":"J-f12e75a0a2","name":"Assemble: Clutch 5","order":20,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-4f47d5d7b1","job_id":"J-f12e75a0a2","name":"Assemble: Clutch 6 &amp; Housing","order":21,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"S-f5cd7cfd6b","job_id":"J-f12e75a0a2","name":"Assemble: Input Trans Gear","order":22,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"S-647d82040c","job_id":"J-f12e75a0a2","name":"Assemble: Connect Planetary Gp","order":23,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"S-c0da413e41","job_id":"J-f12e75a0a2","name":"Assemble: Control Valve","order":24,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"S-e696ef645c","job_id":"J-f12e75a0a2","name":"Test Bench &amp; Completed: Set up","order":25,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":420},{"id":"S-7d4f1a859e","job_id":"J-f12e75a0a2","name":"Test Bench &amp; Completed: Test","order":26,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"S-1197155765","job_id":"J-f12e75a0a2","name":"Test Bench &amp; Completed: Release","order":27,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":360},{"id":"S-71f21d6927","job_id":"J-f12e75a0a2","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":28,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300}],"assignees":[{"id":"12cf269a-3fcd-4435-af09-3ee3a1e43923","job_id":"J-f12e75a0a2","technician_id":"T-25b280e7","assigned_at":"2026-08-13T13:13:29.838Z","is_lead":"1"},{"id":"1db87a48-9c13-40ac-af3f-256b6b08df59","job_id":"J-f12e75a0a2","technician_id":"T-1c1b3289","assigned_at":"2026-08-13T13:13:29.838Z","is_lead":"0"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-25b280e7","status":"busy","current_job_id":"J-f12e75a0a2"},{"id":"T-1c1b3289","status":"busy","current_job_id":"J-f12e75a0a2"}]}</t>
+  </si>
+  <si>
+    <t>55109e91-cade-498d-acf3-834f54d8ba98</t>
+  </si>
+  <si>
+    <t>2026-08-13T13:26:27.840Z</t>
+  </si>
+  <si>
+    <t>{"job":{"id":"J-f12e75a0a2","title":"Recondition Transmission 24H,M","unit":"GR407 — 24H","unit_id":"U-555bc792","description":"Job recondition Transmission 24H,M (time frame standar).","status":"in_progress","technician_id":"T-25b280e7","template_id":"ne-transmission-24h-m","created_at":"2026-08-13T13:13:28.201Z","started_at":"2026-08-13T13:16:36.692Z","completed_at":"","paused_at":"","total_paused_sec":487,"estimated_minutes":7560},"steps":[{"id":"S-62fed7fe57","job_id":"J-f12e75a0a2","name":"Dismantle: Washing Transmission gp","order":1,"status":"done","started_at":"2026-08-13T13:14:01.944Z","completed_at":"2026-08-13T13:15:17.497Z","duration_sec":150,"std_minutes":300},{"id":"S-bdca34bf9c","job_id":"J-f12e75a0a2","name":"Dismantle: Control Valve","order":2,"status":"done","started_at":"2026-08-13T13:25:23.973Z","completed_at":"2026-08-13T13:25:34.794Z","duration_sec":62,"std_minutes":300},{"id":"S-198d547e50","job_id":"J-f12e75a0a2","name":"Dismantle: Input Trans Gear","order":3,"status":"in_progress","started_at":"2026-08-13T13:25:51.187Z","completed_at":"","duration_sec":11,"std_minutes":180},{"id":"S-0a2990beeb","job_id":"J-f12e75a0a2","name":"Dismantle: Disconnect Planetary","order":4,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-1b44880146","job_id":"J-f12e75a0a2","name":"Dismantle: Clutch 6 &amp; Housing","order":5,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"S-9f4ccc66c5","job_id":"J-f12e75a0a2","name":"Dismantle: Clutch 5","order":6,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-ebd5f203d4","job_id":"J-f12e75a0a2","name":"Dismantle: Clutch 4","order":7,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-efc0d8adbe","job_id":"J-f12e75a0a2","name":"Dismantle: Clutch 3","order":8,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-74a4e63638","job_id":"J-f12e75a0a2","name":"Dismantle: Clutch 2","order":9,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-4dd2a4b52f","job_id":"J-f12e75a0a2","name":"Dismantle: Clutch 1","order":10,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-1cf61d6445","job_id":"J-f12e75a0a2","name":"Dismantle: Planetary &amp; Shaft In-Out","order":11,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"S-f8a0d4e613","job_id":"J-f12e75a0a2","name":"Dismantle: Output Trans Gear","order":12,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":480},{"id":"S-738f8cdae4","job_id":"J-f12e75a0a2","name":"Dismantle: Part list &amp; Tear Down","order":13,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"S-7e81ce5baf","job_id":"J-f12e75a0a2","name":"Assemble: Output Trans Gear","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"S-aacd67baa7","job_id":"J-f12e75a0a2","name":"Assemble: Planetary &amp; Shaft In-Out","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":420},{"id":"S-2bc1eb8c7a","job_id":"J-f12e75a0a2","name":"Assemble: Clutch 1","order":16,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-6c41013e7e","job_id":"J-f12e75a0a2","name":"Assemble: Clutch 2","order":17,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-5dfc9e18df","job_id":"J-f12e75a0a2","name":"Assemble: Clutch 3","order":18,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-427f687ce7","job_id":"J-f12e75a0a2","name":"Assemble: Clutch 4","order":19,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-a7a64f1028","job_id":"J-f12e75a0a2","name":"Assemble: Clutch 5","order":20,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-4f47d5d7b1","job_id":"J-f12e75a0a2","name":"Assemble: Clutch 6 &amp; Housing","order":21,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"S-f5cd7cfd6b","job_id":"J-f12e75a0a2","name":"Assemble: Input Trans Gear","order":22,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"S-647d82040c","job_id":"J-f12e75a0a2","name":"Assemble: Connect Planetary Gp","order":23,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"S-c0da413e41","job_id":"J-f12e75a0a2","name":"Assemble: Control Valve","order":24,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"S-e696ef645c","job_id":"J-f12e75a0a2","name":"Test Bench &amp; Completed: Set up","order":25,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":420},{"id":"S-7d4f1a859e","job_id":"J-f12e75a0a2","name":"Test Bench &amp; Completed: Test","order":26,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"S-1197155765","job_id":"J-f12e75a0a2","name":"Test Bench &amp; Completed: Release","order":27,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":360},{"id":"S-71f21d6927","job_id":"J-f12e75a0a2","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":28,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300}],"assignees":[{"id":"12cf269a-3fcd-4435-af09-3ee3a1e43923","job_id":"J-f12e75a0a2","technician_id":"T-25b280e7","assigned_at":"2026-08-13T13:13:29.838Z","is_lead":"1"},{"id":"1db87a48-9c13-40ac-af3f-256b6b08df59","job_id":"J-f12e75a0a2","technician_id":"T-1c1b3289","assigned_at":"2026-08-13T13:13:29.838Z","is_lead":"0"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-25b280e7","status":"busy","current_job_id":"J-f12e75a0a2"},{"id":"T-1c1b3289","status":"busy","current_job_id":"J-f12e75a0a2"}]}</t>
+  </si>
+  <si>
+    <t>0f43a175-3535-43d4-a9ef-f8029b6d5321</t>
+  </si>
+  <si>
+    <t>2026-08-13T13:27:19.300Z</t>
+  </si>
+  <si>
+    <t>{"job":{"id":"J-f12e75a0a2","title":"Recondition Transmission 24H,M","unit":"GR407 — 24H","unit_id":"U-555bc792","description":"Job recondition Transmission 24H,M (time frame standar).","status":"in_progress","technician_id":"T-25b280e7","template_id":"ne-transmission-24h-m","created_at":"2026-08-13T13:13:28.201Z","started_at":"2026-08-13T13:16:36.692Z","completed_at":"","paused_at":"","total_paused_sec":487,"estimated_minutes":7560},"steps":[{"id":"S-62fed7fe57","job_id":"J-f12e75a0a2","name":"Dismantle: Washing Transmission gp","order":1,"status":"done","started_at":"2026-08-13T13:14:01.944Z","completed_at":"2026-08-13T13:15:17.497Z","duration_sec":150,"std_minutes":300},{"id":"S-bdca34bf9c","job_id":"J-f12e75a0a2","name":"Dismantle: Control Valve","order":2,"status":"done","started_at":"2026-08-13T13:25:23.973Z","completed_at":"2026-08-13T13:25:34.794Z","duration_sec":62,"std_minutes":300},{"id":"S-198d547e50","job_id":"J-f12e75a0a2","name":"Dismantle: Input Trans Gear","order":3,"status":"done","started_at":"2026-08-13T13:25:51.187Z","completed_at":"2026-08-13T13:26:50.395Z","duration_sec":129,"std_minutes":180},{"id":"S-0a2990beeb","job_id":"J-f12e75a0a2","name":"Dismantle: Disconnect Planetary","order":4,"status":"in_progress","started_at":"2026-08-13T13:26:50.395Z","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-1b44880146","job_id":"J-f12e75a0a2","name":"Dismantle: Clutch 6 &amp; Housing","order":5,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"S-9f4ccc66c5","job_id":"J-f12e75a0a2","name":"Dismantle: Clutch 5","order":6,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-ebd5f203d4","job_id":"J-f12e75a0a2","name":"Dismantle: Clutch 4","order":7,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-efc0d8adbe","job_id":"J-f12e75a0a2","name":"Dismantle: Clutch 3","order":8,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-74a4e63638","job_id":"J-f12e75a0a2","name":"Dismantle: Clutch 2","order":9,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-4dd2a4b52f","job_id":"J-f12e75a0a2","name":"Dismantle: Clutch 1","order":10,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-1cf61d6445","job_id":"J-f12e75a0a2","name":"Dismantle: Planetary &amp; Shaft In-Out","order":11,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"S-f8a0d4e613","job_id":"J-f12e75a0a2","name":"Dismantle: Output Trans Gear","order":12,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":480},{"id":"S-738f8cdae4","job_id":"J-f12e75a0a2","name":"Dismantle: Part list &amp; Tear Down","order":13,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"S-7e81ce5baf","job_id":"J-f12e75a0a2","name":"Assemble: Output Trans Gear","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"S-aacd67baa7","job_id":"J-f12e75a0a2","name":"Assemble: Planetary &amp; Shaft In-Out","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":420},{"id":"S-2bc1eb8c7a","job_id":"J-f12e75a0a2","name":"Assemble: Clutch 1","order":16,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-6c41013e7e","job_id":"J-f12e75a0a2","name":"Assemble: Clutch 2","order":17,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-5dfc9e18df","job_id":"J-f12e75a0a2","name":"Assemble: Clutch 3","order":18,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-427f687ce7","job_id":"J-f12e75a0a2","name":"Assemble: Clutch 4","order":19,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-a7a64f1028","job_id":"J-f12e75a0a2","name":"Assemble: Clutch 5","order":20,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-4f47d5d7b1","job_id":"J-f12e75a0a2","name":"Assemble: Clutch 6 &amp; Housing","order":21,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"S-f5cd7cfd6b","job_id":"J-f12e75a0a2","name":"Assemble: Input Trans Gear","order":22,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"S-647d82040c","job_id":"J-f12e75a0a2","name":"Assemble: Connect Planetary Gp","order":23,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"S-c0da413e41","job_id":"J-f12e75a0a2","name":"Assemble: Control Valve","order":24,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"S-e696ef645c","job_id":"J-f12e75a0a2","name":"Test Bench &amp; Completed: Set up","order":25,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":420},{"id":"S-7d4f1a859e","job_id":"J-f12e75a0a2","name":"Test Bench &amp; Completed: Test","order":26,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"S-1197155765","job_id":"J-f12e75a0a2","name":"Test Bench &amp; Completed: Release","order":27,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":360},{"id":"S-71f21d6927","job_id":"J-f12e75a0a2","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":28,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300}],"assignees":[{"id":"12cf269a-3fcd-4435-af09-3ee3a1e43923","job_id":"J-f12e75a0a2","technician_id":"T-25b280e7","assigned_at":"2026-08-13T13:13:29.838Z","is_lead":"1"},{"id":"1db87a48-9c13-40ac-af3f-256b6b08df59","job_id":"J-f12e75a0a2","technician_id":"T-1c1b3289","assigned_at":"2026-08-13T13:13:29.838Z","is_lead":"0"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-25b280e7","status":"busy","current_job_id":"J-f12e75a0a2"},{"id":"T-1c1b3289","status":"busy","current_job_id":"J-f12e75a0a2"}]}</t>
+  </si>
+  <si>
+    <t>b0d46747-649e-4871-9409-6297ece288fe</t>
+  </si>
+  <si>
+    <t>2026-08-13T13:27:19.915Z</t>
+  </si>
+  <si>
+    <t>{"job":{"id":"J-f12e75a0a2","title":"Recondition Transmission 24H,M","unit":"GR407 — 24H","unit_id":"U-555bc792","description":"Job recondition Transmission 24H,M (time frame standar).","status":"in_progress","technician_id":"T-25b280e7","template_id":"ne-transmission-24h-m","created_at":"2026-08-13T13:13:28.201Z","started_at":"2026-08-13T13:16:36.692Z","completed_at":"","paused_at":"","total_paused_sec":487,"estimated_minutes":7560},"steps":[{"id":"S-62fed7fe57","job_id":"J-f12e75a0a2","name":"Dismantle: Washing Transmission gp","order":1,"status":"done","started_at":"2026-08-13T13:14:01.944Z","completed_at":"2026-08-13T13:15:17.497Z","duration_sec":150,"std_minutes":300},{"id":"S-bdca34bf9c","job_id":"J-f12e75a0a2","name":"Dismantle: Control Valve","order":2,"status":"done","started_at":"2026-08-13T13:25:23.973Z","completed_at":"2026-08-13T13:25:34.794Z","duration_sec":62,"std_minutes":300},{"id":"S-198d547e50","job_id":"J-f12e75a0a2","name":"Dismantle: Input Trans Gear","order":3,"status":"done","started_at":"2026-08-13T13:25:51.187Z","completed_at":"2026-08-13T13:26:50.395Z","duration_sec":129,"std_minutes":180},{"id":"S-0a2990beeb","job_id":"J-f12e75a0a2","name":"Dismantle: Disconnect Planetary","order":4,"status":"done","started_at":"2026-08-13T13:26:50.395Z","completed_at":"2026-08-13T13:26:58.325Z","duration_sec":14,"std_minutes":180},{"id":"S-1b44880146","job_id":"J-f12e75a0a2","name":"Dismantle: Clutch 6 &amp; Housing","order":5,"status":"in_progress","started_at":"2026-08-13T13:26:58.325Z","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"S-9f4ccc66c5","job_id":"J-f12e75a0a2","name":"Dismantle: Clutch 5","order":6,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-ebd5f203d4","job_id":"J-f12e75a0a2","name":"Dismantle: Clutch 4","order":7,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-efc0d8adbe","job_id":"J-f12e75a0a2","name":"Dismantle: Clutch 3","order":8,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-74a4e63638","job_id":"J-f12e75a0a2","name":"Dismantle: Clutch 2","order":9,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-4dd2a4b52f","job_id":"J-f12e75a0a2","name":"Dismantle: Clutch 1","order":10,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-1cf61d6445","job_id":"J-f12e75a0a2","name":"Dismantle: Planetary &amp; Shaft In-Out","order":11,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"S-f8a0d4e613","job_id":"J-f12e75a0a2","name":"Dismantle: Output Trans Gear","order":12,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":480},{"id":"S-738f8cdae4","job_id":"J-f12e75a0a2","name":"Dismantle: Part list &amp; Tear Down","order":13,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"S-7e81ce5baf","job_id":"J-f12e75a0a2","name":"Assemble: Output Trans Gear","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"S-aacd67baa7","job_id":"J-f12e75a0a2","name":"Assemble: Planetary &amp; Shaft In-Out","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":420},{"id":"S-2bc1eb8c7a","job_id":"J-f12e75a0a2","name":"Assemble: Clutch 1","order":16,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-6c41013e7e","job_id":"J-f12e75a0a2","name":"Assemble: Clutch 2","order":17,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-5dfc9e18df","job_id":"J-f12e75a0a2","name":"Assemble: Clutch 3","order":18,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-427f687ce7","job_id":"J-f12e75a0a2","name":"Assemble: Clutch 4","order":19,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-a7a64f1028","job_id":"J-f12e75a0a2","name":"Assemble: Clutch 5","order":20,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-4f47d5d7b1","job_id":"J-f12e75a0a2","name":"Assemble: Clutch 6 &amp; Housing","order":21,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"S-f5cd7cfd6b","job_id":"J-f12e75a0a2","name":"Assemble: Input Trans Gear","order":22,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"S-647d82040c","job_id":"J-f12e75a0a2","name":"Assemble: Connect Planetary Gp","order":23,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"S-c0da413e41","job_id":"J-f12e75a0a2","name":"Assemble: Control Valve","order":24,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"S-e696ef645c","job_id":"J-f12e75a0a2","name":"Test Bench &amp; Completed: Set up","order":25,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":420},{"id":"S-7d4f1a859e","job_id":"J-f12e75a0a2","name":"Test Bench &amp; Completed: Test","order":26,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"S-1197155765","job_id":"J-f12e75a0a2","name":"Test Bench &amp; Completed: Release","order":27,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":360},{"id":"S-71f21d6927","job_id":"J-f12e75a0a2","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":28,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300}],"assignees":[{"id":"12cf269a-3fcd-4435-af09-3ee3a1e43923","job_id":"J-f12e75a0a2","technician_id":"T-25b280e7","assigned_at":"2026-08-13T13:13:29.838Z","is_lead":"1"},{"id":"1db87a48-9c13-40ac-af3f-256b6b08df59","job_id":"J-f12e75a0a2","technician_id":"T-1c1b3289","assigned_at":"2026-08-13T13:13:29.838Z","is_lead":"0"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-25b280e7","status":"busy","current_job_id":"J-f12e75a0a2"},{"id":"T-1c1b3289","status":"busy","current_job_id":"J-f12e75a0a2"}]}</t>
   </si>
 </sst>
 </file>
@@ -1311,7 +1467,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q84"/>
+  <dimension ref="A1:Q99"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -5766,6 +5922,801 @@
         <v>36</v>
       </c>
     </row>
+    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>308</v>
+      </c>
+      <c r="B85" t="s">
+        <v>309</v>
+      </c>
+      <c r="C85" t="s">
+        <v>19</v>
+      </c>
+      <c r="D85" t="s">
+        <v>20</v>
+      </c>
+      <c r="E85" t="s">
+        <v>21</v>
+      </c>
+      <c r="F85" t="s">
+        <v>54</v>
+      </c>
+      <c r="G85" t="s">
+        <v>23</v>
+      </c>
+      <c r="H85" t="s">
+        <v>310</v>
+      </c>
+      <c r="I85" t="s">
+        <v>310</v>
+      </c>
+      <c r="J85" t="s">
+        <v>311</v>
+      </c>
+      <c r="K85" t="s">
+        <v>36</v>
+      </c>
+      <c r="L85" t="s">
+        <v>312</v>
+      </c>
+      <c r="M85" t="s">
+        <v>35</v>
+      </c>
+      <c r="N85" t="s">
+        <v>36</v>
+      </c>
+      <c r="O85" t="s">
+        <v>36</v>
+      </c>
+      <c r="P85" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q85" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>313</v>
+      </c>
+      <c r="B86" t="s">
+        <v>314</v>
+      </c>
+      <c r="C86" t="s">
+        <v>19</v>
+      </c>
+      <c r="D86" t="s">
+        <v>20</v>
+      </c>
+      <c r="E86" t="s">
+        <v>21</v>
+      </c>
+      <c r="F86" t="s">
+        <v>73</v>
+      </c>
+      <c r="G86" t="s">
+        <v>23</v>
+      </c>
+      <c r="H86" t="s">
+        <v>310</v>
+      </c>
+      <c r="I86" t="s">
+        <v>310</v>
+      </c>
+      <c r="J86" t="s">
+        <v>315</v>
+      </c>
+      <c r="K86" t="s">
+        <v>312</v>
+      </c>
+      <c r="L86" t="s">
+        <v>316</v>
+      </c>
+      <c r="M86" t="s">
+        <v>35</v>
+      </c>
+      <c r="N86" t="s">
+        <v>36</v>
+      </c>
+      <c r="O86" t="s">
+        <v>36</v>
+      </c>
+      <c r="P86" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q86" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>317</v>
+      </c>
+      <c r="B87" t="s">
+        <v>318</v>
+      </c>
+      <c r="C87" t="s">
+        <v>19</v>
+      </c>
+      <c r="D87" t="s">
+        <v>20</v>
+      </c>
+      <c r="E87" t="s">
+        <v>21</v>
+      </c>
+      <c r="F87" t="s">
+        <v>78</v>
+      </c>
+      <c r="G87" t="s">
+        <v>23</v>
+      </c>
+      <c r="H87" t="s">
+        <v>310</v>
+      </c>
+      <c r="I87" t="s">
+        <v>310</v>
+      </c>
+      <c r="J87" t="s">
+        <v>319</v>
+      </c>
+      <c r="K87" t="s">
+        <v>316</v>
+      </c>
+      <c r="L87" t="s">
+        <v>320</v>
+      </c>
+      <c r="M87" t="s">
+        <v>35</v>
+      </c>
+      <c r="N87" t="s">
+        <v>36</v>
+      </c>
+      <c r="O87" t="s">
+        <v>36</v>
+      </c>
+      <c r="P87" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q87" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>321</v>
+      </c>
+      <c r="B88" t="s">
+        <v>322</v>
+      </c>
+      <c r="C88" t="s">
+        <v>19</v>
+      </c>
+      <c r="D88" t="s">
+        <v>20</v>
+      </c>
+      <c r="E88" t="s">
+        <v>21</v>
+      </c>
+      <c r="F88" t="s">
+        <v>32</v>
+      </c>
+      <c r="G88" t="s">
+        <v>23</v>
+      </c>
+      <c r="H88" t="s">
+        <v>310</v>
+      </c>
+      <c r="I88" t="s">
+        <v>310</v>
+      </c>
+      <c r="J88" t="s">
+        <v>323</v>
+      </c>
+      <c r="K88" t="s">
+        <v>320</v>
+      </c>
+      <c r="L88" t="s">
+        <v>324</v>
+      </c>
+      <c r="M88" t="s">
+        <v>35</v>
+      </c>
+      <c r="N88" t="s">
+        <v>36</v>
+      </c>
+      <c r="O88" t="s">
+        <v>36</v>
+      </c>
+      <c r="P88" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q88" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>325</v>
+      </c>
+      <c r="B89" t="s">
+        <v>326</v>
+      </c>
+      <c r="C89" t="s">
+        <v>19</v>
+      </c>
+      <c r="D89" t="s">
+        <v>20</v>
+      </c>
+      <c r="E89" t="s">
+        <v>21</v>
+      </c>
+      <c r="F89" t="s">
+        <v>41</v>
+      </c>
+      <c r="G89" t="s">
+        <v>23</v>
+      </c>
+      <c r="H89" t="s">
+        <v>310</v>
+      </c>
+      <c r="I89" t="s">
+        <v>310</v>
+      </c>
+      <c r="J89" t="s">
+        <v>327</v>
+      </c>
+      <c r="K89" t="s">
+        <v>324</v>
+      </c>
+      <c r="L89" t="s">
+        <v>328</v>
+      </c>
+      <c r="M89" t="s">
+        <v>35</v>
+      </c>
+      <c r="N89" t="s">
+        <v>36</v>
+      </c>
+      <c r="O89" t="s">
+        <v>36</v>
+      </c>
+      <c r="P89" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q89" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>329</v>
+      </c>
+      <c r="B90" t="s">
+        <v>330</v>
+      </c>
+      <c r="C90" t="s">
+        <v>19</v>
+      </c>
+      <c r="D90" t="s">
+        <v>20</v>
+      </c>
+      <c r="E90" t="s">
+        <v>21</v>
+      </c>
+      <c r="F90" t="s">
+        <v>41</v>
+      </c>
+      <c r="G90" t="s">
+        <v>23</v>
+      </c>
+      <c r="H90" t="s">
+        <v>24</v>
+      </c>
+      <c r="I90" t="s">
+        <v>24</v>
+      </c>
+      <c r="J90" t="s">
+        <v>42</v>
+      </c>
+      <c r="K90" t="s">
+        <v>220</v>
+      </c>
+      <c r="L90" t="s">
+        <v>331</v>
+      </c>
+      <c r="M90" t="s">
+        <v>35</v>
+      </c>
+      <c r="N90" t="s">
+        <v>36</v>
+      </c>
+      <c r="O90" t="s">
+        <v>36</v>
+      </c>
+      <c r="P90" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q90" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>332</v>
+      </c>
+      <c r="B91" t="s">
+        <v>333</v>
+      </c>
+      <c r="C91" t="s">
+        <v>19</v>
+      </c>
+      <c r="D91" t="s">
+        <v>20</v>
+      </c>
+      <c r="E91" t="s">
+        <v>21</v>
+      </c>
+      <c r="F91" t="s">
+        <v>46</v>
+      </c>
+      <c r="G91" t="s">
+        <v>23</v>
+      </c>
+      <c r="H91" t="s">
+        <v>24</v>
+      </c>
+      <c r="I91" t="s">
+        <v>24</v>
+      </c>
+      <c r="J91" t="s">
+        <v>47</v>
+      </c>
+      <c r="K91" t="s">
+        <v>331</v>
+      </c>
+      <c r="L91" t="s">
+        <v>334</v>
+      </c>
+      <c r="M91" t="s">
+        <v>35</v>
+      </c>
+      <c r="N91" t="s">
+        <v>36</v>
+      </c>
+      <c r="O91" t="s">
+        <v>36</v>
+      </c>
+      <c r="P91" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q91" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>335</v>
+      </c>
+      <c r="B92" t="s">
+        <v>336</v>
+      </c>
+      <c r="C92" t="s">
+        <v>19</v>
+      </c>
+      <c r="D92" t="s">
+        <v>20</v>
+      </c>
+      <c r="E92" t="s">
+        <v>21</v>
+      </c>
+      <c r="F92" t="s">
+        <v>41</v>
+      </c>
+      <c r="G92" t="s">
+        <v>23</v>
+      </c>
+      <c r="H92" t="s">
+        <v>24</v>
+      </c>
+      <c r="I92" t="s">
+        <v>24</v>
+      </c>
+      <c r="J92" t="s">
+        <v>42</v>
+      </c>
+      <c r="K92" t="s">
+        <v>334</v>
+      </c>
+      <c r="L92" t="s">
+        <v>337</v>
+      </c>
+      <c r="M92" t="s">
+        <v>35</v>
+      </c>
+      <c r="N92" t="s">
+        <v>36</v>
+      </c>
+      <c r="O92" t="s">
+        <v>36</v>
+      </c>
+      <c r="P92" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q92" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>338</v>
+      </c>
+      <c r="B93" t="s">
+        <v>339</v>
+      </c>
+      <c r="C93" t="s">
+        <v>19</v>
+      </c>
+      <c r="D93" t="s">
+        <v>20</v>
+      </c>
+      <c r="E93" t="s">
+        <v>21</v>
+      </c>
+      <c r="F93" t="s">
+        <v>46</v>
+      </c>
+      <c r="G93" t="s">
+        <v>23</v>
+      </c>
+      <c r="H93" t="s">
+        <v>24</v>
+      </c>
+      <c r="I93" t="s">
+        <v>24</v>
+      </c>
+      <c r="J93" t="s">
+        <v>47</v>
+      </c>
+      <c r="K93" t="s">
+        <v>337</v>
+      </c>
+      <c r="L93" t="s">
+        <v>340</v>
+      </c>
+      <c r="M93" t="s">
+        <v>35</v>
+      </c>
+      <c r="N93" t="s">
+        <v>36</v>
+      </c>
+      <c r="O93" t="s">
+        <v>36</v>
+      </c>
+      <c r="P93" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q93" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>341</v>
+      </c>
+      <c r="B94" t="s">
+        <v>342</v>
+      </c>
+      <c r="C94" t="s">
+        <v>19</v>
+      </c>
+      <c r="D94" t="s">
+        <v>20</v>
+      </c>
+      <c r="E94" t="s">
+        <v>21</v>
+      </c>
+      <c r="F94" t="s">
+        <v>46</v>
+      </c>
+      <c r="G94" t="s">
+        <v>23</v>
+      </c>
+      <c r="H94" t="s">
+        <v>310</v>
+      </c>
+      <c r="I94" t="s">
+        <v>310</v>
+      </c>
+      <c r="J94" t="s">
+        <v>343</v>
+      </c>
+      <c r="K94" t="s">
+        <v>328</v>
+      </c>
+      <c r="L94" t="s">
+        <v>344</v>
+      </c>
+      <c r="M94" t="s">
+        <v>35</v>
+      </c>
+      <c r="N94" t="s">
+        <v>36</v>
+      </c>
+      <c r="O94" t="s">
+        <v>36</v>
+      </c>
+      <c r="P94" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q94" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>345</v>
+      </c>
+      <c r="B95" t="s">
+        <v>346</v>
+      </c>
+      <c r="C95" t="s">
+        <v>19</v>
+      </c>
+      <c r="D95" t="s">
+        <v>20</v>
+      </c>
+      <c r="E95" t="s">
+        <v>21</v>
+      </c>
+      <c r="F95" t="s">
+        <v>32</v>
+      </c>
+      <c r="G95" t="s">
+        <v>23</v>
+      </c>
+      <c r="H95" t="s">
+        <v>310</v>
+      </c>
+      <c r="I95" t="s">
+        <v>310</v>
+      </c>
+      <c r="J95" t="s">
+        <v>323</v>
+      </c>
+      <c r="K95" t="s">
+        <v>344</v>
+      </c>
+      <c r="L95" t="s">
+        <v>347</v>
+      </c>
+      <c r="M95" t="s">
+        <v>35</v>
+      </c>
+      <c r="N95" t="s">
+        <v>36</v>
+      </c>
+      <c r="O95" t="s">
+        <v>36</v>
+      </c>
+      <c r="P95" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q95" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>348</v>
+      </c>
+      <c r="B96" t="s">
+        <v>349</v>
+      </c>
+      <c r="C96" t="s">
+        <v>19</v>
+      </c>
+      <c r="D96" t="s">
+        <v>20</v>
+      </c>
+      <c r="E96" t="s">
+        <v>21</v>
+      </c>
+      <c r="F96" t="s">
+        <v>41</v>
+      </c>
+      <c r="G96" t="s">
+        <v>23</v>
+      </c>
+      <c r="H96" t="s">
+        <v>310</v>
+      </c>
+      <c r="I96" t="s">
+        <v>310</v>
+      </c>
+      <c r="J96" t="s">
+        <v>327</v>
+      </c>
+      <c r="K96" t="s">
+        <v>347</v>
+      </c>
+      <c r="L96" t="s">
+        <v>350</v>
+      </c>
+      <c r="M96" t="s">
+        <v>35</v>
+      </c>
+      <c r="N96" t="s">
+        <v>36</v>
+      </c>
+      <c r="O96" t="s">
+        <v>36</v>
+      </c>
+      <c r="P96" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q96" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="97" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>351</v>
+      </c>
+      <c r="B97" t="s">
+        <v>352</v>
+      </c>
+      <c r="C97" t="s">
+        <v>19</v>
+      </c>
+      <c r="D97" t="s">
+        <v>20</v>
+      </c>
+      <c r="E97" t="s">
+        <v>21</v>
+      </c>
+      <c r="F97" t="s">
+        <v>46</v>
+      </c>
+      <c r="G97" t="s">
+        <v>23</v>
+      </c>
+      <c r="H97" t="s">
+        <v>310</v>
+      </c>
+      <c r="I97" t="s">
+        <v>310</v>
+      </c>
+      <c r="J97" t="s">
+        <v>343</v>
+      </c>
+      <c r="K97" t="s">
+        <v>350</v>
+      </c>
+      <c r="L97" t="s">
+        <v>353</v>
+      </c>
+      <c r="M97" t="s">
+        <v>35</v>
+      </c>
+      <c r="N97" t="s">
+        <v>36</v>
+      </c>
+      <c r="O97" t="s">
+        <v>36</v>
+      </c>
+      <c r="P97" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q97" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="98" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>354</v>
+      </c>
+      <c r="B98" t="s">
+        <v>355</v>
+      </c>
+      <c r="C98" t="s">
+        <v>19</v>
+      </c>
+      <c r="D98" t="s">
+        <v>20</v>
+      </c>
+      <c r="E98" t="s">
+        <v>21</v>
+      </c>
+      <c r="F98" t="s">
+        <v>32</v>
+      </c>
+      <c r="G98" t="s">
+        <v>23</v>
+      </c>
+      <c r="H98" t="s">
+        <v>310</v>
+      </c>
+      <c r="I98" t="s">
+        <v>310</v>
+      </c>
+      <c r="J98" t="s">
+        <v>323</v>
+      </c>
+      <c r="K98" t="s">
+        <v>353</v>
+      </c>
+      <c r="L98" t="s">
+        <v>356</v>
+      </c>
+      <c r="M98" t="s">
+        <v>35</v>
+      </c>
+      <c r="N98" t="s">
+        <v>36</v>
+      </c>
+      <c r="O98" t="s">
+        <v>36</v>
+      </c>
+      <c r="P98" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q98" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="99" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>357</v>
+      </c>
+      <c r="B99" t="s">
+        <v>358</v>
+      </c>
+      <c r="C99" t="s">
+        <v>19</v>
+      </c>
+      <c r="D99" t="s">
+        <v>20</v>
+      </c>
+      <c r="E99" t="s">
+        <v>21</v>
+      </c>
+      <c r="F99" t="s">
+        <v>32</v>
+      </c>
+      <c r="G99" t="s">
+        <v>23</v>
+      </c>
+      <c r="H99" t="s">
+        <v>310</v>
+      </c>
+      <c r="I99" t="s">
+        <v>310</v>
+      </c>
+      <c r="J99" t="s">
+        <v>323</v>
+      </c>
+      <c r="K99" t="s">
+        <v>356</v>
+      </c>
+      <c r="L99" t="s">
+        <v>359</v>
+      </c>
+      <c r="M99" t="s">
+        <v>35</v>
+      </c>
+      <c r="N99" t="s">
+        <v>36</v>
+      </c>
+      <c r="O99" t="s">
+        <v>36</v>
+      </c>
+      <c r="P99" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q99" t="s">
+        <v>36</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/data/backup-jobs.xlsx
+++ b/data/backup-jobs.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1683" uniqueCount="360">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1717" uniqueCount="366">
   <si>
     <t>id</t>
   </si>
@@ -1091,6 +1091,24 @@
   </si>
   <si>
     <t>{"job":{"id":"J-f12e75a0a2","title":"Recondition Transmission 24H,M","unit":"GR407 — 24H","unit_id":"U-555bc792","description":"Job recondition Transmission 24H,M (time frame standar).","status":"in_progress","technician_id":"T-25b280e7","template_id":"ne-transmission-24h-m","created_at":"2026-08-13T13:13:28.201Z","started_at":"2026-08-13T13:16:36.692Z","completed_at":"","paused_at":"","total_paused_sec":487,"estimated_minutes":7560},"steps":[{"id":"S-62fed7fe57","job_id":"J-f12e75a0a2","name":"Dismantle: Washing Transmission gp","order":1,"status":"done","started_at":"2026-08-13T13:14:01.944Z","completed_at":"2026-08-13T13:15:17.497Z","duration_sec":150,"std_minutes":300},{"id":"S-bdca34bf9c","job_id":"J-f12e75a0a2","name":"Dismantle: Control Valve","order":2,"status":"done","started_at":"2026-08-13T13:25:23.973Z","completed_at":"2026-08-13T13:25:34.794Z","duration_sec":62,"std_minutes":300},{"id":"S-198d547e50","job_id":"J-f12e75a0a2","name":"Dismantle: Input Trans Gear","order":3,"status":"done","started_at":"2026-08-13T13:25:51.187Z","completed_at":"2026-08-13T13:26:50.395Z","duration_sec":129,"std_minutes":180},{"id":"S-0a2990beeb","job_id":"J-f12e75a0a2","name":"Dismantle: Disconnect Planetary","order":4,"status":"done","started_at":"2026-08-13T13:26:50.395Z","completed_at":"2026-08-13T13:26:58.325Z","duration_sec":14,"std_minutes":180},{"id":"S-1b44880146","job_id":"J-f12e75a0a2","name":"Dismantle: Clutch 6 &amp; Housing","order":5,"status":"in_progress","started_at":"2026-08-13T13:26:58.325Z","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"S-9f4ccc66c5","job_id":"J-f12e75a0a2","name":"Dismantle: Clutch 5","order":6,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-ebd5f203d4","job_id":"J-f12e75a0a2","name":"Dismantle: Clutch 4","order":7,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-efc0d8adbe","job_id":"J-f12e75a0a2","name":"Dismantle: Clutch 3","order":8,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-74a4e63638","job_id":"J-f12e75a0a2","name":"Dismantle: Clutch 2","order":9,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-4dd2a4b52f","job_id":"J-f12e75a0a2","name":"Dismantle: Clutch 1","order":10,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-1cf61d6445","job_id":"J-f12e75a0a2","name":"Dismantle: Planetary &amp; Shaft In-Out","order":11,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"S-f8a0d4e613","job_id":"J-f12e75a0a2","name":"Dismantle: Output Trans Gear","order":12,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":480},{"id":"S-738f8cdae4","job_id":"J-f12e75a0a2","name":"Dismantle: Part list &amp; Tear Down","order":13,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"S-7e81ce5baf","job_id":"J-f12e75a0a2","name":"Assemble: Output Trans Gear","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"S-aacd67baa7","job_id":"J-f12e75a0a2","name":"Assemble: Planetary &amp; Shaft In-Out","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":420},{"id":"S-2bc1eb8c7a","job_id":"J-f12e75a0a2","name":"Assemble: Clutch 1","order":16,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-6c41013e7e","job_id":"J-f12e75a0a2","name":"Assemble: Clutch 2","order":17,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-5dfc9e18df","job_id":"J-f12e75a0a2","name":"Assemble: Clutch 3","order":18,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-427f687ce7","job_id":"J-f12e75a0a2","name":"Assemble: Clutch 4","order":19,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-a7a64f1028","job_id":"J-f12e75a0a2","name":"Assemble: Clutch 5","order":20,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-4f47d5d7b1","job_id":"J-f12e75a0a2","name":"Assemble: Clutch 6 &amp; Housing","order":21,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"S-f5cd7cfd6b","job_id":"J-f12e75a0a2","name":"Assemble: Input Trans Gear","order":22,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"S-647d82040c","job_id":"J-f12e75a0a2","name":"Assemble: Connect Planetary Gp","order":23,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"S-c0da413e41","job_id":"J-f12e75a0a2","name":"Assemble: Control Valve","order":24,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"S-e696ef645c","job_id":"J-f12e75a0a2","name":"Test Bench &amp; Completed: Set up","order":25,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":420},{"id":"S-7d4f1a859e","job_id":"J-f12e75a0a2","name":"Test Bench &amp; Completed: Test","order":26,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"S-1197155765","job_id":"J-f12e75a0a2","name":"Test Bench &amp; Completed: Release","order":27,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":360},{"id":"S-71f21d6927","job_id":"J-f12e75a0a2","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":28,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300}],"assignees":[{"id":"12cf269a-3fcd-4435-af09-3ee3a1e43923","job_id":"J-f12e75a0a2","technician_id":"T-25b280e7","assigned_at":"2026-08-13T13:13:29.838Z","is_lead":"1"},{"id":"1db87a48-9c13-40ac-af3f-256b6b08df59","job_id":"J-f12e75a0a2","technician_id":"T-1c1b3289","assigned_at":"2026-08-13T13:13:29.838Z","is_lead":"0"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-25b280e7","status":"busy","current_job_id":"J-f12e75a0a2"},{"id":"T-1c1b3289","status":"busy","current_job_id":"J-f12e75a0a2"}]}</t>
+  </si>
+  <si>
+    <t>eb09e993-544d-433c-814e-5f6ea44a4440</t>
+  </si>
+  <si>
+    <t>2026-08-13T14:26:52.050Z</t>
+  </si>
+  <si>
+    <t>{"job":{"id":"J03-c0e2","title":"Recondition Transmission D10T,R","unit":"E448 — D10T","unit_id":"a5c2144b-1b29-40f7-9b5c-cfbbc03c3387","description":"Job recondition Transmission D10T,R (time frame standar).","status":"in_progress","technician_id":"T-533ca22c","template_id":"ne-transmission-d10t-r","created_at":"2026-08-10T08:22:13.799Z","started_at":"2026-08-10T08:23:20.053Z","completed_at":"","paused_at":"","total_paused_sec":256,"estimated_minutes":5820},"steps":[{"id":"7609ebf3-f1eb-4d9d-9591-f21d853034e1","job_id":"J03-c0e2","name":"Dismantle: Washing Transmission","order":1,"status":"done","started_at":"2026-08-10T08:23:20.053Z","completed_at":"2026-08-10T08:24:03.692Z","duration_sec":43,"std_minutes":60},{"id":"a3923555-21a4-4b60-9959-c48d814bf136","job_id":"J03-c0e2","name":"Dismantle: Trans Gear","order":2,"status":"done","started_at":"2026-08-10T08:23:32.872Z","completed_at":"2026-08-10T08:24:06.672Z","duration_sec":33,"std_minutes":600},{"id":"39c70957-da00-4dc8-a988-36ee41ef9841","job_id":"J03-c0e2","name":"Dismantle: CV, Harness, &amp; Sensor","order":3,"status":"done","started_at":"2026-08-10T08:24:08.700Z","completed_at":"2026-08-10T08:24:14.772Z","duration_sec":6,"std_minutes":300},{"id":"6feb4f63-8277-4c8a-a4cf-8d8a3d660682","job_id":"J03-c0e2","name":"Dismantle: Clutch 5","order":4,"status":"done","started_at":"2026-08-10T08:23:32.872Z","completed_at":"2026-08-10T08:24:08.700Z","duration_sec":35,"std_minutes":180},{"id":"179574f5-b3d7-43e4-a065-977ebd015bfc","job_id":"J03-c0e2","name":"Dismantle: Clutch 4","order":5,"status":"done","started_at":"2026-08-10T08:24:14.772Z","completed_at":"2026-08-10T10:10:28.558Z","duration_sec":6373,"std_minutes":180},{"id":"8aff0e07-0f40-4945-a9dc-7a8867ffccf4","job_id":"J03-c0e2","name":"Dismantle: Clutch 3","order":6,"status":"done","started_at":"2026-08-11T05:33:18.994Z","completed_at":"2026-08-11T05:33:34.800Z","duration_sec":69782,"std_minutes":180},{"id":"82415ef2-23b1-4eb2-b027-a268df0f4189","job_id":"J03-c0e2","name":"Dismantle: Clutch 2","order":7,"status":"done","started_at":"2026-08-11T05:33:34.800Z","completed_at":"2026-08-11T05:33:47.115Z","duration_sec":12,"std_minutes":180},{"id":"f7c8bcdc-e2d1-4856-aea1-f577d25b0550","job_id":"J03-c0e2","name":"Dismantle: Clutch 1","order":8,"status":"done","started_at":"2026-08-11T05:33:47.115Z","completed_at":"2026-08-11T15:28:10.891Z","duration_sec":35663,"std_minutes":180},{"id":"4391d523-f1d0-4922-95fb-d3827a21b813","job_id":"J03-c0e2","name":"Dismantle: Planetary &amp; Shaft","order":9,"status":"done","started_at":"2026-08-11T15:28:10.891Z","completed_at":"2026-08-11T23:53:02.227Z","duration_sec":30291,"std_minutes":300},{"id":"bdcc79ae-9f46-46e2-963d-fd2ba3d40a2e","job_id":"J03-c0e2","name":"Dismantle: Part list &amp; Tear Down","order":10,"status":"done","started_at":"2026-08-11T23:53:02.227Z","completed_at":"2026-08-12T03:13:34.783Z","duration_sec":12032,"std_minutes":240},{"id":"0670c5ee-3df9-46ba-a7e5-790a2591233a","job_id":"J03-c0e2","name":"Assemble: Planetary &amp; Shaft In-Out","order":11,"status":"done","started_at":"2026-08-12T03:13:34.783Z","completed_at":"2026-08-13T12:03:07.679Z","duration_sec":118172,"std_minutes":300},{"id":"7276104d-e8c7-4ea6-aac7-6cd975141c45","job_id":"J03-c0e2","name":"Assemble: Clutch 1","order":12,"status":"done","started_at":"2026-08-13T12:29:30.475Z","completed_at":"2026-08-13T14:26:51.718Z","duration_sec":15470,"std_minutes":180},{"id":"1781ebaa-7fb0-4896-b642-71d33b8c4878","job_id":"J03-c0e2","name":"Assemble: Clutch 2","order":13,"status":"in_progress","started_at":"2026-08-13T14:26:51.718Z","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"5532b99d-a7fd-4b7d-a752-796f7bc5daff","job_id":"J03-c0e2","name":"Assemble: Clutch 3","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"ff0ed73f-27d1-4b0a-a4f2-7818d3cfbc7e","job_id":"J03-c0e2","name":"Assemble: Clutch 4","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"970a35a3-a96b-48b4-9f04-a2b921b013f0","job_id":"J03-c0e2","name":"Assemble: Clutch 5","order":16,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"698b11d9-e1a3-451f-8a47-ccabcc5718c6","job_id":"J03-c0e2","name":"Assemble: CV, Harness &amp; Sensor","order":17,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"0620fee8-23da-434a-85e6-6354dee830d7","job_id":"J03-c0e2","name":"Assemble: Trans Gear","order":18,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":900},{"id":"ca31c8c2-4542-42f7-be4e-86974a63447b","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Set up","order":19,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"ba2d158c-a9f5-4d98-aea1-fd1f7983c4eb","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Test","order":20,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"d2f96316-8f95-487c-a7ee-94ba19ef4354","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Release","order":21,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"050b2cfc-5ea2-4926-b9c1-c7bdfe6bbd49","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":22,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240}],"assignees":[{"id":"5ece1c51-c36b-46e5-a9d2-f9106a729470","job_id":"J03-c0e2","technician_id":"T-533ca22c","assigned_at":"2026-08-10T08:23:08.120Z","is_lead":"1"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-533ca22c","status":"busy","current_job_id":"J03-c0e2"}]}</t>
+  </si>
+  <si>
+    <t>30d76d8e-ac9d-4c61-9c51-36ca25a8e985</t>
+  </si>
+  <si>
+    <t>2026-08-13T14:28:21.142Z</t>
+  </si>
+  <si>
+    <t>{"job":{"id":"J03-c0e2","title":"Recondition Transmission D10T,R","unit":"E448 — D10T","unit_id":"a5c2144b-1b29-40f7-9b5c-cfbbc03c3387","description":"Job recondition Transmission D10T,R (time frame standar).","status":"in_progress","technician_id":"T-533ca22c","template_id":"ne-transmission-d10t-r","created_at":"2026-08-10T08:22:13.799Z","started_at":"2026-08-10T08:23:20.053Z","completed_at":"","paused_at":"","total_paused_sec":256,"estimated_minutes":5820},"steps":[{"id":"7609ebf3-f1eb-4d9d-9591-f21d853034e1","job_id":"J03-c0e2","name":"Dismantle: Washing Transmission","order":1,"status":"done","started_at":"2026-08-10T08:23:20.053Z","completed_at":"2026-08-10T08:24:03.692Z","duration_sec":43,"std_minutes":60},{"id":"a3923555-21a4-4b60-9959-c48d814bf136","job_id":"J03-c0e2","name":"Dismantle: Trans Gear","order":2,"status":"done","started_at":"2026-08-10T08:23:32.872Z","completed_at":"2026-08-10T08:24:06.672Z","duration_sec":33,"std_minutes":600},{"id":"39c70957-da00-4dc8-a988-36ee41ef9841","job_id":"J03-c0e2","name":"Dismantle: CV, Harness, &amp; Sensor","order":3,"status":"done","started_at":"2026-08-10T08:24:08.700Z","completed_at":"2026-08-10T08:24:14.772Z","duration_sec":6,"std_minutes":300},{"id":"6feb4f63-8277-4c8a-a4cf-8d8a3d660682","job_id":"J03-c0e2","name":"Dismantle: Clutch 5","order":4,"status":"done","started_at":"2026-08-10T08:23:32.872Z","completed_at":"2026-08-10T08:24:08.700Z","duration_sec":35,"std_minutes":180},{"id":"179574f5-b3d7-43e4-a065-977ebd015bfc","job_id":"J03-c0e2","name":"Dismantle: Clutch 4","order":5,"status":"done","started_at":"2026-08-10T08:24:14.772Z","completed_at":"2026-08-10T10:10:28.558Z","duration_sec":6373,"std_minutes":180},{"id":"8aff0e07-0f40-4945-a9dc-7a8867ffccf4","job_id":"J03-c0e2","name":"Dismantle: Clutch 3","order":6,"status":"done","started_at":"2026-08-11T05:33:18.994Z","completed_at":"2026-08-11T05:33:34.800Z","duration_sec":69782,"std_minutes":180},{"id":"82415ef2-23b1-4eb2-b027-a268df0f4189","job_id":"J03-c0e2","name":"Dismantle: Clutch 2","order":7,"status":"done","started_at":"2026-08-11T05:33:34.800Z","completed_at":"2026-08-11T05:33:47.115Z","duration_sec":12,"std_minutes":180},{"id":"f7c8bcdc-e2d1-4856-aea1-f577d25b0550","job_id":"J03-c0e2","name":"Dismantle: Clutch 1","order":8,"status":"done","started_at":"2026-08-11T05:33:47.115Z","completed_at":"2026-08-11T15:28:10.891Z","duration_sec":35663,"std_minutes":180},{"id":"4391d523-f1d0-4922-95fb-d3827a21b813","job_id":"J03-c0e2","name":"Dismantle: Planetary &amp; Shaft","order":9,"status":"done","started_at":"2026-08-11T15:28:10.891Z","completed_at":"2026-08-11T23:53:02.227Z","duration_sec":30291,"std_minutes":300},{"id":"bdcc79ae-9f46-46e2-963d-fd2ba3d40a2e","job_id":"J03-c0e2","name":"Dismantle: Part list &amp; Tear Down","order":10,"status":"done","started_at":"2026-08-11T23:53:02.227Z","completed_at":"2026-08-12T03:13:34.783Z","duration_sec":12032,"std_minutes":240},{"id":"0670c5ee-3df9-46ba-a7e5-790a2591233a","job_id":"J03-c0e2","name":"Assemble: Planetary &amp; Shaft In-Out","order":11,"status":"done","started_at":"2026-08-12T03:13:34.783Z","completed_at":"2026-08-13T12:03:07.679Z","duration_sec":118172,"std_minutes":300},{"id":"7276104d-e8c7-4ea6-aac7-6cd975141c45","job_id":"J03-c0e2","name":"Assemble: Clutch 1","order":12,"status":"done","started_at":"2026-08-13T12:29:30.475Z","completed_at":"2026-08-13T14:26:51.718Z","duration_sec":15470,"std_minutes":180},{"id":"1781ebaa-7fb0-4896-b642-71d33b8c4878","job_id":"J03-c0e2","name":"Assemble: Clutch 2","order":13,"status":"done","started_at":"2026-08-13T14:26:51.718Z","completed_at":"2026-08-13T14:27:45.750Z","duration_sec":108,"std_minutes":180},{"id":"5532b99d-a7fd-4b7d-a752-796f7bc5daff","job_id":"J03-c0e2","name":"Assemble: Clutch 3","order":14,"status":"in_progress","started_at":"2026-08-13T14:27:45.750Z","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"ff0ed73f-27d1-4b0a-a4f2-7818d3cfbc7e","job_id":"J03-c0e2","name":"Assemble: Clutch 4","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"970a35a3-a96b-48b4-9f04-a2b921b013f0","job_id":"J03-c0e2","name":"Assemble: Clutch 5","order":16,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"698b11d9-e1a3-451f-8a47-ccabcc5718c6","job_id":"J03-c0e2","name":"Assemble: CV, Harness &amp; Sensor","order":17,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"0620fee8-23da-434a-85e6-6354dee830d7","job_id":"J03-c0e2","name":"Assemble: Trans Gear","order":18,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":900},{"id":"ca31c8c2-4542-42f7-be4e-86974a63447b","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Set up","order":19,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"ba2d158c-a9f5-4d98-aea1-fd1f7983c4eb","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Test","order":20,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"d2f96316-8f95-487c-a7ee-94ba19ef4354","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Release","order":21,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"050b2cfc-5ea2-4926-b9c1-c7bdfe6bbd49","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":22,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240}],"assignees":[{"id":"5ece1c51-c36b-46e5-a9d2-f9106a729470","job_id":"J03-c0e2","technician_id":"T-533ca22c","assigned_at":"2026-08-10T08:23:08.120Z","is_lead":"1"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-533ca22c","status":"busy","current_job_id":"J03-c0e2"}]}</t>
   </si>
 </sst>
 </file>
@@ -1467,7 +1485,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q99"/>
+  <dimension ref="A1:Q101"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -6717,6 +6735,112 @@
         <v>36</v>
       </c>
     </row>
+    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>360</v>
+      </c>
+      <c r="B100" t="s">
+        <v>361</v>
+      </c>
+      <c r="C100" t="s">
+        <v>19</v>
+      </c>
+      <c r="D100" t="s">
+        <v>20</v>
+      </c>
+      <c r="E100" t="s">
+        <v>21</v>
+      </c>
+      <c r="F100" t="s">
+        <v>32</v>
+      </c>
+      <c r="G100" t="s">
+        <v>23</v>
+      </c>
+      <c r="H100" t="s">
+        <v>55</v>
+      </c>
+      <c r="I100" t="s">
+        <v>55</v>
+      </c>
+      <c r="J100" t="s">
+        <v>88</v>
+      </c>
+      <c r="K100" t="s">
+        <v>304</v>
+      </c>
+      <c r="L100" t="s">
+        <v>362</v>
+      </c>
+      <c r="M100" t="s">
+        <v>35</v>
+      </c>
+      <c r="N100" t="s">
+        <v>36</v>
+      </c>
+      <c r="O100" t="s">
+        <v>36</v>
+      </c>
+      <c r="P100" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q100" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="101" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>363</v>
+      </c>
+      <c r="B101" t="s">
+        <v>364</v>
+      </c>
+      <c r="C101" t="s">
+        <v>19</v>
+      </c>
+      <c r="D101" t="s">
+        <v>20</v>
+      </c>
+      <c r="E101" t="s">
+        <v>21</v>
+      </c>
+      <c r="F101" t="s">
+        <v>32</v>
+      </c>
+      <c r="G101" t="s">
+        <v>23</v>
+      </c>
+      <c r="H101" t="s">
+        <v>55</v>
+      </c>
+      <c r="I101" t="s">
+        <v>55</v>
+      </c>
+      <c r="J101" t="s">
+        <v>88</v>
+      </c>
+      <c r="K101" t="s">
+        <v>362</v>
+      </c>
+      <c r="L101" t="s">
+        <v>365</v>
+      </c>
+      <c r="M101" t="s">
+        <v>35</v>
+      </c>
+      <c r="N101" t="s">
+        <v>36</v>
+      </c>
+      <c r="O101" t="s">
+        <v>36</v>
+      </c>
+      <c r="P101" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q101" t="s">
+        <v>36</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/data/backup-jobs.xlsx
+++ b/data/backup-jobs.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1717" uniqueCount="366">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1751" uniqueCount="372">
   <si>
     <t>id</t>
   </si>
@@ -1109,6 +1109,24 @@
   </si>
   <si>
     <t>{"job":{"id":"J03-c0e2","title":"Recondition Transmission D10T,R","unit":"E448 — D10T","unit_id":"a5c2144b-1b29-40f7-9b5c-cfbbc03c3387","description":"Job recondition Transmission D10T,R (time frame standar).","status":"in_progress","technician_id":"T-533ca22c","template_id":"ne-transmission-d10t-r","created_at":"2026-08-10T08:22:13.799Z","started_at":"2026-08-10T08:23:20.053Z","completed_at":"","paused_at":"","total_paused_sec":256,"estimated_minutes":5820},"steps":[{"id":"7609ebf3-f1eb-4d9d-9591-f21d853034e1","job_id":"J03-c0e2","name":"Dismantle: Washing Transmission","order":1,"status":"done","started_at":"2026-08-10T08:23:20.053Z","completed_at":"2026-08-10T08:24:03.692Z","duration_sec":43,"std_minutes":60},{"id":"a3923555-21a4-4b60-9959-c48d814bf136","job_id":"J03-c0e2","name":"Dismantle: Trans Gear","order":2,"status":"done","started_at":"2026-08-10T08:23:32.872Z","completed_at":"2026-08-10T08:24:06.672Z","duration_sec":33,"std_minutes":600},{"id":"39c70957-da00-4dc8-a988-36ee41ef9841","job_id":"J03-c0e2","name":"Dismantle: CV, Harness, &amp; Sensor","order":3,"status":"done","started_at":"2026-08-10T08:24:08.700Z","completed_at":"2026-08-10T08:24:14.772Z","duration_sec":6,"std_minutes":300},{"id":"6feb4f63-8277-4c8a-a4cf-8d8a3d660682","job_id":"J03-c0e2","name":"Dismantle: Clutch 5","order":4,"status":"done","started_at":"2026-08-10T08:23:32.872Z","completed_at":"2026-08-10T08:24:08.700Z","duration_sec":35,"std_minutes":180},{"id":"179574f5-b3d7-43e4-a065-977ebd015bfc","job_id":"J03-c0e2","name":"Dismantle: Clutch 4","order":5,"status":"done","started_at":"2026-08-10T08:24:14.772Z","completed_at":"2026-08-10T10:10:28.558Z","duration_sec":6373,"std_minutes":180},{"id":"8aff0e07-0f40-4945-a9dc-7a8867ffccf4","job_id":"J03-c0e2","name":"Dismantle: Clutch 3","order":6,"status":"done","started_at":"2026-08-11T05:33:18.994Z","completed_at":"2026-08-11T05:33:34.800Z","duration_sec":69782,"std_minutes":180},{"id":"82415ef2-23b1-4eb2-b027-a268df0f4189","job_id":"J03-c0e2","name":"Dismantle: Clutch 2","order":7,"status":"done","started_at":"2026-08-11T05:33:34.800Z","completed_at":"2026-08-11T05:33:47.115Z","duration_sec":12,"std_minutes":180},{"id":"f7c8bcdc-e2d1-4856-aea1-f577d25b0550","job_id":"J03-c0e2","name":"Dismantle: Clutch 1","order":8,"status":"done","started_at":"2026-08-11T05:33:47.115Z","completed_at":"2026-08-11T15:28:10.891Z","duration_sec":35663,"std_minutes":180},{"id":"4391d523-f1d0-4922-95fb-d3827a21b813","job_id":"J03-c0e2","name":"Dismantle: Planetary &amp; Shaft","order":9,"status":"done","started_at":"2026-08-11T15:28:10.891Z","completed_at":"2026-08-11T23:53:02.227Z","duration_sec":30291,"std_minutes":300},{"id":"bdcc79ae-9f46-46e2-963d-fd2ba3d40a2e","job_id":"J03-c0e2","name":"Dismantle: Part list &amp; Tear Down","order":10,"status":"done","started_at":"2026-08-11T23:53:02.227Z","completed_at":"2026-08-12T03:13:34.783Z","duration_sec":12032,"std_minutes":240},{"id":"0670c5ee-3df9-46ba-a7e5-790a2591233a","job_id":"J03-c0e2","name":"Assemble: Planetary &amp; Shaft In-Out","order":11,"status":"done","started_at":"2026-08-12T03:13:34.783Z","completed_at":"2026-08-13T12:03:07.679Z","duration_sec":118172,"std_minutes":300},{"id":"7276104d-e8c7-4ea6-aac7-6cd975141c45","job_id":"J03-c0e2","name":"Assemble: Clutch 1","order":12,"status":"done","started_at":"2026-08-13T12:29:30.475Z","completed_at":"2026-08-13T14:26:51.718Z","duration_sec":15470,"std_minutes":180},{"id":"1781ebaa-7fb0-4896-b642-71d33b8c4878","job_id":"J03-c0e2","name":"Assemble: Clutch 2","order":13,"status":"done","started_at":"2026-08-13T14:26:51.718Z","completed_at":"2026-08-13T14:27:45.750Z","duration_sec":108,"std_minutes":180},{"id":"5532b99d-a7fd-4b7d-a752-796f7bc5daff","job_id":"J03-c0e2","name":"Assemble: Clutch 3","order":14,"status":"in_progress","started_at":"2026-08-13T14:27:45.750Z","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"ff0ed73f-27d1-4b0a-a4f2-7818d3cfbc7e","job_id":"J03-c0e2","name":"Assemble: Clutch 4","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"970a35a3-a96b-48b4-9f04-a2b921b013f0","job_id":"J03-c0e2","name":"Assemble: Clutch 5","order":16,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"698b11d9-e1a3-451f-8a47-ccabcc5718c6","job_id":"J03-c0e2","name":"Assemble: CV, Harness &amp; Sensor","order":17,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"0620fee8-23da-434a-85e6-6354dee830d7","job_id":"J03-c0e2","name":"Assemble: Trans Gear","order":18,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":900},{"id":"ca31c8c2-4542-42f7-be4e-86974a63447b","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Set up","order":19,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"ba2d158c-a9f5-4d98-aea1-fd1f7983c4eb","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Test","order":20,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"d2f96316-8f95-487c-a7ee-94ba19ef4354","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Release","order":21,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"050b2cfc-5ea2-4926-b9c1-c7bdfe6bbd49","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":22,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240}],"assignees":[{"id":"5ece1c51-c36b-46e5-a9d2-f9106a729470","job_id":"J03-c0e2","technician_id":"T-533ca22c","assigned_at":"2026-08-10T08:23:08.120Z","is_lead":"1"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-533ca22c","status":"busy","current_job_id":"J03-c0e2"}]}</t>
+  </si>
+  <si>
+    <t>1fe9da87-7acb-4069-991f-2e9b0bab159b</t>
+  </si>
+  <si>
+    <t>2026-08-13T14:42:14.393Z</t>
+  </si>
+  <si>
+    <t>{"job":{"id":"J02-dc56","title":"Recondition Transmission 16H,G","unit":"E448 — D10T","unit_id":"a5c2144b-1b29-40f7-9b5c-cfbbc03c3387","description":"Job recondition Transmission 16H,G (time frame standar).","status":"paused","technician_id":"T-37cadb58","template_id":"ne-transmission-16h-g","created_at":"2026-08-09T14:29:20.672Z","started_at":"2026-08-09T15:02:48.075Z","completed_at":"","paused_at":"2026-08-13T14:42:12.534Z","total_paused_sec":103,"estimated_minutes":5340},"steps":[{"id":"91804ed8-5ad4-4ffd-aaad-beba64eb9cb2","job_id":"J02-dc56","name":"Dismantle: Washing Transmission gp","order":1,"status":"done","started_at":"2026-08-09T15:02:48.075Z","completed_at":"2026-08-09T15:20:47.571Z","duration_sec":1079,"std_minutes":240},{"id":"a127f857-f092-4b21-b197-3e3c8a02d549","job_id":"J02-dc56","name":"Dismantle: Control Valve 2EA","order":2,"status":"done","started_at":"2026-08-10T01:30:25.210Z","completed_at":"2026-08-10T01:30:32.748Z","duration_sec":36495,"std_minutes":300},{"id":"3bc8becf-2b5e-4391-8c9f-619d63d7281c","job_id":"J02-dc56","name":"Dismantle: Pump, Lines, &amp; Screen","order":3,"status":"done","started_at":"2026-08-10T01:30:32.748Z","completed_at":"2026-08-10T08:27:37.616Z","duration_sec":25024,"std_minutes":240},{"id":"bacf6ce8-8a97-4831-9f38-3010f4d64a9a","job_id":"J02-dc56","name":"Dismantle: Planetary GP","order":4,"status":"done","started_at":"2026-08-10T08:27:37.616Z","completed_at":"2026-08-11T05:36:57.526Z","duration_sec":76159,"std_minutes":900},{"id":"74bc5c28-b84c-4cfa-b429-25198c968f30","job_id":"J02-dc56","name":"Dismantle: Directional &amp; Idler gear","order":5,"status":"done","started_at":"2026-08-11T05:36:57.526Z","completed_at":"2026-08-11T14:50:26.762Z","duration_sec":33209,"std_minutes":300},{"id":"c3ce574f-16e3-4ce2-815e-10a842f608de","job_id":"J02-dc56","name":"Dismantle: Clean up Housing 2ea","order":6,"status":"done","started_at":"2026-08-11T14:50:26.763Z","completed_at":"2026-08-11T15:28:01.298Z","duration_sec":2254,"std_minutes":120},{"id":"b57a5afd-0b62-47a8-a149-df57cdbec92f","job_id":"J02-dc56","name":"Dismantle: Part list &amp; Tear Down","order":7,"status":"done","started_at":"2026-08-11T15:28:01.298Z","completed_at":"2026-08-12T00:05:46.117Z","duration_sec":31064,"std_minutes":240},{"id":"ef67991d-4f1b-4929-b4b9-3bd70d1c1a8b","job_id":"J02-dc56","name":"Assemble: Directional &amp; Idler gear","order":8,"status":"done","started_at":"2026-08-12T00:05:46.117Z","completed_at":"2026-08-12T03:47:41.223Z","duration_sec":13315,"std_minutes":600},{"id":"19689610-ed31-4c36-959c-6233ef31d9cc","job_id":"J02-dc56","name":"Assemble: Planetary GP","order":9,"status":"done","started_at":"2026-08-12T03:47:41.223Z","completed_at":"2026-08-12T09:25:37.962Z","duration_sec":20276,"std_minutes":600},{"id":"572f712a-0376-495f-a98f-9ee71ead12b3","job_id":"J02-dc56","name":"Assemble: CV 2EA","order":10,"status":"done","started_at":"2026-08-12T09:25:37.962Z","completed_at":"2026-08-13T03:13:58.520Z","duration_sec":64100,"std_minutes":300},{"id":"033a6b1b-8daf-46cc-a1e1-292ad2451d5f","job_id":"J02-dc56","name":"Assemble: Pump, Lines, &amp; Screen","order":11,"status":"done","started_at":"2026-08-13T11:13:08.442Z","completed_at":"2026-08-13T12:00:54.248Z","duration_sec":31601,"std_minutes":300},{"id":"f52cc000-4714-474d-a6c4-a3f41408fbb7","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Set up","order":12,"status":"done","started_at":"2026-08-13T12:00:54.248Z","completed_at":"2026-08-13T12:00:54.894Z","duration_sec":0,"std_minutes":300},{"id":"a9b889d6-b2f7-4421-a27a-fcd6a2fde9f9","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Test","order":13,"status":"in_progress","started_at":"","completed_at":"","duration_sec":9667,"std_minutes":300},{"id":"3edd89d2-41a4-4856-976b-cbc716dc3788","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Release","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"4d87b720-179e-4dbd-bf95-3d44c356f29e","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300}],"assignees":[{"id":"be4e949d-d820-4b28-b15a-054abe52834e","job_id":"J02-dc56","technician_id":"T-37cadb58","assigned_at":"2026-08-13T12:10:34.946Z","is_lead":"1"},{"id":"f54a99f1-4255-448e-98a9-4621ace561ec","job_id":"J02-dc56","technician_id":"T-e4a06545","assigned_at":"2026-08-13T12:10:34.946Z","is_lead":"0"},{"id":"9641f9a5-abbe-471b-bbec-4a731f535ee5","job_id":"J02-dc56","technician_id":"T-d32c7e65","assigned_at":"2026-08-13T12:10:34.946Z","is_lead":"0"},{"id":"9e67f933-012e-4980-a3f0-2c40b4043bb6","job_id":"J02-dc56","technician_id":"T-d6375327","assigned_at":"2026-08-13T12:10:34.946Z","is_lead":"0"},{"id":"545377eb-7418-420b-8d2a-a86555fa4b6e","job_id":"J02-dc56","technician_id":"T-3d0a3937","assigned_at":"2026-08-13T12:10:34.946Z","is_lead":"0"},{"id":"c422779f-8029-4bff-b90e-348b11aa6ea3","job_id":"J02-dc56","technician_id":"T-103b0d90","assigned_at":"2026-08-13T12:10:34.946Z","is_lead":"0"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-37cadb58","status":"busy","current_job_id":"J02-dc56"},{"id":"T-e4a06545","status":"busy","current_job_id":"J02-dc56"},{"id":"T-d32c7e65","status":"busy","current_job_id":"J02-dc56"},{"id":"T-d6375327","status":"busy","current_job_id":"J02-dc56"},{"id":"T-3d0a3937","status":"busy","current_job_id":"J02-dc56"},{"id":"T-103b0d90","status":"busy","current_job_id":"J02-dc56"}]}</t>
+  </si>
+  <si>
+    <t>7af0ff3c-44df-4c43-992e-fff769b64cc0</t>
+  </si>
+  <si>
+    <t>2026-08-13T14:42:28.131Z</t>
+  </si>
+  <si>
+    <t>{"job":{"id":"J02-dc56","title":"Recondition Transmission 16H,G","unit":"E448 — D10T","unit_id":"a5c2144b-1b29-40f7-9b5c-cfbbc03c3387","description":"Job recondition Transmission 16H,G (time frame standar).","status":"in_progress","technician_id":"T-37cadb58","template_id":"ne-transmission-16h-g","created_at":"2026-08-09T14:29:20.672Z","started_at":"2026-08-09T15:02:48.075Z","completed_at":"","paused_at":"","total_paused_sec":118,"estimated_minutes":5340},"steps":[{"id":"91804ed8-5ad4-4ffd-aaad-beba64eb9cb2","job_id":"J02-dc56","name":"Dismantle: Washing Transmission gp","order":1,"status":"done","started_at":"2026-08-09T15:02:48.075Z","completed_at":"2026-08-09T15:20:47.571Z","duration_sec":1079,"std_minutes":240},{"id":"a127f857-f092-4b21-b197-3e3c8a02d549","job_id":"J02-dc56","name":"Dismantle: Control Valve 2EA","order":2,"status":"done","started_at":"2026-08-10T01:30:25.210Z","completed_at":"2026-08-10T01:30:32.748Z","duration_sec":36495,"std_minutes":300},{"id":"3bc8becf-2b5e-4391-8c9f-619d63d7281c","job_id":"J02-dc56","name":"Dismantle: Pump, Lines, &amp; Screen","order":3,"status":"done","started_at":"2026-08-10T01:30:32.748Z","completed_at":"2026-08-10T08:27:37.616Z","duration_sec":25024,"std_minutes":240},{"id":"bacf6ce8-8a97-4831-9f38-3010f4d64a9a","job_id":"J02-dc56","name":"Dismantle: Planetary GP","order":4,"status":"done","started_at":"2026-08-10T08:27:37.616Z","completed_at":"2026-08-11T05:36:57.526Z","duration_sec":76159,"std_minutes":900},{"id":"74bc5c28-b84c-4cfa-b429-25198c968f30","job_id":"J02-dc56","name":"Dismantle: Directional &amp; Idler gear","order":5,"status":"done","started_at":"2026-08-11T05:36:57.526Z","completed_at":"2026-08-11T14:50:26.762Z","duration_sec":33209,"std_minutes":300},{"id":"c3ce574f-16e3-4ce2-815e-10a842f608de","job_id":"J02-dc56","name":"Dismantle: Clean up Housing 2ea","order":6,"status":"done","started_at":"2026-08-11T14:50:26.763Z","completed_at":"2026-08-11T15:28:01.298Z","duration_sec":2254,"std_minutes":120},{"id":"b57a5afd-0b62-47a8-a149-df57cdbec92f","job_id":"J02-dc56","name":"Dismantle: Part list &amp; Tear Down","order":7,"status":"done","started_at":"2026-08-11T15:28:01.298Z","completed_at":"2026-08-12T00:05:46.117Z","duration_sec":31064,"std_minutes":240},{"id":"ef67991d-4f1b-4929-b4b9-3bd70d1c1a8b","job_id":"J02-dc56","name":"Assemble: Directional &amp; Idler gear","order":8,"status":"done","started_at":"2026-08-12T00:05:46.117Z","completed_at":"2026-08-12T03:47:41.223Z","duration_sec":13315,"std_minutes":600},{"id":"19689610-ed31-4c36-959c-6233ef31d9cc","job_id":"J02-dc56","name":"Assemble: Planetary GP","order":9,"status":"done","started_at":"2026-08-12T03:47:41.223Z","completed_at":"2026-08-12T09:25:37.962Z","duration_sec":20276,"std_minutes":600},{"id":"572f712a-0376-495f-a98f-9ee71ead12b3","job_id":"J02-dc56","name":"Assemble: CV 2EA","order":10,"status":"done","started_at":"2026-08-12T09:25:37.962Z","completed_at":"2026-08-13T03:13:58.520Z","duration_sec":64100,"std_minutes":300},{"id":"033a6b1b-8daf-46cc-a1e1-292ad2451d5f","job_id":"J02-dc56","name":"Assemble: Pump, Lines, &amp; Screen","order":11,"status":"done","started_at":"2026-08-13T11:13:08.442Z","completed_at":"2026-08-13T12:00:54.248Z","duration_sec":31601,"std_minutes":300},{"id":"f52cc000-4714-474d-a6c4-a3f41408fbb7","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Set up","order":12,"status":"done","started_at":"2026-08-13T12:00:54.248Z","completed_at":"2026-08-13T12:00:54.894Z","duration_sec":0,"std_minutes":300},{"id":"a9b889d6-b2f7-4421-a27a-fcd6a2fde9f9","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Test","order":13,"status":"in_progress","started_at":"2026-08-13T14:42:27.873Z","completed_at":"","duration_sec":9667,"std_minutes":300},{"id":"3edd89d2-41a4-4856-976b-cbc716dc3788","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Release","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"4d87b720-179e-4dbd-bf95-3d44c356f29e","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300}],"assignees":[{"id":"be4e949d-d820-4b28-b15a-054abe52834e","job_id":"J02-dc56","technician_id":"T-37cadb58","assigned_at":"2026-08-13T12:10:34.946Z","is_lead":"1"},{"id":"f54a99f1-4255-448e-98a9-4621ace561ec","job_id":"J02-dc56","technician_id":"T-e4a06545","assigned_at":"2026-08-13T12:10:34.946Z","is_lead":"0"},{"id":"9641f9a5-abbe-471b-bbec-4a731f535ee5","job_id":"J02-dc56","technician_id":"T-d32c7e65","assigned_at":"2026-08-13T12:10:34.946Z","is_lead":"0"},{"id":"9e67f933-012e-4980-a3f0-2c40b4043bb6","job_id":"J02-dc56","technician_id":"T-d6375327","assigned_at":"2026-08-13T12:10:34.946Z","is_lead":"0"},{"id":"545377eb-7418-420b-8d2a-a86555fa4b6e","job_id":"J02-dc56","technician_id":"T-3d0a3937","assigned_at":"2026-08-13T12:10:34.946Z","is_lead":"0"},{"id":"c422779f-8029-4bff-b90e-348b11aa6ea3","job_id":"J02-dc56","technician_id":"T-103b0d90","assigned_at":"2026-08-13T12:10:34.946Z","is_lead":"0"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-37cadb58","status":"busy","current_job_id":"J02-dc56"},{"id":"T-e4a06545","status":"busy","current_job_id":"J02-dc56"},{"id":"T-d32c7e65","status":"busy","current_job_id":"J02-dc56"},{"id":"T-d6375327","status":"busy","current_job_id":"J02-dc56"},{"id":"T-3d0a3937","status":"busy","current_job_id":"J02-dc56"},{"id":"T-103b0d90","status":"busy","current_job_id":"J02-dc56"}]}</t>
   </si>
 </sst>
 </file>
@@ -1485,7 +1503,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q101"/>
+  <dimension ref="A1:Q103"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -6841,6 +6859,112 @@
         <v>36</v>
       </c>
     </row>
+    <row r="102" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>366</v>
+      </c>
+      <c r="B102" t="s">
+        <v>367</v>
+      </c>
+      <c r="C102" t="s">
+        <v>19</v>
+      </c>
+      <c r="D102" t="s">
+        <v>20</v>
+      </c>
+      <c r="E102" t="s">
+        <v>21</v>
+      </c>
+      <c r="F102" t="s">
+        <v>41</v>
+      </c>
+      <c r="G102" t="s">
+        <v>23</v>
+      </c>
+      <c r="H102" t="s">
+        <v>24</v>
+      </c>
+      <c r="I102" t="s">
+        <v>24</v>
+      </c>
+      <c r="J102" t="s">
+        <v>42</v>
+      </c>
+      <c r="K102" t="s">
+        <v>340</v>
+      </c>
+      <c r="L102" t="s">
+        <v>368</v>
+      </c>
+      <c r="M102" t="s">
+        <v>35</v>
+      </c>
+      <c r="N102" t="s">
+        <v>36</v>
+      </c>
+      <c r="O102" t="s">
+        <v>36</v>
+      </c>
+      <c r="P102" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q102" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="103" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>369</v>
+      </c>
+      <c r="B103" t="s">
+        <v>370</v>
+      </c>
+      <c r="C103" t="s">
+        <v>19</v>
+      </c>
+      <c r="D103" t="s">
+        <v>20</v>
+      </c>
+      <c r="E103" t="s">
+        <v>21</v>
+      </c>
+      <c r="F103" t="s">
+        <v>46</v>
+      </c>
+      <c r="G103" t="s">
+        <v>23</v>
+      </c>
+      <c r="H103" t="s">
+        <v>24</v>
+      </c>
+      <c r="I103" t="s">
+        <v>24</v>
+      </c>
+      <c r="J103" t="s">
+        <v>47</v>
+      </c>
+      <c r="K103" t="s">
+        <v>368</v>
+      </c>
+      <c r="L103" t="s">
+        <v>371</v>
+      </c>
+      <c r="M103" t="s">
+        <v>35</v>
+      </c>
+      <c r="N103" t="s">
+        <v>36</v>
+      </c>
+      <c r="O103" t="s">
+        <v>36</v>
+      </c>
+      <c r="P103" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q103" t="s">
+        <v>36</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/data/backup-jobs.xlsx
+++ b/data/backup-jobs.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1751" uniqueCount="372">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1887" uniqueCount="396">
   <si>
     <t>id</t>
   </si>
@@ -1127,6 +1127,78 @@
   </si>
   <si>
     <t>{"job":{"id":"J02-dc56","title":"Recondition Transmission 16H,G","unit":"E448 — D10T","unit_id":"a5c2144b-1b29-40f7-9b5c-cfbbc03c3387","description":"Job recondition Transmission 16H,G (time frame standar).","status":"in_progress","technician_id":"T-37cadb58","template_id":"ne-transmission-16h-g","created_at":"2026-08-09T14:29:20.672Z","started_at":"2026-08-09T15:02:48.075Z","completed_at":"","paused_at":"","total_paused_sec":118,"estimated_minutes":5340},"steps":[{"id":"91804ed8-5ad4-4ffd-aaad-beba64eb9cb2","job_id":"J02-dc56","name":"Dismantle: Washing Transmission gp","order":1,"status":"done","started_at":"2026-08-09T15:02:48.075Z","completed_at":"2026-08-09T15:20:47.571Z","duration_sec":1079,"std_minutes":240},{"id":"a127f857-f092-4b21-b197-3e3c8a02d549","job_id":"J02-dc56","name":"Dismantle: Control Valve 2EA","order":2,"status":"done","started_at":"2026-08-10T01:30:25.210Z","completed_at":"2026-08-10T01:30:32.748Z","duration_sec":36495,"std_minutes":300},{"id":"3bc8becf-2b5e-4391-8c9f-619d63d7281c","job_id":"J02-dc56","name":"Dismantle: Pump, Lines, &amp; Screen","order":3,"status":"done","started_at":"2026-08-10T01:30:32.748Z","completed_at":"2026-08-10T08:27:37.616Z","duration_sec":25024,"std_minutes":240},{"id":"bacf6ce8-8a97-4831-9f38-3010f4d64a9a","job_id":"J02-dc56","name":"Dismantle: Planetary GP","order":4,"status":"done","started_at":"2026-08-10T08:27:37.616Z","completed_at":"2026-08-11T05:36:57.526Z","duration_sec":76159,"std_minutes":900},{"id":"74bc5c28-b84c-4cfa-b429-25198c968f30","job_id":"J02-dc56","name":"Dismantle: Directional &amp; Idler gear","order":5,"status":"done","started_at":"2026-08-11T05:36:57.526Z","completed_at":"2026-08-11T14:50:26.762Z","duration_sec":33209,"std_minutes":300},{"id":"c3ce574f-16e3-4ce2-815e-10a842f608de","job_id":"J02-dc56","name":"Dismantle: Clean up Housing 2ea","order":6,"status":"done","started_at":"2026-08-11T14:50:26.763Z","completed_at":"2026-08-11T15:28:01.298Z","duration_sec":2254,"std_minutes":120},{"id":"b57a5afd-0b62-47a8-a149-df57cdbec92f","job_id":"J02-dc56","name":"Dismantle: Part list &amp; Tear Down","order":7,"status":"done","started_at":"2026-08-11T15:28:01.298Z","completed_at":"2026-08-12T00:05:46.117Z","duration_sec":31064,"std_minutes":240},{"id":"ef67991d-4f1b-4929-b4b9-3bd70d1c1a8b","job_id":"J02-dc56","name":"Assemble: Directional &amp; Idler gear","order":8,"status":"done","started_at":"2026-08-12T00:05:46.117Z","completed_at":"2026-08-12T03:47:41.223Z","duration_sec":13315,"std_minutes":600},{"id":"19689610-ed31-4c36-959c-6233ef31d9cc","job_id":"J02-dc56","name":"Assemble: Planetary GP","order":9,"status":"done","started_at":"2026-08-12T03:47:41.223Z","completed_at":"2026-08-12T09:25:37.962Z","duration_sec":20276,"std_minutes":600},{"id":"572f712a-0376-495f-a98f-9ee71ead12b3","job_id":"J02-dc56","name":"Assemble: CV 2EA","order":10,"status":"done","started_at":"2026-08-12T09:25:37.962Z","completed_at":"2026-08-13T03:13:58.520Z","duration_sec":64100,"std_minutes":300},{"id":"033a6b1b-8daf-46cc-a1e1-292ad2451d5f","job_id":"J02-dc56","name":"Assemble: Pump, Lines, &amp; Screen","order":11,"status":"done","started_at":"2026-08-13T11:13:08.442Z","completed_at":"2026-08-13T12:00:54.248Z","duration_sec":31601,"std_minutes":300},{"id":"f52cc000-4714-474d-a6c4-a3f41408fbb7","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Set up","order":12,"status":"done","started_at":"2026-08-13T12:00:54.248Z","completed_at":"2026-08-13T12:00:54.894Z","duration_sec":0,"std_minutes":300},{"id":"a9b889d6-b2f7-4421-a27a-fcd6a2fde9f9","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Test","order":13,"status":"in_progress","started_at":"2026-08-13T14:42:27.873Z","completed_at":"","duration_sec":9667,"std_minutes":300},{"id":"3edd89d2-41a4-4856-976b-cbc716dc3788","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Release","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"4d87b720-179e-4dbd-bf95-3d44c356f29e","job_id":"J02-dc56","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300}],"assignees":[{"id":"be4e949d-d820-4b28-b15a-054abe52834e","job_id":"J02-dc56","technician_id":"T-37cadb58","assigned_at":"2026-08-13T12:10:34.946Z","is_lead":"1"},{"id":"f54a99f1-4255-448e-98a9-4621ace561ec","job_id":"J02-dc56","technician_id":"T-e4a06545","assigned_at":"2026-08-13T12:10:34.946Z","is_lead":"0"},{"id":"9641f9a5-abbe-471b-bbec-4a731f535ee5","job_id":"J02-dc56","technician_id":"T-d32c7e65","assigned_at":"2026-08-13T12:10:34.946Z","is_lead":"0"},{"id":"9e67f933-012e-4980-a3f0-2c40b4043bb6","job_id":"J02-dc56","technician_id":"T-d6375327","assigned_at":"2026-08-13T12:10:34.946Z","is_lead":"0"},{"id":"545377eb-7418-420b-8d2a-a86555fa4b6e","job_id":"J02-dc56","technician_id":"T-3d0a3937","assigned_at":"2026-08-13T12:10:34.946Z","is_lead":"0"},{"id":"c422779f-8029-4bff-b90e-348b11aa6ea3","job_id":"J02-dc56","technician_id":"T-103b0d90","assigned_at":"2026-08-13T12:10:34.946Z","is_lead":"0"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-37cadb58","status":"busy","current_job_id":"J02-dc56"},{"id":"T-e4a06545","status":"busy","current_job_id":"J02-dc56"},{"id":"T-d32c7e65","status":"busy","current_job_id":"J02-dc56"},{"id":"T-d6375327","status":"busy","current_job_id":"J02-dc56"},{"id":"T-3d0a3937","status":"busy","current_job_id":"J02-dc56"},{"id":"T-103b0d90","status":"busy","current_job_id":"J02-dc56"}]}</t>
+  </si>
+  <si>
+    <t>09e9bd86-fe88-49d0-ac51-5240f563c06a</t>
+  </si>
+  <si>
+    <t>2026-08-16T11:14:05.194Z</t>
+  </si>
+  <si>
+    <t>{"job":{"id":"J03-c0e2","title":"Recondition Transmission D10T,R","unit":"E448 — D10T","unit_id":"a5c2144b-1b29-40f7-9b5c-cfbbc03c3387","description":"Job recondition Transmission D10T,R (time frame standar).","status":"in_progress","technician_id":"T-533ca22c","template_id":"ne-transmission-d10t-r","created_at":"2026-08-10T08:22:13.799Z","started_at":"2026-08-10T08:23:20.053Z","completed_at":"","paused_at":"","total_paused_sec":256,"estimated_minutes":5820},"steps":[{"id":"7609ebf3-f1eb-4d9d-9591-f21d853034e1","job_id":"J03-c0e2","name":"Dismantle: Washing Transmission","order":1,"status":"done","started_at":"2026-08-10T08:23:20.053Z","completed_at":"2026-08-10T08:24:03.692Z","duration_sec":43,"std_minutes":60},{"id":"a3923555-21a4-4b60-9959-c48d814bf136","job_id":"J03-c0e2","name":"Dismantle: Trans Gear","order":2,"status":"done","started_at":"2026-08-10T08:23:32.872Z","completed_at":"2026-08-10T08:24:06.672Z","duration_sec":33,"std_minutes":600},{"id":"39c70957-da00-4dc8-a988-36ee41ef9841","job_id":"J03-c0e2","name":"Dismantle: CV, Harness, &amp; Sensor","order":3,"status":"done","started_at":"2026-08-10T08:24:08.700Z","completed_at":"2026-08-10T08:24:14.772Z","duration_sec":6,"std_minutes":300},{"id":"6feb4f63-8277-4c8a-a4cf-8d8a3d660682","job_id":"J03-c0e2","name":"Dismantle: Clutch 5","order":4,"status":"done","started_at":"2026-08-10T08:23:32.872Z","completed_at":"2026-08-10T08:24:08.700Z","duration_sec":35,"std_minutes":180},{"id":"179574f5-b3d7-43e4-a065-977ebd015bfc","job_id":"J03-c0e2","name":"Dismantle: Clutch 4","order":5,"status":"done","started_at":"2026-08-10T08:24:14.772Z","completed_at":"2026-08-10T10:10:28.558Z","duration_sec":6373,"std_minutes":180},{"id":"8aff0e07-0f40-4945-a9dc-7a8867ffccf4","job_id":"J03-c0e2","name":"Dismantle: Clutch 3","order":6,"status":"done","started_at":"2026-08-11T05:33:18.994Z","completed_at":"2026-08-11T05:33:34.800Z","duration_sec":69782,"std_minutes":180},{"id":"82415ef2-23b1-4eb2-b027-a268df0f4189","job_id":"J03-c0e2","name":"Dismantle: Clutch 2","order":7,"status":"done","started_at":"2026-08-11T05:33:34.800Z","completed_at":"2026-08-11T05:33:47.115Z","duration_sec":12,"std_minutes":180},{"id":"f7c8bcdc-e2d1-4856-aea1-f577d25b0550","job_id":"J03-c0e2","name":"Dismantle: Clutch 1","order":8,"status":"done","started_at":"2026-08-11T05:33:47.115Z","completed_at":"2026-08-11T15:28:10.891Z","duration_sec":35663,"std_minutes":180},{"id":"4391d523-f1d0-4922-95fb-d3827a21b813","job_id":"J03-c0e2","name":"Dismantle: Planetary &amp; Shaft","order":9,"status":"done","started_at":"2026-08-11T15:28:10.891Z","completed_at":"2026-08-11T23:53:02.227Z","duration_sec":30291,"std_minutes":300},{"id":"bdcc79ae-9f46-46e2-963d-fd2ba3d40a2e","job_id":"J03-c0e2","name":"Dismantle: Part list &amp; Tear Down","order":10,"status":"done","started_at":"2026-08-11T23:53:02.227Z","completed_at":"2026-08-12T03:13:34.783Z","duration_sec":12032,"std_minutes":240},{"id":"0670c5ee-3df9-46ba-a7e5-790a2591233a","job_id":"J03-c0e2","name":"Assemble: Planetary &amp; Shaft In-Out","order":11,"status":"done","started_at":"2026-08-12T03:13:34.783Z","completed_at":"2026-08-13T12:03:07.679Z","duration_sec":118172,"std_minutes":300},{"id":"7276104d-e8c7-4ea6-aac7-6cd975141c45","job_id":"J03-c0e2","name":"Assemble: Clutch 1","order":12,"status":"done","started_at":"2026-08-13T12:29:30.475Z","completed_at":"2026-08-13T14:26:51.718Z","duration_sec":15470,"std_minutes":180},{"id":"1781ebaa-7fb0-4896-b642-71d33b8c4878","job_id":"J03-c0e2","name":"Assemble: Clutch 2","order":13,"status":"done","started_at":"2026-08-13T14:26:51.718Z","completed_at":"2026-08-13T14:27:45.750Z","duration_sec":108,"std_minutes":180},{"id":"5532b99d-a7fd-4b7d-a752-796f7bc5daff","job_id":"J03-c0e2","name":"Assemble: Clutch 3","order":14,"status":"done","started_at":"2026-08-13T14:27:45.750Z","completed_at":"2026-08-16T11:14:03.226Z","duration_sec":495154,"std_minutes":180},{"id":"ff0ed73f-27d1-4b0a-a4f2-7818d3cfbc7e","job_id":"J03-c0e2","name":"Assemble: Clutch 4","order":15,"status":"in_progress","started_at":"2026-08-16T11:14:03.226Z","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"970a35a3-a96b-48b4-9f04-a2b921b013f0","job_id":"J03-c0e2","name":"Assemble: Clutch 5","order":16,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"698b11d9-e1a3-451f-8a47-ccabcc5718c6","job_id":"J03-c0e2","name":"Assemble: CV, Harness &amp; Sensor","order":17,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"0620fee8-23da-434a-85e6-6354dee830d7","job_id":"J03-c0e2","name":"Assemble: Trans Gear","order":18,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":900},{"id":"ca31c8c2-4542-42f7-be4e-86974a63447b","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Set up","order":19,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"ba2d158c-a9f5-4d98-aea1-fd1f7983c4eb","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Test","order":20,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"d2f96316-8f95-487c-a7ee-94ba19ef4354","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Release","order":21,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"050b2cfc-5ea2-4926-b9c1-c7bdfe6bbd49","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":22,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240}],"assignees":[{"id":"5ece1c51-c36b-46e5-a9d2-f9106a729470","job_id":"J03-c0e2","technician_id":"T-533ca22c","assigned_at":"2026-08-10T08:23:08.120Z","is_lead":"1"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-533ca22c","status":"busy","current_job_id":"J03-c0e2"}]}</t>
+  </si>
+  <si>
+    <t>d0540bca-6c72-4e33-a4be-f0e4d1e54584</t>
+  </si>
+  <si>
+    <t>2026-08-16T11:14:13.815Z</t>
+  </si>
+  <si>
+    <t>{"job":{"id":"J03-c0e2","title":"Recondition Transmission D10T,R","unit":"E448 — D10T","unit_id":"a5c2144b-1b29-40f7-9b5c-cfbbc03c3387","description":"Job recondition Transmission D10T,R (time frame standar).","status":"in_progress","technician_id":"T-533ca22c","template_id":"ne-transmission-d10t-r","created_at":"2026-08-10T08:22:13.799Z","started_at":"2026-08-10T08:23:20.053Z","completed_at":"","paused_at":"","total_paused_sec":256,"estimated_minutes":5820},"steps":[{"id":"7609ebf3-f1eb-4d9d-9591-f21d853034e1","job_id":"J03-c0e2","name":"Dismantle: Washing Transmission","order":1,"status":"done","started_at":"2026-08-10T08:23:20.053Z","completed_at":"2026-08-10T08:24:03.692Z","duration_sec":43,"std_minutes":60},{"id":"a3923555-21a4-4b60-9959-c48d814bf136","job_id":"J03-c0e2","name":"Dismantle: Trans Gear","order":2,"status":"done","started_at":"2026-08-10T08:23:32.872Z","completed_at":"2026-08-10T08:24:06.672Z","duration_sec":33,"std_minutes":600},{"id":"39c70957-da00-4dc8-a988-36ee41ef9841","job_id":"J03-c0e2","name":"Dismantle: CV, Harness, &amp; Sensor","order":3,"status":"done","started_at":"2026-08-10T08:24:08.700Z","completed_at":"2026-08-10T08:24:14.772Z","duration_sec":6,"std_minutes":300},{"id":"6feb4f63-8277-4c8a-a4cf-8d8a3d660682","job_id":"J03-c0e2","name":"Dismantle: Clutch 5","order":4,"status":"done","started_at":"2026-08-10T08:23:32.872Z","completed_at":"2026-08-10T08:24:08.700Z","duration_sec":35,"std_minutes":180},{"id":"179574f5-b3d7-43e4-a065-977ebd015bfc","job_id":"J03-c0e2","name":"Dismantle: Clutch 4","order":5,"status":"done","started_at":"2026-08-10T08:24:14.772Z","completed_at":"2026-08-10T10:10:28.558Z","duration_sec":6373,"std_minutes":180},{"id":"8aff0e07-0f40-4945-a9dc-7a8867ffccf4","job_id":"J03-c0e2","name":"Dismantle: Clutch 3","order":6,"status":"done","started_at":"2026-08-11T05:33:18.994Z","completed_at":"2026-08-11T05:33:34.800Z","duration_sec":69782,"std_minutes":180},{"id":"82415ef2-23b1-4eb2-b027-a268df0f4189","job_id":"J03-c0e2","name":"Dismantle: Clutch 2","order":7,"status":"done","started_at":"2026-08-11T05:33:34.800Z","completed_at":"2026-08-11T05:33:47.115Z","duration_sec":12,"std_minutes":180},{"id":"f7c8bcdc-e2d1-4856-aea1-f577d25b0550","job_id":"J03-c0e2","name":"Dismantle: Clutch 1","order":8,"status":"done","started_at":"2026-08-11T05:33:47.115Z","completed_at":"2026-08-11T15:28:10.891Z","duration_sec":35663,"std_minutes":180},{"id":"4391d523-f1d0-4922-95fb-d3827a21b813","job_id":"J03-c0e2","name":"Dismantle: Planetary &amp; Shaft","order":9,"status":"done","started_at":"2026-08-11T15:28:10.891Z","completed_at":"2026-08-11T23:53:02.227Z","duration_sec":30291,"std_minutes":300},{"id":"bdcc79ae-9f46-46e2-963d-fd2ba3d40a2e","job_id":"J03-c0e2","name":"Dismantle: Part list &amp; Tear Down","order":10,"status":"done","started_at":"2026-08-11T23:53:02.227Z","completed_at":"2026-08-12T03:13:34.783Z","duration_sec":12032,"std_minutes":240},{"id":"0670c5ee-3df9-46ba-a7e5-790a2591233a","job_id":"J03-c0e2","name":"Assemble: Planetary &amp; Shaft In-Out","order":11,"status":"done","started_at":"2026-08-12T03:13:34.783Z","completed_at":"2026-08-13T12:03:07.679Z","duration_sec":118172,"std_minutes":300},{"id":"7276104d-e8c7-4ea6-aac7-6cd975141c45","job_id":"J03-c0e2","name":"Assemble: Clutch 1","order":12,"status":"done","started_at":"2026-08-13T12:29:30.475Z","completed_at":"2026-08-13T14:26:51.718Z","duration_sec":15470,"std_minutes":180},{"id":"1781ebaa-7fb0-4896-b642-71d33b8c4878","job_id":"J03-c0e2","name":"Assemble: Clutch 2","order":13,"status":"done","started_at":"2026-08-13T14:26:51.718Z","completed_at":"2026-08-13T14:27:45.750Z","duration_sec":108,"std_minutes":180},{"id":"5532b99d-a7fd-4b7d-a752-796f7bc5daff","job_id":"J03-c0e2","name":"Assemble: Clutch 3","order":14,"status":"done","started_at":"2026-08-13T14:27:45.750Z","completed_at":"2026-08-16T11:14:03.226Z","duration_sec":495154,"std_minutes":180},{"id":"ff0ed73f-27d1-4b0a-a4f2-7818d3cfbc7e","job_id":"J03-c0e2","name":"Assemble: Clutch 4","order":15,"status":"done","started_at":"2026-08-16T11:14:03.226Z","completed_at":"2026-08-16T11:14:13.083Z","duration_sec":18,"std_minutes":180},{"id":"970a35a3-a96b-48b4-9f04-a2b921b013f0","job_id":"J03-c0e2","name":"Assemble: Clutch 5","order":16,"status":"in_progress","started_at":"2026-08-16T11:14:13.083Z","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"698b11d9-e1a3-451f-8a47-ccabcc5718c6","job_id":"J03-c0e2","name":"Assemble: CV, Harness &amp; Sensor","order":17,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"0620fee8-23da-434a-85e6-6354dee830d7","job_id":"J03-c0e2","name":"Assemble: Trans Gear","order":18,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":900},{"id":"ca31c8c2-4542-42f7-be4e-86974a63447b","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Set up","order":19,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"ba2d158c-a9f5-4d98-aea1-fd1f7983c4eb","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Test","order":20,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"d2f96316-8f95-487c-a7ee-94ba19ef4354","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Release","order":21,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"050b2cfc-5ea2-4926-b9c1-c7bdfe6bbd49","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":22,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240}],"assignees":[{"id":"5ece1c51-c36b-46e5-a9d2-f9106a729470","job_id":"J03-c0e2","technician_id":"T-533ca22c","assigned_at":"2026-08-10T08:23:08.120Z","is_lead":"1"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-533ca22c","status":"busy","current_job_id":"J03-c0e2"}]}</t>
+  </si>
+  <si>
+    <t>0644dcaf-533f-4d58-988a-386029e7c61c</t>
+  </si>
+  <si>
+    <t>2026-08-16T11:14:32.798Z</t>
+  </si>
+  <si>
+    <t>{"job":{"id":"J03-c0e2","title":"Recondition Transmission D10T,R","unit":"E448 — D10T","unit_id":"a5c2144b-1b29-40f7-9b5c-cfbbc03c3387","description":"Job recondition Transmission D10T,R (time frame standar).","status":"in_progress","technician_id":"T-533ca22c","template_id":"ne-transmission-d10t-r","created_at":"2026-08-10T08:22:13.799Z","started_at":"2026-08-10T08:23:20.053Z","completed_at":"","paused_at":"","total_paused_sec":256,"estimated_minutes":5820},"steps":[{"id":"7609ebf3-f1eb-4d9d-9591-f21d853034e1","job_id":"J03-c0e2","name":"Dismantle: Washing Transmission","order":1,"status":"done","started_at":"2026-08-10T08:23:20.053Z","completed_at":"2026-08-10T08:24:03.692Z","duration_sec":43,"std_minutes":60},{"id":"a3923555-21a4-4b60-9959-c48d814bf136","job_id":"J03-c0e2","name":"Dismantle: Trans Gear","order":2,"status":"done","started_at":"2026-08-10T08:23:32.872Z","completed_at":"2026-08-10T08:24:06.672Z","duration_sec":33,"std_minutes":600},{"id":"39c70957-da00-4dc8-a988-36ee41ef9841","job_id":"J03-c0e2","name":"Dismantle: CV, Harness, &amp; Sensor","order":3,"status":"done","started_at":"2026-08-10T08:24:08.700Z","completed_at":"2026-08-10T08:24:14.772Z","duration_sec":6,"std_minutes":300},{"id":"6feb4f63-8277-4c8a-a4cf-8d8a3d660682","job_id":"J03-c0e2","name":"Dismantle: Clutch 5","order":4,"status":"done","started_at":"2026-08-10T08:23:32.872Z","completed_at":"2026-08-10T08:24:08.700Z","duration_sec":35,"std_minutes":180},{"id":"179574f5-b3d7-43e4-a065-977ebd015bfc","job_id":"J03-c0e2","name":"Dismantle: Clutch 4","order":5,"status":"done","started_at":"2026-08-10T08:24:14.772Z","completed_at":"2026-08-10T10:10:28.558Z","duration_sec":6373,"std_minutes":180},{"id":"8aff0e07-0f40-4945-a9dc-7a8867ffccf4","job_id":"J03-c0e2","name":"Dismantle: Clutch 3","order":6,"status":"done","started_at":"2026-08-11T05:33:18.994Z","completed_at":"2026-08-11T05:33:34.800Z","duration_sec":69782,"std_minutes":180},{"id":"82415ef2-23b1-4eb2-b027-a268df0f4189","job_id":"J03-c0e2","name":"Dismantle: Clutch 2","order":7,"status":"done","started_at":"2026-08-11T05:33:34.800Z","completed_at":"2026-08-11T05:33:47.115Z","duration_sec":12,"std_minutes":180},{"id":"f7c8bcdc-e2d1-4856-aea1-f577d25b0550","job_id":"J03-c0e2","name":"Dismantle: Clutch 1","order":8,"status":"done","started_at":"2026-08-11T05:33:47.115Z","completed_at":"2026-08-11T15:28:10.891Z","duration_sec":35663,"std_minutes":180},{"id":"4391d523-f1d0-4922-95fb-d3827a21b813","job_id":"J03-c0e2","name":"Dismantle: Planetary &amp; Shaft","order":9,"status":"done","started_at":"2026-08-11T15:28:10.891Z","completed_at":"2026-08-11T23:53:02.227Z","duration_sec":30291,"std_minutes":300},{"id":"bdcc79ae-9f46-46e2-963d-fd2ba3d40a2e","job_id":"J03-c0e2","name":"Dismantle: Part list &amp; Tear Down","order":10,"status":"done","started_at":"2026-08-11T23:53:02.227Z","completed_at":"2026-08-12T03:13:34.783Z","duration_sec":12032,"std_minutes":240},{"id":"0670c5ee-3df9-46ba-a7e5-790a2591233a","job_id":"J03-c0e2","name":"Assemble: Planetary &amp; Shaft In-Out","order":11,"status":"done","started_at":"2026-08-12T03:13:34.783Z","completed_at":"2026-08-13T12:03:07.679Z","duration_sec":118172,"std_minutes":300},{"id":"7276104d-e8c7-4ea6-aac7-6cd975141c45","job_id":"J03-c0e2","name":"Assemble: Clutch 1","order":12,"status":"done","started_at":"2026-08-13T12:29:30.475Z","completed_at":"2026-08-13T14:26:51.718Z","duration_sec":15470,"std_minutes":180},{"id":"1781ebaa-7fb0-4896-b642-71d33b8c4878","job_id":"J03-c0e2","name":"Assemble: Clutch 2","order":13,"status":"done","started_at":"2026-08-13T14:26:51.718Z","completed_at":"2026-08-13T14:27:45.750Z","duration_sec":108,"std_minutes":180},{"id":"5532b99d-a7fd-4b7d-a752-796f7bc5daff","job_id":"J03-c0e2","name":"Assemble: Clutch 3","order":14,"status":"done","started_at":"2026-08-13T14:27:45.750Z","completed_at":"2026-08-16T11:14:03.226Z","duration_sec":495154,"std_minutes":180},{"id":"ff0ed73f-27d1-4b0a-a4f2-7818d3cfbc7e","job_id":"J03-c0e2","name":"Assemble: Clutch 4","order":15,"status":"done","started_at":"2026-08-16T11:14:03.226Z","completed_at":"2026-08-16T11:14:13.083Z","duration_sec":18,"std_minutes":180},{"id":"970a35a3-a96b-48b4-9f04-a2b921b013f0","job_id":"J03-c0e2","name":"Assemble: Clutch 5","order":16,"status":"done","started_at":"2026-08-16T11:14:13.083Z","completed_at":"2026-08-16T11:14:32.420Z","duration_sec":38,"std_minutes":180},{"id":"698b11d9-e1a3-451f-8a47-ccabcc5718c6","job_id":"J03-c0e2","name":"Assemble: CV, Harness &amp; Sensor","order":17,"status":"in_progress","started_at":"2026-08-16T11:14:32.420Z","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"0620fee8-23da-434a-85e6-6354dee830d7","job_id":"J03-c0e2","name":"Assemble: Trans Gear","order":18,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":900},{"id":"ca31c8c2-4542-42f7-be4e-86974a63447b","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Set up","order":19,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"ba2d158c-a9f5-4d98-aea1-fd1f7983c4eb","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Test","order":20,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"d2f96316-8f95-487c-a7ee-94ba19ef4354","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Release","order":21,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"050b2cfc-5ea2-4926-b9c1-c7bdfe6bbd49","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":22,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240}],"assignees":[{"id":"5ece1c51-c36b-46e5-a9d2-f9106a729470","job_id":"J03-c0e2","technician_id":"T-533ca22c","assigned_at":"2026-08-10T08:23:08.120Z","is_lead":"1"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-533ca22c","status":"busy","current_job_id":"J03-c0e2"}]}</t>
+  </si>
+  <si>
+    <t>13f1cdf6-42bd-42b4-acb8-cf9df5b63b06</t>
+  </si>
+  <si>
+    <t>2026-08-16T11:15:01.428Z</t>
+  </si>
+  <si>
+    <t>{"job":{"id":"J03-1833","title":"Recondition Transmission 16H,G","unit":"E448 — D10T","unit_id":"a5c2144b-1b29-40f7-9b5c-cfbbc03c3387","description":"Job recondition Transmission 16H,G (time frame standar).","status":"in_progress","technician_id":"T-c23ed9a4","template_id":"ne-transmission-16h-g","created_at":"2026-08-11T05:30:21.056Z","started_at":"2026-08-11T05:32:14.074Z","completed_at":"","paused_at":"","total_paused_sec":1927,"estimated_minutes":5340},"steps":[{"id":"e21019ab-05cb-4d4f-8f8f-fb85fa9004da","job_id":"J03-1833","name":"Dismantle: Washing Transmission gp","order":1,"status":"done","started_at":"2026-08-11T05:32:14.074Z","completed_at":"2026-08-11T23:52:49.552Z","duration_sec":66035,"std_minutes":240},{"id":"5ceecb87-2473-4297-a2a0-db873217f383","job_id":"J03-1833","name":"Dismantle: Control Valve 2EA","order":2,"status":"done","started_at":"2026-08-11T05:32:33.253Z","completed_at":"2026-08-11T23:52:32.616Z","duration_sec":65999,"std_minutes":300},{"id":"11997f0b-4cc8-4b54-8bdd-db3614b948c1","job_id":"J03-1833","name":"Dismantle: Pump, Lines, &amp; Screen","order":3,"status":"done","started_at":"2026-08-11T05:32:33.253Z","completed_at":"2026-08-11T23:52:51.817Z","duration_sec":66018,"std_minutes":240},{"id":"6c426149-ef7a-48c2-9585-5909fe86eca9","job_id":"J03-1833","name":"Dismantle: Planetary GP","order":4,"status":"done","started_at":"2026-08-11T23:52:51.817Z","completed_at":"2026-08-13T12:08:28.871Z","duration_sec":130537,"std_minutes":900},{"id":"5d3baced-8d6d-491b-9df4-09eaef47f6b9","job_id":"J03-1833","name":"Dismantle: Directional &amp; Idler gear","order":5,"status":"done","started_at":"2026-08-13T12:08:28.871Z","completed_at":"2026-08-13T12:08:40.688Z","duration_sec":11,"std_minutes":300},{"id":"0feaac14-da1a-4360-98f3-a99ad7b2fd45","job_id":"J03-1833","name":"Dismantle: Clean up Housing 2ea","order":6,"status":"done","started_at":"2026-08-13T12:24:22.396Z","completed_at":"2026-08-13T12:37:05.549Z","duration_sec":1682,"std_minutes":120},{"id":"5b00b8bb-18f9-4ef9-ac8c-5d5f25f11170","job_id":"J03-1833","name":"Dismantle: Part list &amp; Tear Down","order":7,"status":"done","started_at":"2026-08-13T12:42:11.028Z","completed_at":"2026-08-16T11:15:01.112Z","duration_sec":507940,"std_minutes":240},{"id":"c536fdc6-3459-4ab5-a588-3454f07f08c7","job_id":"J03-1833","name":"Assemble: Directional &amp; Idler gear","order":8,"status":"in_progress","started_at":"2026-08-16T11:15:01.112Z","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"89d1ae15-daf2-4871-9bc0-5940279c96f6","job_id":"J03-1833","name":"Assemble: Planetary GP","order":9,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"1197b5dd-9928-4565-ae50-91f382e2beb0","job_id":"J03-1833","name":"Assemble: CV 2EA","order":10,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"6a936f7e-e97a-47f4-9e03-24e38ef315fc","job_id":"J03-1833","name":"Assemble: Pump, Lines, &amp; Screen","order":11,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"80894723-ea93-40ff-aa35-420c027d3f95","job_id":"J03-1833","name":"Test Bench &amp; Completed: Set up","order":12,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"acf6bd0c-0d96-40b6-8b9e-ee8c27ee1625","job_id":"J03-1833","name":"Test Bench &amp; Completed: Test","order":13,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"81692dde-b76a-433d-9b5d-3476cf3cd7f6","job_id":"J03-1833","name":"Test Bench &amp; Completed: Release","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"b69b87c3-9d4b-450e-8c0e-162eb755ff75","job_id":"J03-1833","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300}],"assignees":[{"id":"a58e3fbd-80eb-4c64-bd6b-bb7196830ed8","job_id":"J03-1833","technician_id":"T-c23ed9a4","assigned_at":"2026-08-11T05:31:58.767Z","is_lead":"1"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-c23ed9a4","status":"busy","current_job_id":"J03-1833"}]}</t>
+  </si>
+  <si>
+    <t>05e5d8af-fda8-40c9-bd80-763c645a839e</t>
+  </si>
+  <si>
+    <t>2026-08-16T11:15:15.767Z</t>
+  </si>
+  <si>
+    <t>{"job":{"id":"J03-1833","title":"Recondition Transmission 16H,G","unit":"E448 — D10T","unit_id":"a5c2144b-1b29-40f7-9b5c-cfbbc03c3387","description":"Job recondition Transmission 16H,G (time frame standar).","status":"in_progress","technician_id":"T-c23ed9a4","template_id":"ne-transmission-16h-g","created_at":"2026-08-11T05:30:21.056Z","started_at":"2026-08-11T05:32:14.074Z","completed_at":"","paused_at":"","total_paused_sec":1927,"estimated_minutes":5340},"steps":[{"id":"e21019ab-05cb-4d4f-8f8f-fb85fa9004da","job_id":"J03-1833","name":"Dismantle: Washing Transmission gp","order":1,"status":"done","started_at":"2026-08-11T05:32:14.074Z","completed_at":"2026-08-11T23:52:49.552Z","duration_sec":66035,"std_minutes":240},{"id":"5ceecb87-2473-4297-a2a0-db873217f383","job_id":"J03-1833","name":"Dismantle: Control Valve 2EA","order":2,"status":"done","started_at":"2026-08-11T05:32:33.253Z","completed_at":"2026-08-11T23:52:32.616Z","duration_sec":65999,"std_minutes":300},{"id":"11997f0b-4cc8-4b54-8bdd-db3614b948c1","job_id":"J03-1833","name":"Dismantle: Pump, Lines, &amp; Screen","order":3,"status":"done","started_at":"2026-08-11T05:32:33.253Z","completed_at":"2026-08-11T23:52:51.817Z","duration_sec":66018,"std_minutes":240},{"id":"6c426149-ef7a-48c2-9585-5909fe86eca9","job_id":"J03-1833","name":"Dismantle: Planetary GP","order":4,"status":"done","started_at":"2026-08-11T23:52:51.817Z","completed_at":"2026-08-13T12:08:28.871Z","duration_sec":130537,"std_minutes":900},{"id":"5d3baced-8d6d-491b-9df4-09eaef47f6b9","job_id":"J03-1833","name":"Dismantle: Directional &amp; Idler gear","order":5,"status":"done","started_at":"2026-08-13T12:08:28.871Z","completed_at":"2026-08-13T12:08:40.688Z","duration_sec":11,"std_minutes":300},{"id":"0feaac14-da1a-4360-98f3-a99ad7b2fd45","job_id":"J03-1833","name":"Dismantle: Clean up Housing 2ea","order":6,"status":"done","started_at":"2026-08-13T12:24:22.396Z","completed_at":"2026-08-13T12:37:05.549Z","duration_sec":1682,"std_minutes":120},{"id":"5b00b8bb-18f9-4ef9-ac8c-5d5f25f11170","job_id":"J03-1833","name":"Dismantle: Part list &amp; Tear Down","order":7,"status":"done","started_at":"2026-08-13T12:42:11.028Z","completed_at":"2026-08-16T11:15:01.112Z","duration_sec":507940,"std_minutes":240},{"id":"c536fdc6-3459-4ab5-a588-3454f07f08c7","job_id":"J03-1833","name":"Assemble: Directional &amp; Idler gear","order":8,"status":"done","started_at":"2026-08-16T11:15:01.112Z","completed_at":"2026-08-16T11:15:15.440Z","duration_sec":28,"std_minutes":600},{"id":"89d1ae15-daf2-4871-9bc0-5940279c96f6","job_id":"J03-1833","name":"Assemble: Planetary GP","order":9,"status":"in_progress","started_at":"2026-08-16T11:15:15.440Z","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"1197b5dd-9928-4565-ae50-91f382e2beb0","job_id":"J03-1833","name":"Assemble: CV 2EA","order":10,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"6a936f7e-e97a-47f4-9e03-24e38ef315fc","job_id":"J03-1833","name":"Assemble: Pump, Lines, &amp; Screen","order":11,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"80894723-ea93-40ff-aa35-420c027d3f95","job_id":"J03-1833","name":"Test Bench &amp; Completed: Set up","order":12,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"acf6bd0c-0d96-40b6-8b9e-ee8c27ee1625","job_id":"J03-1833","name":"Test Bench &amp; Completed: Test","order":13,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"81692dde-b76a-433d-9b5d-3476cf3cd7f6","job_id":"J03-1833","name":"Test Bench &amp; Completed: Release","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"b69b87c3-9d4b-450e-8c0e-162eb755ff75","job_id":"J03-1833","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300}],"assignees":[{"id":"a58e3fbd-80eb-4c64-bd6b-bb7196830ed8","job_id":"J03-1833","technician_id":"T-c23ed9a4","assigned_at":"2026-08-11T05:31:58.767Z","is_lead":"1"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-c23ed9a4","status":"busy","current_job_id":"J03-1833"}]}</t>
+  </si>
+  <si>
+    <t>c77cd99d-4d98-4fd3-9479-e69c01e3c692</t>
+  </si>
+  <si>
+    <t>2026-08-16T11:16:29.998Z</t>
+  </si>
+  <si>
+    <t>{"job":{"id":"J-f12e75a0a2","title":"Recondition Transmission 24H,M","unit":"GR407 — 24H","unit_id":"U-555bc792","description":"Job recondition Transmission 24H,M (time frame standar).","status":"in_progress","technician_id":"T-25b280e7","template_id":"ne-transmission-24h-m","created_at":"2026-08-13T13:13:28.201Z","started_at":"2026-08-13T13:16:36.692Z","completed_at":"","paused_at":"","total_paused_sec":487,"estimated_minutes":7560},"steps":[{"id":"S-62fed7fe57","job_id":"J-f12e75a0a2","name":"Dismantle: Washing Transmission gp","order":1,"status":"done","started_at":"2026-08-13T13:14:01.944Z","completed_at":"2026-08-13T13:15:17.497Z","duration_sec":150,"std_minutes":300},{"id":"S-bdca34bf9c","job_id":"J-f12e75a0a2","name":"Dismantle: Control Valve","order":2,"status":"done","started_at":"2026-08-13T13:25:23.973Z","completed_at":"2026-08-13T13:25:34.794Z","duration_sec":62,"std_minutes":300},{"id":"S-198d547e50","job_id":"J-f12e75a0a2","name":"Dismantle: Input Trans Gear","order":3,"status":"done","started_at":"2026-08-13T13:25:51.187Z","completed_at":"2026-08-13T13:26:50.395Z","duration_sec":129,"std_minutes":180},{"id":"S-0a2990beeb","job_id":"J-f12e75a0a2","name":"Dismantle: Disconnect Planetary","order":4,"status":"done","started_at":"2026-08-13T13:26:50.395Z","completed_at":"2026-08-13T13:26:58.325Z","duration_sec":14,"std_minutes":180},{"id":"S-1b44880146","job_id":"J-f12e75a0a2","name":"Dismantle: Clutch 6 &amp; Housing","order":5,"status":"done","started_at":"2026-08-13T13:26:58.325Z","completed_at":"2026-08-16T11:16:29.634Z","duration_sec":502742,"std_minutes":240},{"id":"S-9f4ccc66c5","job_id":"J-f12e75a0a2","name":"Dismantle: Clutch 5","order":6,"status":"in_progress","started_at":"2026-08-16T11:16:29.634Z","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-ebd5f203d4","job_id":"J-f12e75a0a2","name":"Dismantle: Clutch 4","order":7,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-efc0d8adbe","job_id":"J-f12e75a0a2","name":"Dismantle: Clutch 3","order":8,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-74a4e63638","job_id":"J-f12e75a0a2","name":"Dismantle: Clutch 2","order":9,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-4dd2a4b52f","job_id":"J-f12e75a0a2","name":"Dismantle: Clutch 1","order":10,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-1cf61d6445","job_id":"J-f12e75a0a2","name":"Dismantle: Planetary &amp; Shaft In-Out","order":11,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"S-f8a0d4e613","job_id":"J-f12e75a0a2","name":"Dismantle: Output Trans Gear","order":12,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":480},{"id":"S-738f8cdae4","job_id":"J-f12e75a0a2","name":"Dismantle: Part list &amp; Tear Down","order":13,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"S-7e81ce5baf","job_id":"J-f12e75a0a2","name":"Assemble: Output Trans Gear","order":14,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":600},{"id":"S-aacd67baa7","job_id":"J-f12e75a0a2","name":"Assemble: Planetary &amp; Shaft In-Out","order":15,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":420},{"id":"S-2bc1eb8c7a","job_id":"J-f12e75a0a2","name":"Assemble: Clutch 1","order":16,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-6c41013e7e","job_id":"J-f12e75a0a2","name":"Assemble: Clutch 2","order":17,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-5dfc9e18df","job_id":"J-f12e75a0a2","name":"Assemble: Clutch 3","order":18,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-427f687ce7","job_id":"J-f12e75a0a2","name":"Assemble: Clutch 4","order":19,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-a7a64f1028","job_id":"J-f12e75a0a2","name":"Assemble: Clutch 5","order":20,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":180},{"id":"S-4f47d5d7b1","job_id":"J-f12e75a0a2","name":"Assemble: Clutch 6 &amp; Housing","order":21,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"S-f5cd7cfd6b","job_id":"J-f12e75a0a2","name":"Assemble: Input Trans Gear","order":22,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"S-647d82040c","job_id":"J-f12e75a0a2","name":"Assemble: Connect Planetary Gp","order":23,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"S-c0da413e41","job_id":"J-f12e75a0a2","name":"Assemble: Control Valve","order":24,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"S-e696ef645c","job_id":"J-f12e75a0a2","name":"Test Bench &amp; Completed: Set up","order":25,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":420},{"id":"S-7d4f1a859e","job_id":"J-f12e75a0a2","name":"Test Bench &amp; Completed: Test","order":26,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"S-1197155765","job_id":"J-f12e75a0a2","name":"Test Bench &amp; Completed: Release","order":27,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":360},{"id":"S-71f21d6927","job_id":"J-f12e75a0a2","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":28,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300}],"assignees":[{"id":"12cf269a-3fcd-4435-af09-3ee3a1e43923","job_id":"J-f12e75a0a2","technician_id":"T-25b280e7","assigned_at":"2026-08-13T13:13:29.838Z","is_lead":"1"},{"id":"1db87a48-9c13-40ac-af3f-256b6b08df59","job_id":"J-f12e75a0a2","technician_id":"T-1c1b3289","assigned_at":"2026-08-13T13:13:29.838Z","is_lead":"0"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-25b280e7","status":"busy","current_job_id":"J-f12e75a0a2"},{"id":"T-1c1b3289","status":"busy","current_job_id":"J-f12e75a0a2"}]}</t>
+  </si>
+  <si>
+    <t>71c0c32d-a498-4f5e-a29b-f3021568da90</t>
+  </si>
+  <si>
+    <t>2026-08-16T11:19:19.698Z</t>
+  </si>
+  <si>
+    <t>{"job":{"id":"J03-c0e2","title":"Recondition Transmission D10T,R","unit":"E448 — D10T","unit_id":"a5c2144b-1b29-40f7-9b5c-cfbbc03c3387","description":"Job recondition Transmission D10T,R (time frame standar).","status":"in_progress","technician_id":"T-533ca22c","template_id":"ne-transmission-d10t-r","created_at":"2026-08-10T08:22:13.799Z","started_at":"2026-08-10T08:23:20.053Z","completed_at":"","paused_at":"","total_paused_sec":256,"estimated_minutes":5820},"steps":[{"id":"7609ebf3-f1eb-4d9d-9591-f21d853034e1","job_id":"J03-c0e2","name":"Dismantle: Washing Transmission","order":1,"status":"done","started_at":"2026-08-10T08:23:20.053Z","completed_at":"2026-08-10T08:24:03.692Z","duration_sec":43,"std_minutes":60},{"id":"a3923555-21a4-4b60-9959-c48d814bf136","job_id":"J03-c0e2","name":"Dismantle: Trans Gear","order":2,"status":"done","started_at":"2026-08-10T08:23:32.872Z","completed_at":"2026-08-10T08:24:06.672Z","duration_sec":33,"std_minutes":600},{"id":"39c70957-da00-4dc8-a988-36ee41ef9841","job_id":"J03-c0e2","name":"Dismantle: CV, Harness, &amp; Sensor","order":3,"status":"done","started_at":"2026-08-10T08:24:08.700Z","completed_at":"2026-08-10T08:24:14.772Z","duration_sec":6,"std_minutes":300},{"id":"6feb4f63-8277-4c8a-a4cf-8d8a3d660682","job_id":"J03-c0e2","name":"Dismantle: Clutch 5","order":4,"status":"done","started_at":"2026-08-10T08:23:32.872Z","completed_at":"2026-08-10T08:24:08.700Z","duration_sec":35,"std_minutes":180},{"id":"179574f5-b3d7-43e4-a065-977ebd015bfc","job_id":"J03-c0e2","name":"Dismantle: Clutch 4","order":5,"status":"done","started_at":"2026-08-10T08:24:14.772Z","completed_at":"2026-08-10T10:10:28.558Z","duration_sec":6373,"std_minutes":180},{"id":"8aff0e07-0f40-4945-a9dc-7a8867ffccf4","job_id":"J03-c0e2","name":"Dismantle: Clutch 3","order":6,"status":"done","started_at":"2026-08-11T05:33:18.994Z","completed_at":"2026-08-11T05:33:34.800Z","duration_sec":69782,"std_minutes":180},{"id":"82415ef2-23b1-4eb2-b027-a268df0f4189","job_id":"J03-c0e2","name":"Dismantle: Clutch 2","order":7,"status":"done","started_at":"2026-08-11T05:33:34.800Z","completed_at":"2026-08-11T05:33:47.115Z","duration_sec":12,"std_minutes":180},{"id":"f7c8bcdc-e2d1-4856-aea1-f577d25b0550","job_id":"J03-c0e2","name":"Dismantle: Clutch 1","order":8,"status":"done","started_at":"2026-08-11T05:33:47.115Z","completed_at":"2026-08-11T15:28:10.891Z","duration_sec":35663,"std_minutes":180},{"id":"4391d523-f1d0-4922-95fb-d3827a21b813","job_id":"J03-c0e2","name":"Dismantle: Planetary &amp; Shaft","order":9,"status":"done","started_at":"2026-08-11T15:28:10.891Z","completed_at":"2026-08-11T23:53:02.227Z","duration_sec":30291,"std_minutes":300},{"id":"bdcc79ae-9f46-46e2-963d-fd2ba3d40a2e","job_id":"J03-c0e2","name":"Dismantle: Part list &amp; Tear Down","order":10,"status":"done","started_at":"2026-08-11T23:53:02.227Z","completed_at":"2026-08-12T03:13:34.783Z","duration_sec":12032,"std_minutes":240},{"id":"0670c5ee-3df9-46ba-a7e5-790a2591233a","job_id":"J03-c0e2","name":"Assemble: Planetary &amp; Shaft In-Out","order":11,"status":"done","started_at":"2026-08-12T03:13:34.783Z","completed_at":"2026-08-13T12:03:07.679Z","duration_sec":118172,"std_minutes":300},{"id":"7276104d-e8c7-4ea6-aac7-6cd975141c45","job_id":"J03-c0e2","name":"Assemble: Clutch 1","order":12,"status":"done","started_at":"2026-08-13T12:29:30.475Z","completed_at":"2026-08-13T14:26:51.718Z","duration_sec":15470,"std_minutes":180},{"id":"1781ebaa-7fb0-4896-b642-71d33b8c4878","job_id":"J03-c0e2","name":"Assemble: Clutch 2","order":13,"status":"done","started_at":"2026-08-13T14:26:51.718Z","completed_at":"2026-08-13T14:27:45.750Z","duration_sec":108,"std_minutes":180},{"id":"5532b99d-a7fd-4b7d-a752-796f7bc5daff","job_id":"J03-c0e2","name":"Assemble: Clutch 3","order":14,"status":"done","started_at":"2026-08-13T14:27:45.750Z","completed_at":"2026-08-16T11:14:03.226Z","duration_sec":495154,"std_minutes":180},{"id":"ff0ed73f-27d1-4b0a-a4f2-7818d3cfbc7e","job_id":"J03-c0e2","name":"Assemble: Clutch 4","order":15,"status":"done","started_at":"2026-08-16T11:14:03.226Z","completed_at":"2026-08-16T11:14:13.083Z","duration_sec":18,"std_minutes":180},{"id":"970a35a3-a96b-48b4-9f04-a2b921b013f0","job_id":"J03-c0e2","name":"Assemble: Clutch 5","order":16,"status":"done","started_at":"2026-08-16T11:14:13.083Z","completed_at":"2026-08-16T11:14:32.420Z","duration_sec":38,"std_minutes":180},{"id":"698b11d9-e1a3-451f-8a47-ccabcc5718c6","job_id":"J03-c0e2","name":"Assemble: CV, Harness &amp; Sensor","order":17,"status":"done","started_at":"2026-08-16T11:14:32.420Z","completed_at":"2026-08-16T11:19:19.372Z","duration_sec":286,"std_minutes":300},{"id":"0620fee8-23da-434a-85e6-6354dee830d7","job_id":"J03-c0e2","name":"Assemble: Trans Gear","order":18,"status":"in_progress","started_at":"2026-08-16T11:19:19.372Z","completed_at":"","duration_sec":0,"std_minutes":900},{"id":"ca31c8c2-4542-42f7-be4e-86974a63447b","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Set up","order":19,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"ba2d158c-a9f5-4d98-aea1-fd1f7983c4eb","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Test","order":20,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"d2f96316-8f95-487c-a7ee-94ba19ef4354","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Release","order":21,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"050b2cfc-5ea2-4926-b9c1-c7bdfe6bbd49","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":22,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240}],"assignees":[{"id":"5ece1c51-c36b-46e5-a9d2-f9106a729470","job_id":"J03-c0e2","technician_id":"T-533ca22c","assigned_at":"2026-08-10T08:23:08.120Z","is_lead":"1"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-533ca22c","status":"busy","current_job_id":"J03-c0e2"}]}</t>
+  </si>
+  <si>
+    <t>84160f7e-f90c-440a-8754-db0847badd75</t>
+  </si>
+  <si>
+    <t>2026-08-16T11:19:25.838Z</t>
+  </si>
+  <si>
+    <t>{"job":{"id":"J03-c0e2","title":"Recondition Transmission D10T,R","unit":"E448 — D10T","unit_id":"a5c2144b-1b29-40f7-9b5c-cfbbc03c3387","description":"Job recondition Transmission D10T,R (time frame standar).","status":"in_progress","technician_id":"T-533ca22c","template_id":"ne-transmission-d10t-r","created_at":"2026-08-10T08:22:13.799Z","started_at":"2026-08-10T08:23:20.053Z","completed_at":"","paused_at":"","total_paused_sec":256,"estimated_minutes":5820},"steps":[{"id":"7609ebf3-f1eb-4d9d-9591-f21d853034e1","job_id":"J03-c0e2","name":"Dismantle: Washing Transmission","order":1,"status":"done","started_at":"2026-08-10T08:23:20.053Z","completed_at":"2026-08-10T08:24:03.692Z","duration_sec":43,"std_minutes":60},{"id":"a3923555-21a4-4b60-9959-c48d814bf136","job_id":"J03-c0e2","name":"Dismantle: Trans Gear","order":2,"status":"done","started_at":"2026-08-10T08:23:32.872Z","completed_at":"2026-08-10T08:24:06.672Z","duration_sec":33,"std_minutes":600},{"id":"39c70957-da00-4dc8-a988-36ee41ef9841","job_id":"J03-c0e2","name":"Dismantle: CV, Harness, &amp; Sensor","order":3,"status":"done","started_at":"2026-08-10T08:24:08.700Z","completed_at":"2026-08-10T08:24:14.772Z","duration_sec":6,"std_minutes":300},{"id":"6feb4f63-8277-4c8a-a4cf-8d8a3d660682","job_id":"J03-c0e2","name":"Dismantle: Clutch 5","order":4,"status":"done","started_at":"2026-08-10T08:23:32.872Z","completed_at":"2026-08-10T08:24:08.700Z","duration_sec":35,"std_minutes":180},{"id":"179574f5-b3d7-43e4-a065-977ebd015bfc","job_id":"J03-c0e2","name":"Dismantle: Clutch 4","order":5,"status":"done","started_at":"2026-08-10T08:24:14.772Z","completed_at":"2026-08-10T10:10:28.558Z","duration_sec":6373,"std_minutes":180},{"id":"8aff0e07-0f40-4945-a9dc-7a8867ffccf4","job_id":"J03-c0e2","name":"Dismantle: Clutch 3","order":6,"status":"done","started_at":"2026-08-11T05:33:18.994Z","completed_at":"2026-08-11T05:33:34.800Z","duration_sec":69782,"std_minutes":180},{"id":"82415ef2-23b1-4eb2-b027-a268df0f4189","job_id":"J03-c0e2","name":"Dismantle: Clutch 2","order":7,"status":"done","started_at":"2026-08-11T05:33:34.800Z","completed_at":"2026-08-11T05:33:47.115Z","duration_sec":12,"std_minutes":180},{"id":"f7c8bcdc-e2d1-4856-aea1-f577d25b0550","job_id":"J03-c0e2","name":"Dismantle: Clutch 1","order":8,"status":"done","started_at":"2026-08-11T05:33:47.115Z","completed_at":"2026-08-11T15:28:10.891Z","duration_sec":35663,"std_minutes":180},{"id":"4391d523-f1d0-4922-95fb-d3827a21b813","job_id":"J03-c0e2","name":"Dismantle: Planetary &amp; Shaft","order":9,"status":"done","started_at":"2026-08-11T15:28:10.891Z","completed_at":"2026-08-11T23:53:02.227Z","duration_sec":30291,"std_minutes":300},{"id":"bdcc79ae-9f46-46e2-963d-fd2ba3d40a2e","job_id":"J03-c0e2","name":"Dismantle: Part list &amp; Tear Down","order":10,"status":"done","started_at":"2026-08-11T23:53:02.227Z","completed_at":"2026-08-12T03:13:34.783Z","duration_sec":12032,"std_minutes":240},{"id":"0670c5ee-3df9-46ba-a7e5-790a2591233a","job_id":"J03-c0e2","name":"Assemble: Planetary &amp; Shaft In-Out","order":11,"status":"done","started_at":"2026-08-12T03:13:34.783Z","completed_at":"2026-08-13T12:03:07.679Z","duration_sec":118172,"std_minutes":300},{"id":"7276104d-e8c7-4ea6-aac7-6cd975141c45","job_id":"J03-c0e2","name":"Assemble: Clutch 1","order":12,"status":"done","started_at":"2026-08-13T12:29:30.475Z","completed_at":"2026-08-13T14:26:51.718Z","duration_sec":15470,"std_minutes":180},{"id":"1781ebaa-7fb0-4896-b642-71d33b8c4878","job_id":"J03-c0e2","name":"Assemble: Clutch 2","order":13,"status":"done","started_at":"2026-08-13T14:26:51.718Z","completed_at":"2026-08-13T14:27:45.750Z","duration_sec":108,"std_minutes":180},{"id":"5532b99d-a7fd-4b7d-a752-796f7bc5daff","job_id":"J03-c0e2","name":"Assemble: Clutch 3","order":14,"status":"done","started_at":"2026-08-13T14:27:45.750Z","completed_at":"2026-08-16T11:14:03.226Z","duration_sec":495154,"std_minutes":180},{"id":"ff0ed73f-27d1-4b0a-a4f2-7818d3cfbc7e","job_id":"J03-c0e2","name":"Assemble: Clutch 4","order":15,"status":"done","started_at":"2026-08-16T11:14:03.226Z","completed_at":"2026-08-16T11:14:13.083Z","duration_sec":18,"std_minutes":180},{"id":"970a35a3-a96b-48b4-9f04-a2b921b013f0","job_id":"J03-c0e2","name":"Assemble: Clutch 5","order":16,"status":"done","started_at":"2026-08-16T11:14:13.083Z","completed_at":"2026-08-16T11:14:32.420Z","duration_sec":38,"std_minutes":180},{"id":"698b11d9-e1a3-451f-8a47-ccabcc5718c6","job_id":"J03-c0e2","name":"Assemble: CV, Harness &amp; Sensor","order":17,"status":"done","started_at":"2026-08-16T11:14:32.420Z","completed_at":"2026-08-16T11:19:19.372Z","duration_sec":286,"std_minutes":300},{"id":"0620fee8-23da-434a-85e6-6354dee830d7","job_id":"J03-c0e2","name":"Assemble: Trans Gear","order":18,"status":"done","started_at":"2026-08-16T11:19:19.372Z","completed_at":"2026-08-16T11:19:25.593Z","duration_sec":6,"std_minutes":900},{"id":"ca31c8c2-4542-42f7-be4e-86974a63447b","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Set up","order":19,"status":"in_progress","started_at":"2026-08-16T11:19:25.593Z","completed_at":"","duration_sec":0,"std_minutes":300},{"id":"ba2d158c-a9f5-4d98-aea1-fd1f7983c4eb","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Test","order":20,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"d2f96316-8f95-487c-a7ee-94ba19ef4354","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Release","order":21,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240},{"id":"050b2cfc-5ea2-4926-b9c1-c7bdfe6bbd49","job_id":"J03-c0e2","name":"Test Bench &amp; Completed: Completed &amp; Painting","order":22,"status":"pending","started_at":"","completed_at":"","duration_sec":0,"std_minutes":240}],"assignees":[{"id":"5ece1c51-c36b-46e5-a9d2-f9106a729470","job_id":"J03-c0e2","technician_id":"T-533ca22c","assigned_at":"2026-08-10T08:23:08.120Z","is_lead":"1"}],"handovers":[],"part_loans":[],"technicians":[{"id":"T-533ca22c","status":"busy","current_job_id":"J03-c0e2"}]}</t>
   </si>
 </sst>
 </file>
@@ -1503,7 +1575,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q103"/>
+  <dimension ref="A1:Q111"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -6965,6 +7037,430 @@
         <v>36</v>
       </c>
     </row>
+    <row r="104" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>372</v>
+      </c>
+      <c r="B104" t="s">
+        <v>373</v>
+      </c>
+      <c r="C104" t="s">
+        <v>19</v>
+      </c>
+      <c r="D104" t="s">
+        <v>20</v>
+      </c>
+      <c r="E104" t="s">
+        <v>21</v>
+      </c>
+      <c r="F104" t="s">
+        <v>32</v>
+      </c>
+      <c r="G104" t="s">
+        <v>23</v>
+      </c>
+      <c r="H104" t="s">
+        <v>55</v>
+      </c>
+      <c r="I104" t="s">
+        <v>55</v>
+      </c>
+      <c r="J104" t="s">
+        <v>88</v>
+      </c>
+      <c r="K104" t="s">
+        <v>365</v>
+      </c>
+      <c r="L104" t="s">
+        <v>374</v>
+      </c>
+      <c r="M104" t="s">
+        <v>35</v>
+      </c>
+      <c r="N104" t="s">
+        <v>36</v>
+      </c>
+      <c r="O104" t="s">
+        <v>36</v>
+      </c>
+      <c r="P104" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q104" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="105" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>375</v>
+      </c>
+      <c r="B105" t="s">
+        <v>376</v>
+      </c>
+      <c r="C105" t="s">
+        <v>19</v>
+      </c>
+      <c r="D105" t="s">
+        <v>20</v>
+      </c>
+      <c r="E105" t="s">
+        <v>21</v>
+      </c>
+      <c r="F105" t="s">
+        <v>32</v>
+      </c>
+      <c r="G105" t="s">
+        <v>23</v>
+      </c>
+      <c r="H105" t="s">
+        <v>55</v>
+      </c>
+      <c r="I105" t="s">
+        <v>55</v>
+      </c>
+      <c r="J105" t="s">
+        <v>88</v>
+      </c>
+      <c r="K105" t="s">
+        <v>374</v>
+      </c>
+      <c r="L105" t="s">
+        <v>377</v>
+      </c>
+      <c r="M105" t="s">
+        <v>35</v>
+      </c>
+      <c r="N105" t="s">
+        <v>36</v>
+      </c>
+      <c r="O105" t="s">
+        <v>36</v>
+      </c>
+      <c r="P105" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q105" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="106" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>378</v>
+      </c>
+      <c r="B106" t="s">
+        <v>379</v>
+      </c>
+      <c r="C106" t="s">
+        <v>19</v>
+      </c>
+      <c r="D106" t="s">
+        <v>20</v>
+      </c>
+      <c r="E106" t="s">
+        <v>21</v>
+      </c>
+      <c r="F106" t="s">
+        <v>32</v>
+      </c>
+      <c r="G106" t="s">
+        <v>23</v>
+      </c>
+      <c r="H106" t="s">
+        <v>55</v>
+      </c>
+      <c r="I106" t="s">
+        <v>55</v>
+      </c>
+      <c r="J106" t="s">
+        <v>88</v>
+      </c>
+      <c r="K106" t="s">
+        <v>377</v>
+      </c>
+      <c r="L106" t="s">
+        <v>380</v>
+      </c>
+      <c r="M106" t="s">
+        <v>35</v>
+      </c>
+      <c r="N106" t="s">
+        <v>36</v>
+      </c>
+      <c r="O106" t="s">
+        <v>36</v>
+      </c>
+      <c r="P106" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q106" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="107" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>381</v>
+      </c>
+      <c r="B107" t="s">
+        <v>382</v>
+      </c>
+      <c r="C107" t="s">
+        <v>19</v>
+      </c>
+      <c r="D107" t="s">
+        <v>20</v>
+      </c>
+      <c r="E107" t="s">
+        <v>21</v>
+      </c>
+      <c r="F107" t="s">
+        <v>32</v>
+      </c>
+      <c r="G107" t="s">
+        <v>23</v>
+      </c>
+      <c r="H107" t="s">
+        <v>107</v>
+      </c>
+      <c r="I107" t="s">
+        <v>107</v>
+      </c>
+      <c r="J107" t="s">
+        <v>33</v>
+      </c>
+      <c r="K107" t="s">
+        <v>307</v>
+      </c>
+      <c r="L107" t="s">
+        <v>383</v>
+      </c>
+      <c r="M107" t="s">
+        <v>35</v>
+      </c>
+      <c r="N107" t="s">
+        <v>36</v>
+      </c>
+      <c r="O107" t="s">
+        <v>36</v>
+      </c>
+      <c r="P107" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q107" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="108" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>384</v>
+      </c>
+      <c r="B108" t="s">
+        <v>385</v>
+      </c>
+      <c r="C108" t="s">
+        <v>19</v>
+      </c>
+      <c r="D108" t="s">
+        <v>20</v>
+      </c>
+      <c r="E108" t="s">
+        <v>21</v>
+      </c>
+      <c r="F108" t="s">
+        <v>32</v>
+      </c>
+      <c r="G108" t="s">
+        <v>23</v>
+      </c>
+      <c r="H108" t="s">
+        <v>107</v>
+      </c>
+      <c r="I108" t="s">
+        <v>107</v>
+      </c>
+      <c r="J108" t="s">
+        <v>33</v>
+      </c>
+      <c r="K108" t="s">
+        <v>383</v>
+      </c>
+      <c r="L108" t="s">
+        <v>386</v>
+      </c>
+      <c r="M108" t="s">
+        <v>35</v>
+      </c>
+      <c r="N108" t="s">
+        <v>36</v>
+      </c>
+      <c r="O108" t="s">
+        <v>36</v>
+      </c>
+      <c r="P108" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q108" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="109" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>387</v>
+      </c>
+      <c r="B109" t="s">
+        <v>388</v>
+      </c>
+      <c r="C109" t="s">
+        <v>19</v>
+      </c>
+      <c r="D109" t="s">
+        <v>20</v>
+      </c>
+      <c r="E109" t="s">
+        <v>21</v>
+      </c>
+      <c r="F109" t="s">
+        <v>32</v>
+      </c>
+      <c r="G109" t="s">
+        <v>23</v>
+      </c>
+      <c r="H109" t="s">
+        <v>310</v>
+      </c>
+      <c r="I109" t="s">
+        <v>310</v>
+      </c>
+      <c r="J109" t="s">
+        <v>323</v>
+      </c>
+      <c r="K109" t="s">
+        <v>359</v>
+      </c>
+      <c r="L109" t="s">
+        <v>389</v>
+      </c>
+      <c r="M109" t="s">
+        <v>35</v>
+      </c>
+      <c r="N109" t="s">
+        <v>36</v>
+      </c>
+      <c r="O109" t="s">
+        <v>36</v>
+      </c>
+      <c r="P109" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q109" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="110" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>390</v>
+      </c>
+      <c r="B110" t="s">
+        <v>391</v>
+      </c>
+      <c r="C110" t="s">
+        <v>19</v>
+      </c>
+      <c r="D110" t="s">
+        <v>20</v>
+      </c>
+      <c r="E110" t="s">
+        <v>21</v>
+      </c>
+      <c r="F110" t="s">
+        <v>32</v>
+      </c>
+      <c r="G110" t="s">
+        <v>23</v>
+      </c>
+      <c r="H110" t="s">
+        <v>55</v>
+      </c>
+      <c r="I110" t="s">
+        <v>55</v>
+      </c>
+      <c r="J110" t="s">
+        <v>88</v>
+      </c>
+      <c r="K110" t="s">
+        <v>380</v>
+      </c>
+      <c r="L110" t="s">
+        <v>392</v>
+      </c>
+      <c r="M110" t="s">
+        <v>35</v>
+      </c>
+      <c r="N110" t="s">
+        <v>36</v>
+      </c>
+      <c r="O110" t="s">
+        <v>36</v>
+      </c>
+      <c r="P110" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q110" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="111" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>393</v>
+      </c>
+      <c r="B111" t="s">
+        <v>394</v>
+      </c>
+      <c r="C111" t="s">
+        <v>19</v>
+      </c>
+      <c r="D111" t="s">
+        <v>20</v>
+      </c>
+      <c r="E111" t="s">
+        <v>21</v>
+      </c>
+      <c r="F111" t="s">
+        <v>32</v>
+      </c>
+      <c r="G111" t="s">
+        <v>23</v>
+      </c>
+      <c r="H111" t="s">
+        <v>55</v>
+      </c>
+      <c r="I111" t="s">
+        <v>55</v>
+      </c>
+      <c r="J111" t="s">
+        <v>88</v>
+      </c>
+      <c r="K111" t="s">
+        <v>392</v>
+      </c>
+      <c r="L111" t="s">
+        <v>395</v>
+      </c>
+      <c r="M111" t="s">
+        <v>35</v>
+      </c>
+      <c r="N111" t="s">
+        <v>36</v>
+      </c>
+      <c r="O111" t="s">
+        <v>36</v>
+      </c>
+      <c r="P111" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q111" t="s">
+        <v>36</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
